--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3909" uniqueCount="1268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3951" uniqueCount="1300">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -3437,6 +3437,21 @@
     <t xml:space="preserve">classes_summary/01 - 27 Jun - Python Setup &amp; API Basics.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Dev setup with UV and VS Code, Python basics as agent vocabulary, first API call, plain-function tools and a @tool registry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.1 to 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python book was empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code snippets copied from the summary; tools.py decorator and calculator guard run and checked; currency.py not run (no network)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC420</t>
   </si>
   <si>
@@ -3446,6 +3461,15 @@
     <t xml:space="preserve">classes_summary/02 - 28 Jun - Python Refresher.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Lists and indexing, classes, dataclasses, decorators, why Python needs Pydantic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.1 to 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code files _0 to _4 not opened yet (separate rows); dataclass and decorator claims run and checked</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC421</t>
   </si>
   <si>
@@ -3455,6 +3479,15 @@
     <t xml:space="preserve">classes_summary/03 - 4 Jul - Pydantic Deep Dive.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Pydantic BaseModel, Field, validators, nested models, validating LLM JSON; five AI terms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3 › 3.1 to 3.7; LLM › Ch 3 › 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI vocabulary placed in LLM book on your instruction; Pydantic snippets run and checked</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC422</t>
   </si>
   <si>
@@ -3464,6 +3497,15 @@
     <t xml:space="preserve">classes_summary/04 - 5 Jul - Anatomy of an Agent.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Stateless LLM calls, model vs chatbot vs agent, four providers, Pydantic extraction, manual tool call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 4 › 4.1 to 4.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider code not run (needs API keys); model names may be out of date, flagged in the chapter</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC423</t>
   </si>
   <si>
@@ -3608,6 +3650,21 @@
     <t xml:space="preserve">classes_transcription_summary/01 - 27 June - Python Setup &amp; API Basics.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 1 transcript: ground rules, UV room analogy, project mode, VS Code vs Jupyter, API analogy, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.1 to 1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Q&amp;A table (course fit for non-tech learners, Copilot vs Claude Code, codebase-understanding tools, industry handbook, Copilot Studio); ground rules and job referrals left out as no teaching content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added UV analogy, UV Q&amp;A, why not CMD, VS Code vs Jupyter, timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q&amp;A rows are opinion and logistics; say if you want them in</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC439</t>
   </si>
   <si>
@@ -3617,16 +3674,55 @@
     <t xml:space="preserve">classes_transcription_summary/02 - 28 June - Python Refresher.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 2 transcript: Windows fix-up, indexing, BankAccount, dataclasses, decorators, type safety, Pydantic intro, roadmap, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.1 to 2.5; Ch 3 › 3.1, 3.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Q&amp;A table (framework token cost, GraphQL vs REST, TypeScript for agents, DevOps agents, vibe coding to the Play Store, guardrails, AgentOps timing, 3.0 vs 2.0) and the course roadmap diagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added indexing table, self/__init__, gift-wrap analogy, *args/**kwargs, dataclass vs Pydantic table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q&amp;A rows are opinion, scheduling and future topics; say if you want them in</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC440</t>
   </si>
   <si>
     <t xml:space="preserve">classes_transcription_summary/03 - 4 Jul - Pydantic Deep Dive.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 3 transcript: why Pydantic, three blueprint styles, optional fields, coercion, Field, special types, validators, nested models, AI vocabulary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3 › 3.1 to 3.5; LLM › Ch 3 › 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added typing background, comparison table, coercion table, EmailStr/HttpUrl/SecretStr, model_validator and order, inheritance Q&amp;A, AI term analogies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Course news and job reminder left out as no teaching content</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC441</t>
   </si>
   <si>
     <t xml:space="preserve">classes_transcription_summary/04 - 5 Jul - Anatomy of an Agent.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 4 transcript: stateless calls, context window demo, web app vs API, OpenRouter, brain-memory-tools anatomy, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 4 › 4.1, 4.3, 4.7; LLM › Ch 3 › 3.2, 3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added memory and tools build-up, intern analogy, OpenRouter, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recap and song aside left out as no teaching content</t>
   </si>
   <si>
     <t xml:space="preserve">LC442</t>
@@ -4292,15 +4388,15 @@
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,B$3)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,C$3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,D$3)</f>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,E$3)</f>
@@ -4466,15 +4562,15 @@
       </c>
       <c r="B10" s="3" t="n">
         <f aca="false">SUM(B4:B9)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
         <f aca="false">SUM(C4:C9)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">SUM(D4:D9)</f>
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E10" s="3" t="n">
         <f aca="false">SUM(E4:E9)</f>
@@ -4531,7 +4627,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4545,7 +4641,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4573,7 +4669,7 @@
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A17)</f>
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4587,7 +4683,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4601,7 +4697,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -18396,25 +18492,35 @@
       <c r="E420" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="F420" s="3"/>
+      <c r="F420" s="3" t="s">
+        <v>1137</v>
+      </c>
       <c r="G420" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H420" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I420" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I420" s="3" t="s">
+        <v>1138</v>
+      </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L420" s="3"/>
-      <c r="M420" s="3"/>
-      <c r="N420" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L420" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M420" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N420" s="3" t="s">
+        <v>1141</v>
+      </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>37</v>
@@ -18423,30 +18529,40 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F421" s="3"/>
+        <v>1144</v>
+      </c>
+      <c r="F421" s="3" t="s">
+        <v>1145</v>
+      </c>
       <c r="G421" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H421" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I421" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I421" s="3" t="s">
+        <v>1146</v>
+      </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L421" s="3"/>
-      <c r="M421" s="3"/>
-      <c r="N421" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L421" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M421" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N421" s="3" t="s">
+        <v>1147</v>
+      </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>37</v>
@@ -18455,30 +18571,40 @@
         <v>8</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F422" s="3"/>
+        <v>1150</v>
+      </c>
+      <c r="F422" s="3" t="s">
+        <v>1151</v>
+      </c>
       <c r="G422" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I422" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I422" s="3" t="s">
+        <v>1152</v>
+      </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L422" s="3"/>
-      <c r="M422" s="3"/>
-      <c r="N422" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L422" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M422" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N422" s="3" t="s">
+        <v>1153</v>
+      </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>37</v>
@@ -18487,30 +18613,40 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F423" s="3"/>
+        <v>1156</v>
+      </c>
+      <c r="F423" s="3" t="s">
+        <v>1157</v>
+      </c>
       <c r="G423" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H423" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I423" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I423" s="3" t="s">
+        <v>1158</v>
+      </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L423" s="3"/>
-      <c r="M423" s="3"/>
-      <c r="N423" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L423" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M423" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N423" s="3" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1146</v>
+        <v>1160</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>37</v>
@@ -18519,10 +18655,10 @@
         <v>9</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1147</v>
+        <v>1161</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1148</v>
+        <v>1162</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
@@ -18542,7 +18678,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1149</v>
+        <v>1163</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>37</v>
@@ -18551,10 +18687,10 @@
         <v>10</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1150</v>
+        <v>1164</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1151</v>
+        <v>1165</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -18574,7 +18710,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1152</v>
+        <v>1166</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>37</v>
@@ -18583,10 +18719,10 @@
         <v>10</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1153</v>
+        <v>1167</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -18606,7 +18742,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>37</v>
@@ -18615,10 +18751,10 @@
         <v>9</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1156</v>
+        <v>1170</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1157</v>
+        <v>1171</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -18638,7 +18774,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1158</v>
+        <v>1172</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>37</v>
@@ -18647,10 +18783,10 @@
         <v>10</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1159</v>
+        <v>1173</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1160</v>
+        <v>1174</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -18670,7 +18806,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1161</v>
+        <v>1175</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>37</v>
@@ -18679,10 +18815,10 @@
         <v>10</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1162</v>
+        <v>1176</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1163</v>
+        <v>1177</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -18702,7 +18838,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1164</v>
+        <v>1178</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>37</v>
@@ -18711,10 +18847,10 @@
         <v>10</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1165</v>
+        <v>1179</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1166</v>
+        <v>1180</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -18734,7 +18870,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1167</v>
+        <v>1181</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>37</v>
@@ -18743,10 +18879,10 @@
         <v>10</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1169</v>
+        <v>1183</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -18766,7 +18902,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1170</v>
+        <v>1184</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>37</v>
@@ -18775,10 +18911,10 @@
         <v>10</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1171</v>
+        <v>1185</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1172</v>
+        <v>1186</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -18798,7 +18934,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1173</v>
+        <v>1187</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>37</v>
@@ -18807,10 +18943,10 @@
         <v>10</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1174</v>
+        <v>1188</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1175</v>
+        <v>1189</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -18830,7 +18966,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1176</v>
+        <v>1190</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>37</v>
@@ -18839,10 +18975,10 @@
         <v>10</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1177</v>
+        <v>1191</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1178</v>
+        <v>1192</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -18862,7 +18998,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1179</v>
+        <v>1193</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>37</v>
@@ -18871,10 +19007,10 @@
         <v>11</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1181</v>
+        <v>1195</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -18894,7 +19030,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1182</v>
+        <v>1196</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>37</v>
@@ -18903,10 +19039,10 @@
         <v>11</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1183</v>
+        <v>1197</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1184</v>
+        <v>1198</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -18926,7 +19062,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1185</v>
+        <v>1199</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>37</v>
@@ -18935,10 +19071,10 @@
         <v>11</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1186</v>
+        <v>1200</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1187</v>
+        <v>1201</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -18958,7 +19094,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>37</v>
@@ -18967,10 +19103,10 @@
         <v>9</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1189</v>
+        <v>1203</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1190</v>
+        <v>1204</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
@@ -18990,7 +19126,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1191</v>
+        <v>1205</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>37</v>
@@ -18999,30 +19135,42 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1192</v>
+        <v>1206</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F439" s="3"/>
+        <v>1207</v>
+      </c>
+      <c r="F439" s="3" t="s">
+        <v>1208</v>
+      </c>
       <c r="G439" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H439" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I439" s="3"/>
-      <c r="J439" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I439" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J439" s="3" t="s">
+        <v>1210</v>
+      </c>
       <c r="K439" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L439" s="3"/>
-      <c r="M439" s="3"/>
-      <c r="N439" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L439" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M439" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N439" s="3" t="s">
+        <v>1212</v>
+      </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>37</v>
@@ -19031,30 +19179,42 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1195</v>
+        <v>1214</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F440" s="3"/>
+        <v>1215</v>
+      </c>
+      <c r="F440" s="3" t="s">
+        <v>1216</v>
+      </c>
       <c r="G440" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H440" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I440" s="3"/>
-      <c r="J440" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I440" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J440" s="3" t="s">
+        <v>1218</v>
+      </c>
       <c r="K440" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L440" s="3"/>
-      <c r="M440" s="3"/>
-      <c r="N440" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L440" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M440" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N440" s="3" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1197</v>
+        <v>1221</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>37</v>
@@ -19063,30 +19223,40 @@
         <v>8</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F441" s="3"/>
+        <v>1222</v>
+      </c>
+      <c r="F441" s="3" t="s">
+        <v>1223</v>
+      </c>
       <c r="G441" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H441" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I441" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I441" s="3" t="s">
+        <v>1224</v>
+      </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L441" s="3"/>
-      <c r="M441" s="3"/>
-      <c r="N441" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L441" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M441" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N441" s="3" t="s">
+        <v>1226</v>
+      </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1199</v>
+        <v>1227</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>37</v>
@@ -19095,30 +19265,40 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F442" s="3"/>
+        <v>1228</v>
+      </c>
+      <c r="F442" s="3" t="s">
+        <v>1229</v>
+      </c>
       <c r="G442" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H442" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I442" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I442" s="3" t="s">
+        <v>1230</v>
+      </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L442" s="3"/>
-      <c r="M442" s="3"/>
-      <c r="N442" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L442" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M442" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N442" s="3" t="s">
+        <v>1232</v>
+      </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1201</v>
+        <v>1233</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>37</v>
@@ -19127,10 +19307,10 @@
         <v>9</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1202</v>
+        <v>1234</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1203</v>
+        <v>1235</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
@@ -19150,7 +19330,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1204</v>
+        <v>1236</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>37</v>
@@ -19159,10 +19339,10 @@
         <v>10</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1150</v>
+        <v>1164</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1205</v>
+        <v>1237</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -19182,7 +19362,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1206</v>
+        <v>1238</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>37</v>
@@ -19191,10 +19371,10 @@
         <v>10</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1153</v>
+        <v>1167</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1207</v>
+        <v>1239</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -19214,7 +19394,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1208</v>
+        <v>1240</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>37</v>
@@ -19223,10 +19403,10 @@
         <v>9</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1209</v>
+        <v>1241</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1210</v>
+        <v>1242</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -19246,7 +19426,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1211</v>
+        <v>1243</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>37</v>
@@ -19255,10 +19435,10 @@
         <v>10</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1212</v>
+        <v>1244</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1213</v>
+        <v>1245</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -19278,7 +19458,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1214</v>
+        <v>1246</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>37</v>
@@ -19287,10 +19467,10 @@
         <v>10</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1215</v>
+        <v>1247</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -19310,7 +19490,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1217</v>
+        <v>1249</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>37</v>
@@ -19319,10 +19499,10 @@
         <v>10</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1218</v>
+        <v>1250</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1219</v>
+        <v>1251</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -19342,7 +19522,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1220</v>
+        <v>1252</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>37</v>
@@ -19351,10 +19531,10 @@
         <v>10</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1221</v>
+        <v>1253</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -19374,7 +19554,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1223</v>
+        <v>1255</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>37</v>
@@ -19383,10 +19563,10 @@
         <v>10</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1224</v>
+        <v>1256</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1225</v>
+        <v>1257</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -19406,7 +19586,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1226</v>
+        <v>1258</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>37</v>
@@ -19415,10 +19595,10 @@
         <v>10</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1227</v>
+        <v>1259</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1228</v>
+        <v>1260</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -19438,7 +19618,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1229</v>
+        <v>1261</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>37</v>
@@ -19447,10 +19627,10 @@
         <v>10</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1231</v>
+        <v>1263</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -19470,7 +19650,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1232</v>
+        <v>1264</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>37</v>
@@ -19479,10 +19659,10 @@
         <v>11</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -19502,7 +19682,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1234</v>
+        <v>1266</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>37</v>
@@ -19511,10 +19691,10 @@
         <v>11</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1235</v>
+        <v>1267</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1236</v>
+        <v>1268</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -19534,7 +19714,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1237</v>
+        <v>1269</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>37</v>
@@ -19543,10 +19723,10 @@
         <v>11</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1238</v>
+        <v>1270</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1239</v>
+        <v>1271</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -19566,7 +19746,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1240</v>
+        <v>1272</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>37</v>
@@ -19575,10 +19755,10 @@
         <v>11</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1241</v>
+        <v>1273</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1242</v>
+        <v>1274</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -19598,7 +19778,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1243</v>
+        <v>1275</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>37</v>
@@ -19607,10 +19787,10 @@
         <v>11</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1244</v>
+        <v>1276</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1245</v>
+        <v>1277</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -19630,7 +19810,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1246</v>
+        <v>1278</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>37</v>
@@ -19639,10 +19819,10 @@
         <v>11</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1247</v>
+        <v>1279</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1248</v>
+        <v>1280</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -19662,7 +19842,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1249</v>
+        <v>1281</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>37</v>
@@ -19671,10 +19851,10 @@
         <v>11</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1250</v>
+        <v>1282</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1251</v>
+        <v>1283</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -19694,7 +19874,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1252</v>
+        <v>1284</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>37</v>
@@ -19703,10 +19883,10 @@
         <v>10</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1253</v>
+        <v>1285</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1254</v>
+        <v>1286</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -19726,7 +19906,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1255</v>
+        <v>1287</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>37</v>
@@ -19735,10 +19915,10 @@
         <v>9</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1256</v>
+        <v>1288</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1257</v>
+        <v>1289</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
@@ -19758,7 +19938,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1258</v>
+        <v>1290</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>37</v>
@@ -19767,10 +19947,10 @@
         <v>9</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1259</v>
+        <v>1291</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1260</v>
+        <v>1292</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
@@ -19790,7 +19970,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1261</v>
+        <v>1293</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>37</v>
@@ -19799,10 +19979,10 @@
         <v>11</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1263</v>
+        <v>1295</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -19822,7 +20002,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1264</v>
+        <v>1296</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>37</v>
@@ -19831,10 +20011,10 @@
         <v>13</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1265</v>
+        <v>1297</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1266</v>
+        <v>1298</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -19849,7 +20029,7 @@
         <v>20</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1267</v>
+        <v>1299</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3952" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3995" uniqueCount="1331">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -866,6 +866,24 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/OOPS.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Outline of six OOP words (classes, objects, inheritance, polymorphism, abstraction, encapsulation), comments only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › The OOP outline from class 01; classes and objects in Ch 2 › 2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explanations of inheritance, polymorphism, abstraction and encapsulation (the file only lists them; the summaries do not explain them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the outline and said what is not yet explained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File is 6 comment lines; I did not explain the other four terms from memory</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC095</t>
   </si>
   <si>
@@ -875,12 +893,36 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/Python_foundamentals.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Variables, types, f-strings, control flow with agent captions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added box analogy, type() line, else branch, run output, closing line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run and output checked</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC096</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 01 write-up repeated, plus file table and run commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.1 to 1.5 and 'Run the class code'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added file table, uv run commands, Windows activation path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest repeats the class 01 summary already written</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC097</t>
   </si>
   <si>
@@ -890,6 +932,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/currency.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Live currency API call with requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same request, timeout, raise_for_status and try/except are already in Ch 1 › 1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run: no network in sandbox</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC098</t>
   </si>
   <si>
@@ -899,6 +953,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/functions or tools.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Two plain functions previewing tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get_current_time and get_weather are already in Ch 1 › 1.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC099</t>
   </si>
   <si>
@@ -911,12 +974,27 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/my-first-project/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">First uv init project: uv sync then uv run main.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added uv sync and uv run main.py</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC101</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/my-first-project/main.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Hello-world main() proving the uv project works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical to the snippet in Ch 1 › 1.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC102</t>
   </si>
   <si>
@@ -950,6 +1028,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/notebook.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Companion notebook: types and f-string demo, two empty cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same variables and f-string demo, covered after the 1.2 enrichment; nothing else in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two cells are empty</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC106</t>
   </si>
   <si>
@@ -959,6 +1046,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/tools.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Hand-built @tool decorator and TOOL_REGISTRY with three tools and a guarded calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added why the registry exists, the three tools, the demo block and its output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run and output checked. A comment calls the agent loop 'Class 4'; the course index says Class 05</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC107</t>
   </si>
   <si>
@@ -3447,9 +3543,6 @@
   </si>
   <si>
     <t xml:space="preserve">Python book was empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-31</t>
   </si>
   <si>
     <t xml:space="preserve">Code snippets copied from the summary; tools.py decorator and calculator guard run and checked; currency.py not run (no network)</t>
@@ -4033,7 +4126,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4054,15 +4147,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4407,15 +4492,15 @@
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,B$3)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,C$3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,D$3)</f>
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,E$3)</f>
@@ -4429,7 +4514,7 @@
         <f aca="false">SUM(B4:F4)</f>
         <v>40</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
@@ -4459,7 +4544,7 @@
         <f aca="false">SUM(B5:F5)</f>
         <v>13</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -4489,7 +4574,7 @@
         <f aca="false">SUM(B6:F6)</f>
         <v>26</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -4519,7 +4604,7 @@
         <f aca="false">SUM(B7:F7)</f>
         <v>112</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -4549,7 +4634,7 @@
         <f aca="false">SUM(B8:F8)</f>
         <v>93</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
@@ -4579,7 +4664,7 @@
         <f aca="false">SUM(B9:F9)</f>
         <v>175</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -4609,37 +4694,37 @@
         <f aca="false">SUM(B10:F10)</f>
         <v>5</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>6</v>
-      </c>
-      <c r="C11" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
-        <v>2</v>
-      </c>
-      <c r="D11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>354</v>
-      </c>
-      <c r="E11" s="6" t="n">
+        <v>345</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
         <v>102</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="n">
         <f aca="false">SUM(G4:G10)</f>
         <v>464</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
@@ -4649,7 +4734,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="5"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -4663,7 +4748,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
@@ -4671,14 +4756,14 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="5"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
@@ -4686,14 +4771,14 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="5"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -4708,7 +4793,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="5"/>
+      <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
@@ -4723,7 +4808,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
@@ -4731,14 +4816,14 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="5"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
@@ -4746,14 +4831,14 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="5"/>
+      <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -4761,14 +4846,14 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="5"/>
+      <c r="H20" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4806,46 +4891,46 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7899,25 +7984,37 @@
       <c r="E95" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="G95" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="K95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>38</v>
@@ -7926,30 +8023,40 @@
         <v>8</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="F96" s="3"/>
+        <v>288</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="G96" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="J96" s="3"/>
       <c r="K96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>38</v>
@@ -7961,27 +8068,37 @@
         <v>52</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="F97" s="3"/>
+        <v>294</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="G97" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I97" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="J97" s="3"/>
       <c r="K97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>38</v>
@@ -7990,30 +8107,40 @@
         <v>8</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F98" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="G98" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I98" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="J98" s="3"/>
       <c r="K98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>38</v>
@@ -8022,30 +8149,38 @@
         <v>8</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F99" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="G99" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I99" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="J99" s="3"/>
       <c r="K99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="N99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>38</v>
@@ -8057,7 +8192,7 @@
         <v>63</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
@@ -8079,7 +8214,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>38</v>
@@ -8091,27 +8226,35 @@
         <v>52</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F101" s="3"/>
+        <v>315</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="G101" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="J101" s="3"/>
       <c r="K101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="N101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>38</v>
@@ -8123,27 +8266,35 @@
         <v>124</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F102" s="3"/>
+        <v>320</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="G102" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="J102" s="3"/>
       <c r="K102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="N102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>38</v>
@@ -8155,7 +8306,7 @@
         <v>71</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
@@ -8177,7 +8328,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>38</v>
@@ -8186,10 +8337,10 @@
         <v>8</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
@@ -8204,14 +8355,14 @@
         <v>21</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>38</v>
@@ -8223,7 +8374,7 @@
         <v>83</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
@@ -8245,7 +8396,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>38</v>
@@ -8254,30 +8405,40 @@
         <v>8</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F106" s="3"/>
+        <v>333</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>334</v>
+      </c>
       <c r="G106" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I106" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="J106" s="3"/>
       <c r="K106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L106" s="3"/>
-      <c r="M106" s="3"/>
-      <c r="N106" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N106" s="3" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>38</v>
@@ -8286,30 +8447,40 @@
         <v>8</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="E107" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I107" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L107" s="3"/>
-      <c r="M107" s="3"/>
-      <c r="N107" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="M107" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N107" s="3" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>38</v>
@@ -8318,10 +8489,10 @@
         <v>8</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
@@ -8341,7 +8512,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>38</v>
@@ -8353,7 +8524,7 @@
         <v>63</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
@@ -8375,7 +8546,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>38</v>
@@ -8384,10 +8555,10 @@
         <v>9</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
@@ -8407,7 +8578,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>38</v>
@@ -8416,10 +8587,10 @@
         <v>9</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
@@ -8439,7 +8610,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>38</v>
@@ -8451,7 +8622,7 @@
         <v>52</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
@@ -8471,7 +8642,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>38</v>
@@ -8483,7 +8654,7 @@
         <v>124</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
@@ -8503,7 +8674,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>38</v>
@@ -8515,7 +8686,7 @@
         <v>71</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
@@ -8537,7 +8708,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>38</v>
@@ -8546,10 +8717,10 @@
         <v>9</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
@@ -8569,7 +8740,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>38</v>
@@ -8578,10 +8749,10 @@
         <v>8</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
@@ -8601,7 +8772,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>38</v>
@@ -8610,10 +8781,10 @@
         <v>8</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
@@ -8633,7 +8804,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>38</v>
@@ -8642,10 +8813,10 @@
         <v>8</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3" t="s">
@@ -8665,7 +8836,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>38</v>
@@ -8677,7 +8848,7 @@
         <v>52</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="3" t="s">
@@ -8697,7 +8868,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>38</v>
@@ -8706,10 +8877,10 @@
         <v>8</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3" t="s">
@@ -8729,7 +8900,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>38</v>
@@ -8738,10 +8909,10 @@
         <v>9</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="3" t="s">
@@ -8761,7 +8932,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>38</v>
@@ -8770,10 +8941,10 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
@@ -8793,7 +8964,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>38</v>
@@ -8802,10 +8973,10 @@
         <v>8</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
@@ -8825,7 +8996,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>38</v>
@@ -8834,10 +9005,10 @@
         <v>8</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
@@ -8857,7 +9028,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>38</v>
@@ -8866,10 +9037,10 @@
         <v>8</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
@@ -8889,7 +9060,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>38</v>
@@ -8898,10 +9069,10 @@
         <v>8</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="3" t="s">
@@ -8921,7 +9092,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>38</v>
@@ -8930,10 +9101,10 @@
         <v>8</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
@@ -8953,7 +9124,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>38</v>
@@ -8962,10 +9133,10 @@
         <v>8</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3" t="s">
@@ -8985,7 +9156,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>38</v>
@@ -8994,10 +9165,10 @@
         <v>8</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
@@ -9017,7 +9188,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>38</v>
@@ -9026,10 +9197,10 @@
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="3" t="s">
@@ -9049,7 +9220,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>38</v>
@@ -9058,10 +9229,10 @@
         <v>8</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3" t="s">
@@ -9081,7 +9252,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>38</v>
@@ -9090,10 +9261,10 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3" t="s">
@@ -9113,7 +9284,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>38</v>
@@ -9122,10 +9293,10 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3" t="s">
@@ -9145,7 +9316,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>38</v>
@@ -9154,10 +9325,10 @@
         <v>9</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3" t="s">
@@ -9177,7 +9348,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>38</v>
@@ -9189,7 +9360,7 @@
         <v>71</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
@@ -9211,7 +9382,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>38</v>
@@ -9223,7 +9394,7 @@
         <v>83</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -9245,7 +9416,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>38</v>
@@ -9254,10 +9425,10 @@
         <v>10</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
@@ -9277,7 +9448,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>38</v>
@@ -9289,7 +9460,7 @@
         <v>52</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="3" t="s">
@@ -9309,7 +9480,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>38</v>
@@ -9321,7 +9492,7 @@
         <v>45</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
@@ -9340,12 +9511,12 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>38</v>
@@ -9357,7 +9528,7 @@
         <v>52</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3" t="s">
@@ -9374,12 +9545,12 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -9388,10 +9559,10 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3" t="s">
@@ -9408,12 +9579,12 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -9422,10 +9593,10 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
@@ -9442,12 +9613,12 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -9456,10 +9627,10 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
@@ -9476,12 +9647,12 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
       <c r="N143" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -9490,10 +9661,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
@@ -9510,12 +9681,12 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -9524,10 +9695,10 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -9544,12 +9715,12 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -9558,10 +9729,10 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
@@ -9578,12 +9749,12 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -9592,10 +9763,10 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
@@ -9612,12 +9783,12 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -9626,10 +9797,10 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
@@ -9646,12 +9817,12 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -9663,7 +9834,7 @@
         <v>71</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -9682,12 +9853,12 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -9699,7 +9870,7 @@
         <v>52</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3" t="s">
@@ -9716,12 +9887,12 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -9733,7 +9904,7 @@
         <v>52</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
@@ -9750,12 +9921,12 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -9764,10 +9935,10 @@
         <v>11</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -9787,7 +9958,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -9799,7 +9970,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -9821,7 +9992,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -9833,7 +10004,7 @@
         <v>63</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -9855,7 +10026,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -9864,10 +10035,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -9887,7 +10058,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -9899,7 +10070,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -9919,7 +10090,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -9928,10 +10099,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -9951,7 +10122,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -9960,10 +10131,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -9983,7 +10154,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -9992,10 +10163,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -10015,7 +10186,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -10027,7 +10198,7 @@
         <v>124</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -10047,7 +10218,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -10059,7 +10230,7 @@
         <v>71</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -10081,7 +10252,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -10093,7 +10264,7 @@
         <v>83</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -10115,7 +10286,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -10127,7 +10298,7 @@
         <v>52</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -10147,7 +10318,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -10156,10 +10327,10 @@
         <v>11</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -10176,12 +10347,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -10193,7 +10364,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -10212,12 +10383,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -10229,7 +10400,7 @@
         <v>63</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -10248,12 +10419,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -10262,10 +10433,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -10282,12 +10453,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -10296,10 +10467,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -10316,12 +10487,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -10330,10 +10501,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -10350,12 +10521,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -10364,10 +10535,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -10384,12 +10555,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -10398,10 +10569,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -10418,12 +10589,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -10432,10 +10603,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -10452,12 +10623,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -10469,7 +10640,7 @@
         <v>52</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -10486,12 +10657,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -10503,7 +10674,7 @@
         <v>124</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -10520,12 +10691,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -10537,7 +10708,7 @@
         <v>71</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -10556,12 +10727,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -10570,10 +10741,10 @@
         <v>11</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -10588,16 +10759,16 @@
         <v>21</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -10609,7 +10780,7 @@
         <v>83</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -10628,12 +10799,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -10642,10 +10813,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -10662,12 +10833,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -10676,10 +10847,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -10696,12 +10867,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -10710,10 +10881,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -10730,12 +10901,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -10744,10 +10915,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -10764,12 +10935,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -10778,10 +10949,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -10798,12 +10969,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -10812,10 +10983,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -10832,12 +11003,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -10849,7 +11020,7 @@
         <v>52</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -10866,12 +11037,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -10883,7 +11054,7 @@
         <v>52</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -10900,12 +11071,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -10914,10 +11085,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -10934,12 +11105,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -10948,10 +11119,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -10968,12 +11139,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -10982,10 +11153,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -11002,12 +11173,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -11016,10 +11187,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -11036,12 +11207,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -11050,10 +11221,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -11070,12 +11241,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -11084,10 +11255,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -11104,12 +11275,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -11118,10 +11289,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -11138,12 +11309,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -11152,10 +11323,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -11172,12 +11343,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -11186,10 +11357,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -11206,12 +11377,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -11223,7 +11394,7 @@
         <v>52</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -11240,12 +11411,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -11257,7 +11428,7 @@
         <v>52</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -11274,12 +11445,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -11288,10 +11459,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -11313,7 +11484,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -11322,10 +11493,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -11345,7 +11516,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -11354,10 +11525,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>556</v>
+        <v>588</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -11377,7 +11548,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -11386,10 +11557,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -11409,7 +11580,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -11418,10 +11589,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>562</v>
+        <v>594</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -11441,7 +11612,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>563</v>
+        <v>595</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -11450,10 +11621,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>565</v>
+        <v>597</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -11473,7 +11644,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>566</v>
+        <v>598</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -11485,7 +11656,7 @@
         <v>52</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -11505,7 +11676,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>568</v>
+        <v>600</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -11517,7 +11688,7 @@
         <v>52</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -11537,7 +11708,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -11546,10 +11717,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>571</v>
+        <v>603</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -11571,7 +11742,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -11580,10 +11751,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -11603,7 +11774,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -11612,10 +11783,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -11637,7 +11808,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -11646,10 +11817,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -11669,7 +11840,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -11681,7 +11852,7 @@
         <v>52</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -11701,7 +11872,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -11713,7 +11884,7 @@
         <v>52</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -11733,7 +11904,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -11745,7 +11916,7 @@
         <v>52</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>584</v>
+        <v>616</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -11765,7 +11936,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -11774,10 +11945,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>586</v>
+        <v>618</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>587</v>
+        <v>619</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -11799,7 +11970,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -11808,10 +11979,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -11831,7 +12002,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -11840,10 +12011,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>592</v>
+        <v>624</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -11863,7 +12034,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -11875,7 +12046,7 @@
         <v>49</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -11895,7 +12066,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -11904,10 +12075,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -11927,7 +12098,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -11939,7 +12110,7 @@
         <v>206</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -11959,7 +12130,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -11971,7 +12142,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -11993,7 +12164,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -12005,7 +12176,7 @@
         <v>63</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>604</v>
+        <v>636</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -12027,7 +12198,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -12039,7 +12210,7 @@
         <v>52</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -12059,7 +12230,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -12071,7 +12242,7 @@
         <v>71</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -12093,7 +12264,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -12105,7 +12276,7 @@
         <v>74</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -12125,7 +12296,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -12137,7 +12308,7 @@
         <v>80</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -12157,7 +12328,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -12169,7 +12340,7 @@
         <v>83</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -12191,7 +12362,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -12203,7 +12374,7 @@
         <v>259</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -12223,7 +12394,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -12235,7 +12406,7 @@
         <v>52</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>618</v>
+        <v>650</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -12255,7 +12426,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -12267,7 +12438,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>620</v>
+        <v>652</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -12287,7 +12458,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -12296,10 +12467,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>623</v>
+        <v>655</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -12319,7 +12490,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -12328,10 +12499,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -12351,7 +12522,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>627</v>
+        <v>659</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -12360,10 +12531,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -12383,7 +12554,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -12392,10 +12563,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>631</v>
+        <v>663</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -12415,7 +12586,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -12427,7 +12598,7 @@
         <v>52</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -12447,7 +12618,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>635</v>
+        <v>667</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -12456,10 +12627,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>636</v>
+        <v>668</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -12481,7 +12652,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -12493,7 +12664,7 @@
         <v>253</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -12513,7 +12684,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -12525,7 +12696,7 @@
         <v>256</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -12545,7 +12716,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -12554,10 +12725,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -12577,7 +12748,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -12589,7 +12760,7 @@
         <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -12609,7 +12780,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -12621,7 +12792,7 @@
         <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -12641,7 +12812,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -12653,7 +12824,7 @@
         <v>55</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -12673,7 +12844,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -12685,7 +12856,7 @@
         <v>58</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -12705,7 +12876,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -12717,7 +12888,7 @@
         <v>52</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>654</v>
+        <v>686</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -12737,7 +12908,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>655</v>
+        <v>687</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -12749,7 +12920,7 @@
         <v>63</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -12771,7 +12942,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -12783,7 +12954,7 @@
         <v>52</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -12803,7 +12974,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -12815,7 +12986,7 @@
         <v>121</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -12835,7 +13006,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -12847,7 +13018,7 @@
         <v>124</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -12867,7 +13038,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -12879,7 +13050,7 @@
         <v>145</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -12899,7 +13070,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -12911,7 +13082,7 @@
         <v>71</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -12933,7 +13104,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -12945,7 +13116,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -12965,7 +13136,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -12977,7 +13148,7 @@
         <v>190</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -12999,7 +13170,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -13011,7 +13182,7 @@
         <v>193</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>672</v>
+        <v>704</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -13033,7 +13204,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -13045,7 +13216,7 @@
         <v>129</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -13067,7 +13238,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>675</v>
+        <v>707</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -13079,7 +13250,7 @@
         <v>83</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>676</v>
+        <v>708</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -13101,7 +13272,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>677</v>
+        <v>709</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -13113,7 +13284,7 @@
         <v>203</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>678</v>
+        <v>710</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -13133,7 +13304,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -13145,7 +13316,7 @@
         <v>63</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -13167,7 +13338,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -13179,7 +13350,7 @@
         <v>52</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>682</v>
+        <v>714</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -13199,7 +13370,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -13211,7 +13382,7 @@
         <v>216</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>684</v>
+        <v>716</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -13233,7 +13404,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -13245,7 +13416,7 @@
         <v>124</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -13265,7 +13436,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -13277,7 +13448,7 @@
         <v>71</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>688</v>
+        <v>720</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -13299,7 +13470,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -13311,7 +13482,7 @@
         <v>55</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>690</v>
+        <v>722</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -13331,7 +13502,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>691</v>
+        <v>723</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -13343,7 +13514,7 @@
         <v>58</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -13363,7 +13534,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>693</v>
+        <v>725</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -13375,7 +13546,7 @@
         <v>83</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>694</v>
+        <v>726</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -13397,7 +13568,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>695</v>
+        <v>727</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -13409,7 +13580,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>696</v>
+        <v>728</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -13431,7 +13602,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>697</v>
+        <v>729</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -13443,7 +13614,7 @@
         <v>63</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -13465,7 +13636,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -13477,7 +13648,7 @@
         <v>52</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -13497,7 +13668,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>701</v>
+        <v>733</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -13509,7 +13680,7 @@
         <v>68</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -13529,7 +13700,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -13541,7 +13712,7 @@
         <v>71</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -13563,7 +13734,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -13575,7 +13746,7 @@
         <v>74</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -13595,7 +13766,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -13607,7 +13778,7 @@
         <v>77</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>708</v>
+        <v>740</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -13627,7 +13798,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -13639,7 +13810,7 @@
         <v>80</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -13659,7 +13830,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -13671,7 +13842,7 @@
         <v>83</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -13693,7 +13864,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -13705,7 +13876,7 @@
         <v>52</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>714</v>
+        <v>746</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -13725,7 +13896,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -13737,7 +13908,7 @@
         <v>63</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -13759,7 +13930,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -13768,10 +13939,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>719</v>
+        <v>751</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -13791,7 +13962,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -13803,7 +13974,7 @@
         <v>52</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -13823,7 +13994,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -13832,10 +14003,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -13855,7 +14026,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>725</v>
+        <v>757</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -13867,7 +14038,7 @@
         <v>124</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -13887,7 +14058,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>727</v>
+        <v>759</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -13899,7 +14070,7 @@
         <v>71</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -13921,7 +14092,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -13933,7 +14104,7 @@
         <v>83</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -13955,7 +14126,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -13967,7 +14138,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -13986,12 +14157,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -14000,10 +14171,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>735</v>
+        <v>767</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -14020,12 +14191,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -14034,10 +14205,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -14054,12 +14225,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -14068,10 +14239,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>741</v>
+        <v>773</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>742</v>
+        <v>774</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -14090,12 +14261,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>743</v>
+        <v>775</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -14104,10 +14275,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>745</v>
+        <v>777</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -14124,12 +14295,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -14138,10 +14309,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>747</v>
+        <v>779</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>748</v>
+        <v>780</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -14160,12 +14331,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>749</v>
+        <v>781</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -14174,10 +14345,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>750</v>
+        <v>782</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>751</v>
+        <v>783</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -14194,12 +14365,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>752</v>
+        <v>784</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -14208,10 +14379,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>753</v>
+        <v>785</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>754</v>
+        <v>786</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -14230,12 +14401,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -14244,10 +14415,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>757</v>
+        <v>789</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -14264,12 +14435,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>758</v>
+        <v>790</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -14281,7 +14452,7 @@
         <v>71</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>759</v>
+        <v>791</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -14300,12 +14471,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>760</v>
+        <v>792</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -14317,7 +14488,7 @@
         <v>83</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>761</v>
+        <v>793</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -14336,12 +14507,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>762</v>
+        <v>794</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -14353,7 +14524,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>763</v>
+        <v>795</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -14375,7 +14546,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>764</v>
+        <v>796</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -14384,10 +14555,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>766</v>
+        <v>798</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -14407,7 +14578,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -14416,10 +14587,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -14439,7 +14610,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>770</v>
+        <v>802</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -14448,10 +14619,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>771</v>
+        <v>803</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -14471,7 +14642,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>773</v>
+        <v>805</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -14480,10 +14651,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>774</v>
+        <v>806</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>775</v>
+        <v>807</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -14503,7 +14674,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>776</v>
+        <v>808</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -14512,10 +14683,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>777</v>
+        <v>809</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>778</v>
+        <v>810</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -14535,7 +14706,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -14544,10 +14715,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>780</v>
+        <v>812</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>781</v>
+        <v>813</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -14567,7 +14738,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>782</v>
+        <v>814</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -14579,7 +14750,7 @@
         <v>52</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>783</v>
+        <v>815</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -14599,7 +14770,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -14611,7 +14782,7 @@
         <v>71</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>785</v>
+        <v>817</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -14633,7 +14804,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>786</v>
+        <v>818</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -14642,10 +14813,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>787</v>
+        <v>819</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>788</v>
+        <v>820</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -14665,7 +14836,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>789</v>
+        <v>821</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -14677,7 +14848,7 @@
         <v>83</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>790</v>
+        <v>822</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -14699,7 +14870,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>791</v>
+        <v>823</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -14708,10 +14879,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -14733,7 +14904,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>794</v>
+        <v>826</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -14742,10 +14913,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>796</v>
+        <v>828</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -14767,7 +14938,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -14776,10 +14947,10 @@
         <v>13</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -14799,7 +14970,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -14808,10 +14979,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -14833,7 +15004,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -14845,7 +15016,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>803</v>
+        <v>835</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -14867,7 +15038,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>804</v>
+        <v>836</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -14876,10 +15047,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>805</v>
+        <v>837</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>806</v>
+        <v>838</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -14899,7 +15070,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>807</v>
+        <v>839</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -14908,10 +15079,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>808</v>
+        <v>840</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>809</v>
+        <v>841</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -14926,14 +15097,14 @@
         <v>21</v>
       </c>
       <c r="L307" s="3" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="M307" s="3"/>
       <c r="N307" s="3"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>810</v>
+        <v>842</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -14945,7 +15116,7 @@
         <v>52</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>811</v>
+        <v>843</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -14965,7 +15136,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>812</v>
+        <v>844</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -14977,7 +15148,7 @@
         <v>80</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -14997,7 +15168,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>814</v>
+        <v>846</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -15006,10 +15177,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>815</v>
+        <v>847</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>816</v>
+        <v>848</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -15029,7 +15200,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>817</v>
+        <v>849</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -15038,10 +15209,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>818</v>
+        <v>850</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>819</v>
+        <v>851</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -15061,7 +15232,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>820</v>
+        <v>852</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -15070,10 +15241,10 @@
         <v>13</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>821</v>
+        <v>853</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -15093,7 +15264,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -15105,7 +15276,7 @@
         <v>80</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>823</v>
+        <v>855</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -15125,7 +15296,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>824</v>
+        <v>856</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -15134,10 +15305,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>825</v>
+        <v>857</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -15157,7 +15328,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>827</v>
+        <v>859</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -15169,7 +15340,7 @@
         <v>124</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>828</v>
+        <v>860</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -15189,7 +15360,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>829</v>
+        <v>861</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -15198,10 +15369,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>830</v>
+        <v>862</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -15221,7 +15392,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>832</v>
+        <v>864</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -15233,7 +15404,7 @@
         <v>80</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>833</v>
+        <v>865</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -15253,7 +15424,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>834</v>
+        <v>866</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -15262,10 +15433,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>836</v>
+        <v>868</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -15285,7 +15456,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>837</v>
+        <v>869</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -15297,7 +15468,7 @@
         <v>80</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>838</v>
+        <v>870</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -15317,7 +15488,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>839</v>
+        <v>871</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -15326,10 +15497,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>840</v>
+        <v>872</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -15349,7 +15520,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -15361,7 +15532,7 @@
         <v>80</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>843</v>
+        <v>875</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -15381,7 +15552,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>844</v>
+        <v>876</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -15390,10 +15561,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>845</v>
+        <v>877</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>846</v>
+        <v>878</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -15413,7 +15584,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -15422,10 +15593,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -15445,7 +15616,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -15454,10 +15625,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>851</v>
+        <v>883</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>852</v>
+        <v>884</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -15477,7 +15648,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -15486,10 +15657,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>854</v>
+        <v>886</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -15509,7 +15680,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>856</v>
+        <v>888</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -15518,10 +15689,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>857</v>
+        <v>889</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -15541,7 +15712,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>859</v>
+        <v>891</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -15550,10 +15721,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>860</v>
+        <v>892</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>861</v>
+        <v>893</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -15573,7 +15744,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>862</v>
+        <v>894</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -15582,10 +15753,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>863</v>
+        <v>895</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -15605,7 +15776,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -15614,10 +15785,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>866</v>
+        <v>898</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>867</v>
+        <v>899</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -15639,7 +15810,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -15648,10 +15819,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>869</v>
+        <v>901</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>870</v>
+        <v>902</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -15673,7 +15844,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>871</v>
+        <v>903</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -15682,10 +15853,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>873</v>
+        <v>905</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -15705,7 +15876,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -15717,7 +15888,7 @@
         <v>190</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>875</v>
+        <v>907</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -15739,7 +15910,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -15748,10 +15919,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>877</v>
+        <v>909</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -15773,7 +15944,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>879</v>
+        <v>911</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -15782,10 +15953,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>880</v>
+        <v>912</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>881</v>
+        <v>913</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -15807,7 +15978,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -15816,10 +15987,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>883</v>
+        <v>915</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -15839,7 +16010,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>885</v>
+        <v>917</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -15848,10 +16019,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>887</v>
+        <v>919</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -15871,7 +16042,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>888</v>
+        <v>920</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -15880,10 +16051,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>889</v>
+        <v>921</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>890</v>
+        <v>922</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -15903,7 +16074,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>891</v>
+        <v>923</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -15912,10 +16083,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>893</v>
+        <v>925</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -15937,7 +16108,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>894</v>
+        <v>926</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -15946,10 +16117,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>895</v>
+        <v>927</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -15969,7 +16140,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>897</v>
+        <v>929</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -15978,10 +16149,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>898</v>
+        <v>930</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>899</v>
+        <v>931</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -16001,7 +16172,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -16010,10 +16181,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>901</v>
+        <v>933</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>902</v>
+        <v>934</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -16033,7 +16204,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>903</v>
+        <v>935</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -16042,10 +16213,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>905</v>
+        <v>937</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -16065,7 +16236,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>906</v>
+        <v>938</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -16074,10 +16245,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>908</v>
+        <v>940</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -16097,7 +16268,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>909</v>
+        <v>941</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -16106,10 +16277,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>910</v>
+        <v>942</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>911</v>
+        <v>943</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -16129,7 +16300,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -16138,10 +16309,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -16161,7 +16332,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -16170,10 +16341,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>916</v>
+        <v>948</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>917</v>
+        <v>949</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -16193,7 +16364,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -16202,10 +16373,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>919</v>
+        <v>951</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>920</v>
+        <v>952</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -16225,7 +16396,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -16234,10 +16405,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>922</v>
+        <v>954</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>923</v>
+        <v>955</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -16257,7 +16428,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -16266,10 +16437,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -16289,7 +16460,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -16298,10 +16469,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -16321,7 +16492,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>930</v>
+        <v>962</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -16330,10 +16501,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>932</v>
+        <v>964</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -16353,7 +16524,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -16362,10 +16533,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>934</v>
+        <v>966</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>935</v>
+        <v>967</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -16385,7 +16556,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>936</v>
+        <v>968</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -16394,10 +16565,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>938</v>
+        <v>970</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -16417,7 +16588,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -16426,10 +16597,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>940</v>
+        <v>972</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>941</v>
+        <v>973</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -16449,7 +16620,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -16458,10 +16629,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>943</v>
+        <v>975</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>944</v>
+        <v>976</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -16481,7 +16652,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>945</v>
+        <v>977</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -16490,10 +16661,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>946</v>
+        <v>978</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -16513,7 +16684,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>948</v>
+        <v>980</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -16522,10 +16693,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>950</v>
+        <v>982</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -16545,7 +16716,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -16554,10 +16725,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>953</v>
+        <v>985</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -16577,7 +16748,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>954</v>
+        <v>986</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -16586,10 +16757,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>955</v>
+        <v>987</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -16609,7 +16780,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>957</v>
+        <v>989</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -16618,10 +16789,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>958</v>
+        <v>990</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -16641,7 +16812,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>960</v>
+        <v>992</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -16650,10 +16821,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>961</v>
+        <v>993</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>962</v>
+        <v>994</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -16673,7 +16844,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>963</v>
+        <v>995</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -16682,10 +16853,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>964</v>
+        <v>996</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>965</v>
+        <v>997</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -16705,7 +16876,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -16714,10 +16885,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>968</v>
+        <v>1000</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -16737,7 +16908,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>969</v>
+        <v>1001</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -16746,10 +16917,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>970</v>
+        <v>1002</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -16769,7 +16940,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>972</v>
+        <v>1004</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -16778,10 +16949,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>973</v>
+        <v>1005</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>974</v>
+        <v>1006</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -16801,7 +16972,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>975</v>
+        <v>1007</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -16810,10 +16981,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>976</v>
+        <v>1008</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>977</v>
+        <v>1009</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -16833,7 +17004,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>978</v>
+        <v>1010</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -16842,10 +17013,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>979</v>
+        <v>1011</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -16865,7 +17036,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>981</v>
+        <v>1013</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -16874,10 +17045,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>982</v>
+        <v>1014</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>983</v>
+        <v>1015</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -16897,7 +17068,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>984</v>
+        <v>1016</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -16906,10 +17077,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>985</v>
+        <v>1017</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>986</v>
+        <v>1018</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -16929,7 +17100,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>987</v>
+        <v>1019</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -16938,10 +17109,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>988</v>
+        <v>1020</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>989</v>
+        <v>1021</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -16961,7 +17132,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>990</v>
+        <v>1022</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -16970,10 +17141,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>991</v>
+        <v>1023</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>992</v>
+        <v>1024</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -16993,7 +17164,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>993</v>
+        <v>1025</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -17002,10 +17173,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>994</v>
+        <v>1026</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>995</v>
+        <v>1027</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -17025,7 +17196,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>996</v>
+        <v>1028</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -17034,10 +17205,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>997</v>
+        <v>1029</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>998</v>
+        <v>1030</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -17057,7 +17228,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>999</v>
+        <v>1031</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -17066,10 +17237,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1000</v>
+        <v>1032</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1001</v>
+        <v>1033</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -17089,7 +17260,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1002</v>
+        <v>1034</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -17098,10 +17269,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1003</v>
+        <v>1035</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1004</v>
+        <v>1036</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -17121,7 +17292,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1005</v>
+        <v>1037</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -17130,10 +17301,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1006</v>
+        <v>1038</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1007</v>
+        <v>1039</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -17153,7 +17324,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -17162,10 +17333,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1009</v>
+        <v>1041</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1010</v>
+        <v>1042</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -17185,7 +17356,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1011</v>
+        <v>1043</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -17194,10 +17365,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1012</v>
+        <v>1044</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1013</v>
+        <v>1045</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -17217,7 +17388,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1014</v>
+        <v>1046</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -17226,10 +17397,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1015</v>
+        <v>1047</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1016</v>
+        <v>1048</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -17249,7 +17420,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1017</v>
+        <v>1049</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -17258,10 +17429,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1018</v>
+        <v>1050</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1019</v>
+        <v>1051</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -17281,7 +17452,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1020</v>
+        <v>1052</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -17290,10 +17461,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1021</v>
+        <v>1053</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1022</v>
+        <v>1054</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -17313,7 +17484,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1023</v>
+        <v>1055</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -17322,10 +17493,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1024</v>
+        <v>1056</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1025</v>
+        <v>1057</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -17345,7 +17516,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -17354,10 +17525,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1027</v>
+        <v>1059</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1028</v>
+        <v>1060</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -17377,7 +17548,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1029</v>
+        <v>1061</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -17386,10 +17557,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1030</v>
+        <v>1062</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1031</v>
+        <v>1063</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -17409,7 +17580,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1032</v>
+        <v>1064</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -17418,10 +17589,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1034</v>
+        <v>1066</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -17441,7 +17612,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -17450,10 +17621,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1036</v>
+        <v>1068</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1037</v>
+        <v>1069</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -17473,7 +17644,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -17482,10 +17653,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1040</v>
+        <v>1072</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -17505,7 +17676,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1041</v>
+        <v>1073</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -17514,10 +17685,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1042</v>
+        <v>1074</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1043</v>
+        <v>1075</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -17537,7 +17708,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1044</v>
+        <v>1076</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -17546,10 +17717,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1045</v>
+        <v>1077</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1046</v>
+        <v>1078</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -17569,7 +17740,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -17578,10 +17749,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -17601,7 +17772,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1050</v>
+        <v>1082</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -17610,10 +17781,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1052</v>
+        <v>1084</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -17633,7 +17804,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -17642,10 +17813,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -17665,7 +17836,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1056</v>
+        <v>1088</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -17674,10 +17845,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1057</v>
+        <v>1089</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1058</v>
+        <v>1090</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -17697,7 +17868,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -17706,10 +17877,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -17729,7 +17900,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -17738,10 +17909,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1057</v>
+        <v>1089</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1063</v>
+        <v>1095</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -17761,7 +17932,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1064</v>
+        <v>1096</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -17770,10 +17941,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1065</v>
+        <v>1097</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1066</v>
+        <v>1098</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -17795,7 +17966,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1067</v>
+        <v>1099</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -17804,10 +17975,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1068</v>
+        <v>1100</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1069</v>
+        <v>1101</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -17827,7 +17998,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1070</v>
+        <v>1102</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -17836,10 +18007,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1071</v>
+        <v>1103</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1072</v>
+        <v>1104</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -17859,7 +18030,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1073</v>
+        <v>1105</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -17868,10 +18039,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1074</v>
+        <v>1106</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1075</v>
+        <v>1107</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -17891,7 +18062,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1076</v>
+        <v>1108</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -17900,10 +18071,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -17923,7 +18094,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -17932,10 +18103,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -17955,7 +18126,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1082</v>
+        <v>1114</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -17964,10 +18135,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1083</v>
+        <v>1115</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1084</v>
+        <v>1116</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -17987,7 +18158,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1085</v>
+        <v>1117</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -17996,10 +18167,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1086</v>
+        <v>1118</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1087</v>
+        <v>1119</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -18019,7 +18190,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -18028,10 +18199,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1089</v>
+        <v>1121</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1090</v>
+        <v>1122</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -18051,7 +18222,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1091</v>
+        <v>1123</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -18060,10 +18231,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1092</v>
+        <v>1124</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1093</v>
+        <v>1125</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -18083,7 +18254,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1094</v>
+        <v>1126</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -18092,10 +18263,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1095</v>
+        <v>1127</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1096</v>
+        <v>1128</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -18117,7 +18288,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1097</v>
+        <v>1129</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -18126,10 +18297,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1098</v>
+        <v>1130</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1099</v>
+        <v>1131</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -18151,7 +18322,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1100</v>
+        <v>1132</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -18160,10 +18331,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1101</v>
+        <v>1133</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1102</v>
+        <v>1134</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -18185,7 +18356,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1103</v>
+        <v>1135</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -18194,10 +18365,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1104</v>
+        <v>1136</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1105</v>
+        <v>1137</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -18217,7 +18388,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1106</v>
+        <v>1138</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -18226,10 +18397,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1107</v>
+        <v>1139</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1108</v>
+        <v>1140</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -18249,7 +18420,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1109</v>
+        <v>1141</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -18258,10 +18429,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1110</v>
+        <v>1142</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1111</v>
+        <v>1143</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -18281,7 +18452,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1112</v>
+        <v>1144</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -18290,10 +18461,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1113</v>
+        <v>1145</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1114</v>
+        <v>1146</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -18308,14 +18479,14 @@
         <v>21</v>
       </c>
       <c r="L412" s="3" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="M412" s="3"/>
       <c r="N412" s="3"/>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1115</v>
+        <v>1147</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -18324,10 +18495,10 @@
         <v>13</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1116</v>
+        <v>1148</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -18342,14 +18513,14 @@
         <v>21</v>
       </c>
       <c r="L413" s="3" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="M413" s="3"/>
       <c r="N413" s="3"/>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1117</v>
+        <v>1149</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -18358,10 +18529,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1118</v>
+        <v>1150</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1119</v>
+        <v>1151</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -18381,7 +18552,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1120</v>
+        <v>1152</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -18390,10 +18561,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1121</v>
+        <v>1153</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1122</v>
+        <v>1154</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -18413,7 +18584,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1123</v>
+        <v>1155</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -18422,10 +18593,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1124</v>
+        <v>1156</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1125</v>
+        <v>1157</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -18445,7 +18616,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1126</v>
+        <v>1158</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -18454,10 +18625,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1127</v>
+        <v>1159</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1128</v>
+        <v>1160</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -18477,7 +18648,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1129</v>
+        <v>1161</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -18486,10 +18657,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1130</v>
+        <v>1162</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1130</v>
+        <v>1162</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -18504,14 +18675,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1131</v>
+        <v>1163</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1132</v>
+        <v>1164</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -18520,10 +18691,10 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1133</v>
+        <v>1165</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1134</v>
+        <v>1166</v>
       </c>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
@@ -18543,7 +18714,7 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1135</v>
+        <v>1167</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -18552,13 +18723,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1136</v>
+        <v>1168</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1137</v>
+        <v>1169</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1138</v>
+        <v>1170</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -18567,25 +18738,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1139</v>
+        <v>1171</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1140</v>
+        <v>1172</v>
       </c>
       <c r="M420" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1142</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1143</v>
+        <v>1174</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -18594,13 +18765,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1144</v>
+        <v>1175</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1145</v>
+        <v>1176</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1146</v>
+        <v>1177</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -18609,25 +18780,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1147</v>
+        <v>1178</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1140</v>
+        <v>1172</v>
       </c>
       <c r="M421" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1148</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1149</v>
+        <v>1180</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -18636,13 +18807,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1150</v>
+        <v>1181</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1151</v>
+        <v>1182</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1152</v>
+        <v>1183</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -18651,25 +18822,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1140</v>
+        <v>1172</v>
       </c>
       <c r="M422" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1154</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1155</v>
+        <v>1186</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -18678,13 +18849,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1157</v>
+        <v>1188</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1158</v>
+        <v>1189</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -18693,25 +18864,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1159</v>
+        <v>1190</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1140</v>
+        <v>1172</v>
       </c>
       <c r="M423" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1160</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -18720,10 +18891,10 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1163</v>
+        <v>1194</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
@@ -18743,7 +18914,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1164</v>
+        <v>1195</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -18752,10 +18923,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1165</v>
+        <v>1196</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1166</v>
+        <v>1197</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -18775,7 +18946,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1167</v>
+        <v>1198</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -18784,10 +18955,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1168</v>
+        <v>1199</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1169</v>
+        <v>1200</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -18807,7 +18978,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1170</v>
+        <v>1201</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -18816,10 +18987,10 @@
         <v>10</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1171</v>
+        <v>1202</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1172</v>
+        <v>1203</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -18839,7 +19010,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1173</v>
+        <v>1204</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -18848,10 +19019,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1174</v>
+        <v>1205</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1175</v>
+        <v>1206</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -18871,7 +19042,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1176</v>
+        <v>1207</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -18880,10 +19051,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1177</v>
+        <v>1208</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1178</v>
+        <v>1209</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -18903,7 +19074,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1179</v>
+        <v>1210</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -18912,10 +19083,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1180</v>
+        <v>1211</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1181</v>
+        <v>1212</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -18935,7 +19106,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1182</v>
+        <v>1213</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -18944,10 +19115,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1183</v>
+        <v>1214</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1184</v>
+        <v>1215</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -18967,7 +19138,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1185</v>
+        <v>1216</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -18976,10 +19147,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1186</v>
+        <v>1217</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1187</v>
+        <v>1218</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -18999,7 +19170,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1188</v>
+        <v>1219</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -19008,10 +19179,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1189</v>
+        <v>1220</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1190</v>
+        <v>1221</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -19031,7 +19202,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1191</v>
+        <v>1222</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -19040,10 +19211,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1192</v>
+        <v>1223</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -19063,7 +19234,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -19072,10 +19243,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1195</v>
+        <v>1226</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1196</v>
+        <v>1227</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -19095,7 +19266,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1197</v>
+        <v>1228</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -19104,10 +19275,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -19127,7 +19298,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -19136,10 +19307,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1201</v>
+        <v>1232</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1202</v>
+        <v>1233</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -19159,7 +19330,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1203</v>
+        <v>1234</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -19168,10 +19339,10 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
@@ -19191,7 +19362,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1206</v>
+        <v>1237</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -19200,13 +19371,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1207</v>
+        <v>1238</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1208</v>
+        <v>1239</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1209</v>
+        <v>1240</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -19215,27 +19386,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1210</v>
+        <v>1241</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1211</v>
+        <v>1242</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1212</v>
+        <v>1243</v>
       </c>
       <c r="M439" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1213</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1214</v>
+        <v>1245</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -19244,13 +19415,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1215</v>
+        <v>1246</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1216</v>
+        <v>1247</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1217</v>
+        <v>1248</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -19259,27 +19430,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1218</v>
+        <v>1249</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1219</v>
+        <v>1250</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1220</v>
+        <v>1251</v>
       </c>
       <c r="M440" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1221</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1222</v>
+        <v>1253</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -19288,13 +19459,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1150</v>
+        <v>1181</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1223</v>
+        <v>1254</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1224</v>
+        <v>1255</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -19303,25 +19474,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1225</v>
+        <v>1256</v>
       </c>
       <c r="M441" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1226</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1227</v>
+        <v>1258</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -19330,13 +19501,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1229</v>
+        <v>1260</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -19345,25 +19516,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1230</v>
+        <v>1261</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1231</v>
+        <v>1262</v>
       </c>
       <c r="M442" s="3" t="s">
-        <v>1141</v>
+        <v>284</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1232</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1233</v>
+        <v>1264</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -19372,10 +19543,10 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1234</v>
+        <v>1265</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1235</v>
+        <v>1266</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
@@ -19395,7 +19566,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1236</v>
+        <v>1267</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -19404,10 +19575,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1165</v>
+        <v>1196</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1237</v>
+        <v>1268</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -19427,7 +19598,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -19436,10 +19607,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1168</v>
+        <v>1199</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1239</v>
+        <v>1270</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -19459,7 +19630,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1240</v>
+        <v>1271</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -19468,10 +19639,10 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1241</v>
+        <v>1272</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1242</v>
+        <v>1273</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -19491,7 +19662,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1243</v>
+        <v>1274</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -19500,10 +19671,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1244</v>
+        <v>1275</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1245</v>
+        <v>1276</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -19523,7 +19694,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1246</v>
+        <v>1277</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -19532,10 +19703,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1247</v>
+        <v>1278</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1248</v>
+        <v>1279</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -19555,7 +19726,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1249</v>
+        <v>1280</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -19564,10 +19735,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1250</v>
+        <v>1281</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1251</v>
+        <v>1282</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -19587,7 +19758,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1252</v>
+        <v>1283</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -19596,10 +19767,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1253</v>
+        <v>1284</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1254</v>
+        <v>1285</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -19619,7 +19790,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1255</v>
+        <v>1286</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -19628,10 +19799,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1256</v>
+        <v>1287</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1257</v>
+        <v>1288</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -19651,7 +19822,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1258</v>
+        <v>1289</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -19660,10 +19831,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1259</v>
+        <v>1290</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1260</v>
+        <v>1291</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -19683,7 +19854,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1261</v>
+        <v>1292</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -19692,10 +19863,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1262</v>
+        <v>1293</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -19715,7 +19886,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1264</v>
+        <v>1295</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -19724,10 +19895,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1195</v>
+        <v>1226</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -19747,7 +19918,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1266</v>
+        <v>1297</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -19756,10 +19927,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1267</v>
+        <v>1298</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1268</v>
+        <v>1299</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -19779,7 +19950,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1269</v>
+        <v>1300</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -19788,10 +19959,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1270</v>
+        <v>1301</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1271</v>
+        <v>1302</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -19811,7 +19982,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1272</v>
+        <v>1303</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -19820,10 +19991,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1273</v>
+        <v>1304</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1274</v>
+        <v>1305</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -19843,7 +20014,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1275</v>
+        <v>1306</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -19852,10 +20023,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1276</v>
+        <v>1307</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1277</v>
+        <v>1308</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -19875,7 +20046,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1278</v>
+        <v>1309</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -19884,10 +20055,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1279</v>
+        <v>1310</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1280</v>
+        <v>1311</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -19907,7 +20078,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1281</v>
+        <v>1312</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -19916,10 +20087,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1282</v>
+        <v>1313</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1283</v>
+        <v>1314</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -19939,7 +20110,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1284</v>
+        <v>1315</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -19948,10 +20119,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1285</v>
+        <v>1316</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1286</v>
+        <v>1317</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -19971,7 +20142,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1287</v>
+        <v>1318</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -19980,10 +20151,10 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1288</v>
+        <v>1319</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1289</v>
+        <v>1320</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
@@ -20003,7 +20174,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1290</v>
+        <v>1321</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -20012,10 +20183,10 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1291</v>
+        <v>1322</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1292</v>
+        <v>1323</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
@@ -20035,7 +20206,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1293</v>
+        <v>1324</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -20044,10 +20215,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1294</v>
+        <v>1325</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1295</v>
+        <v>1326</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -20067,7 +20238,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1296</v>
+        <v>1327</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -20076,10 +20247,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1297</v>
+        <v>1328</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1298</v>
+        <v>1329</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -20094,7 +20265,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1299</v>
+        <v>1330</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3995" uniqueCount="1331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="1363">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -1142,12 +1142,36 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/Python_run.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Class notebook repeating comparisons, a mixed-type list, and a dict demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added that a list can mix types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Its 'Array vs List' table is only a comment with nothing under it; not invented</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC118</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 02-03 folder guide: 15-file table, set-up, run order, naming rule, testing note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added file table with where each is covered, set-up, underscore rule, self-contained note, testing note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README says its live calls were tested only with mocked responses</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC119</t>
   </si>
   <si>
@@ -1157,6 +1181,12 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_0_basics_refresher.py</t>
   </si>
   <si>
+    <t xml:space="preserve">elif chains, comparison operators, and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added elif, comparisons and and</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC120</t>
   </si>
   <si>
@@ -1211,6 +1241,12 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_1_data_structures.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Lists, tuples and unpacking, dicts, list of dicts, list comprehension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added tuples, dict operations, list of dicts and comprehension</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC126</t>
   </si>
   <si>
@@ -1220,6 +1256,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_2_oop_classes.py</t>
   </si>
   <si>
+    <t xml:space="preserve">BankAccount with show_history, separate state per object, Book dataclass with add_tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.2, 2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added show_history, two accounts, add_tag, commented tags pitfall</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC127</t>
   </si>
   <si>
@@ -1229,6 +1274,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_3_error_handling.py</t>
   </si>
   <si>
+    <t xml:space="preserve">try/except, several except blocks, finally, KeyError</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in the book before</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC128</t>
   </si>
   <si>
@@ -1238,6 +1292,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_4_decorators.py</t>
   </si>
   <si>
+    <t xml:space="preserve">announce and timed decorators, then stacked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">announce, timed and stacking are already in Ch 2 › 2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple greet and slow_addition demos not repeated; not needed</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC129</t>
   </si>
   <si>
@@ -1247,6 +1313,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_5_calling_a_real_api.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Simple request, then convert_currency wrapped with error handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added convert_currency and its two except blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run (no network). Uses api.frankfurter.dev/v1, while class 01 currency.py uses api.frankfurter.app; I have not checked which is current</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC130</t>
   </si>
   <si>
@@ -1256,6 +1334,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_6_fake_ai_call.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Fake OpenAI-shaped client, plus a plain-dict fake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3 › 3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run and output checked. Second fake runs at module level, so importing the file prints extra lines</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC131</t>
   </si>
   <si>
@@ -1263,6 +1350,15 @@
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_7_ai_call_free_and_paid.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groq, OpenRouter and OpenAI calls in one shape, with fallback to the fake client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added OpenRouter and openrouter/free, dotenv, fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run with no keys (fallback path) and output checked; real calls not run (need keys)</t>
   </si>
   <si>
     <t xml:space="preserve">LC132</t>
@@ -4492,7 +4588,7 @@
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,B$3)</f>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,C$3)</f>
@@ -4500,7 +4596,7 @@
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,D$3)</f>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,E$3)</f>
@@ -4702,7 +4798,7 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
@@ -4710,7 +4806,7 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -4756,7 +4852,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4771,7 +4867,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4786,7 +4882,7 @@
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A16)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4816,7 +4912,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4831,7 +4927,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4846,7 +4942,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -8818,25 +8914,35 @@
       <c r="E118" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="F118" s="3"/>
+      <c r="F118" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="G118" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I118" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="J118" s="3"/>
       <c r="K118" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="M118" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N118" s="3" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>38</v>
@@ -8848,27 +8954,37 @@
         <v>52</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="F119" s="3"/>
+        <v>377</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="G119" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I119" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="J119" s="3"/>
       <c r="K119" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="M119" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N119" s="3" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>38</v>
@@ -8877,30 +8993,40 @@
         <v>8</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F120" s="3"/>
+        <v>384</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="G120" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I120" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="J120" s="3"/>
       <c r="K120" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="M120" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N120" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>38</v>
@@ -8909,10 +9035,10 @@
         <v>9</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="3" t="s">
@@ -8932,7 +9058,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>38</v>
@@ -8941,10 +9067,10 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
@@ -8964,7 +9090,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>38</v>
@@ -8973,10 +9099,10 @@
         <v>8</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
@@ -8996,7 +9122,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>38</v>
@@ -9005,10 +9131,10 @@
         <v>8</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
@@ -9028,7 +9154,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>38</v>
@@ -9037,10 +9163,10 @@
         <v>8</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
@@ -9060,7 +9186,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>38</v>
@@ -9069,30 +9195,40 @@
         <v>8</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="F126" s="3"/>
+        <v>404</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>405</v>
+      </c>
       <c r="G126" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I126" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>373</v>
+      </c>
       <c r="J126" s="3"/>
       <c r="K126" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L126" s="3"/>
-      <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="M126" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N126" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>38</v>
@@ -9101,30 +9237,40 @@
         <v>8</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F127" s="3"/>
+        <v>409</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>410</v>
+      </c>
       <c r="G127" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I127" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L127" s="3"/>
-      <c r="M127" s="3"/>
-      <c r="N127" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L127" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M127" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N127" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>38</v>
@@ -9133,30 +9279,40 @@
         <v>8</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F128" s="3"/>
+        <v>415</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>416</v>
+      </c>
       <c r="G128" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I128" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>417</v>
+      </c>
       <c r="J128" s="3"/>
       <c r="K128" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L128" s="3"/>
-      <c r="M128" s="3"/>
-      <c r="N128" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N128" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>38</v>
@@ -9165,30 +9321,40 @@
         <v>8</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F129" s="3"/>
+        <v>421</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="G129" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I129" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>423</v>
+      </c>
       <c r="J129" s="3"/>
       <c r="K129" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L129" s="3"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L129" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="M129" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N129" s="3" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>38</v>
@@ -9197,30 +9363,40 @@
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F130" s="3"/>
+        <v>428</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>429</v>
+      </c>
       <c r="G130" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I130" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>430</v>
+      </c>
       <c r="J130" s="3"/>
       <c r="K130" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L130" s="3"/>
-      <c r="M130" s="3"/>
-      <c r="N130" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="M130" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N130" s="3" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>38</v>
@@ -9229,30 +9405,40 @@
         <v>8</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="F131" s="3"/>
+        <v>435</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>436</v>
+      </c>
       <c r="G131" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I131" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>437</v>
+      </c>
       <c r="J131" s="3"/>
       <c r="K131" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L131" s="3"/>
-      <c r="M131" s="3"/>
-      <c r="N131" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L131" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="M131" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N131" s="3" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>38</v>
@@ -9261,30 +9447,40 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F132" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>442</v>
+      </c>
       <c r="G132" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I132" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>437</v>
+      </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L132" s="3"/>
-      <c r="M132" s="3"/>
-      <c r="N132" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N132" s="3" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>38</v>
@@ -9293,10 +9489,10 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3" t="s">
@@ -9316,7 +9512,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>38</v>
@@ -9325,10 +9521,10 @@
         <v>9</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="3" t="s">
@@ -9348,7 +9544,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>38</v>
@@ -9360,7 +9556,7 @@
         <v>71</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
@@ -9382,7 +9578,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>38</v>
@@ -9394,7 +9590,7 @@
         <v>83</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -9416,7 +9612,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>38</v>
@@ -9425,10 +9621,10 @@
         <v>10</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
@@ -9448,7 +9644,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>38</v>
@@ -9460,7 +9656,7 @@
         <v>52</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="3" t="s">
@@ -9480,7 +9676,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>38</v>
@@ -9492,7 +9688,7 @@
         <v>45</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
@@ -9511,12 +9707,12 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>38</v>
@@ -9528,7 +9724,7 @@
         <v>52</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3" t="s">
@@ -9545,12 +9741,12 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -9559,10 +9755,10 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3" t="s">
@@ -9579,12 +9775,12 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -9593,10 +9789,10 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
@@ -9613,12 +9809,12 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -9627,10 +9823,10 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
@@ -9647,12 +9843,12 @@
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
       <c r="N143" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -9661,10 +9857,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
@@ -9681,12 +9877,12 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -9695,10 +9891,10 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -9715,12 +9911,12 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -9729,10 +9925,10 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
@@ -9749,12 +9945,12 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -9763,10 +9959,10 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
@@ -9783,12 +9979,12 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -9797,10 +9993,10 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
@@ -9817,12 +10013,12 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -9834,7 +10030,7 @@
         <v>71</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -9853,12 +10049,12 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -9870,7 +10066,7 @@
         <v>52</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3" t="s">
@@ -9887,12 +10083,12 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -9904,7 +10100,7 @@
         <v>52</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
@@ -9921,12 +10117,12 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -9938,7 +10134,7 @@
         <v>344</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -9958,7 +10154,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -9970,7 +10166,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -9992,7 +10188,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10004,7 +10200,7 @@
         <v>63</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10026,7 +10222,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -10035,10 +10231,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -10058,7 +10254,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10070,7 +10266,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -10090,7 +10286,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -10099,10 +10295,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -10122,7 +10318,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -10131,10 +10327,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -10154,7 +10350,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -10163,10 +10359,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -10186,7 +10382,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -10198,7 +10394,7 @@
         <v>124</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -10218,7 +10414,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -10230,7 +10426,7 @@
         <v>71</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -10252,7 +10448,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -10264,7 +10460,7 @@
         <v>83</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -10286,7 +10482,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -10298,7 +10494,7 @@
         <v>52</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -10318,7 +10514,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -10330,7 +10526,7 @@
         <v>344</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -10347,12 +10543,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -10364,7 +10560,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -10383,12 +10579,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -10400,7 +10596,7 @@
         <v>63</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -10419,12 +10615,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -10433,10 +10629,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -10453,12 +10649,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -10467,10 +10663,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -10487,12 +10683,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -10501,10 +10697,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -10521,12 +10717,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -10535,10 +10731,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -10555,12 +10751,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -10569,10 +10765,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -10589,12 +10785,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -10603,10 +10799,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -10623,12 +10819,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -10640,7 +10836,7 @@
         <v>52</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -10657,12 +10853,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -10674,7 +10870,7 @@
         <v>124</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -10691,12 +10887,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -10708,7 +10904,7 @@
         <v>71</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -10727,12 +10923,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -10744,7 +10940,7 @@
         <v>326</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -10763,12 +10959,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -10780,7 +10976,7 @@
         <v>83</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -10799,12 +10995,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -10813,10 +11009,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -10833,12 +11029,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -10847,10 +11043,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -10867,12 +11063,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -10881,10 +11077,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -10901,12 +11097,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -10915,10 +11111,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -10935,12 +11131,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -10949,10 +11145,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -10969,12 +11165,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -10983,10 +11179,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11003,12 +11199,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11020,7 +11216,7 @@
         <v>52</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11037,12 +11233,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11054,7 +11250,7 @@
         <v>52</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11071,12 +11267,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -11085,10 +11281,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -11105,12 +11301,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -11119,10 +11315,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -11139,12 +11335,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -11153,10 +11349,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>556</v>
+        <v>588</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -11173,12 +11369,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -11187,10 +11383,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -11207,12 +11403,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -11221,10 +11417,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>562</v>
+        <v>594</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>563</v>
+        <v>595</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -11241,12 +11437,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -11255,10 +11451,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>565</v>
+        <v>597</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>566</v>
+        <v>598</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -11275,12 +11471,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -11289,10 +11485,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>568</v>
+        <v>600</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -11309,12 +11505,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -11323,10 +11519,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>571</v>
+        <v>603</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -11343,12 +11539,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -11357,10 +11553,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -11377,12 +11573,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -11394,7 +11590,7 @@
         <v>52</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -11411,12 +11607,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -11428,7 +11624,7 @@
         <v>52</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -11445,12 +11641,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -11459,10 +11655,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -11484,7 +11680,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -11493,10 +11689,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>584</v>
+        <v>616</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -11516,7 +11712,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>586</v>
+        <v>618</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -11525,10 +11721,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>587</v>
+        <v>619</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -11548,7 +11744,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -11557,10 +11753,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -11580,7 +11776,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>592</v>
+        <v>624</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -11589,10 +11785,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -11612,7 +11808,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -11621,10 +11817,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -11644,7 +11840,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -11656,7 +11852,7 @@
         <v>52</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -11676,7 +11872,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -11688,7 +11884,7 @@
         <v>52</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -11708,7 +11904,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -11717,10 +11913,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -11742,7 +11938,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>604</v>
+        <v>636</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -11751,10 +11947,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>584</v>
+        <v>616</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -11774,7 +11970,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -11783,10 +11979,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -11808,7 +12004,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -11817,10 +12013,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -11840,7 +12036,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -11852,7 +12048,7 @@
         <v>52</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -11872,7 +12068,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -11884,7 +12080,7 @@
         <v>52</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -11904,7 +12100,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -11916,7 +12112,7 @@
         <v>52</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -11936,7 +12132,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -11945,10 +12141,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>618</v>
+        <v>650</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -11970,7 +12166,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>620</v>
+        <v>652</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -11979,10 +12175,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12002,7 +12198,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>623</v>
+        <v>655</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12011,10 +12207,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12034,7 +12230,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12046,7 +12242,7 @@
         <v>49</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>627</v>
+        <v>659</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12066,7 +12262,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12075,10 +12271,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -12098,7 +12294,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>631</v>
+        <v>663</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -12110,7 +12306,7 @@
         <v>206</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -12130,7 +12326,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -12142,7 +12338,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -12164,7 +12360,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>635</v>
+        <v>667</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -12176,7 +12372,7 @@
         <v>63</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>636</v>
+        <v>668</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -12198,7 +12394,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -12210,7 +12406,7 @@
         <v>52</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -12230,7 +12426,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -12242,7 +12438,7 @@
         <v>71</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -12264,7 +12460,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -12276,7 +12472,7 @@
         <v>74</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -12296,7 +12492,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -12308,7 +12504,7 @@
         <v>80</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -12328,7 +12524,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -12340,7 +12536,7 @@
         <v>83</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -12362,7 +12558,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -12374,7 +12570,7 @@
         <v>259</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -12394,7 +12590,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -12406,7 +12602,7 @@
         <v>52</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -12426,7 +12622,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -12438,7 +12634,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -12458,7 +12654,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -12467,10 +12663,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>654</v>
+        <v>686</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>655</v>
+        <v>687</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -12490,7 +12686,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -12499,10 +12695,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -12522,7 +12718,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -12531,10 +12727,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -12554,7 +12750,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -12563,10 +12759,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -12586,7 +12782,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -12598,7 +12794,7 @@
         <v>52</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -12618,7 +12814,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -12627,10 +12823,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -12652,7 +12848,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -12664,7 +12860,7 @@
         <v>253</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -12684,7 +12880,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>672</v>
+        <v>704</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -12696,7 +12892,7 @@
         <v>256</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -12716,7 +12912,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -12725,10 +12921,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>675</v>
+        <v>707</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>676</v>
+        <v>708</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -12748,7 +12944,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>677</v>
+        <v>709</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -12760,7 +12956,7 @@
         <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>678</v>
+        <v>710</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -12780,7 +12976,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -12792,7 +12988,7 @@
         <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -12812,7 +13008,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -12824,7 +13020,7 @@
         <v>55</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>682</v>
+        <v>714</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -12844,7 +13040,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -12856,7 +13052,7 @@
         <v>58</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>684</v>
+        <v>716</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -12876,7 +13072,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -12888,7 +13084,7 @@
         <v>52</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -12908,7 +13104,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -12920,7 +13116,7 @@
         <v>63</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>688</v>
+        <v>720</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -12942,7 +13138,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -12954,7 +13150,7 @@
         <v>52</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>690</v>
+        <v>722</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -12974,7 +13170,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>691</v>
+        <v>723</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -12986,7 +13182,7 @@
         <v>121</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13006,7 +13202,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>693</v>
+        <v>725</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13018,7 +13214,7 @@
         <v>124</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>694</v>
+        <v>726</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13038,7 +13234,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>695</v>
+        <v>727</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13050,7 +13246,7 @@
         <v>145</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>696</v>
+        <v>728</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13070,7 +13266,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>697</v>
+        <v>729</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -13082,7 +13278,7 @@
         <v>71</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -13104,7 +13300,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -13116,7 +13312,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -13136,7 +13332,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>701</v>
+        <v>733</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -13148,7 +13344,7 @@
         <v>190</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -13170,7 +13366,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -13182,7 +13378,7 @@
         <v>193</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -13204,7 +13400,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -13216,7 +13412,7 @@
         <v>129</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -13238,7 +13434,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -13250,7 +13446,7 @@
         <v>83</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>708</v>
+        <v>740</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -13272,7 +13468,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -13284,7 +13480,7 @@
         <v>203</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -13304,7 +13500,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -13316,7 +13512,7 @@
         <v>63</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -13338,7 +13534,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -13350,7 +13546,7 @@
         <v>52</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>714</v>
+        <v>746</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -13370,7 +13566,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -13382,7 +13578,7 @@
         <v>216</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -13404,7 +13600,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -13416,7 +13612,7 @@
         <v>124</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -13436,7 +13632,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>719</v>
+        <v>751</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -13448,7 +13644,7 @@
         <v>71</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -13470,7 +13666,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -13482,7 +13678,7 @@
         <v>55</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -13502,7 +13698,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -13514,7 +13710,7 @@
         <v>58</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -13534,7 +13730,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>725</v>
+        <v>757</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -13546,7 +13742,7 @@
         <v>83</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -13568,7 +13764,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>727</v>
+        <v>759</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -13580,7 +13776,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -13602,7 +13798,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -13614,7 +13810,7 @@
         <v>63</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -13636,7 +13832,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -13648,7 +13844,7 @@
         <v>52</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -13668,7 +13864,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -13680,7 +13876,7 @@
         <v>68</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -13700,7 +13896,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>735</v>
+        <v>767</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -13712,7 +13908,7 @@
         <v>71</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -13734,7 +13930,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -13746,7 +13942,7 @@
         <v>74</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -13766,7 +13962,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -13778,7 +13974,7 @@
         <v>77</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -13798,7 +13994,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>741</v>
+        <v>773</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -13810,7 +14006,7 @@
         <v>80</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>742</v>
+        <v>774</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -13830,7 +14026,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>743</v>
+        <v>775</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -13842,7 +14038,7 @@
         <v>83</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -13864,7 +14060,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>745</v>
+        <v>777</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -13876,7 +14072,7 @@
         <v>52</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -13896,7 +14092,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>747</v>
+        <v>779</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -13908,7 +14104,7 @@
         <v>63</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>748</v>
+        <v>780</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -13930,7 +14126,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>749</v>
+        <v>781</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -13939,10 +14135,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>750</v>
+        <v>782</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>751</v>
+        <v>783</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -13962,7 +14158,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>752</v>
+        <v>784</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -13974,7 +14170,7 @@
         <v>52</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>753</v>
+        <v>785</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -13994,7 +14190,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>754</v>
+        <v>786</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14003,10 +14199,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14026,7 +14222,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>757</v>
+        <v>789</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14038,7 +14234,7 @@
         <v>124</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>758</v>
+        <v>790</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14058,7 +14254,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>759</v>
+        <v>791</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14070,7 +14266,7 @@
         <v>71</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>760</v>
+        <v>792</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -14092,7 +14288,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>761</v>
+        <v>793</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -14104,7 +14300,7 @@
         <v>83</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>762</v>
+        <v>794</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -14126,7 +14322,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>763</v>
+        <v>795</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -14138,7 +14334,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>764</v>
+        <v>796</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -14157,12 +14353,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>766</v>
+        <v>798</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -14171,10 +14367,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -14191,12 +14387,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -14205,10 +14401,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>770</v>
+        <v>802</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>771</v>
+        <v>803</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -14225,12 +14421,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -14239,10 +14435,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>773</v>
+        <v>805</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>774</v>
+        <v>806</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -14261,12 +14457,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>775</v>
+        <v>807</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -14275,10 +14471,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>776</v>
+        <v>808</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>777</v>
+        <v>809</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -14295,12 +14491,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>778</v>
+        <v>810</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -14309,10 +14505,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>780</v>
+        <v>812</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -14331,12 +14527,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>781</v>
+        <v>813</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -14345,10 +14541,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>782</v>
+        <v>814</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>783</v>
+        <v>815</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -14365,12 +14561,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -14379,10 +14575,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>785</v>
+        <v>817</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>786</v>
+        <v>818</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -14401,12 +14597,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>787</v>
+        <v>819</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -14415,10 +14611,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>788</v>
+        <v>820</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>789</v>
+        <v>821</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -14435,12 +14631,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>790</v>
+        <v>822</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -14452,7 +14648,7 @@
         <v>71</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>791</v>
+        <v>823</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -14471,12 +14667,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>792</v>
+        <v>824</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -14488,7 +14684,7 @@
         <v>83</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -14507,12 +14703,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>794</v>
+        <v>826</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -14524,7 +14720,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -14546,7 +14742,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>796</v>
+        <v>828</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -14555,10 +14751,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -14578,7 +14774,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -14587,10 +14783,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -14610,7 +14806,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>802</v>
+        <v>834</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -14619,10 +14815,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>803</v>
+        <v>835</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>804</v>
+        <v>836</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -14642,7 +14838,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>805</v>
+        <v>837</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -14651,10 +14847,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>806</v>
+        <v>838</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>807</v>
+        <v>839</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -14674,7 +14870,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>808</v>
+        <v>840</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -14683,10 +14879,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>809</v>
+        <v>841</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>810</v>
+        <v>842</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -14706,7 +14902,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>811</v>
+        <v>843</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -14715,10 +14911,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>812</v>
+        <v>844</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -14738,7 +14934,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>814</v>
+        <v>846</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -14750,7 +14946,7 @@
         <v>52</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>815</v>
+        <v>847</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -14770,7 +14966,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>816</v>
+        <v>848</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -14782,7 +14978,7 @@
         <v>71</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>817</v>
+        <v>849</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -14804,7 +15000,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>818</v>
+        <v>850</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -14813,10 +15009,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>819</v>
+        <v>851</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>820</v>
+        <v>852</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -14836,7 +15032,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>821</v>
+        <v>853</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -14848,7 +15044,7 @@
         <v>83</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -14870,7 +15066,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>823</v>
+        <v>855</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -14879,10 +15075,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>824</v>
+        <v>856</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>825</v>
+        <v>857</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -14904,7 +15100,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -14913,10 +15109,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>827</v>
+        <v>859</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>828</v>
+        <v>860</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -14938,7 +15134,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>829</v>
+        <v>861</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -14950,7 +15146,7 @@
         <v>344</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>830</v>
+        <v>862</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -14970,7 +15166,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -14979,10 +15175,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>832</v>
+        <v>864</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>833</v>
+        <v>865</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15004,7 +15200,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>834</v>
+        <v>866</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15016,7 +15212,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>835</v>
+        <v>867</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15038,7 +15234,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>836</v>
+        <v>868</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15047,10 +15243,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>837</v>
+        <v>869</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>838</v>
+        <v>870</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15070,7 +15266,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>839</v>
+        <v>871</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -15079,10 +15275,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>840</v>
+        <v>872</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -15104,7 +15300,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -15116,7 +15312,7 @@
         <v>52</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>843</v>
+        <v>875</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -15136,7 +15332,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>844</v>
+        <v>876</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -15148,7 +15344,7 @@
         <v>80</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>845</v>
+        <v>877</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -15168,7 +15364,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>846</v>
+        <v>878</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -15177,10 +15373,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -15200,7 +15396,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -15209,10 +15405,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>851</v>
+        <v>883</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -15232,7 +15428,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>852</v>
+        <v>884</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -15244,7 +15440,7 @@
         <v>338</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -15264,7 +15460,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>854</v>
+        <v>886</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -15276,7 +15472,7 @@
         <v>80</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -15296,7 +15492,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>856</v>
+        <v>888</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -15305,10 +15501,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>857</v>
+        <v>889</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -15328,7 +15524,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>859</v>
+        <v>891</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -15340,7 +15536,7 @@
         <v>124</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>860</v>
+        <v>892</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -15360,7 +15556,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>861</v>
+        <v>893</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -15369,10 +15565,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>862</v>
+        <v>894</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>863</v>
+        <v>895</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -15392,7 +15588,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -15404,7 +15600,7 @@
         <v>80</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -15424,7 +15620,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>866</v>
+        <v>898</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -15433,10 +15629,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>867</v>
+        <v>899</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -15456,7 +15652,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>869</v>
+        <v>901</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -15468,7 +15664,7 @@
         <v>80</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>870</v>
+        <v>902</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -15488,7 +15684,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>871</v>
+        <v>903</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -15497,10 +15693,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>872</v>
+        <v>904</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>873</v>
+        <v>905</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -15520,7 +15716,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -15532,7 +15728,7 @@
         <v>80</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>875</v>
+        <v>907</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -15552,7 +15748,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -15561,10 +15757,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>877</v>
+        <v>909</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -15584,7 +15780,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>879</v>
+        <v>911</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -15593,10 +15789,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>880</v>
+        <v>912</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>881</v>
+        <v>913</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -15616,7 +15812,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -15625,10 +15821,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>883</v>
+        <v>915</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>884</v>
+        <v>916</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -15648,7 +15844,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>885</v>
+        <v>917</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -15657,10 +15853,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>887</v>
+        <v>919</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -15680,7 +15876,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>888</v>
+        <v>920</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -15689,10 +15885,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>889</v>
+        <v>921</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>890</v>
+        <v>922</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -15712,7 +15908,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>891</v>
+        <v>923</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -15721,10 +15917,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>893</v>
+        <v>925</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -15744,7 +15940,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>894</v>
+        <v>926</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -15753,10 +15949,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>895</v>
+        <v>927</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -15776,7 +15972,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>897</v>
+        <v>929</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -15785,10 +15981,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>898</v>
+        <v>930</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>899</v>
+        <v>931</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -15810,7 +16006,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -15819,10 +16015,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>901</v>
+        <v>933</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>902</v>
+        <v>934</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -15844,7 +16040,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>903</v>
+        <v>935</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -15853,10 +16049,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>905</v>
+        <v>937</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -15876,7 +16072,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>906</v>
+        <v>938</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -15888,7 +16084,7 @@
         <v>190</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>907</v>
+        <v>939</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -15910,7 +16106,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>908</v>
+        <v>940</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -15919,10 +16115,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>909</v>
+        <v>941</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>910</v>
+        <v>942</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -15944,7 +16140,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>911</v>
+        <v>943</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -15953,10 +16149,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>913</v>
+        <v>945</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -15978,7 +16174,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -15987,10 +16183,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>916</v>
+        <v>948</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16010,7 +16206,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>917</v>
+        <v>949</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16019,10 +16215,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>919</v>
+        <v>951</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16042,7 +16238,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>920</v>
+        <v>952</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16051,10 +16247,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>921</v>
+        <v>953</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>922</v>
+        <v>954</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16074,7 +16270,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>923</v>
+        <v>955</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -16083,10 +16279,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>924</v>
+        <v>956</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>925</v>
+        <v>957</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -16108,7 +16304,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>926</v>
+        <v>958</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -16117,10 +16313,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>928</v>
+        <v>960</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -16140,7 +16336,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -16149,10 +16345,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>930</v>
+        <v>962</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -16172,7 +16368,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>932</v>
+        <v>964</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -16181,10 +16377,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>933</v>
+        <v>965</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>934</v>
+        <v>966</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -16204,7 +16400,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>935</v>
+        <v>967</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -16213,10 +16409,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>936</v>
+        <v>968</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>937</v>
+        <v>969</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -16236,7 +16432,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>938</v>
+        <v>970</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -16245,10 +16441,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>939</v>
+        <v>971</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>940</v>
+        <v>972</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -16268,7 +16464,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>941</v>
+        <v>973</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -16277,10 +16473,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>943</v>
+        <v>975</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -16300,7 +16496,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>944</v>
+        <v>976</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -16309,10 +16505,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>945</v>
+        <v>977</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>946</v>
+        <v>978</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -16332,7 +16528,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -16341,10 +16537,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>948</v>
+        <v>980</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -16364,7 +16560,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>950</v>
+        <v>982</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -16373,10 +16569,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -16396,7 +16592,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>953</v>
+        <v>985</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -16405,10 +16601,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>954</v>
+        <v>986</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>955</v>
+        <v>987</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -16428,7 +16624,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>956</v>
+        <v>988</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -16437,10 +16633,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>957</v>
+        <v>989</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>958</v>
+        <v>990</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -16460,7 +16656,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -16469,10 +16665,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>960</v>
+        <v>992</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>961</v>
+        <v>993</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -16492,7 +16688,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>962</v>
+        <v>994</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -16501,10 +16697,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>963</v>
+        <v>995</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>964</v>
+        <v>996</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -16524,7 +16720,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>965</v>
+        <v>997</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -16533,10 +16729,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -16556,7 +16752,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>968</v>
+        <v>1000</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -16565,10 +16761,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>969</v>
+        <v>1001</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>970</v>
+        <v>1002</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -16588,7 +16784,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -16597,10 +16793,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>972</v>
+        <v>1004</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>973</v>
+        <v>1005</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -16620,7 +16816,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>974</v>
+        <v>1006</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -16629,10 +16825,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>975</v>
+        <v>1007</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>976</v>
+        <v>1008</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -16652,7 +16848,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>977</v>
+        <v>1009</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -16661,10 +16857,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>978</v>
+        <v>1010</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>979</v>
+        <v>1011</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -16684,7 +16880,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -16693,10 +16889,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>981</v>
+        <v>1013</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>982</v>
+        <v>1014</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -16716,7 +16912,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>983</v>
+        <v>1015</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -16725,10 +16921,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>984</v>
+        <v>1016</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>985</v>
+        <v>1017</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -16748,7 +16944,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>986</v>
+        <v>1018</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -16757,10 +16953,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>987</v>
+        <v>1019</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>988</v>
+        <v>1020</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -16780,7 +16976,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>989</v>
+        <v>1021</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -16789,10 +16985,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>990</v>
+        <v>1022</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>991</v>
+        <v>1023</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -16812,7 +17008,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>992</v>
+        <v>1024</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -16821,10 +17017,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>993</v>
+        <v>1025</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>994</v>
+        <v>1026</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -16844,7 +17040,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>995</v>
+        <v>1027</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -16853,10 +17049,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>996</v>
+        <v>1028</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>997</v>
+        <v>1029</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -16876,7 +17072,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>998</v>
+        <v>1030</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -16885,10 +17081,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>999</v>
+        <v>1031</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1000</v>
+        <v>1032</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -16908,7 +17104,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1001</v>
+        <v>1033</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -16917,10 +17113,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1002</v>
+        <v>1034</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1003</v>
+        <v>1035</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -16940,7 +17136,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1004</v>
+        <v>1036</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -16949,10 +17145,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1005</v>
+        <v>1037</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1006</v>
+        <v>1038</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -16972,7 +17168,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1007</v>
+        <v>1039</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -16981,10 +17177,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1009</v>
+        <v>1041</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17004,7 +17200,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1010</v>
+        <v>1042</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17013,10 +17209,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1011</v>
+        <v>1043</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1012</v>
+        <v>1044</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17036,7 +17232,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1013</v>
+        <v>1045</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17045,10 +17241,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1014</v>
+        <v>1046</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1015</v>
+        <v>1047</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17068,7 +17264,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1016</v>
+        <v>1048</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17077,10 +17273,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1017</v>
+        <v>1049</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1018</v>
+        <v>1050</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -17100,7 +17296,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1019</v>
+        <v>1051</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -17109,10 +17305,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1020</v>
+        <v>1052</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1021</v>
+        <v>1053</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -17132,7 +17328,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1022</v>
+        <v>1054</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -17141,10 +17337,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1023</v>
+        <v>1055</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1024</v>
+        <v>1056</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -17164,7 +17360,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1025</v>
+        <v>1057</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -17173,10 +17369,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1027</v>
+        <v>1059</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -17196,7 +17392,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1028</v>
+        <v>1060</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -17205,10 +17401,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1029</v>
+        <v>1061</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1030</v>
+        <v>1062</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -17228,7 +17424,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1031</v>
+        <v>1063</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -17237,10 +17433,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1032</v>
+        <v>1064</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -17260,7 +17456,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1034</v>
+        <v>1066</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -17269,10 +17465,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1036</v>
+        <v>1068</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -17292,7 +17488,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1037</v>
+        <v>1069</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -17301,10 +17497,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1038</v>
+        <v>1070</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1039</v>
+        <v>1071</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -17324,7 +17520,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1040</v>
+        <v>1072</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -17333,10 +17529,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1041</v>
+        <v>1073</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1042</v>
+        <v>1074</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -17356,7 +17552,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1043</v>
+        <v>1075</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -17365,10 +17561,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1044</v>
+        <v>1076</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1045</v>
+        <v>1077</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -17388,7 +17584,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1046</v>
+        <v>1078</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -17397,10 +17593,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1048</v>
+        <v>1080</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -17420,7 +17616,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -17429,10 +17625,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1050</v>
+        <v>1082</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -17452,7 +17648,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1052</v>
+        <v>1084</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -17461,10 +17657,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -17484,7 +17680,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1055</v>
+        <v>1087</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -17493,10 +17689,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1056</v>
+        <v>1088</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1057</v>
+        <v>1089</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -17516,7 +17712,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1058</v>
+        <v>1090</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -17525,10 +17721,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1059</v>
+        <v>1091</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -17548,7 +17744,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1061</v>
+        <v>1093</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -17557,10 +17753,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1063</v>
+        <v>1095</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -17580,7 +17776,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1064</v>
+        <v>1096</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -17589,10 +17785,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1065</v>
+        <v>1097</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1066</v>
+        <v>1098</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -17612,7 +17808,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1067</v>
+        <v>1099</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -17621,10 +17817,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1068</v>
+        <v>1100</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1069</v>
+        <v>1101</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -17644,7 +17840,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1070</v>
+        <v>1102</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -17653,10 +17849,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1071</v>
+        <v>1103</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1072</v>
+        <v>1104</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -17676,7 +17872,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1073</v>
+        <v>1105</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -17685,10 +17881,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1074</v>
+        <v>1106</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1075</v>
+        <v>1107</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -17708,7 +17904,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1076</v>
+        <v>1108</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -17717,10 +17913,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1077</v>
+        <v>1109</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1078</v>
+        <v>1110</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -17740,7 +17936,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1079</v>
+        <v>1111</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -17749,10 +17945,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1080</v>
+        <v>1112</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -17772,7 +17968,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1082</v>
+        <v>1114</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -17781,10 +17977,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1083</v>
+        <v>1115</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1084</v>
+        <v>1116</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -17804,7 +18000,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1085</v>
+        <v>1117</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -17813,10 +18009,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1086</v>
+        <v>1118</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1087</v>
+        <v>1119</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -17836,7 +18032,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1088</v>
+        <v>1120</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -17845,10 +18041,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1089</v>
+        <v>1121</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1090</v>
+        <v>1122</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -17868,7 +18064,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1091</v>
+        <v>1123</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -17877,10 +18073,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1092</v>
+        <v>1124</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1093</v>
+        <v>1125</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -17900,7 +18096,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1094</v>
+        <v>1126</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -17909,10 +18105,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1089</v>
+        <v>1121</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1095</v>
+        <v>1127</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -17932,7 +18128,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1096</v>
+        <v>1128</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -17941,10 +18137,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1097</v>
+        <v>1129</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1098</v>
+        <v>1130</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -17966,7 +18162,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1099</v>
+        <v>1131</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -17975,10 +18171,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1100</v>
+        <v>1132</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1101</v>
+        <v>1133</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -17998,7 +18194,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1102</v>
+        <v>1134</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18007,10 +18203,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1103</v>
+        <v>1135</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1104</v>
+        <v>1136</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18030,7 +18226,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1105</v>
+        <v>1137</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18039,10 +18235,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1106</v>
+        <v>1138</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1107</v>
+        <v>1139</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18062,7 +18258,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1108</v>
+        <v>1140</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18071,10 +18267,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1109</v>
+        <v>1141</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1110</v>
+        <v>1142</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -18094,7 +18290,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1111</v>
+        <v>1143</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -18103,10 +18299,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1112</v>
+        <v>1144</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1113</v>
+        <v>1145</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -18126,7 +18322,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1114</v>
+        <v>1146</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -18135,10 +18331,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1115</v>
+        <v>1147</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1116</v>
+        <v>1148</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -18158,7 +18354,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1117</v>
+        <v>1149</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -18167,10 +18363,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1118</v>
+        <v>1150</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1119</v>
+        <v>1151</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -18190,7 +18386,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1120</v>
+        <v>1152</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -18199,10 +18395,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1121</v>
+        <v>1153</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1122</v>
+        <v>1154</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -18222,7 +18418,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1123</v>
+        <v>1155</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -18231,10 +18427,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1124</v>
+        <v>1156</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1125</v>
+        <v>1157</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -18254,7 +18450,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1126</v>
+        <v>1158</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -18263,10 +18459,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1127</v>
+        <v>1159</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1128</v>
+        <v>1160</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -18288,7 +18484,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1129</v>
+        <v>1161</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -18297,10 +18493,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1130</v>
+        <v>1162</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1131</v>
+        <v>1163</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -18322,7 +18518,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1132</v>
+        <v>1164</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -18331,10 +18527,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1133</v>
+        <v>1165</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1134</v>
+        <v>1166</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -18356,7 +18552,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1135</v>
+        <v>1167</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -18365,10 +18561,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1136</v>
+        <v>1168</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1137</v>
+        <v>1169</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -18388,7 +18584,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1138</v>
+        <v>1170</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -18397,10 +18593,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1139</v>
+        <v>1171</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1140</v>
+        <v>1172</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -18420,7 +18616,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1141</v>
+        <v>1173</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -18429,10 +18625,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1142</v>
+        <v>1174</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1143</v>
+        <v>1175</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -18452,7 +18648,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1144</v>
+        <v>1176</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -18461,10 +18657,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1145</v>
+        <v>1177</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1146</v>
+        <v>1178</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -18486,7 +18682,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1147</v>
+        <v>1179</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -18498,7 +18694,7 @@
         <v>326</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1148</v>
+        <v>1180</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -18520,7 +18716,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1149</v>
+        <v>1181</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -18529,10 +18725,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1150</v>
+        <v>1182</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1151</v>
+        <v>1183</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -18552,7 +18748,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1152</v>
+        <v>1184</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -18561,10 +18757,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1153</v>
+        <v>1185</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1154</v>
+        <v>1186</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -18584,7 +18780,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1155</v>
+        <v>1187</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -18593,10 +18789,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1156</v>
+        <v>1188</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1157</v>
+        <v>1189</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -18616,7 +18812,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1158</v>
+        <v>1190</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -18625,10 +18821,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1159</v>
+        <v>1191</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1160</v>
+        <v>1192</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -18648,7 +18844,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1161</v>
+        <v>1193</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -18657,10 +18853,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1162</v>
+        <v>1194</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1162</v>
+        <v>1194</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -18675,14 +18871,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1163</v>
+        <v>1195</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1164</v>
+        <v>1196</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -18691,10 +18887,10 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1165</v>
+        <v>1197</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1166</v>
+        <v>1198</v>
       </c>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
@@ -18714,7 +18910,7 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1167</v>
+        <v>1199</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -18723,13 +18919,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1168</v>
+        <v>1200</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1169</v>
+        <v>1201</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1170</v>
+        <v>1202</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -18738,25 +18934,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1171</v>
+        <v>1203</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1172</v>
+        <v>1204</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1173</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1174</v>
+        <v>1206</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -18765,13 +18961,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1175</v>
+        <v>1207</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1176</v>
+        <v>1208</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1177</v>
+        <v>1209</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -18780,25 +18976,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1178</v>
+        <v>1210</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1172</v>
+        <v>1204</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1179</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1180</v>
+        <v>1212</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -18807,13 +19003,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1181</v>
+        <v>1213</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1182</v>
+        <v>1214</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1183</v>
+        <v>1215</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -18822,25 +19018,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1184</v>
+        <v>1216</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1172</v>
+        <v>1204</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1185</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1186</v>
+        <v>1218</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -18849,13 +19045,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1187</v>
+        <v>1219</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1188</v>
+        <v>1220</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1189</v>
+        <v>1221</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -18864,25 +19060,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1190</v>
+        <v>1222</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1172</v>
+        <v>1204</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1191</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1192</v>
+        <v>1224</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -18891,10 +19087,10 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1193</v>
+        <v>1225</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1194</v>
+        <v>1226</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
@@ -18914,7 +19110,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1195</v>
+        <v>1227</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -18923,10 +19119,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1196</v>
+        <v>1228</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1197</v>
+        <v>1229</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -18946,7 +19142,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1198</v>
+        <v>1230</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -18955,10 +19151,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1200</v>
+        <v>1232</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -18978,7 +19174,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1201</v>
+        <v>1233</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -18987,10 +19183,10 @@
         <v>10</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1202</v>
+        <v>1234</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1203</v>
+        <v>1235</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -19010,7 +19206,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1204</v>
+        <v>1236</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19019,10 +19215,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1205</v>
+        <v>1237</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1206</v>
+        <v>1238</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19042,7 +19238,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1207</v>
+        <v>1239</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -19051,10 +19247,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1208</v>
+        <v>1240</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1209</v>
+        <v>1241</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -19074,7 +19270,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1210</v>
+        <v>1242</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -19083,10 +19279,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1211</v>
+        <v>1243</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1212</v>
+        <v>1244</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -19106,7 +19302,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1213</v>
+        <v>1245</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -19115,10 +19311,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1214</v>
+        <v>1246</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1215</v>
+        <v>1247</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -19138,7 +19334,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -19147,10 +19343,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1217</v>
+        <v>1249</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1218</v>
+        <v>1250</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -19170,7 +19366,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1219</v>
+        <v>1251</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -19179,10 +19375,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1220</v>
+        <v>1252</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1221</v>
+        <v>1253</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -19202,7 +19398,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -19211,10 +19407,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1223</v>
+        <v>1255</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1224</v>
+        <v>1256</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -19234,7 +19430,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1225</v>
+        <v>1257</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -19243,10 +19439,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1226</v>
+        <v>1258</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1227</v>
+        <v>1259</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -19266,7 +19462,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1228</v>
+        <v>1260</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -19275,10 +19471,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1229</v>
+        <v>1261</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -19298,7 +19494,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1231</v>
+        <v>1263</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -19307,10 +19503,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1232</v>
+        <v>1264</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -19330,7 +19526,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1234</v>
+        <v>1266</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -19339,10 +19535,10 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1235</v>
+        <v>1267</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1236</v>
+        <v>1268</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
@@ -19362,7 +19558,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1237</v>
+        <v>1269</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -19371,13 +19567,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1238</v>
+        <v>1270</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1239</v>
+        <v>1271</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1240</v>
+        <v>1272</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -19386,27 +19582,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1241</v>
+        <v>1273</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1242</v>
+        <v>1274</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1243</v>
+        <v>1275</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1244</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1245</v>
+        <v>1277</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -19415,13 +19611,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1246</v>
+        <v>1278</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1247</v>
+        <v>1279</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1248</v>
+        <v>1280</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -19430,27 +19626,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1249</v>
+        <v>1281</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1250</v>
+        <v>1282</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1251</v>
+        <v>1283</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1252</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1253</v>
+        <v>1285</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -19459,13 +19655,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1181</v>
+        <v>1213</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1254</v>
+        <v>1286</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1255</v>
+        <v>1287</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -19474,25 +19670,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1184</v>
+        <v>1216</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1256</v>
+        <v>1288</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1257</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1258</v>
+        <v>1290</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -19501,13 +19697,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1187</v>
+        <v>1219</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1259</v>
+        <v>1291</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1260</v>
+        <v>1292</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -19516,25 +19712,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1261</v>
+        <v>1293</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1262</v>
+        <v>1294</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1263</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1264</v>
+        <v>1296</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -19543,10 +19739,10 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1265</v>
+        <v>1297</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1266</v>
+        <v>1298</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
@@ -19566,7 +19762,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1267</v>
+        <v>1299</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -19575,10 +19771,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1196</v>
+        <v>1228</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1268</v>
+        <v>1300</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -19598,7 +19794,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1269</v>
+        <v>1301</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -19607,10 +19803,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1270</v>
+        <v>1302</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -19630,7 +19826,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1271</v>
+        <v>1303</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -19639,10 +19835,10 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1272</v>
+        <v>1304</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1273</v>
+        <v>1305</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -19662,7 +19858,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1274</v>
+        <v>1306</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -19671,10 +19867,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1275</v>
+        <v>1307</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1276</v>
+        <v>1308</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -19694,7 +19890,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1277</v>
+        <v>1309</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -19703,10 +19899,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1278</v>
+        <v>1310</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1279</v>
+        <v>1311</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -19726,7 +19922,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1280</v>
+        <v>1312</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -19735,10 +19931,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1281</v>
+        <v>1313</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1282</v>
+        <v>1314</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -19758,7 +19954,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1283</v>
+        <v>1315</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -19767,10 +19963,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1284</v>
+        <v>1316</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1285</v>
+        <v>1317</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -19790,7 +19986,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -19799,10 +19995,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1287</v>
+        <v>1319</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1288</v>
+        <v>1320</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -19822,7 +20018,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1289</v>
+        <v>1321</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -19831,10 +20027,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1290</v>
+        <v>1322</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1291</v>
+        <v>1323</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -19854,7 +20050,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1292</v>
+        <v>1324</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -19863,10 +20059,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1293</v>
+        <v>1325</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1294</v>
+        <v>1326</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -19886,7 +20082,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1295</v>
+        <v>1327</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -19895,10 +20091,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1226</v>
+        <v>1258</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1296</v>
+        <v>1328</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -19918,7 +20114,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1297</v>
+        <v>1329</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -19927,10 +20123,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1298</v>
+        <v>1330</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1299</v>
+        <v>1331</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -19950,7 +20146,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1300</v>
+        <v>1332</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -19959,10 +20155,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1301</v>
+        <v>1333</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1302</v>
+        <v>1334</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -19982,7 +20178,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1303</v>
+        <v>1335</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -19991,10 +20187,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1304</v>
+        <v>1336</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1305</v>
+        <v>1337</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -20014,7 +20210,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1306</v>
+        <v>1338</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -20023,10 +20219,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1307</v>
+        <v>1339</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1308</v>
+        <v>1340</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -20046,7 +20242,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1309</v>
+        <v>1341</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -20055,10 +20251,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1310</v>
+        <v>1342</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1311</v>
+        <v>1343</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -20078,7 +20274,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1312</v>
+        <v>1344</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -20087,10 +20283,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1313</v>
+        <v>1345</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1314</v>
+        <v>1346</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -20110,7 +20306,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1315</v>
+        <v>1347</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -20119,10 +20315,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1316</v>
+        <v>1348</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1317</v>
+        <v>1349</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -20142,7 +20338,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1318</v>
+        <v>1350</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -20151,10 +20347,10 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1319</v>
+        <v>1351</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1320</v>
+        <v>1352</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
@@ -20174,7 +20370,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1321</v>
+        <v>1353</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -20183,10 +20379,10 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1322</v>
+        <v>1354</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1323</v>
+        <v>1355</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
@@ -20206,7 +20402,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1324</v>
+        <v>1356</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -20215,10 +20411,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1325</v>
+        <v>1357</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1326</v>
+        <v>1358</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -20238,7 +20434,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1327</v>
+        <v>1359</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -20247,10 +20443,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1328</v>
+        <v>1360</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1329</v>
+        <v>1361</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -20265,7 +20461,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1330</v>
+        <v>1362</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="1363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="1394">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -1079,6 +1079,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/8_Pydantic/1. Why Pydantic.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Typed lists and dicts, hints not enforced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 1 › 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added typed collections and that hints are not enforced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never run alone: three lines of annotations</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC110</t>
   </si>
   <si>
@@ -1088,18 +1100,51 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/8_Pydantic/Pydantic_From_Scratch.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">85-cell step-by-step build: problem, hints, coercion, Field, EmailStr, SecretStr, validators, computed_field, nested models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 1 › 1.1, 1.2; Ch 2 › SecretStr; Ch 3 › 3.2, 3.3; Ch 4 › constraint pitfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The year-suffix validator (strip_years_suffix) was left out at your instruction (its docstring says it runs before the integer check, but it does not unless mode='before'); most cells are empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added register_user problem, hints, required fields, bool coercion, model_dump, SecretStr details, disposable-email validator, pitfalls, computed_field, nested Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behaviour run on Pydantic 2.13. EmailStr not run (email-validator not installed in sandbox). Source quirks recorded: duplicate validator name, raise ValidationError, Field(gt) on str, model_dump(mode='json') masks the password</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC111</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/8_Pydantic/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Folder guide: files and uv sync / uv run main.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 1 › mini-project folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added file table and run commands</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC112</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/8_Pydantic/main.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Hello-world scaffold, no Pydantic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only prints 'Hello from 8-pydantic!'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentioned in the Ch 1 file table</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC113</t>
   </si>
   <si>
@@ -1115,6 +1160,12 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/8_Pydantic/test.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Two empty cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing in it</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC115</t>
   </si>
   <si>
@@ -1196,6 +1247,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_10_tool_with_ai_call.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Validated tool and AI call side by side, with @tool registry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 5 › 5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added call_tool_safely, kwargs logging, ask_ai fallback and the 'neither knows the other' point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run with no key; live tool call not run (no network)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC121</t>
   </si>
   <si>
@@ -1370,6 +1433,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_8_pydantic_with_ai.py</t>
   </si>
   <si>
+    <t xml:space="preserve">BaseModel, Field, field_validator, nested models, model_validate_json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 1 to 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every part is already in Pydantic Ch 1 to 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC133</t>
   </si>
   <si>
@@ -1379,6 +1451,15 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_9_api_call_with_structure.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Validate arguments with Pydantic before calling the API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 5 › 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad-argument path run; live API call not run (no network)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC134</t>
   </si>
   <si>
@@ -1448,6 +1529,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_03_structuring_with_pydantic.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Pydantic-validated extraction of a weather question, four-provider picker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 5 › 5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added provider priority order, RuntimeError, main loop, debug prints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run (needs an API key)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC143</t>
   </si>
   <si>
@@ -3692,7 +3785,7 @@
     <t xml:space="preserve">Stateless LLM calls, model vs chatbot vs agent, four providers, Pydantic extraction, manual tool call</t>
   </si>
   <si>
-    <t xml:space="preserve">Python › Ch 3 › 3.1 to 3.6; Pydantic › Ch 5 › 5.2</t>
+    <t xml:space="preserve">Python › Ch 3 › 3.1 to 3.6; Pydantic › Ch 5 › 5.4</t>
   </si>
   <si>
     <t xml:space="preserve">Provider code not run (needs API keys); model names may be out of date, flagged in the chapter</t>
@@ -4618,15 +4711,15 @@
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A5,Master!$H$2:$H$465,B$3)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A5,Master!$H$2:$H$465,C$3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A5,Master!$H$2:$H$465,D$3)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A5,Master!$H$2:$H$465,E$3)</f>
@@ -4634,7 +4727,7 @@
       </c>
       <c r="F5" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A5,Master!$H$2:$H$465,F$3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
         <f aca="false">SUM(B5:F5)</f>
@@ -4798,15 +4891,15 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -4814,7 +4907,7 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">SUM(G4:G10)</f>
@@ -4852,7 +4945,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4867,7 +4960,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4882,7 +4975,7 @@
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A16)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4912,7 +5005,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4927,7 +5020,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4942,7 +5035,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -8656,25 +8749,35 @@
       <c r="E110" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F110" s="3"/>
+      <c r="F110" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="G110" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I110" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="J110" s="3"/>
       <c r="K110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>38</v>
@@ -8683,30 +8786,42 @@
         <v>9</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F111" s="3"/>
+        <v>357</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="G111" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>360</v>
+      </c>
       <c r="K111" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L111" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="M111" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N111" s="3" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>38</v>
@@ -8718,27 +8833,35 @@
         <v>52</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F112" s="3"/>
+        <v>364</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>365</v>
+      </c>
       <c r="G112" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I112" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>366</v>
+      </c>
       <c r="J112" s="3"/>
       <c r="K112" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="N112" s="3"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>38</v>
@@ -8750,27 +8873,35 @@
         <v>124</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="F113" s="3"/>
+        <v>369</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>370</v>
+      </c>
       <c r="G113" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N113" s="3" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>38</v>
@@ -8782,7 +8913,7 @@
         <v>71</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
@@ -8804,7 +8935,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>38</v>
@@ -8813,30 +8944,38 @@
         <v>9</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="F115" s="3"/>
+        <v>377</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="G115" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
       <c r="K115" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>38</v>
@@ -8845,10 +8984,10 @@
         <v>8</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
@@ -8868,7 +9007,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>38</v>
@@ -8877,10 +9016,10 @@
         <v>8</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
@@ -8900,7 +9039,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>38</v>
@@ -8909,13 +9048,13 @@
         <v>8</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>22</v>
@@ -8924,25 +9063,25 @@
         <v>2</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="J118" s="3"/>
       <c r="K118" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>38</v>
@@ -8954,10 +9093,10 @@
         <v>52</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>22</v>
@@ -8966,25 +9105,25 @@
         <v>2</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="J119" s="3"/>
       <c r="K119" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="M119" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>38</v>
@@ -8993,13 +9132,13 @@
         <v>8</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>22</v>
@@ -9008,14 +9147,14 @@
         <v>2</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="J120" s="3"/>
       <c r="K120" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="M120" s="3" t="s">
         <v>284</v>
@@ -9026,7 +9165,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>38</v>
@@ -9035,30 +9174,40 @@
         <v>9</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="F121" s="3"/>
+        <v>406</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>407</v>
+      </c>
       <c r="G121" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I121" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>408</v>
+      </c>
       <c r="J121" s="3"/>
       <c r="K121" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L121" s="3"/>
-      <c r="M121" s="3"/>
-      <c r="N121" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="M121" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N121" s="3" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>38</v>
@@ -9067,10 +9216,10 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
@@ -9090,7 +9239,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>38</v>
@@ -9099,10 +9248,10 @@
         <v>8</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
@@ -9122,7 +9271,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>38</v>
@@ -9131,10 +9280,10 @@
         <v>8</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
@@ -9154,7 +9303,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>38</v>
@@ -9163,10 +9312,10 @@
         <v>8</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
@@ -9186,7 +9335,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>38</v>
@@ -9195,13 +9344,13 @@
         <v>8</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>22</v>
@@ -9210,14 +9359,14 @@
         <v>2</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="J126" s="3"/>
       <c r="K126" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="M126" s="3" t="s">
         <v>284</v>
@@ -9228,7 +9377,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>38</v>
@@ -9237,13 +9386,13 @@
         <v>8</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>22</v>
@@ -9252,14 +9401,14 @@
         <v>2</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="M127" s="3" t="s">
         <v>284</v>
@@ -9270,7 +9419,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>38</v>
@@ -9279,13 +9428,13 @@
         <v>8</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>22</v>
@@ -9294,14 +9443,14 @@
         <v>2</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="J128" s="3"/>
       <c r="K128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="M128" s="3" t="s">
         <v>284</v>
@@ -9312,7 +9461,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>38</v>
@@ -9321,13 +9470,13 @@
         <v>8</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>22</v>
@@ -9336,25 +9485,25 @@
         <v>2</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="J129" s="3"/>
       <c r="K129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="M129" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>38</v>
@@ -9363,13 +9512,13 @@
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>22</v>
@@ -9378,25 +9527,25 @@
         <v>2</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="J130" s="3"/>
       <c r="K130" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="M130" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>38</v>
@@ -9405,13 +9554,13 @@
         <v>8</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>22</v>
@@ -9420,25 +9569,25 @@
         <v>2</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="J131" s="3"/>
       <c r="K131" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="M131" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>38</v>
@@ -9447,13 +9596,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>22</v>
@@ -9462,25 +9611,25 @@
         <v>2</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="M132" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>38</v>
@@ -9489,30 +9638,40 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="F133" s="3"/>
+        <v>468</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>469</v>
+      </c>
       <c r="G133" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I133" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>470</v>
+      </c>
       <c r="J133" s="3"/>
       <c r="K133" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L133" s="3"/>
-      <c r="M133" s="3"/>
-      <c r="N133" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L133" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="M133" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N133" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>38</v>
@@ -9521,30 +9680,40 @@
         <v>9</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="F134" s="3"/>
+        <v>474</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>475</v>
+      </c>
       <c r="G134" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I134" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>476</v>
+      </c>
       <c r="J134" s="3"/>
       <c r="K134" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L134" s="3"/>
-      <c r="M134" s="3"/>
-      <c r="N134" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N134" s="3" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>38</v>
@@ -9556,7 +9725,7 @@
         <v>71</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
@@ -9578,7 +9747,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>38</v>
@@ -9590,7 +9759,7 @@
         <v>83</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -9612,7 +9781,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>38</v>
@@ -9621,10 +9790,10 @@
         <v>10</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
@@ -9644,7 +9813,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>38</v>
@@ -9656,7 +9825,7 @@
         <v>52</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="F138" s="3"/>
       <c r="G138" s="3" t="s">
@@ -9676,7 +9845,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>38</v>
@@ -9688,7 +9857,7 @@
         <v>45</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
@@ -9707,12 +9876,12 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>38</v>
@@ -9724,7 +9893,7 @@
         <v>52</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3" t="s">
@@ -9741,12 +9910,12 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -9755,10 +9924,10 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3" t="s">
@@ -9775,12 +9944,12 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -9789,10 +9958,10 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
@@ -9809,12 +9978,12 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -9823,32 +9992,40 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="F143" s="3"/>
+        <v>500</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="G143" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I143" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L143" s="3"/>
-      <c r="M143" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="M143" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="N143" s="3" t="s">
-        <v>462</v>
+        <v>504</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -9857,10 +10034,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
@@ -9877,12 +10054,12 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -9891,10 +10068,10 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -9911,12 +10088,12 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -9925,10 +10102,10 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
@@ -9945,12 +10122,12 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -9959,10 +10136,10 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
@@ -9979,12 +10156,12 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -9993,10 +10170,10 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
@@ -10013,12 +10190,12 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -10030,7 +10207,7 @@
         <v>71</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -10049,12 +10226,12 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -10066,7 +10243,7 @@
         <v>52</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3" t="s">
@@ -10083,12 +10260,12 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -10100,7 +10277,7 @@
         <v>52</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
@@ -10117,12 +10294,12 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -10134,7 +10311,7 @@
         <v>344</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -10154,7 +10331,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>497</v>
+        <v>528</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -10166,7 +10343,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -10188,7 +10365,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10200,7 +10377,7 @@
         <v>63</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10222,7 +10399,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -10231,10 +10408,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -10254,7 +10431,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10266,7 +10443,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -10286,7 +10463,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -10295,10 +10472,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -10318,7 +10495,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -10327,10 +10504,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -10350,7 +10527,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -10359,10 +10536,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -10382,7 +10559,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -10394,7 +10571,7 @@
         <v>124</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -10414,7 +10591,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -10426,7 +10603,7 @@
         <v>71</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -10448,7 +10625,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -10460,7 +10637,7 @@
         <v>83</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -10482,7 +10659,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -10494,7 +10671,7 @@
         <v>52</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -10514,7 +10691,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -10526,7 +10703,7 @@
         <v>344</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -10543,12 +10720,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -10560,7 +10737,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -10579,12 +10756,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -10596,7 +10773,7 @@
         <v>63</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -10615,12 +10792,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -10629,10 +10806,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -10649,12 +10826,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -10663,10 +10840,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -10683,12 +10860,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -10697,10 +10874,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -10717,12 +10894,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -10731,10 +10908,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -10751,12 +10928,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -10765,10 +10942,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -10785,12 +10962,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -10799,10 +10976,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -10819,12 +10996,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>548</v>
+        <v>579</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -10836,7 +11013,7 @@
         <v>52</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -10853,12 +11030,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -10870,7 +11047,7 @@
         <v>124</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -10887,12 +11064,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -10904,7 +11081,7 @@
         <v>71</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -10923,12 +11100,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -10940,7 +11117,7 @@
         <v>326</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -10959,12 +11136,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -10976,7 +11153,7 @@
         <v>83</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -10995,12 +11172,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11009,10 +11186,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>559</v>
+        <v>590</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11029,12 +11206,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>561</v>
+        <v>592</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11043,10 +11220,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>563</v>
+        <v>594</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -11063,12 +11240,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -11077,10 +11254,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>565</v>
+        <v>596</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -11097,12 +11274,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -11111,10 +11288,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -11131,12 +11308,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>570</v>
+        <v>601</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -11145,10 +11322,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>571</v>
+        <v>602</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -11165,12 +11342,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>573</v>
+        <v>604</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -11179,10 +11356,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>574</v>
+        <v>605</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11199,12 +11376,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11216,7 +11393,7 @@
         <v>52</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11233,12 +11410,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>578</v>
+        <v>609</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11250,7 +11427,7 @@
         <v>52</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11267,12 +11444,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -11281,10 +11458,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -11301,12 +11478,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -11315,10 +11492,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>585</v>
+        <v>616</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -11335,12 +11512,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -11349,10 +11526,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -11369,12 +11546,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -11383,10 +11560,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>592</v>
+        <v>623</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -11403,12 +11580,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>593</v>
+        <v>624</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -11417,10 +11594,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>595</v>
+        <v>626</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -11437,12 +11614,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -11451,10 +11628,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -11471,12 +11648,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>599</v>
+        <v>630</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -11485,10 +11662,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -11505,12 +11682,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -11519,10 +11696,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -11539,12 +11716,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -11553,10 +11730,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -11573,12 +11750,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -11590,7 +11767,7 @@
         <v>52</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -11607,12 +11784,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -11624,7 +11801,7 @@
         <v>52</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -11641,12 +11818,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -11655,10 +11832,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>614</v>
+        <v>645</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -11680,7 +11857,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -11689,10 +11866,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -11712,7 +11889,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>618</v>
+        <v>649</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -11721,10 +11898,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>620</v>
+        <v>651</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -11744,7 +11921,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>621</v>
+        <v>652</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -11753,10 +11930,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>622</v>
+        <v>653</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -11776,7 +11953,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -11785,10 +11962,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -11808,7 +11985,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>627</v>
+        <v>658</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -11817,10 +11994,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>629</v>
+        <v>660</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -11840,7 +12017,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>630</v>
+        <v>661</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -11852,7 +12029,7 @@
         <v>52</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>631</v>
+        <v>662</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -11872,7 +12049,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>632</v>
+        <v>663</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -11884,7 +12061,7 @@
         <v>52</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -11904,7 +12081,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -11913,10 +12090,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -11938,7 +12115,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -11947,10 +12124,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -11970,7 +12147,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -11979,10 +12156,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>639</v>
+        <v>670</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>640</v>
+        <v>671</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12004,7 +12181,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12013,10 +12190,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12036,7 +12213,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12048,7 +12225,7 @@
         <v>52</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>644</v>
+        <v>675</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -12068,7 +12245,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>645</v>
+        <v>676</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -12080,7 +12257,7 @@
         <v>52</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -12100,7 +12277,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -12112,7 +12289,7 @@
         <v>52</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -12132,7 +12309,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -12141,10 +12318,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>650</v>
+        <v>681</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -12166,7 +12343,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -12175,10 +12352,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12198,7 +12375,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>655</v>
+        <v>686</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12207,10 +12384,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12230,7 +12407,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>658</v>
+        <v>689</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12242,7 +12419,7 @@
         <v>49</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12262,7 +12439,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12271,10 +12448,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>662</v>
+        <v>693</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -12294,7 +12471,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -12306,7 +12483,7 @@
         <v>206</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -12326,7 +12503,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -12338,7 +12515,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -12360,7 +12537,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -12372,7 +12549,7 @@
         <v>63</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -12394,7 +12571,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>669</v>
+        <v>700</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -12406,7 +12583,7 @@
         <v>52</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>670</v>
+        <v>701</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -12426,7 +12603,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>671</v>
+        <v>702</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -12438,7 +12615,7 @@
         <v>71</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -12460,7 +12637,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -12472,7 +12649,7 @@
         <v>74</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -12492,7 +12669,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -12504,7 +12681,7 @@
         <v>80</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -12524,7 +12701,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -12536,7 +12713,7 @@
         <v>83</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -12558,7 +12735,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>679</v>
+        <v>710</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -12570,7 +12747,7 @@
         <v>259</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>680</v>
+        <v>711</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -12590,7 +12767,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>681</v>
+        <v>712</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -12602,7 +12779,7 @@
         <v>52</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>682</v>
+        <v>713</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -12622,7 +12799,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -12634,7 +12811,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>684</v>
+        <v>715</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -12654,7 +12831,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>685</v>
+        <v>716</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -12663,10 +12840,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>686</v>
+        <v>717</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>687</v>
+        <v>718</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -12686,7 +12863,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -12695,10 +12872,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>690</v>
+        <v>721</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -12718,7 +12895,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>691</v>
+        <v>722</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -12727,10 +12904,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>693</v>
+        <v>724</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -12750,7 +12927,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>694</v>
+        <v>725</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -12759,10 +12936,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>696</v>
+        <v>727</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -12782,7 +12959,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>697</v>
+        <v>728</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -12794,7 +12971,7 @@
         <v>52</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>698</v>
+        <v>729</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -12814,7 +12991,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -12823,10 +13000,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>701</v>
+        <v>732</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -12848,7 +13025,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -12860,7 +13037,7 @@
         <v>253</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>703</v>
+        <v>734</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -12880,7 +13057,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>704</v>
+        <v>735</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -12892,7 +13069,7 @@
         <v>256</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -12912,7 +13089,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -12921,10 +13098,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>707</v>
+        <v>738</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>708</v>
+        <v>739</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -12944,7 +13121,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>709</v>
+        <v>740</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -12956,7 +13133,7 @@
         <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -12976,7 +13153,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>711</v>
+        <v>742</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -12988,7 +13165,7 @@
         <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>712</v>
+        <v>743</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13008,7 +13185,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>713</v>
+        <v>744</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13020,7 +13197,7 @@
         <v>55</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13040,7 +13217,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>715</v>
+        <v>746</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13052,7 +13229,7 @@
         <v>58</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>716</v>
+        <v>747</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -13072,7 +13249,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>717</v>
+        <v>748</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -13084,7 +13261,7 @@
         <v>52</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>718</v>
+        <v>749</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -13104,7 +13281,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -13116,7 +13293,7 @@
         <v>63</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>720</v>
+        <v>751</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -13138,7 +13315,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>721</v>
+        <v>752</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -13150,7 +13327,7 @@
         <v>52</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>722</v>
+        <v>753</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -13170,7 +13347,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>723</v>
+        <v>754</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -13182,7 +13359,7 @@
         <v>121</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>724</v>
+        <v>755</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13202,7 +13379,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>725</v>
+        <v>756</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13214,7 +13391,7 @@
         <v>124</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>726</v>
+        <v>757</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13234,7 +13411,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>727</v>
+        <v>758</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13246,7 +13423,7 @@
         <v>145</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>728</v>
+        <v>759</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13266,7 +13443,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>729</v>
+        <v>760</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -13278,7 +13455,7 @@
         <v>71</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>730</v>
+        <v>761</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -13300,7 +13477,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>731</v>
+        <v>762</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -13312,7 +13489,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>732</v>
+        <v>763</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -13332,7 +13509,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>733</v>
+        <v>764</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -13344,7 +13521,7 @@
         <v>190</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>734</v>
+        <v>765</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -13366,7 +13543,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>735</v>
+        <v>766</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -13378,7 +13555,7 @@
         <v>193</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>736</v>
+        <v>767</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -13400,7 +13577,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>737</v>
+        <v>768</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -13412,7 +13589,7 @@
         <v>129</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>738</v>
+        <v>769</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -13434,7 +13611,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -13446,7 +13623,7 @@
         <v>83</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>740</v>
+        <v>771</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -13468,7 +13645,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>741</v>
+        <v>772</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -13480,7 +13657,7 @@
         <v>203</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -13500,7 +13677,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -13512,7 +13689,7 @@
         <v>63</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -13534,7 +13711,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>745</v>
+        <v>776</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -13546,7 +13723,7 @@
         <v>52</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>746</v>
+        <v>777</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -13566,7 +13743,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>747</v>
+        <v>778</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -13578,7 +13755,7 @@
         <v>216</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>748</v>
+        <v>779</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -13600,7 +13777,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>749</v>
+        <v>780</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -13612,7 +13789,7 @@
         <v>124</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>750</v>
+        <v>781</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -13632,7 +13809,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>751</v>
+        <v>782</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -13644,7 +13821,7 @@
         <v>71</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>752</v>
+        <v>783</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -13666,7 +13843,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>753</v>
+        <v>784</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -13678,7 +13855,7 @@
         <v>55</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>754</v>
+        <v>785</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -13698,7 +13875,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -13710,7 +13887,7 @@
         <v>58</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -13730,7 +13907,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -13742,7 +13919,7 @@
         <v>83</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>758</v>
+        <v>789</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -13764,7 +13941,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>759</v>
+        <v>790</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -13776,7 +13953,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -13798,7 +13975,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>761</v>
+        <v>792</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -13810,7 +13987,7 @@
         <v>63</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>762</v>
+        <v>793</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -13832,7 +14009,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>763</v>
+        <v>794</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -13844,7 +14021,7 @@
         <v>52</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -13864,7 +14041,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -13876,7 +14053,7 @@
         <v>68</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>766</v>
+        <v>797</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -13896,7 +14073,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>767</v>
+        <v>798</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -13908,7 +14085,7 @@
         <v>71</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>768</v>
+        <v>799</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -13930,7 +14107,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -13942,7 +14119,7 @@
         <v>74</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -13962,7 +14139,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>771</v>
+        <v>802</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -13974,7 +14151,7 @@
         <v>77</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>772</v>
+        <v>803</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -13994,7 +14171,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>773</v>
+        <v>804</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14006,7 +14183,7 @@
         <v>80</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>774</v>
+        <v>805</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14026,7 +14203,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>775</v>
+        <v>806</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14038,7 +14215,7 @@
         <v>83</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14060,7 +14237,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>777</v>
+        <v>808</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -14072,7 +14249,7 @@
         <v>52</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>778</v>
+        <v>809</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -14092,7 +14269,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>779</v>
+        <v>810</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -14104,7 +14281,7 @@
         <v>63</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>780</v>
+        <v>811</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -14126,7 +14303,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>781</v>
+        <v>812</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -14135,10 +14312,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>782</v>
+        <v>813</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>783</v>
+        <v>814</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -14158,7 +14335,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>784</v>
+        <v>815</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -14170,7 +14347,7 @@
         <v>52</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>785</v>
+        <v>816</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -14190,7 +14367,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>786</v>
+        <v>817</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14199,10 +14376,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>787</v>
+        <v>818</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>788</v>
+        <v>819</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14222,7 +14399,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>789</v>
+        <v>820</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14234,7 +14411,7 @@
         <v>124</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>790</v>
+        <v>821</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14254,7 +14431,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14266,7 +14443,7 @@
         <v>71</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>792</v>
+        <v>823</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -14288,7 +14465,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -14300,7 +14477,7 @@
         <v>83</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -14322,7 +14499,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>795</v>
+        <v>826</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -14334,7 +14511,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>796</v>
+        <v>827</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -14353,12 +14530,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>798</v>
+        <v>829</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -14367,10 +14544,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>799</v>
+        <v>830</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>800</v>
+        <v>831</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -14387,12 +14564,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -14401,10 +14578,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>802</v>
+        <v>833</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>803</v>
+        <v>834</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -14421,12 +14598,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>804</v>
+        <v>835</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -14435,10 +14612,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>805</v>
+        <v>836</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>806</v>
+        <v>837</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -14457,12 +14634,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>807</v>
+        <v>838</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -14471,10 +14648,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>808</v>
+        <v>839</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>809</v>
+        <v>840</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -14491,12 +14668,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>810</v>
+        <v>841</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -14505,10 +14682,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>811</v>
+        <v>842</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -14527,12 +14704,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>813</v>
+        <v>844</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -14541,10 +14718,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>814</v>
+        <v>845</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>815</v>
+        <v>846</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -14561,12 +14738,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>816</v>
+        <v>847</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -14575,10 +14752,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>818</v>
+        <v>849</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -14597,12 +14774,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>819</v>
+        <v>850</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -14611,10 +14788,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -14631,12 +14808,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>822</v>
+        <v>853</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -14648,7 +14825,7 @@
         <v>71</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>823</v>
+        <v>854</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -14667,12 +14844,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>824</v>
+        <v>855</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -14684,7 +14861,7 @@
         <v>83</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>825</v>
+        <v>856</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -14703,12 +14880,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>826</v>
+        <v>857</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -14720,7 +14897,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>827</v>
+        <v>858</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -14742,7 +14919,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>828</v>
+        <v>859</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -14751,10 +14928,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>830</v>
+        <v>861</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -14774,7 +14951,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -14783,10 +14960,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>832</v>
+        <v>863</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>833</v>
+        <v>864</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -14806,7 +14983,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>834</v>
+        <v>865</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -14815,10 +14992,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>835</v>
+        <v>866</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>836</v>
+        <v>867</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -14838,7 +15015,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>837</v>
+        <v>868</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -14847,10 +15024,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>838</v>
+        <v>869</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>839</v>
+        <v>870</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -14870,7 +15047,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>840</v>
+        <v>871</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -14879,10 +15056,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>841</v>
+        <v>872</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>842</v>
+        <v>873</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -14902,7 +15079,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>843</v>
+        <v>874</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -14911,10 +15088,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>844</v>
+        <v>875</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -14934,7 +15111,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -14946,7 +15123,7 @@
         <v>52</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>847</v>
+        <v>878</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -14966,7 +15143,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>848</v>
+        <v>879</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -14978,7 +15155,7 @@
         <v>71</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>849</v>
+        <v>880</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15000,7 +15177,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>850</v>
+        <v>881</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15009,10 +15186,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>851</v>
+        <v>882</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15032,7 +15209,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>853</v>
+        <v>884</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15044,7 +15221,7 @@
         <v>83</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>854</v>
+        <v>885</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -15066,7 +15243,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>855</v>
+        <v>886</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -15075,10 +15252,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>856</v>
+        <v>887</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>857</v>
+        <v>888</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -15100,7 +15277,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>858</v>
+        <v>889</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -15109,10 +15286,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>859</v>
+        <v>890</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -15134,7 +15311,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>861</v>
+        <v>892</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -15146,7 +15323,7 @@
         <v>344</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -15166,7 +15343,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>863</v>
+        <v>894</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -15175,10 +15352,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>864</v>
+        <v>895</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>865</v>
+        <v>896</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15200,7 +15377,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>866</v>
+        <v>897</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15212,7 +15389,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>867</v>
+        <v>898</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15234,7 +15411,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>868</v>
+        <v>899</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15243,10 +15420,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>870</v>
+        <v>901</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15266,7 +15443,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>871</v>
+        <v>902</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -15275,10 +15452,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>872</v>
+        <v>903</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>873</v>
+        <v>904</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -15300,7 +15477,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>874</v>
+        <v>905</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -15312,7 +15489,7 @@
         <v>52</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>875</v>
+        <v>906</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -15332,7 +15509,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>876</v>
+        <v>907</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -15344,7 +15521,7 @@
         <v>80</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>877</v>
+        <v>908</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -15364,7 +15541,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>878</v>
+        <v>909</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -15373,10 +15550,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>879</v>
+        <v>910</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>880</v>
+        <v>911</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -15396,7 +15573,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -15405,10 +15582,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>882</v>
+        <v>913</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>883</v>
+        <v>914</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -15428,7 +15605,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>884</v>
+        <v>915</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -15440,7 +15617,7 @@
         <v>338</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>885</v>
+        <v>916</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -15460,7 +15637,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>886</v>
+        <v>917</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -15472,7 +15649,7 @@
         <v>80</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>887</v>
+        <v>918</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -15492,7 +15669,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>888</v>
+        <v>919</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -15501,10 +15678,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>889</v>
+        <v>920</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -15524,7 +15701,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -15536,7 +15713,7 @@
         <v>124</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -15556,7 +15733,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -15565,10 +15742,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>895</v>
+        <v>926</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -15588,7 +15765,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>896</v>
+        <v>927</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -15600,7 +15777,7 @@
         <v>80</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>897</v>
+        <v>928</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -15620,7 +15797,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>898</v>
+        <v>929</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -15629,10 +15806,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>899</v>
+        <v>930</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>900</v>
+        <v>931</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -15652,7 +15829,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>901</v>
+        <v>932</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -15664,7 +15841,7 @@
         <v>80</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>902</v>
+        <v>933</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -15684,7 +15861,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>903</v>
+        <v>934</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -15693,10 +15870,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>904</v>
+        <v>935</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>905</v>
+        <v>936</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -15716,7 +15893,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>906</v>
+        <v>937</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -15728,7 +15905,7 @@
         <v>80</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>907</v>
+        <v>938</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -15748,7 +15925,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>908</v>
+        <v>939</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -15757,10 +15934,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>909</v>
+        <v>940</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>910</v>
+        <v>941</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -15780,7 +15957,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>911</v>
+        <v>942</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -15789,10 +15966,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>912</v>
+        <v>943</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>913</v>
+        <v>944</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -15812,7 +15989,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>914</v>
+        <v>945</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -15821,10 +15998,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>915</v>
+        <v>946</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>916</v>
+        <v>947</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -15844,7 +16021,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>917</v>
+        <v>948</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -15853,10 +16030,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>918</v>
+        <v>949</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>919</v>
+        <v>950</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -15876,7 +16053,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>920</v>
+        <v>951</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -15885,10 +16062,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>921</v>
+        <v>952</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>922</v>
+        <v>953</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -15908,7 +16085,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>923</v>
+        <v>954</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -15917,10 +16094,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>924</v>
+        <v>955</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>925</v>
+        <v>956</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -15940,7 +16117,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>926</v>
+        <v>957</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -15949,10 +16126,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>928</v>
+        <v>959</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -15972,7 +16149,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>929</v>
+        <v>960</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -15981,10 +16158,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>930</v>
+        <v>961</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>931</v>
+        <v>962</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16006,7 +16183,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16015,10 +16192,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>933</v>
+        <v>964</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>934</v>
+        <v>965</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16040,7 +16217,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>935</v>
+        <v>966</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16049,10 +16226,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>936</v>
+        <v>967</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>937</v>
+        <v>968</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -16072,7 +16249,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>938</v>
+        <v>969</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -16084,7 +16261,7 @@
         <v>190</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>939</v>
+        <v>970</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -16106,7 +16283,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>940</v>
+        <v>971</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -16115,10 +16292,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>941</v>
+        <v>972</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>942</v>
+        <v>973</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -16140,7 +16317,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>943</v>
+        <v>974</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -16149,10 +16326,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>944</v>
+        <v>975</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>945</v>
+        <v>976</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -16174,7 +16351,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>946</v>
+        <v>977</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -16183,10 +16360,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>947</v>
+        <v>978</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>948</v>
+        <v>979</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16206,7 +16383,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16215,10 +16392,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>950</v>
+        <v>981</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>951</v>
+        <v>982</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16238,7 +16415,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>952</v>
+        <v>983</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16247,10 +16424,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>953</v>
+        <v>984</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>954</v>
+        <v>985</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16270,7 +16447,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>955</v>
+        <v>986</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -16279,10 +16456,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>956</v>
+        <v>987</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>957</v>
+        <v>988</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -16304,7 +16481,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>958</v>
+        <v>989</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -16313,10 +16490,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>959</v>
+        <v>990</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -16336,7 +16513,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>961</v>
+        <v>992</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -16345,10 +16522,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>962</v>
+        <v>993</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>963</v>
+        <v>994</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -16368,7 +16545,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -16377,10 +16554,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>965</v>
+        <v>996</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>966</v>
+        <v>997</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -16400,7 +16577,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>967</v>
+        <v>998</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -16409,10 +16586,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>968</v>
+        <v>999</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>969</v>
+        <v>1000</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -16432,7 +16609,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>970</v>
+        <v>1001</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -16441,10 +16618,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>971</v>
+        <v>1002</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>972</v>
+        <v>1003</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -16464,7 +16641,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>973</v>
+        <v>1004</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -16473,10 +16650,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>974</v>
+        <v>1005</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>975</v>
+        <v>1006</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -16496,7 +16673,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>976</v>
+        <v>1007</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -16505,10 +16682,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>977</v>
+        <v>1008</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>978</v>
+        <v>1009</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -16528,7 +16705,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>979</v>
+        <v>1010</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -16537,10 +16714,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>980</v>
+        <v>1011</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>981</v>
+        <v>1012</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -16560,7 +16737,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>982</v>
+        <v>1013</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -16569,10 +16746,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>983</v>
+        <v>1014</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>984</v>
+        <v>1015</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -16592,7 +16769,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>985</v>
+        <v>1016</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -16601,10 +16778,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>986</v>
+        <v>1017</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>987</v>
+        <v>1018</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -16624,7 +16801,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>988</v>
+        <v>1019</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -16633,10 +16810,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>989</v>
+        <v>1020</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>990</v>
+        <v>1021</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -16656,7 +16833,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>991</v>
+        <v>1022</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -16665,10 +16842,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>992</v>
+        <v>1023</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>993</v>
+        <v>1024</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -16688,7 +16865,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>994</v>
+        <v>1025</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -16697,10 +16874,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>995</v>
+        <v>1026</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>996</v>
+        <v>1027</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -16720,7 +16897,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>997</v>
+        <v>1028</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -16729,10 +16906,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>998</v>
+        <v>1029</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>999</v>
+        <v>1030</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -16752,7 +16929,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1000</v>
+        <v>1031</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -16761,10 +16938,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1001</v>
+        <v>1032</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1002</v>
+        <v>1033</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -16784,7 +16961,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1003</v>
+        <v>1034</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -16793,10 +16970,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1004</v>
+        <v>1035</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1005</v>
+        <v>1036</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -16816,7 +16993,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1006</v>
+        <v>1037</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -16825,10 +17002,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1007</v>
+        <v>1038</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1008</v>
+        <v>1039</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -16848,7 +17025,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1009</v>
+        <v>1040</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -16857,10 +17034,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1010</v>
+        <v>1041</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1011</v>
+        <v>1042</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -16880,7 +17057,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1012</v>
+        <v>1043</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -16889,10 +17066,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1013</v>
+        <v>1044</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -16912,7 +17089,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1015</v>
+        <v>1046</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -16921,10 +17098,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1016</v>
+        <v>1047</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1017</v>
+        <v>1048</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -16944,7 +17121,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1018</v>
+        <v>1049</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -16953,10 +17130,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1019</v>
+        <v>1050</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1020</v>
+        <v>1051</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -16976,7 +17153,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1021</v>
+        <v>1052</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -16985,10 +17162,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1022</v>
+        <v>1053</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1023</v>
+        <v>1054</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17008,7 +17185,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1024</v>
+        <v>1055</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17017,10 +17194,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1025</v>
+        <v>1056</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1026</v>
+        <v>1057</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17040,7 +17217,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1027</v>
+        <v>1058</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17049,10 +17226,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1028</v>
+        <v>1059</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1029</v>
+        <v>1060</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -17072,7 +17249,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1030</v>
+        <v>1061</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -17081,10 +17258,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1031</v>
+        <v>1062</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1032</v>
+        <v>1063</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -17104,7 +17281,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1033</v>
+        <v>1064</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -17113,10 +17290,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1034</v>
+        <v>1065</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -17136,7 +17313,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1036</v>
+        <v>1067</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -17145,10 +17322,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1037</v>
+        <v>1068</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1038</v>
+        <v>1069</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -17168,7 +17345,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1039</v>
+        <v>1070</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -17177,10 +17354,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1040</v>
+        <v>1071</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1041</v>
+        <v>1072</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17200,7 +17377,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1042</v>
+        <v>1073</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17209,10 +17386,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1043</v>
+        <v>1074</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1044</v>
+        <v>1075</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17232,7 +17409,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1045</v>
+        <v>1076</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17241,10 +17418,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1046</v>
+        <v>1077</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1047</v>
+        <v>1078</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17264,7 +17441,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1048</v>
+        <v>1079</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17273,10 +17450,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1049</v>
+        <v>1080</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1050</v>
+        <v>1081</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -17296,7 +17473,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1051</v>
+        <v>1082</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -17305,10 +17482,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1052</v>
+        <v>1083</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1053</v>
+        <v>1084</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -17328,7 +17505,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1054</v>
+        <v>1085</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -17337,10 +17514,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1055</v>
+        <v>1086</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1056</v>
+        <v>1087</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -17360,7 +17537,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1057</v>
+        <v>1088</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -17369,10 +17546,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1058</v>
+        <v>1089</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1059</v>
+        <v>1090</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -17392,7 +17569,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1060</v>
+        <v>1091</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -17401,10 +17578,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1061</v>
+        <v>1092</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1062</v>
+        <v>1093</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -17424,7 +17601,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1063</v>
+        <v>1094</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -17433,10 +17610,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1064</v>
+        <v>1095</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1065</v>
+        <v>1096</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -17456,7 +17633,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1066</v>
+        <v>1097</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -17465,10 +17642,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1067</v>
+        <v>1098</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1068</v>
+        <v>1099</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -17488,7 +17665,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1069</v>
+        <v>1100</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -17497,10 +17674,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1070</v>
+        <v>1101</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1071</v>
+        <v>1102</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -17520,7 +17697,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1072</v>
+        <v>1103</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -17529,10 +17706,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1073</v>
+        <v>1104</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -17552,7 +17729,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1075</v>
+        <v>1106</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -17561,10 +17738,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1076</v>
+        <v>1107</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1077</v>
+        <v>1108</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -17584,7 +17761,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1078</v>
+        <v>1109</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -17593,10 +17770,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1079</v>
+        <v>1110</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1080</v>
+        <v>1111</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -17616,7 +17793,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1081</v>
+        <v>1112</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -17625,10 +17802,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1082</v>
+        <v>1113</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1083</v>
+        <v>1114</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -17648,7 +17825,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1084</v>
+        <v>1115</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -17657,10 +17834,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -17680,7 +17857,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1087</v>
+        <v>1118</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -17689,10 +17866,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1088</v>
+        <v>1119</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1089</v>
+        <v>1120</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -17712,7 +17889,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1090</v>
+        <v>1121</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -17721,10 +17898,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1091</v>
+        <v>1122</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1092</v>
+        <v>1123</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -17744,7 +17921,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1093</v>
+        <v>1124</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -17753,10 +17930,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1094</v>
+        <v>1125</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1095</v>
+        <v>1126</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -17776,7 +17953,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1096</v>
+        <v>1127</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -17785,10 +17962,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1097</v>
+        <v>1128</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1098</v>
+        <v>1129</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -17808,7 +17985,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1099</v>
+        <v>1130</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -17817,10 +17994,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1100</v>
+        <v>1131</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1101</v>
+        <v>1132</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -17840,7 +18017,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1102</v>
+        <v>1133</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -17849,10 +18026,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1103</v>
+        <v>1134</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1104</v>
+        <v>1135</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -17872,7 +18049,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1105</v>
+        <v>1136</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -17881,10 +18058,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1106</v>
+        <v>1137</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1107</v>
+        <v>1138</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -17904,7 +18081,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1108</v>
+        <v>1139</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -17913,10 +18090,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1109</v>
+        <v>1140</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1110</v>
+        <v>1141</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -17936,7 +18113,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1111</v>
+        <v>1142</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -17945,10 +18122,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1112</v>
+        <v>1143</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1113</v>
+        <v>1144</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -17968,7 +18145,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1114</v>
+        <v>1145</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -17977,10 +18154,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1115</v>
+        <v>1146</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1116</v>
+        <v>1147</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18000,7 +18177,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1117</v>
+        <v>1148</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18009,10 +18186,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1118</v>
+        <v>1149</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1119</v>
+        <v>1150</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18032,7 +18209,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1120</v>
+        <v>1151</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18041,10 +18218,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1122</v>
+        <v>1153</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18064,7 +18241,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1123</v>
+        <v>1154</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -18073,10 +18250,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1124</v>
+        <v>1155</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1125</v>
+        <v>1156</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -18096,7 +18273,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1126</v>
+        <v>1157</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -18105,10 +18282,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1121</v>
+        <v>1152</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1127</v>
+        <v>1158</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -18128,7 +18305,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1128</v>
+        <v>1159</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -18137,10 +18314,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1130</v>
+        <v>1161</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -18162,7 +18339,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1131</v>
+        <v>1162</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -18171,10 +18348,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1132</v>
+        <v>1163</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -18194,7 +18371,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1134</v>
+        <v>1165</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18203,10 +18380,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1135</v>
+        <v>1166</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1136</v>
+        <v>1167</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18226,7 +18403,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18235,10 +18412,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1139</v>
+        <v>1170</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18258,7 +18435,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1140</v>
+        <v>1171</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18267,10 +18444,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1141</v>
+        <v>1172</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1142</v>
+        <v>1173</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -18290,7 +18467,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1143</v>
+        <v>1174</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -18299,10 +18476,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1144</v>
+        <v>1175</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1145</v>
+        <v>1176</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -18322,7 +18499,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1146</v>
+        <v>1177</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -18331,10 +18508,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1147</v>
+        <v>1178</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1148</v>
+        <v>1179</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -18354,7 +18531,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1149</v>
+        <v>1180</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -18363,10 +18540,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1150</v>
+        <v>1181</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1151</v>
+        <v>1182</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -18386,7 +18563,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1152</v>
+        <v>1183</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -18395,10 +18572,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1154</v>
+        <v>1185</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -18418,7 +18595,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1155</v>
+        <v>1186</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -18427,10 +18604,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1157</v>
+        <v>1188</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -18450,7 +18627,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1158</v>
+        <v>1189</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -18459,10 +18636,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1159</v>
+        <v>1190</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1160</v>
+        <v>1191</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -18484,7 +18661,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -18493,10 +18670,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1162</v>
+        <v>1193</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1163</v>
+        <v>1194</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -18518,7 +18695,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1164</v>
+        <v>1195</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -18527,10 +18704,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1165</v>
+        <v>1196</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1166</v>
+        <v>1197</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -18552,7 +18729,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1167</v>
+        <v>1198</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -18561,10 +18738,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1168</v>
+        <v>1199</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1169</v>
+        <v>1200</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -18584,7 +18761,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1170</v>
+        <v>1201</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -18593,10 +18770,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1171</v>
+        <v>1202</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1172</v>
+        <v>1203</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -18616,7 +18793,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1173</v>
+        <v>1204</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -18625,10 +18802,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1174</v>
+        <v>1205</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1175</v>
+        <v>1206</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -18648,7 +18825,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1176</v>
+        <v>1207</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -18657,10 +18834,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1177</v>
+        <v>1208</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1178</v>
+        <v>1209</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -18682,7 +18859,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1179</v>
+        <v>1210</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -18694,7 +18871,7 @@
         <v>326</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1180</v>
+        <v>1211</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -18716,7 +18893,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1181</v>
+        <v>1212</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -18725,10 +18902,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1182</v>
+        <v>1213</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1183</v>
+        <v>1214</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -18748,7 +18925,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1184</v>
+        <v>1215</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -18757,10 +18934,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1185</v>
+        <v>1216</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1186</v>
+        <v>1217</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -18780,7 +18957,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1187</v>
+        <v>1218</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -18789,10 +18966,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1188</v>
+        <v>1219</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1189</v>
+        <v>1220</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -18812,7 +18989,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1190</v>
+        <v>1221</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -18821,10 +18998,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1191</v>
+        <v>1222</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1192</v>
+        <v>1223</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -18844,7 +19021,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1193</v>
+        <v>1224</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -18853,10 +19030,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1194</v>
+        <v>1225</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -18871,14 +19048,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1195</v>
+        <v>1226</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1196</v>
+        <v>1227</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -18887,10 +19064,10 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1197</v>
+        <v>1228</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1198</v>
+        <v>1229</v>
       </c>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
@@ -18910,7 +19087,7 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1199</v>
+        <v>1230</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -18919,13 +19096,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1201</v>
+        <v>1232</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1202</v>
+        <v>1233</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -18934,25 +19111,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1203</v>
+        <v>1234</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1206</v>
+        <v>1237</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -18961,13 +19138,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1207</v>
+        <v>1238</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1208</v>
+        <v>1239</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1209</v>
+        <v>1240</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -18976,25 +19153,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1210</v>
+        <v>1241</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1211</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1212</v>
+        <v>1243</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19003,13 +19180,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1213</v>
+        <v>1244</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1214</v>
+        <v>1245</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1215</v>
+        <v>1246</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19018,25 +19195,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1216</v>
+        <v>1247</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1217</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1218</v>
+        <v>1249</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19045,13 +19222,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1219</v>
+        <v>1250</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1220</v>
+        <v>1251</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1221</v>
+        <v>1252</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -19060,25 +19237,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1222</v>
+        <v>1253</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1223</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1224</v>
+        <v>1255</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -19087,10 +19264,10 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1225</v>
+        <v>1256</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1226</v>
+        <v>1257</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
@@ -19110,7 +19287,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1227</v>
+        <v>1258</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -19119,10 +19296,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1229</v>
+        <v>1260</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -19142,7 +19319,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1230</v>
+        <v>1261</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -19151,10 +19328,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1231</v>
+        <v>1262</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1232</v>
+        <v>1263</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -19174,7 +19351,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1233</v>
+        <v>1264</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -19183,10 +19360,10 @@
         <v>10</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1234</v>
+        <v>1265</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1235</v>
+        <v>1266</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -19206,7 +19383,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1236</v>
+        <v>1267</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19215,10 +19392,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1237</v>
+        <v>1268</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19238,7 +19415,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1239</v>
+        <v>1270</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -19247,10 +19424,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1240</v>
+        <v>1271</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1241</v>
+        <v>1272</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -19270,7 +19447,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1242</v>
+        <v>1273</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -19279,10 +19456,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1243</v>
+        <v>1274</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1244</v>
+        <v>1275</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -19302,7 +19479,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1245</v>
+        <v>1276</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -19311,10 +19488,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1246</v>
+        <v>1277</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1247</v>
+        <v>1278</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -19334,7 +19511,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1248</v>
+        <v>1279</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -19343,10 +19520,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1249</v>
+        <v>1280</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1250</v>
+        <v>1281</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -19366,7 +19543,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1251</v>
+        <v>1282</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -19375,10 +19552,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1252</v>
+        <v>1283</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1253</v>
+        <v>1284</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -19398,7 +19575,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1254</v>
+        <v>1285</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -19407,10 +19584,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1255</v>
+        <v>1286</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1256</v>
+        <v>1287</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -19430,7 +19607,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1257</v>
+        <v>1288</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -19439,10 +19616,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1258</v>
+        <v>1289</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1259</v>
+        <v>1290</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -19462,7 +19639,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1260</v>
+        <v>1291</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -19471,10 +19648,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1261</v>
+        <v>1292</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1262</v>
+        <v>1293</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -19494,7 +19671,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -19503,10 +19680,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1264</v>
+        <v>1295</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -19526,7 +19703,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1266</v>
+        <v>1297</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -19535,10 +19712,10 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1267</v>
+        <v>1298</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1268</v>
+        <v>1299</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
@@ -19558,7 +19735,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1269</v>
+        <v>1300</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -19567,13 +19744,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1270</v>
+        <v>1301</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1271</v>
+        <v>1302</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1272</v>
+        <v>1303</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -19582,27 +19759,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1273</v>
+        <v>1304</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1274</v>
+        <v>1305</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1275</v>
+        <v>1306</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1276</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1277</v>
+        <v>1308</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -19611,13 +19788,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1278</v>
+        <v>1309</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1279</v>
+        <v>1310</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1280</v>
+        <v>1311</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -19626,27 +19803,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1281</v>
+        <v>1312</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1282</v>
+        <v>1313</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1283</v>
+        <v>1314</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1284</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1285</v>
+        <v>1316</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -19655,13 +19832,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1213</v>
+        <v>1244</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1286</v>
+        <v>1317</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1287</v>
+        <v>1318</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -19670,25 +19847,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1216</v>
+        <v>1247</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1288</v>
+        <v>1319</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1289</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1290</v>
+        <v>1321</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -19697,13 +19874,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1219</v>
+        <v>1250</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1291</v>
+        <v>1322</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1292</v>
+        <v>1323</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -19712,25 +19889,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1293</v>
+        <v>1324</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1294</v>
+        <v>1325</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>284</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1295</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1296</v>
+        <v>1327</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -19739,10 +19916,10 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1297</v>
+        <v>1328</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1298</v>
+        <v>1329</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
@@ -19762,7 +19939,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1299</v>
+        <v>1330</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -19771,10 +19948,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1300</v>
+        <v>1331</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -19794,7 +19971,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1301</v>
+        <v>1332</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -19803,10 +19980,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1231</v>
+        <v>1262</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1302</v>
+        <v>1333</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -19826,7 +20003,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1303</v>
+        <v>1334</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -19835,10 +20012,10 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1304</v>
+        <v>1335</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1305</v>
+        <v>1336</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -19858,7 +20035,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1306</v>
+        <v>1337</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -19867,10 +20044,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1307</v>
+        <v>1338</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1308</v>
+        <v>1339</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -19890,7 +20067,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1309</v>
+        <v>1340</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -19899,10 +20076,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1310</v>
+        <v>1341</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1311</v>
+        <v>1342</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -19922,7 +20099,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1312</v>
+        <v>1343</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -19931,10 +20108,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1313</v>
+        <v>1344</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1314</v>
+        <v>1345</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -19954,7 +20131,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1315</v>
+        <v>1346</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -19963,10 +20140,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1316</v>
+        <v>1347</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1317</v>
+        <v>1348</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -19986,7 +20163,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1318</v>
+        <v>1349</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -19995,10 +20172,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1319</v>
+        <v>1350</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1320</v>
+        <v>1351</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -20018,7 +20195,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1321</v>
+        <v>1352</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -20027,10 +20204,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1322</v>
+        <v>1353</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1323</v>
+        <v>1354</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -20050,7 +20227,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1324</v>
+        <v>1355</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -20059,10 +20236,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1325</v>
+        <v>1356</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1326</v>
+        <v>1357</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -20082,7 +20259,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1327</v>
+        <v>1358</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -20091,10 +20268,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1258</v>
+        <v>1289</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1328</v>
+        <v>1359</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -20114,7 +20291,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1329</v>
+        <v>1360</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -20123,10 +20300,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1330</v>
+        <v>1361</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1331</v>
+        <v>1362</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -20146,7 +20323,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1332</v>
+        <v>1363</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -20155,10 +20332,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1333</v>
+        <v>1364</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1334</v>
+        <v>1365</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -20178,7 +20355,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1335</v>
+        <v>1366</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -20187,10 +20364,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1336</v>
+        <v>1367</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1337</v>
+        <v>1368</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -20210,7 +20387,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1338</v>
+        <v>1369</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -20219,10 +20396,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1339</v>
+        <v>1370</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1340</v>
+        <v>1371</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -20242,7 +20419,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1341</v>
+        <v>1372</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -20251,10 +20428,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1342</v>
+        <v>1373</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1343</v>
+        <v>1374</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -20274,7 +20451,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1344</v>
+        <v>1375</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -20283,10 +20460,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1345</v>
+        <v>1376</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -20306,7 +20483,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1347</v>
+        <v>1378</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -20315,10 +20492,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1348</v>
+        <v>1379</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1349</v>
+        <v>1380</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -20338,7 +20515,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1350</v>
+        <v>1381</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -20347,10 +20524,10 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1351</v>
+        <v>1382</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1352</v>
+        <v>1383</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
@@ -20370,7 +20547,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1353</v>
+        <v>1384</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -20379,10 +20556,10 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1354</v>
+        <v>1385</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1355</v>
+        <v>1386</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
@@ -20402,7 +20579,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1356</v>
+        <v>1387</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -20411,10 +20588,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1357</v>
+        <v>1388</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1358</v>
+        <v>1389</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -20434,7 +20611,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1359</v>
+        <v>1390</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -20443,10 +20620,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1360</v>
+        <v>1391</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1361</v>
+        <v>1392</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -20461,7 +20638,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1362</v>
+        <v>1393</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="1394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4112" uniqueCount="1413">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -857,6 +857,21 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/01 - 27 Jun - Python Setup &amp; API Basics/Class-1-Python-and-AI.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 01 whiteboard: tools to install, UV, venv and versions, uv init file table, class rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 1 › 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added UV facts, tools, version check, venv picture and the six-row uv init file table; corrected the uv.lock line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiteboard PDF: read text and viewed the page. Left out as no teaching content: class timings, Zoom rules, first-4-classes list, study pictures, two job-description screenshots. Slide crosses out Anaconda; transcript says conda is fine if not mixed. '10-100x faster' is the slide's claim, not measured</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC094</t>
   </si>
   <si>
@@ -878,9 +893,6 @@
     <t xml:space="preserve">Added the outline and said what is not yet explained</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-31</t>
-  </si>
-  <si>
     <t xml:space="preserve">File is 6 comment lines; I did not explain the other four terms from memory</t>
   </si>
   <si>
@@ -977,9 +989,6 @@
     <t xml:space="preserve">First uv init project: uv sync then uv run main.py</t>
   </si>
   <si>
-    <t xml:space="preserve">Python › Ch 1 › 1.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Added uv sync and uv run main.py</t>
   </si>
   <si>
@@ -1064,6 +1073,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/.env.example</t>
   </si>
   <si>
+    <t xml:space="preserve">Three placeholder key lines for Groq, OpenRouter and OpenAI, all optional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.8; Python › Ch 3 › 3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key names and the fallback note are already in Ch 2 and Ch 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked for secrets: placeholders only, no real keys</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC108</t>
   </si>
   <si>
@@ -1175,6 +1196,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/Agentic-3-0.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Course brochure and Day 2 whiteboard: platform, syllabus, 2.0 vs 3.0, dynamic typing, why Pydantic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 2 › 2.7; Pydantic › Ch 1; Python › Ch 1 › 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teaching ideas (dynamic typing, not type safe, Pydantic purpose, Git Bash, Linux servers) already in the books; the rest is logistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logistics left out: agenda, class notifications, Agentic 2.0 vs 3.0, FAQ questions</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC116</t>
   </si>
   <si>
@@ -1184,6 +1217,18 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/Class-3-4.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 03-04 whiteboard: Pydantic blueprint analogy, tokens and pricing, embeddings, stateless calls, web vs API, agent anatomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pydantic › Ch 1 › 1.1; LLM › Ch 3 › 3.1, 3.3; Python › Ch 3 › 3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added customs-form analogy, Google analogy, token example, 6x output price, controlled buffet vs a la carte, agent prompt with tools and tool-call flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiteboard PDF: viewed the page. Price card ($5/$30, labelled 5.5) has no unit; check current prices. One student question has no answer on the slide</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC117</t>
   </si>
   <si>
@@ -1485,6 +1530,18 @@
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekend 01 overview and navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Says class 01 covers '.env hygiene' but gives no details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation page; no detail to write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left out</t>
   </si>
   <si>
     <t xml:space="preserve">LC138</t>
@@ -4681,7 +4738,7 @@
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,B$3)</f>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,C$3)</f>
@@ -4689,7 +4746,7 @@
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,D$3)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,E$3)</f>
@@ -4697,7 +4754,7 @@
       </c>
       <c r="F4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,F$3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <f aca="false">SUM(B4:F4)</f>
@@ -4891,7 +4948,7 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
@@ -4899,7 +4956,7 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -4907,7 +4964,7 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">SUM(G4:G10)</f>
@@ -4945,7 +5002,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4960,7 +5017,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -5005,7 +5062,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5020,7 +5077,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5035,7 +5092,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -8141,25 +8198,35 @@
       <c r="E94" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="G94" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="J94" s="3"/>
       <c r="K94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-      <c r="N94" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>38</v>
@@ -8168,13 +8235,13 @@
         <v>8</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>22</v>
@@ -8183,27 +8250,27 @@
         <v>3</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>38</v>
@@ -8212,13 +8279,13 @@
         <v>8</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>22</v>
@@ -8227,25 +8294,25 @@
         <v>2</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J96" s="3"/>
       <c r="K96" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>38</v>
@@ -8257,10 +8324,10 @@
         <v>52</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>22</v>
@@ -8269,25 +8336,25 @@
         <v>2</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J97" s="3"/>
       <c r="K97" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>38</v>
@@ -8296,13 +8363,13 @@
         <v>8</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>22</v>
@@ -8311,25 +8378,25 @@
         <v>2</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J98" s="3"/>
       <c r="K98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>38</v>
@@ -8338,13 +8405,13 @@
         <v>8</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>22</v>
@@ -8353,23 +8420,23 @@
         <v>2</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="J99" s="3"/>
       <c r="K99" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>38</v>
@@ -8381,7 +8448,7 @@
         <v>63</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
@@ -8403,7 +8470,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>38</v>
@@ -8415,10 +8482,10 @@
         <v>52</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>22</v>
@@ -8427,23 +8494,23 @@
         <v>2</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>317</v>
+        <v>278</v>
       </c>
       <c r="J101" s="3"/>
       <c r="K101" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>38</v>
@@ -8455,10 +8522,10 @@
         <v>124</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>22</v>
@@ -8467,23 +8534,23 @@
         <v>2</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>317</v>
+        <v>278</v>
       </c>
       <c r="J102" s="3"/>
       <c r="K102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>38</v>
@@ -8495,7 +8562,7 @@
         <v>71</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
@@ -8517,7 +8584,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>38</v>
@@ -8526,10 +8593,10 @@
         <v>8</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
@@ -8544,14 +8611,14 @@
         <v>21</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>38</v>
@@ -8563,7 +8630,7 @@
         <v>83</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
@@ -8585,7 +8652,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>38</v>
@@ -8594,13 +8661,13 @@
         <v>8</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>22</v>
@@ -8609,25 +8676,25 @@
         <v>2</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J106" s="3"/>
       <c r="K106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>38</v>
@@ -8636,13 +8703,13 @@
         <v>8</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>22</v>
@@ -8651,25 +8718,25 @@
         <v>2</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="J107" s="3"/>
       <c r="K107" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>38</v>
@@ -8678,30 +8745,40 @@
         <v>8</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F108" s="3"/>
+        <v>348</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="G108" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I108" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="J108" s="3"/>
       <c r="K108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L108" s="3"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M108" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N108" s="3" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>38</v>
@@ -8713,7 +8790,7 @@
         <v>63</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
@@ -8735,7 +8812,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>38</v>
@@ -8744,13 +8821,13 @@
         <v>9</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>22</v>
@@ -8759,25 +8836,25 @@
         <v>2</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="J110" s="3"/>
       <c r="K110" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>38</v>
@@ -8786,13 +8863,13 @@
         <v>9</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>22</v>
@@ -8801,27 +8878,27 @@
         <v>3</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>38</v>
@@ -8833,10 +8910,10 @@
         <v>52</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>22</v>
@@ -8845,23 +8922,23 @@
         <v>2</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="J112" s="3"/>
       <c r="K112" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N112" s="3"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>38</v>
@@ -8873,10 +8950,10 @@
         <v>124</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>22</v>
@@ -8890,18 +8967,18 @@
         <v>17</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>38</v>
@@ -8913,7 +8990,7 @@
         <v>71</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
@@ -8935,7 +9012,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>38</v>
@@ -8944,13 +9021,13 @@
         <v>9</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>22</v>
@@ -8964,18 +9041,18 @@
         <v>17</v>
       </c>
       <c r="L115" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N115" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="M115" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="N115" s="3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>38</v>
@@ -8984,30 +9061,40 @@
         <v>8</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="F116" s="3"/>
+        <v>389</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>390</v>
+      </c>
       <c r="G116" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I116" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="J116" s="3"/>
       <c r="K116" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N116" s="3" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>38</v>
@@ -9016,30 +9103,40 @@
         <v>8</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F117" s="3"/>
+        <v>396</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="G117" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I117" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>398</v>
+      </c>
       <c r="J117" s="3"/>
       <c r="K117" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L117" s="3"/>
-      <c r="M117" s="3"/>
-      <c r="N117" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="M117" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N117" s="3" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>38</v>
@@ -9048,13 +9145,13 @@
         <v>8</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>22</v>
@@ -9063,25 +9160,25 @@
         <v>2</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="J118" s="3"/>
       <c r="K118" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>38</v>
@@ -9093,10 +9190,10 @@
         <v>52</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>22</v>
@@ -9105,25 +9202,25 @@
         <v>2</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="J119" s="3"/>
       <c r="K119" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>38</v>
@@ -9132,13 +9229,13 @@
         <v>8</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>22</v>
@@ -9147,25 +9244,25 @@
         <v>2</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="J120" s="3"/>
       <c r="K120" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>38</v>
@@ -9174,13 +9271,13 @@
         <v>9</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>22</v>
@@ -9189,25 +9286,25 @@
         <v>2</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="J121" s="3"/>
       <c r="K121" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>38</v>
@@ -9216,10 +9313,10 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
@@ -9239,7 +9336,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>38</v>
@@ -9248,10 +9345,10 @@
         <v>8</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
@@ -9271,7 +9368,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>38</v>
@@ -9280,10 +9377,10 @@
         <v>8</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
@@ -9303,7 +9400,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>38</v>
@@ -9312,10 +9409,10 @@
         <v>8</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
@@ -9335,7 +9432,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>38</v>
@@ -9344,13 +9441,13 @@
         <v>8</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>22</v>
@@ -9359,25 +9456,25 @@
         <v>2</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="J126" s="3"/>
       <c r="K126" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>38</v>
@@ -9386,13 +9483,13 @@
         <v>8</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>22</v>
@@ -9401,25 +9498,25 @@
         <v>2</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>38</v>
@@ -9428,13 +9525,13 @@
         <v>8</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>22</v>
@@ -9443,25 +9540,25 @@
         <v>2</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="J128" s="3"/>
       <c r="K128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>38</v>
@@ -9470,13 +9567,13 @@
         <v>8</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>22</v>
@@ -9485,25 +9582,25 @@
         <v>2</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="J129" s="3"/>
       <c r="K129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>38</v>
@@ -9512,13 +9609,13 @@
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>22</v>
@@ -9527,25 +9624,25 @@
         <v>2</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="J130" s="3"/>
       <c r="K130" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>38</v>
@@ -9554,13 +9651,13 @@
         <v>8</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>22</v>
@@ -9569,25 +9666,25 @@
         <v>2</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="J131" s="3"/>
       <c r="K131" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>38</v>
@@ -9596,13 +9693,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>22</v>
@@ -9611,25 +9708,25 @@
         <v>2</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>38</v>
@@ -9638,13 +9735,13 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>22</v>
@@ -9653,25 +9750,25 @@
         <v>2</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="J133" s="3"/>
       <c r="K133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>38</v>
@@ -9680,13 +9777,13 @@
         <v>9</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>22</v>
@@ -9695,25 +9792,25 @@
         <v>2</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="J134" s="3"/>
       <c r="K134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>38</v>
@@ -9725,7 +9822,7 @@
         <v>71</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
@@ -9747,7 +9844,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>38</v>
@@ -9759,7 +9856,7 @@
         <v>83</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -9781,7 +9878,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>38</v>
@@ -9790,10 +9887,10 @@
         <v>10</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
@@ -9813,7 +9910,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>38</v>
@@ -9825,27 +9922,37 @@
         <v>52</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="F138" s="3"/>
+        <v>501</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="G138" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I138" s="3"/>
-      <c r="J138" s="3"/>
+      <c r="J138" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="K138" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L138" s="3"/>
-      <c r="M138" s="3"/>
-      <c r="N138" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="N138" s="3" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>38</v>
@@ -9857,7 +9964,7 @@
         <v>45</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
@@ -9876,12 +9983,12 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>38</v>
@@ -9893,7 +10000,7 @@
         <v>52</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3" t="s">
@@ -9910,12 +10017,12 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -9924,10 +10031,10 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3" t="s">
@@ -9944,12 +10051,12 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -9958,10 +10065,10 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
@@ -9978,12 +10085,12 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -9992,13 +10099,13 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
@@ -10007,25 +10114,25 @@
         <v>2</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="M143" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -10034,10 +10141,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
@@ -10054,12 +10161,12 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -10068,10 +10175,10 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -10088,12 +10195,12 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -10102,10 +10209,10 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
@@ -10122,12 +10229,12 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -10136,10 +10243,10 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
@@ -10156,12 +10263,12 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -10170,10 +10277,10 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
@@ -10190,12 +10297,12 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -10207,7 +10314,7 @@
         <v>71</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -10226,12 +10333,12 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -10243,7 +10350,7 @@
         <v>52</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3" t="s">
@@ -10260,12 +10367,12 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -10277,7 +10384,7 @@
         <v>52</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
@@ -10294,12 +10401,12 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -10308,10 +10415,10 @@
         <v>11</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -10331,7 +10438,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -10343,7 +10450,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -10365,7 +10472,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10377,7 +10484,7 @@
         <v>63</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10399,7 +10506,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -10408,10 +10515,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -10431,7 +10538,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10443,7 +10550,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -10463,7 +10570,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -10472,10 +10579,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -10495,7 +10602,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -10504,10 +10611,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -10527,7 +10634,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -10536,10 +10643,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -10559,7 +10666,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -10571,7 +10678,7 @@
         <v>124</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -10591,7 +10698,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -10603,7 +10710,7 @@
         <v>71</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -10625,7 +10732,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -10637,7 +10744,7 @@
         <v>83</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -10659,7 +10766,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -10671,7 +10778,7 @@
         <v>52</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -10691,7 +10798,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -10700,10 +10807,10 @@
         <v>11</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -10720,12 +10827,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -10737,7 +10844,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -10756,12 +10863,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -10773,7 +10880,7 @@
         <v>63</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -10792,12 +10899,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -10806,10 +10913,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -10826,12 +10933,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -10840,10 +10947,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -10860,12 +10967,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -10874,10 +10981,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -10894,12 +11001,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -10908,10 +11015,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>572</v>
+        <v>591</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -10928,12 +11035,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -10942,10 +11049,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -10962,12 +11069,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -10976,10 +11083,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -10996,12 +11103,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -11013,7 +11120,7 @@
         <v>52</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -11030,12 +11137,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -11047,7 +11154,7 @@
         <v>124</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -11064,12 +11171,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -11081,7 +11188,7 @@
         <v>71</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -11100,12 +11207,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -11114,10 +11221,10 @@
         <v>11</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -11132,16 +11239,16 @@
         <v>21</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -11153,7 +11260,7 @@
         <v>83</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -11172,12 +11279,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11186,10 +11293,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11206,12 +11313,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11220,10 +11327,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -11240,12 +11347,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -11254,10 +11361,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -11274,12 +11381,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -11288,10 +11395,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>599</v>
+        <v>618</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -11308,12 +11415,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -11322,10 +11429,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -11342,12 +11449,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -11356,10 +11463,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>605</v>
+        <v>624</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11376,12 +11483,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11393,7 +11500,7 @@
         <v>52</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11410,12 +11517,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11427,7 +11534,7 @@
         <v>52</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11444,12 +11551,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -11458,10 +11565,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -11478,12 +11585,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -11492,10 +11599,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>617</v>
+        <v>636</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -11512,12 +11619,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -11526,10 +11633,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>620</v>
+        <v>639</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -11546,12 +11653,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>621</v>
+        <v>640</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -11560,10 +11667,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>622</v>
+        <v>641</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -11580,12 +11687,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -11594,10 +11701,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>626</v>
+        <v>645</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -11614,12 +11721,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -11628,10 +11735,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>628</v>
+        <v>647</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>629</v>
+        <v>648</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -11648,12 +11755,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>630</v>
+        <v>649</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -11662,10 +11769,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>631</v>
+        <v>650</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>632</v>
+        <v>651</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -11682,12 +11789,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>633</v>
+        <v>652</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -11696,10 +11803,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>634</v>
+        <v>653</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -11716,12 +11823,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -11730,10 +11837,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>637</v>
+        <v>656</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -11750,12 +11857,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -11767,7 +11874,7 @@
         <v>52</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -11784,12 +11891,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -11801,7 +11908,7 @@
         <v>52</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>642</v>
+        <v>661</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -11818,12 +11925,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -11832,10 +11939,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>644</v>
+        <v>663</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>645</v>
+        <v>664</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -11857,7 +11964,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -11866,10 +11973,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>647</v>
+        <v>666</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>648</v>
+        <v>667</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -11889,7 +11996,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -11898,10 +12005,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -11921,7 +12028,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -11930,10 +12037,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>654</v>
+        <v>673</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -11953,7 +12060,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>655</v>
+        <v>674</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -11962,10 +12069,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -11985,7 +12092,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>658</v>
+        <v>677</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -11994,10 +12101,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>660</v>
+        <v>679</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -12017,7 +12124,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -12029,7 +12136,7 @@
         <v>52</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -12049,7 +12156,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -12061,7 +12168,7 @@
         <v>52</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -12081,7 +12188,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -12090,10 +12197,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>644</v>
+        <v>663</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -12115,7 +12222,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>667</v>
+        <v>686</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -12124,10 +12231,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>647</v>
+        <v>666</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -12147,7 +12254,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -12156,10 +12263,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>671</v>
+        <v>690</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12181,7 +12288,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>672</v>
+        <v>691</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12190,10 +12297,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>673</v>
+        <v>692</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12213,7 +12320,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12225,7 +12332,7 @@
         <v>52</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>675</v>
+        <v>694</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -12245,7 +12352,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -12257,7 +12364,7 @@
         <v>52</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -12277,7 +12384,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>678</v>
+        <v>697</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -12289,7 +12396,7 @@
         <v>52</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>679</v>
+        <v>698</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -12309,7 +12416,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -12318,10 +12425,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>681</v>
+        <v>700</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>682</v>
+        <v>701</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -12343,7 +12450,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -12352,10 +12459,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12375,7 +12482,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>686</v>
+        <v>705</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12384,10 +12491,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>687</v>
+        <v>706</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>688</v>
+        <v>707</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12407,7 +12514,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>689</v>
+        <v>708</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12419,7 +12526,7 @@
         <v>49</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12439,7 +12546,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>691</v>
+        <v>710</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12448,10 +12555,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -12471,7 +12578,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -12483,7 +12590,7 @@
         <v>206</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -12503,7 +12610,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -12515,7 +12622,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -12537,7 +12644,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -12549,7 +12656,7 @@
         <v>63</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>699</v>
+        <v>718</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -12571,7 +12678,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -12583,7 +12690,7 @@
         <v>52</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -12603,7 +12710,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>702</v>
+        <v>721</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -12615,7 +12722,7 @@
         <v>71</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -12637,7 +12744,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -12649,7 +12756,7 @@
         <v>74</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>705</v>
+        <v>724</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -12669,7 +12776,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>706</v>
+        <v>725</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -12681,7 +12788,7 @@
         <v>80</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>707</v>
+        <v>726</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -12701,7 +12808,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>708</v>
+        <v>727</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -12713,7 +12820,7 @@
         <v>83</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -12735,7 +12842,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>710</v>
+        <v>729</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -12747,7 +12854,7 @@
         <v>259</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>711</v>
+        <v>730</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -12767,7 +12874,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -12779,7 +12886,7 @@
         <v>52</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>713</v>
+        <v>732</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -12799,7 +12906,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>714</v>
+        <v>733</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -12811,7 +12918,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -12831,7 +12938,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>716</v>
+        <v>735</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -12840,10 +12947,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>717</v>
+        <v>736</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>718</v>
+        <v>737</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -12863,7 +12970,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>719</v>
+        <v>738</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -12872,10 +12979,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>720</v>
+        <v>739</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>721</v>
+        <v>740</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -12895,7 +13002,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>722</v>
+        <v>741</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -12904,10 +13011,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>723</v>
+        <v>742</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>724</v>
+        <v>743</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -12927,7 +13034,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -12936,10 +13043,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>726</v>
+        <v>745</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>727</v>
+        <v>746</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -12959,7 +13066,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>728</v>
+        <v>747</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -12971,7 +13078,7 @@
         <v>52</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>729</v>
+        <v>748</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -12991,7 +13098,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -13000,10 +13107,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -13025,7 +13132,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>733</v>
+        <v>752</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -13037,7 +13144,7 @@
         <v>253</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>734</v>
+        <v>753</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -13057,7 +13164,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -13069,7 +13176,7 @@
         <v>256</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>736</v>
+        <v>755</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -13089,7 +13196,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -13098,10 +13205,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -13121,7 +13228,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>740</v>
+        <v>759</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -13133,7 +13240,7 @@
         <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -13153,7 +13260,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -13165,7 +13272,7 @@
         <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13185,7 +13292,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>744</v>
+        <v>763</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13197,7 +13304,7 @@
         <v>55</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>745</v>
+        <v>764</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13217,7 +13324,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>746</v>
+        <v>765</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13229,7 +13336,7 @@
         <v>58</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>747</v>
+        <v>766</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -13249,7 +13356,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>748</v>
+        <v>767</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -13261,7 +13368,7 @@
         <v>52</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>749</v>
+        <v>768</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -13281,7 +13388,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>750</v>
+        <v>769</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -13293,7 +13400,7 @@
         <v>63</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>751</v>
+        <v>770</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -13315,7 +13422,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>752</v>
+        <v>771</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -13327,7 +13434,7 @@
         <v>52</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>753</v>
+        <v>772</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -13347,7 +13454,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>754</v>
+        <v>773</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -13359,7 +13466,7 @@
         <v>121</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>755</v>
+        <v>774</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13379,7 +13486,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13391,7 +13498,7 @@
         <v>124</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>757</v>
+        <v>776</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13411,7 +13518,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>758</v>
+        <v>777</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13423,7 +13530,7 @@
         <v>145</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13443,7 +13550,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -13455,7 +13562,7 @@
         <v>71</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -13477,7 +13584,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -13489,7 +13596,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -13509,7 +13616,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -13521,7 +13628,7 @@
         <v>190</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -13543,7 +13650,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>766</v>
+        <v>785</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -13555,7 +13662,7 @@
         <v>193</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -13577,7 +13684,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -13589,7 +13696,7 @@
         <v>129</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -13611,7 +13718,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>770</v>
+        <v>789</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -13623,7 +13730,7 @@
         <v>83</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>771</v>
+        <v>790</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -13645,7 +13752,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>772</v>
+        <v>791</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -13657,7 +13764,7 @@
         <v>203</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>773</v>
+        <v>792</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -13677,7 +13784,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -13689,7 +13796,7 @@
         <v>63</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>775</v>
+        <v>794</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -13711,7 +13818,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -13723,7 +13830,7 @@
         <v>52</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>777</v>
+        <v>796</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -13743,7 +13850,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>778</v>
+        <v>797</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -13755,7 +13862,7 @@
         <v>216</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>779</v>
+        <v>798</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -13777,7 +13884,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>780</v>
+        <v>799</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -13789,7 +13896,7 @@
         <v>124</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>781</v>
+        <v>800</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -13809,7 +13916,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -13821,7 +13928,7 @@
         <v>71</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -13843,7 +13950,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -13855,7 +13962,7 @@
         <v>55</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -13875,7 +13982,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>786</v>
+        <v>805</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -13887,7 +13994,7 @@
         <v>58</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>787</v>
+        <v>806</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -13907,7 +14014,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>788</v>
+        <v>807</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -13919,7 +14026,7 @@
         <v>83</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>789</v>
+        <v>808</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -13941,7 +14048,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>790</v>
+        <v>809</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -13953,7 +14060,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -13975,7 +14082,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>792</v>
+        <v>811</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -13987,7 +14094,7 @@
         <v>63</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>793</v>
+        <v>812</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -14009,7 +14116,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -14021,7 +14128,7 @@
         <v>52</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>795</v>
+        <v>814</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -14041,7 +14148,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>796</v>
+        <v>815</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -14053,7 +14160,7 @@
         <v>68</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -14073,7 +14180,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>798</v>
+        <v>817</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -14085,7 +14192,7 @@
         <v>71</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -14107,7 +14214,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>800</v>
+        <v>819</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -14119,7 +14226,7 @@
         <v>74</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -14139,7 +14246,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -14151,7 +14258,7 @@
         <v>77</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>803</v>
+        <v>822</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -14171,7 +14278,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14183,7 +14290,7 @@
         <v>80</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>805</v>
+        <v>824</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14203,7 +14310,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>806</v>
+        <v>825</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14215,7 +14322,7 @@
         <v>83</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>807</v>
+        <v>826</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14237,7 +14344,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>808</v>
+        <v>827</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -14249,7 +14356,7 @@
         <v>52</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>809</v>
+        <v>828</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -14269,7 +14376,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>810</v>
+        <v>829</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -14281,7 +14388,7 @@
         <v>63</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>811</v>
+        <v>830</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -14303,7 +14410,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>812</v>
+        <v>831</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -14312,10 +14419,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>813</v>
+        <v>832</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>814</v>
+        <v>833</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -14335,7 +14442,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>815</v>
+        <v>834</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -14347,7 +14454,7 @@
         <v>52</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>816</v>
+        <v>835</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -14367,7 +14474,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>817</v>
+        <v>836</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14376,10 +14483,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>819</v>
+        <v>838</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14399,7 +14506,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14411,7 +14518,7 @@
         <v>124</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>821</v>
+        <v>840</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14431,7 +14538,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>822</v>
+        <v>841</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14443,7 +14550,7 @@
         <v>71</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -14465,7 +14572,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -14477,7 +14584,7 @@
         <v>83</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>825</v>
+        <v>844</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -14499,7 +14606,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -14511,7 +14618,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>827</v>
+        <v>846</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -14530,12 +14637,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>829</v>
+        <v>848</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -14544,10 +14651,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>830</v>
+        <v>849</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>831</v>
+        <v>850</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -14564,12 +14671,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>832</v>
+        <v>851</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -14578,10 +14685,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>833</v>
+        <v>852</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>834</v>
+        <v>853</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -14598,12 +14705,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>835</v>
+        <v>854</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -14612,10 +14719,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>836</v>
+        <v>855</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>837</v>
+        <v>856</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -14634,12 +14741,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>838</v>
+        <v>857</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -14648,10 +14755,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>839</v>
+        <v>858</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>840</v>
+        <v>859</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -14668,12 +14775,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>841</v>
+        <v>860</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -14682,10 +14789,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>842</v>
+        <v>861</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -14704,12 +14811,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>844</v>
+        <v>863</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -14718,10 +14825,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -14738,12 +14845,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -14752,10 +14859,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>848</v>
+        <v>867</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -14774,12 +14881,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>850</v>
+        <v>869</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -14788,10 +14895,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>851</v>
+        <v>870</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>852</v>
+        <v>871</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -14808,12 +14915,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>853</v>
+        <v>872</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -14825,7 +14932,7 @@
         <v>71</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>854</v>
+        <v>873</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -14844,12 +14951,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>855</v>
+        <v>874</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -14861,7 +14968,7 @@
         <v>83</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>856</v>
+        <v>875</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -14880,12 +14987,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>828</v>
+        <v>847</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -14897,7 +15004,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -14919,7 +15026,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>859</v>
+        <v>878</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -14928,10 +15035,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>860</v>
+        <v>879</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>861</v>
+        <v>880</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -14951,7 +15058,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>862</v>
+        <v>881</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -14960,10 +15067,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>863</v>
+        <v>882</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>864</v>
+        <v>883</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -14983,7 +15090,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>865</v>
+        <v>884</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -14992,10 +15099,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>866</v>
+        <v>885</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>867</v>
+        <v>886</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -15015,7 +15122,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -15024,10 +15131,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -15047,7 +15154,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -15056,10 +15163,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>872</v>
+        <v>891</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>873</v>
+        <v>892</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -15079,7 +15186,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -15088,10 +15195,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>875</v>
+        <v>894</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -15111,7 +15218,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>877</v>
+        <v>896</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -15123,7 +15230,7 @@
         <v>52</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>878</v>
+        <v>897</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -15143,7 +15250,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>879</v>
+        <v>898</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -15155,7 +15262,7 @@
         <v>71</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>880</v>
+        <v>899</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15177,7 +15284,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15186,10 +15293,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>882</v>
+        <v>901</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>883</v>
+        <v>902</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15209,7 +15316,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>884</v>
+        <v>903</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15221,7 +15328,7 @@
         <v>83</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>885</v>
+        <v>904</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -15243,7 +15350,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -15252,10 +15359,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>887</v>
+        <v>906</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -15277,7 +15384,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -15286,10 +15393,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -15311,7 +15418,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>892</v>
+        <v>911</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -15320,10 +15427,10 @@
         <v>13</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -15343,7 +15450,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>894</v>
+        <v>913</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -15352,10 +15459,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15377,7 +15484,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15389,7 +15496,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15411,7 +15518,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15420,10 +15527,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>901</v>
+        <v>920</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15443,7 +15550,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -15452,10 +15559,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -15470,14 +15577,14 @@
         <v>21</v>
       </c>
       <c r="L307" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M307" s="3"/>
       <c r="N307" s="3"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -15489,7 +15596,7 @@
         <v>52</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -15509,7 +15616,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>907</v>
+        <v>926</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -15521,7 +15628,7 @@
         <v>80</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -15541,7 +15648,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>909</v>
+        <v>928</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -15550,10 +15657,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -15573,7 +15680,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>912</v>
+        <v>931</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -15582,10 +15689,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>913</v>
+        <v>932</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -15605,7 +15712,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>915</v>
+        <v>934</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -15614,10 +15721,10 @@
         <v>13</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>916</v>
+        <v>935</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -15637,7 +15744,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>917</v>
+        <v>936</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -15649,7 +15756,7 @@
         <v>80</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>918</v>
+        <v>937</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -15669,7 +15776,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>919</v>
+        <v>938</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -15678,10 +15785,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -15701,7 +15808,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>922</v>
+        <v>941</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -15713,7 +15820,7 @@
         <v>124</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>923</v>
+        <v>942</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -15733,7 +15840,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>924</v>
+        <v>943</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -15742,10 +15849,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>925</v>
+        <v>944</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -15765,7 +15872,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>927</v>
+        <v>946</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -15777,7 +15884,7 @@
         <v>80</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>928</v>
+        <v>947</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -15797,7 +15904,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>929</v>
+        <v>948</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -15806,10 +15913,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>930</v>
+        <v>949</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -15829,7 +15936,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>932</v>
+        <v>951</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -15841,7 +15948,7 @@
         <v>80</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>933</v>
+        <v>952</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -15861,7 +15968,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>934</v>
+        <v>953</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -15870,10 +15977,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>935</v>
+        <v>954</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>936</v>
+        <v>955</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -15893,7 +16000,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>937</v>
+        <v>956</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -15905,7 +16012,7 @@
         <v>80</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -15925,7 +16032,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -15934,10 +16041,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -15957,7 +16064,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>942</v>
+        <v>961</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -15966,10 +16073,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>943</v>
+        <v>962</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>944</v>
+        <v>963</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -15989,7 +16096,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>945</v>
+        <v>964</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -15998,10 +16105,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>946</v>
+        <v>965</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>947</v>
+        <v>966</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -16021,7 +16128,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>948</v>
+        <v>967</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -16030,10 +16137,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>949</v>
+        <v>968</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>950</v>
+        <v>969</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -16053,7 +16160,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>951</v>
+        <v>970</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -16062,10 +16169,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>952</v>
+        <v>971</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>953</v>
+        <v>972</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -16085,7 +16192,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>954</v>
+        <v>973</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -16094,10 +16201,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>955</v>
+        <v>974</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>956</v>
+        <v>975</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -16117,7 +16224,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>957</v>
+        <v>976</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -16126,10 +16233,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>958</v>
+        <v>977</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>959</v>
+        <v>978</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -16149,7 +16256,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>960</v>
+        <v>979</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -16158,10 +16265,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>961</v>
+        <v>980</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>962</v>
+        <v>981</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16183,7 +16290,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>963</v>
+        <v>982</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16192,10 +16299,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>964</v>
+        <v>983</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>965</v>
+        <v>984</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16217,7 +16324,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>966</v>
+        <v>985</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16226,10 +16333,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>967</v>
+        <v>986</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>968</v>
+        <v>987</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -16249,7 +16356,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>969</v>
+        <v>988</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -16261,7 +16368,7 @@
         <v>190</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>970</v>
+        <v>989</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -16283,7 +16390,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>971</v>
+        <v>990</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -16292,10 +16399,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>972</v>
+        <v>991</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>973</v>
+        <v>992</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -16317,7 +16424,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>974</v>
+        <v>993</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -16326,10 +16433,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>975</v>
+        <v>994</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>976</v>
+        <v>995</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -16351,7 +16458,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>977</v>
+        <v>996</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -16360,10 +16467,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>978</v>
+        <v>997</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>979</v>
+        <v>998</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16383,7 +16490,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>980</v>
+        <v>999</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16392,10 +16499,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>981</v>
+        <v>1000</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>982</v>
+        <v>1001</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16415,7 +16522,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>983</v>
+        <v>1002</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16424,10 +16531,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>984</v>
+        <v>1003</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>985</v>
+        <v>1004</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16447,7 +16554,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>986</v>
+        <v>1005</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -16456,10 +16563,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>988</v>
+        <v>1007</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -16481,7 +16588,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>989</v>
+        <v>1008</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -16490,10 +16597,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>990</v>
+        <v>1009</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>991</v>
+        <v>1010</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -16513,7 +16620,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>992</v>
+        <v>1011</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -16522,10 +16629,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>993</v>
+        <v>1012</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -16545,7 +16652,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -16554,10 +16661,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>996</v>
+        <v>1015</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>997</v>
+        <v>1016</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -16577,7 +16684,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>998</v>
+        <v>1017</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -16586,10 +16693,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>999</v>
+        <v>1018</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1000</v>
+        <v>1019</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -16609,7 +16716,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>1001</v>
+        <v>1020</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -16618,10 +16725,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1002</v>
+        <v>1021</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1003</v>
+        <v>1022</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -16641,7 +16748,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>1004</v>
+        <v>1023</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -16650,10 +16757,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1005</v>
+        <v>1024</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1006</v>
+        <v>1025</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -16673,7 +16780,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>1007</v>
+        <v>1026</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -16682,10 +16789,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1008</v>
+        <v>1027</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1009</v>
+        <v>1028</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -16705,7 +16812,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>1010</v>
+        <v>1029</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -16714,10 +16821,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1011</v>
+        <v>1030</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1012</v>
+        <v>1031</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -16737,7 +16844,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>1013</v>
+        <v>1032</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -16746,10 +16853,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1014</v>
+        <v>1033</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1015</v>
+        <v>1034</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -16769,7 +16876,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>1016</v>
+        <v>1035</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -16778,10 +16885,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1017</v>
+        <v>1036</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1018</v>
+        <v>1037</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -16801,7 +16908,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>1019</v>
+        <v>1038</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -16810,10 +16917,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1020</v>
+        <v>1039</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1021</v>
+        <v>1040</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -16833,7 +16940,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>1022</v>
+        <v>1041</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -16842,10 +16949,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1023</v>
+        <v>1042</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1024</v>
+        <v>1043</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -16865,7 +16972,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>1025</v>
+        <v>1044</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -16874,10 +16981,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1026</v>
+        <v>1045</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1027</v>
+        <v>1046</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -16897,7 +17004,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>1028</v>
+        <v>1047</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -16906,10 +17013,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1029</v>
+        <v>1048</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1030</v>
+        <v>1049</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -16929,7 +17036,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1031</v>
+        <v>1050</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -16938,10 +17045,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -16961,7 +17068,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1034</v>
+        <v>1053</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -16970,10 +17077,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1035</v>
+        <v>1054</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1036</v>
+        <v>1055</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -16993,7 +17100,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -17002,10 +17109,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1038</v>
+        <v>1057</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1039</v>
+        <v>1058</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -17025,7 +17132,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1040</v>
+        <v>1059</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -17034,10 +17141,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1042</v>
+        <v>1061</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -17057,7 +17164,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1043</v>
+        <v>1062</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -17066,10 +17173,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1044</v>
+        <v>1063</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1045</v>
+        <v>1064</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -17089,7 +17196,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1046</v>
+        <v>1065</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -17098,10 +17205,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1047</v>
+        <v>1066</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1048</v>
+        <v>1067</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -17121,7 +17228,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1049</v>
+        <v>1068</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -17130,10 +17237,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1050</v>
+        <v>1069</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1051</v>
+        <v>1070</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -17153,7 +17260,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1052</v>
+        <v>1071</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -17162,10 +17269,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1053</v>
+        <v>1072</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1054</v>
+        <v>1073</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17185,7 +17292,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1055</v>
+        <v>1074</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17194,10 +17301,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1056</v>
+        <v>1075</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1057</v>
+        <v>1076</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17217,7 +17324,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1058</v>
+        <v>1077</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17226,10 +17333,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1059</v>
+        <v>1078</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1060</v>
+        <v>1079</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -17249,7 +17356,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1061</v>
+        <v>1080</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -17258,10 +17365,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1062</v>
+        <v>1081</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1063</v>
+        <v>1082</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -17281,7 +17388,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1064</v>
+        <v>1083</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -17290,10 +17397,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1065</v>
+        <v>1084</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1066</v>
+        <v>1085</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -17313,7 +17420,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1067</v>
+        <v>1086</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -17322,10 +17429,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1068</v>
+        <v>1087</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1069</v>
+        <v>1088</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -17345,7 +17452,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1070</v>
+        <v>1089</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -17354,10 +17461,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1071</v>
+        <v>1090</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1072</v>
+        <v>1091</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17377,7 +17484,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1073</v>
+        <v>1092</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17386,10 +17493,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1074</v>
+        <v>1093</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1075</v>
+        <v>1094</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17409,7 +17516,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1076</v>
+        <v>1095</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17418,10 +17525,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1077</v>
+        <v>1096</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1078</v>
+        <v>1097</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17441,7 +17548,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1079</v>
+        <v>1098</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17450,10 +17557,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1080</v>
+        <v>1099</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1081</v>
+        <v>1100</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -17473,7 +17580,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1082</v>
+        <v>1101</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -17482,10 +17589,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1083</v>
+        <v>1102</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1084</v>
+        <v>1103</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -17505,7 +17612,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1085</v>
+        <v>1104</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -17514,10 +17621,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1086</v>
+        <v>1105</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1087</v>
+        <v>1106</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -17537,7 +17644,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1088</v>
+        <v>1107</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -17546,10 +17653,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1089</v>
+        <v>1108</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -17569,7 +17676,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -17578,10 +17685,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1092</v>
+        <v>1111</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1093</v>
+        <v>1112</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -17601,7 +17708,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1094</v>
+        <v>1113</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -17610,10 +17717,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1095</v>
+        <v>1114</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -17633,7 +17740,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1097</v>
+        <v>1116</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -17642,10 +17749,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1098</v>
+        <v>1117</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -17665,7 +17772,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1100</v>
+        <v>1119</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -17674,10 +17781,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1101</v>
+        <v>1120</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1102</v>
+        <v>1121</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -17697,7 +17804,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1103</v>
+        <v>1122</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -17706,10 +17813,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1104</v>
+        <v>1123</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1105</v>
+        <v>1124</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -17729,7 +17836,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -17738,10 +17845,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1107</v>
+        <v>1126</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -17761,7 +17868,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1109</v>
+        <v>1128</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -17770,10 +17877,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1110</v>
+        <v>1129</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -17793,7 +17900,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1112</v>
+        <v>1131</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -17802,10 +17909,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1113</v>
+        <v>1132</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1114</v>
+        <v>1133</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -17825,7 +17932,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1115</v>
+        <v>1134</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -17834,10 +17941,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1116</v>
+        <v>1135</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1117</v>
+        <v>1136</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -17857,7 +17964,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1118</v>
+        <v>1137</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -17866,10 +17973,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1119</v>
+        <v>1138</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1120</v>
+        <v>1139</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -17889,7 +17996,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1121</v>
+        <v>1140</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -17898,10 +18005,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1122</v>
+        <v>1141</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1123</v>
+        <v>1142</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -17921,7 +18028,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1124</v>
+        <v>1143</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -17930,10 +18037,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1125</v>
+        <v>1144</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -17953,7 +18060,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1127</v>
+        <v>1146</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -17962,10 +18069,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1128</v>
+        <v>1147</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1129</v>
+        <v>1148</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -17985,7 +18092,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1130</v>
+        <v>1149</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -17994,10 +18101,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1131</v>
+        <v>1150</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1132</v>
+        <v>1151</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -18017,7 +18124,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1133</v>
+        <v>1152</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -18026,10 +18133,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1134</v>
+        <v>1153</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1135</v>
+        <v>1154</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -18049,7 +18156,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1136</v>
+        <v>1155</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -18058,10 +18165,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1137</v>
+        <v>1156</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1138</v>
+        <v>1157</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -18081,7 +18188,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1139</v>
+        <v>1158</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -18090,10 +18197,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1140</v>
+        <v>1159</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1141</v>
+        <v>1160</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -18113,7 +18220,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1142</v>
+        <v>1161</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -18122,10 +18229,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1143</v>
+        <v>1162</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1144</v>
+        <v>1163</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -18145,7 +18252,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1145</v>
+        <v>1164</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -18154,10 +18261,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1146</v>
+        <v>1165</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1147</v>
+        <v>1166</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18177,7 +18284,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1148</v>
+        <v>1167</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18186,10 +18293,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1149</v>
+        <v>1168</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1150</v>
+        <v>1169</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18209,7 +18316,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1151</v>
+        <v>1170</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18218,10 +18325,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1152</v>
+        <v>1171</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1153</v>
+        <v>1172</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18241,7 +18348,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1154</v>
+        <v>1173</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -18250,10 +18357,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1155</v>
+        <v>1174</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1156</v>
+        <v>1175</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -18273,7 +18380,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1157</v>
+        <v>1176</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -18282,10 +18389,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1152</v>
+        <v>1171</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1158</v>
+        <v>1177</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -18305,7 +18412,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1159</v>
+        <v>1178</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -18314,10 +18421,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1160</v>
+        <v>1179</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1161</v>
+        <v>1180</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -18339,7 +18446,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1162</v>
+        <v>1181</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -18348,10 +18455,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1163</v>
+        <v>1182</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1164</v>
+        <v>1183</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -18371,7 +18478,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1165</v>
+        <v>1184</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18380,10 +18487,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1166</v>
+        <v>1185</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1167</v>
+        <v>1186</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18403,7 +18510,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1168</v>
+        <v>1187</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18412,10 +18519,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1170</v>
+        <v>1189</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18435,7 +18542,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1171</v>
+        <v>1190</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18444,10 +18551,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1173</v>
+        <v>1192</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -18467,7 +18574,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -18476,10 +18583,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1175</v>
+        <v>1194</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1176</v>
+        <v>1195</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -18499,7 +18606,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1177</v>
+        <v>1196</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -18508,10 +18615,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1178</v>
+        <v>1197</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -18531,7 +18638,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1180</v>
+        <v>1199</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -18540,10 +18647,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1181</v>
+        <v>1200</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1182</v>
+        <v>1201</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -18563,7 +18670,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1183</v>
+        <v>1202</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -18572,10 +18679,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -18595,7 +18702,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -18604,10 +18711,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1187</v>
+        <v>1206</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1188</v>
+        <v>1207</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -18627,7 +18734,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -18636,10 +18743,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1190</v>
+        <v>1209</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1191</v>
+        <v>1210</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -18661,7 +18768,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1192</v>
+        <v>1211</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -18670,10 +18777,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1193</v>
+        <v>1212</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -18695,7 +18802,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1195</v>
+        <v>1214</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -18704,10 +18811,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1196</v>
+        <v>1215</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1197</v>
+        <v>1216</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -18729,7 +18836,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1198</v>
+        <v>1217</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -18738,10 +18845,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1199</v>
+        <v>1218</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1200</v>
+        <v>1219</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -18761,7 +18868,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1201</v>
+        <v>1220</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -18770,10 +18877,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1202</v>
+        <v>1221</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1203</v>
+        <v>1222</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -18793,7 +18900,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1204</v>
+        <v>1223</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -18802,10 +18909,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1205</v>
+        <v>1224</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -18825,7 +18932,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -18834,10 +18941,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -18852,14 +18959,14 @@
         <v>21</v>
       </c>
       <c r="L412" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M412" s="3"/>
       <c r="N412" s="3"/>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -18868,10 +18975,10 @@
         <v>13</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1211</v>
+        <v>1230</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -18886,14 +18993,14 @@
         <v>21</v>
       </c>
       <c r="L413" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M413" s="3"/>
       <c r="N413" s="3"/>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1212</v>
+        <v>1231</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -18902,10 +19009,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1213</v>
+        <v>1232</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1214</v>
+        <v>1233</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -18925,7 +19032,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1215</v>
+        <v>1234</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -18934,10 +19041,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1216</v>
+        <v>1235</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1217</v>
+        <v>1236</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -18957,7 +19064,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1218</v>
+        <v>1237</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -18966,10 +19073,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1219</v>
+        <v>1238</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1220</v>
+        <v>1239</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -18989,7 +19096,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1221</v>
+        <v>1240</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -18998,10 +19105,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1222</v>
+        <v>1241</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1223</v>
+        <v>1242</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -19021,7 +19128,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1224</v>
+        <v>1243</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -19030,10 +19137,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1225</v>
+        <v>1244</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1225</v>
+        <v>1244</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -19048,14 +19155,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1226</v>
+        <v>1245</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1227</v>
+        <v>1246</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -19064,10 +19171,10 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1228</v>
+        <v>1247</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1229</v>
+        <v>1248</v>
       </c>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
@@ -19087,7 +19194,7 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1230</v>
+        <v>1249</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -19096,13 +19203,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1231</v>
+        <v>1250</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1232</v>
+        <v>1251</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1233</v>
+        <v>1252</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -19111,25 +19218,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1234</v>
+        <v>1253</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1235</v>
+        <v>1254</v>
       </c>
       <c r="M420" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1236</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1237</v>
+        <v>1256</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -19138,13 +19245,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1238</v>
+        <v>1257</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1239</v>
+        <v>1258</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1240</v>
+        <v>1259</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -19153,25 +19260,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1241</v>
+        <v>1260</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1235</v>
+        <v>1254</v>
       </c>
       <c r="M421" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1242</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1243</v>
+        <v>1262</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19180,13 +19287,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1244</v>
+        <v>1263</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1245</v>
+        <v>1264</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1246</v>
+        <v>1265</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19195,25 +19302,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1247</v>
+        <v>1266</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1235</v>
+        <v>1254</v>
       </c>
       <c r="M422" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1248</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1249</v>
+        <v>1268</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19222,13 +19329,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1250</v>
+        <v>1269</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1251</v>
+        <v>1270</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1252</v>
+        <v>1271</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -19237,25 +19344,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1253</v>
+        <v>1272</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1235</v>
+        <v>1254</v>
       </c>
       <c r="M423" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1254</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1255</v>
+        <v>1274</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -19264,10 +19371,10 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1256</v>
+        <v>1275</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1257</v>
+        <v>1276</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
@@ -19287,7 +19394,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1258</v>
+        <v>1277</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -19296,10 +19403,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1259</v>
+        <v>1278</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1260</v>
+        <v>1279</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -19319,7 +19426,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1261</v>
+        <v>1280</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -19328,10 +19435,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1262</v>
+        <v>1281</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1263</v>
+        <v>1282</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -19351,7 +19458,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1264</v>
+        <v>1283</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -19360,10 +19467,10 @@
         <v>10</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1265</v>
+        <v>1284</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -19383,7 +19490,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19392,10 +19499,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1268</v>
+        <v>1287</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1269</v>
+        <v>1288</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19415,7 +19522,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1270</v>
+        <v>1289</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -19424,10 +19531,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1271</v>
+        <v>1290</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1272</v>
+        <v>1291</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -19447,7 +19554,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1273</v>
+        <v>1292</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -19456,10 +19563,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1274</v>
+        <v>1293</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1275</v>
+        <v>1294</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -19479,7 +19586,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1276</v>
+        <v>1295</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -19488,10 +19595,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1278</v>
+        <v>1297</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -19511,7 +19618,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1279</v>
+        <v>1298</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -19520,10 +19627,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1280</v>
+        <v>1299</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1281</v>
+        <v>1300</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -19543,7 +19650,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1282</v>
+        <v>1301</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -19552,10 +19659,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1283</v>
+        <v>1302</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1284</v>
+        <v>1303</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -19575,7 +19682,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1285</v>
+        <v>1304</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -19584,10 +19691,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1286</v>
+        <v>1305</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1287</v>
+        <v>1306</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -19607,7 +19714,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1288</v>
+        <v>1307</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -19616,10 +19723,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1289</v>
+        <v>1308</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1290</v>
+        <v>1309</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -19639,7 +19746,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1291</v>
+        <v>1310</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -19648,10 +19755,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1292</v>
+        <v>1311</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1293</v>
+        <v>1312</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -19671,7 +19778,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1294</v>
+        <v>1313</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -19680,10 +19787,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1295</v>
+        <v>1314</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1296</v>
+        <v>1315</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -19703,7 +19810,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1297</v>
+        <v>1316</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -19712,10 +19819,10 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1298</v>
+        <v>1317</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1299</v>
+        <v>1318</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
@@ -19735,7 +19842,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1300</v>
+        <v>1319</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -19744,13 +19851,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1301</v>
+        <v>1320</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1302</v>
+        <v>1321</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1303</v>
+        <v>1322</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -19759,27 +19866,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1304</v>
+        <v>1323</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1305</v>
+        <v>1324</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1306</v>
+        <v>1325</v>
       </c>
       <c r="M439" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1307</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1308</v>
+        <v>1327</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -19788,13 +19895,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1309</v>
+        <v>1328</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1311</v>
+        <v>1330</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -19803,27 +19910,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1312</v>
+        <v>1331</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1313</v>
+        <v>1332</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1314</v>
+        <v>1333</v>
       </c>
       <c r="M440" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1315</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1316</v>
+        <v>1335</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -19832,13 +19939,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1244</v>
+        <v>1263</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1317</v>
+        <v>1336</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1318</v>
+        <v>1337</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -19847,25 +19954,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1247</v>
+        <v>1266</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1319</v>
+        <v>1338</v>
       </c>
       <c r="M441" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1320</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -19874,13 +19981,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1250</v>
+        <v>1269</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1322</v>
+        <v>1341</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1323</v>
+        <v>1342</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -19889,25 +19996,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1324</v>
+        <v>1343</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1325</v>
+        <v>1344</v>
       </c>
       <c r="M442" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -19916,10 +20023,10 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1329</v>
+        <v>1348</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
@@ -19939,7 +20046,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1330</v>
+        <v>1349</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -19948,10 +20055,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1259</v>
+        <v>1278</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -19971,7 +20078,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1332</v>
+        <v>1351</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -19980,10 +20087,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1262</v>
+        <v>1281</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1333</v>
+        <v>1352</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -20003,7 +20110,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1334</v>
+        <v>1353</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -20012,10 +20119,10 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1335</v>
+        <v>1354</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1336</v>
+        <v>1355</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -20035,7 +20142,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1337</v>
+        <v>1356</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -20044,10 +20151,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1338</v>
+        <v>1357</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1339</v>
+        <v>1358</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -20067,7 +20174,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1340</v>
+        <v>1359</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -20076,10 +20183,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1341</v>
+        <v>1360</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -20099,7 +20206,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1343</v>
+        <v>1362</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -20108,10 +20215,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1344</v>
+        <v>1363</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1345</v>
+        <v>1364</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -20131,7 +20238,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1346</v>
+        <v>1365</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -20140,10 +20247,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1347</v>
+        <v>1366</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1348</v>
+        <v>1367</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -20163,7 +20270,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1349</v>
+        <v>1368</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -20172,10 +20279,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1350</v>
+        <v>1369</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1351</v>
+        <v>1370</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -20195,7 +20302,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1352</v>
+        <v>1371</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -20204,10 +20311,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1353</v>
+        <v>1372</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -20227,7 +20334,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1355</v>
+        <v>1374</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -20236,10 +20343,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1356</v>
+        <v>1375</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1357</v>
+        <v>1376</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -20259,7 +20366,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1358</v>
+        <v>1377</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -20268,10 +20375,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1289</v>
+        <v>1308</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1359</v>
+        <v>1378</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -20291,7 +20398,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1360</v>
+        <v>1379</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -20300,10 +20407,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1361</v>
+        <v>1380</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1362</v>
+        <v>1381</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -20323,7 +20430,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1363</v>
+        <v>1382</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -20332,10 +20439,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1364</v>
+        <v>1383</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1365</v>
+        <v>1384</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -20355,7 +20462,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1366</v>
+        <v>1385</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -20364,10 +20471,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1367</v>
+        <v>1386</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1368</v>
+        <v>1387</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -20387,7 +20494,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1369</v>
+        <v>1388</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -20396,10 +20503,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1370</v>
+        <v>1389</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -20419,7 +20526,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -20428,10 +20535,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1373</v>
+        <v>1392</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1374</v>
+        <v>1393</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -20451,7 +20558,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1375</v>
+        <v>1394</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -20460,10 +20567,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1376</v>
+        <v>1395</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1377</v>
+        <v>1396</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -20483,7 +20590,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1378</v>
+        <v>1397</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -20492,10 +20599,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1379</v>
+        <v>1398</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1380</v>
+        <v>1399</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -20515,7 +20622,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1381</v>
+        <v>1400</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -20524,10 +20631,10 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1383</v>
+        <v>1402</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
@@ -20547,7 +20654,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1384</v>
+        <v>1403</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -20556,10 +20663,10 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1385</v>
+        <v>1404</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1386</v>
+        <v>1405</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
@@ -20579,7 +20686,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1387</v>
+        <v>1406</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -20588,10 +20695,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1388</v>
+        <v>1407</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1389</v>
+        <v>1408</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -20611,7 +20718,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1390</v>
+        <v>1409</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -20620,10 +20727,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1391</v>
+        <v>1410</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1392</v>
+        <v>1411</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -20638,7 +20745,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1393</v>
+        <v>1412</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4112" uniqueCount="1413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="1414">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -1311,6 +1311,9 @@
   </si>
   <si>
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/02-03 - 28 Jun &amp; 4 Jul - Python Refresher &amp; Pydantic Deep Dive/_11_agent_class_ai_only.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You said to skip these agent files</t>
   </si>
   <si>
     <t xml:space="preserve">LC122</t>
@@ -4746,11 +4749,11 @@
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,D$3)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,E$3)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A4,Master!$H$2:$H$465,F$3)</f>
@@ -4956,11 +4959,11 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
@@ -9323,20 +9326,24 @@
         <v>23</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
       <c r="K122" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L122" s="3"/>
-      <c r="M122" s="3"/>
+      <c r="L122" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="N122" s="3"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>38</v>
@@ -9345,30 +9352,34 @@
         <v>8</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
       <c r="K123" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L123" s="3"/>
-      <c r="M123" s="3"/>
+      <c r="L123" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="N123" s="3"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>38</v>
@@ -9377,30 +9388,34 @@
         <v>8</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
       <c r="K124" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L124" s="3"/>
-      <c r="M124" s="3"/>
+      <c r="L124" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="N124" s="3"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>38</v>
@@ -9409,30 +9424,34 @@
         <v>8</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
       <c r="K125" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L125" s="3"/>
-      <c r="M125" s="3"/>
+      <c r="L125" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="M125" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="N125" s="3"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>38</v>
@@ -9441,13 +9460,13 @@
         <v>8</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>22</v>
@@ -9463,7 +9482,7 @@
         <v>18</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M126" s="3" t="s">
         <v>280</v>
@@ -9474,7 +9493,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>38</v>
@@ -9483,13 +9502,13 @@
         <v>8</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>22</v>
@@ -9498,14 +9517,14 @@
         <v>2</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M127" s="3" t="s">
         <v>280</v>
@@ -9516,7 +9535,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>38</v>
@@ -9525,13 +9544,13 @@
         <v>8</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>22</v>
@@ -9540,14 +9559,14 @@
         <v>2</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J128" s="3"/>
       <c r="K128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M128" s="3" t="s">
         <v>280</v>
@@ -9558,7 +9577,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>38</v>
@@ -9567,13 +9586,13 @@
         <v>8</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>22</v>
@@ -9582,25 +9601,25 @@
         <v>2</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J129" s="3"/>
       <c r="K129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M129" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>38</v>
@@ -9609,13 +9628,13 @@
         <v>8</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>22</v>
@@ -9624,25 +9643,25 @@
         <v>2</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J130" s="3"/>
       <c r="K130" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M130" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>38</v>
@@ -9651,13 +9670,13 @@
         <v>8</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>22</v>
@@ -9666,25 +9685,25 @@
         <v>2</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J131" s="3"/>
       <c r="K131" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M131" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>38</v>
@@ -9693,13 +9712,13 @@
         <v>8</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>22</v>
@@ -9708,25 +9727,25 @@
         <v>2</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M132" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>38</v>
@@ -9735,13 +9754,13 @@
         <v>9</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>22</v>
@@ -9750,14 +9769,14 @@
         <v>2</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J133" s="3"/>
       <c r="K133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M133" s="3" t="s">
         <v>280</v>
@@ -9768,7 +9787,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>38</v>
@@ -9777,13 +9796,13 @@
         <v>9</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>22</v>
@@ -9792,25 +9811,25 @@
         <v>2</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J134" s="3"/>
       <c r="K134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M134" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>38</v>
@@ -9822,7 +9841,7 @@
         <v>71</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
@@ -9844,7 +9863,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>38</v>
@@ -9856,7 +9875,7 @@
         <v>83</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="3" t="s">
@@ -9878,7 +9897,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>38</v>
@@ -9887,10 +9906,10 @@
         <v>10</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
@@ -9910,7 +9929,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>38</v>
@@ -9922,10 +9941,10 @@
         <v>52</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>22</v>
@@ -9935,24 +9954,24 @@
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M138" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>38</v>
@@ -9964,7 +9983,7 @@
         <v>45</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
@@ -9983,12 +10002,12 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>38</v>
@@ -10000,7 +10019,7 @@
         <v>52</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="3" t="s">
@@ -10017,12 +10036,12 @@
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -10031,10 +10050,10 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="3" t="s">
@@ -10051,12 +10070,12 @@
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -10065,10 +10084,10 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
@@ -10085,12 +10104,12 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -10099,13 +10118,13 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
@@ -10114,25 +10133,25 @@
         <v>2</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M143" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -10141,10 +10160,10 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
@@ -10161,12 +10180,12 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -10175,10 +10194,10 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -10195,12 +10214,12 @@
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -10209,10 +10228,10 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
@@ -10229,12 +10248,12 @@
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -10243,10 +10262,10 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
@@ -10263,12 +10282,12 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -10277,10 +10296,10 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
@@ -10297,12 +10316,12 @@
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -10314,7 +10333,7 @@
         <v>71</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -10333,12 +10352,12 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -10350,7 +10369,7 @@
         <v>52</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="3" t="s">
@@ -10367,12 +10386,12 @@
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -10384,7 +10403,7 @@
         <v>52</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
@@ -10401,12 +10420,12 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -10418,7 +10437,7 @@
         <v>347</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -10438,7 +10457,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -10450,7 +10469,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -10472,7 +10491,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10484,7 +10503,7 @@
         <v>63</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10506,7 +10525,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -10515,10 +10534,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -10538,7 +10557,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10550,7 +10569,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -10570,7 +10589,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -10579,10 +10598,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -10602,7 +10621,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -10611,10 +10630,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -10634,7 +10653,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -10643,10 +10662,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -10666,7 +10685,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -10678,7 +10697,7 @@
         <v>124</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -10698,7 +10717,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -10710,7 +10729,7 @@
         <v>71</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -10732,7 +10751,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -10744,7 +10763,7 @@
         <v>83</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -10766,7 +10785,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -10778,7 +10797,7 @@
         <v>52</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -10798,7 +10817,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -10810,7 +10829,7 @@
         <v>347</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -10827,12 +10846,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -10844,7 +10863,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -10863,12 +10882,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -10880,7 +10899,7 @@
         <v>63</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -10899,12 +10918,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -10913,10 +10932,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -10933,12 +10952,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -10947,10 +10966,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -10967,12 +10986,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -10981,10 +11000,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -11001,12 +11020,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -11015,10 +11034,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -11035,12 +11054,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -11049,10 +11068,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -11069,12 +11088,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -11083,10 +11102,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -11103,12 +11122,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -11120,7 +11139,7 @@
         <v>52</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -11137,12 +11156,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -11154,7 +11173,7 @@
         <v>124</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -11171,12 +11190,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -11188,7 +11207,7 @@
         <v>71</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -11207,12 +11226,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -11224,7 +11243,7 @@
         <v>329</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -11243,12 +11262,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -11260,7 +11279,7 @@
         <v>83</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -11279,12 +11298,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11293,10 +11312,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11313,12 +11332,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11327,10 +11346,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -11347,12 +11366,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -11361,10 +11380,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -11381,12 +11400,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -11395,10 +11414,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -11415,12 +11434,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -11429,10 +11448,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -11449,12 +11468,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -11463,10 +11482,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11483,12 +11502,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11500,7 +11519,7 @@
         <v>52</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11517,12 +11536,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11534,7 +11553,7 @@
         <v>52</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11551,12 +11570,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -11565,10 +11584,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -11585,12 +11604,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -11599,10 +11618,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -11619,12 +11638,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -11633,10 +11652,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -11653,12 +11672,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -11667,10 +11686,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -11687,12 +11706,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -11701,10 +11720,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -11721,12 +11740,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -11735,10 +11754,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -11755,12 +11774,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -11769,10 +11788,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -11789,12 +11808,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -11803,10 +11822,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -11823,12 +11842,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -11837,10 +11856,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -11857,12 +11876,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -11874,7 +11893,7 @@
         <v>52</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -11891,12 +11910,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -11908,7 +11927,7 @@
         <v>52</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -11925,12 +11944,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -11939,10 +11958,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -11964,7 +11983,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -11973,10 +11992,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -11996,7 +12015,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -12005,10 +12024,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -12028,7 +12047,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -12037,10 +12056,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -12060,7 +12079,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -12069,10 +12088,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -12092,7 +12111,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -12101,10 +12120,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -12124,7 +12143,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -12136,7 +12155,7 @@
         <v>52</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -12156,7 +12175,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -12168,7 +12187,7 @@
         <v>52</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -12188,7 +12207,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -12197,10 +12216,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -12222,7 +12241,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -12231,10 +12250,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -12254,7 +12273,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -12263,10 +12282,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12288,7 +12307,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12297,10 +12316,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12320,7 +12339,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12332,7 +12351,7 @@
         <v>52</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -12352,7 +12371,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -12364,7 +12383,7 @@
         <v>52</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -12384,7 +12403,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -12396,7 +12415,7 @@
         <v>52</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -12416,7 +12435,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -12425,10 +12444,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -12450,7 +12469,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -12459,10 +12478,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12482,7 +12501,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12491,10 +12510,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12514,7 +12533,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12526,7 +12545,7 @@
         <v>49</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12546,7 +12565,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12555,10 +12574,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -12578,7 +12597,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -12590,7 +12609,7 @@
         <v>206</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -12610,7 +12629,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -12622,7 +12641,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -12644,7 +12663,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -12656,7 +12675,7 @@
         <v>63</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -12678,7 +12697,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -12690,7 +12709,7 @@
         <v>52</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -12710,7 +12729,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -12722,7 +12741,7 @@
         <v>71</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -12744,7 +12763,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -12756,7 +12775,7 @@
         <v>74</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -12776,7 +12795,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -12788,7 +12807,7 @@
         <v>80</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -12808,7 +12827,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -12820,7 +12839,7 @@
         <v>83</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -12842,7 +12861,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -12854,7 +12873,7 @@
         <v>259</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -12874,7 +12893,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -12886,7 +12905,7 @@
         <v>52</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -12906,7 +12925,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -12918,7 +12937,7 @@
         <v>52</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -12938,7 +12957,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -12947,10 +12966,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -12970,7 +12989,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -12979,10 +12998,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -13002,7 +13021,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -13011,10 +13030,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -13034,7 +13053,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -13043,10 +13062,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -13066,7 +13085,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -13078,7 +13097,7 @@
         <v>52</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -13098,7 +13117,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -13107,10 +13126,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -13132,7 +13151,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -13144,7 +13163,7 @@
         <v>253</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -13164,7 +13183,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -13176,7 +13195,7 @@
         <v>256</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -13196,7 +13215,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -13205,10 +13224,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -13228,7 +13247,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -13240,7 +13259,7 @@
         <v>52</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -13260,7 +13279,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -13272,7 +13291,7 @@
         <v>52</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13292,7 +13311,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13304,7 +13323,7 @@
         <v>55</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13324,7 +13343,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13336,7 +13355,7 @@
         <v>58</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -13356,7 +13375,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -13368,7 +13387,7 @@
         <v>52</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -13388,7 +13407,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -13400,7 +13419,7 @@
         <v>63</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -13422,7 +13441,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -13434,7 +13453,7 @@
         <v>52</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -13454,7 +13473,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -13466,7 +13485,7 @@
         <v>121</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13486,7 +13505,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13498,7 +13517,7 @@
         <v>124</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13518,7 +13537,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13530,7 +13549,7 @@
         <v>145</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13550,7 +13569,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -13562,7 +13581,7 @@
         <v>71</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -13584,7 +13603,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -13596,7 +13615,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -13616,7 +13635,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -13628,7 +13647,7 @@
         <v>190</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -13650,7 +13669,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -13662,7 +13681,7 @@
         <v>193</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -13684,7 +13703,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -13696,7 +13715,7 @@
         <v>129</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -13718,7 +13737,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -13730,7 +13749,7 @@
         <v>83</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -13752,7 +13771,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -13764,7 +13783,7 @@
         <v>203</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -13784,7 +13803,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -13796,7 +13815,7 @@
         <v>63</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -13818,7 +13837,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -13830,7 +13849,7 @@
         <v>52</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -13850,7 +13869,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -13862,7 +13881,7 @@
         <v>216</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -13884,7 +13903,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -13896,7 +13915,7 @@
         <v>124</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -13916,7 +13935,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -13928,7 +13947,7 @@
         <v>71</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -13950,7 +13969,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -13962,7 +13981,7 @@
         <v>55</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -13982,7 +14001,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -13994,7 +14013,7 @@
         <v>58</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -14014,7 +14033,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -14026,7 +14045,7 @@
         <v>83</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -14048,7 +14067,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -14060,7 +14079,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -14082,7 +14101,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -14094,7 +14113,7 @@
         <v>63</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -14116,7 +14135,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -14128,7 +14147,7 @@
         <v>52</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -14148,7 +14167,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -14160,7 +14179,7 @@
         <v>68</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -14180,7 +14199,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -14192,7 +14211,7 @@
         <v>71</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -14214,7 +14233,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -14226,7 +14245,7 @@
         <v>74</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -14246,7 +14265,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -14258,7 +14277,7 @@
         <v>77</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -14278,7 +14297,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14290,7 +14309,7 @@
         <v>80</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14310,7 +14329,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14322,7 +14341,7 @@
         <v>83</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14344,7 +14363,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -14356,7 +14375,7 @@
         <v>52</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -14376,7 +14395,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -14388,7 +14407,7 @@
         <v>63</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -14410,7 +14429,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -14419,10 +14438,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -14442,7 +14461,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -14454,7 +14473,7 @@
         <v>52</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -14474,7 +14493,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14483,10 +14502,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14506,7 +14525,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14518,7 +14537,7 @@
         <v>124</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14538,7 +14557,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14550,7 +14569,7 @@
         <v>71</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -14572,7 +14591,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -14584,7 +14603,7 @@
         <v>83</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -14606,7 +14625,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -14618,7 +14637,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -14637,12 +14656,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -14651,10 +14670,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -14671,12 +14690,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -14685,10 +14704,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -14705,12 +14724,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -14719,10 +14738,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -14741,12 +14760,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -14755,10 +14774,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -14775,12 +14794,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -14789,10 +14808,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -14811,12 +14830,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -14825,10 +14844,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -14845,12 +14864,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -14859,10 +14878,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -14881,12 +14900,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -14895,10 +14914,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -14915,12 +14934,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -14932,7 +14951,7 @@
         <v>71</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -14951,12 +14970,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -14968,7 +14987,7 @@
         <v>83</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -14987,12 +15006,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -15004,7 +15023,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -15026,7 +15045,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -15035,10 +15054,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -15058,7 +15077,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -15067,10 +15086,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -15090,7 +15109,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -15099,10 +15118,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -15122,7 +15141,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -15131,10 +15150,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -15154,7 +15173,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -15163,10 +15182,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -15186,7 +15205,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -15195,10 +15214,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -15218,7 +15237,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -15230,7 +15249,7 @@
         <v>52</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -15250,7 +15269,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -15262,7 +15281,7 @@
         <v>71</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15284,7 +15303,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15293,10 +15312,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15316,7 +15335,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15328,7 +15347,7 @@
         <v>83</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -15350,7 +15369,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -15359,10 +15378,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -15384,7 +15403,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -15393,10 +15412,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -15418,7 +15437,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -15430,7 +15449,7 @@
         <v>347</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -15450,7 +15469,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -15459,10 +15478,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15484,7 +15503,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15496,7 +15515,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15518,7 +15537,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15527,10 +15546,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15550,7 +15569,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -15559,10 +15578,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -15584,7 +15603,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -15596,7 +15615,7 @@
         <v>52</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -15616,7 +15635,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -15628,7 +15647,7 @@
         <v>80</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -15648,7 +15667,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -15657,10 +15676,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -15680,7 +15699,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -15689,10 +15708,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -15712,7 +15731,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -15724,7 +15743,7 @@
         <v>341</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -15744,7 +15763,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -15756,7 +15775,7 @@
         <v>80</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -15776,7 +15795,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -15785,10 +15804,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -15808,7 +15827,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -15820,7 +15839,7 @@
         <v>124</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -15840,7 +15859,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -15849,10 +15868,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -15872,7 +15891,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -15884,7 +15903,7 @@
         <v>80</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -15904,7 +15923,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -15913,10 +15932,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -15936,7 +15955,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -15948,7 +15967,7 @@
         <v>80</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -15968,7 +15987,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -15977,10 +15996,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -16000,7 +16019,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -16012,7 +16031,7 @@
         <v>80</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -16032,7 +16051,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -16041,10 +16060,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -16064,7 +16083,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -16073,10 +16092,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -16096,7 +16115,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -16105,10 +16124,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -16128,7 +16147,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -16137,10 +16156,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -16160,7 +16179,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -16169,10 +16188,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -16192,7 +16211,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -16201,10 +16220,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -16224,7 +16243,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -16233,10 +16252,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -16256,7 +16275,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -16265,10 +16284,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16290,7 +16309,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16299,10 +16318,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16324,7 +16343,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16333,10 +16352,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -16356,7 +16375,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -16368,7 +16387,7 @@
         <v>190</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -16390,7 +16409,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -16399,10 +16418,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -16424,7 +16443,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -16433,10 +16452,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -16458,7 +16477,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -16467,10 +16486,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16490,7 +16509,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16499,10 +16518,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16522,7 +16541,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16531,10 +16550,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16554,7 +16573,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -16563,10 +16582,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -16588,7 +16607,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -16597,10 +16616,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -16620,7 +16639,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -16629,10 +16648,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -16652,7 +16671,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -16661,10 +16680,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -16684,7 +16703,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -16693,10 +16712,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -16716,7 +16735,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -16725,10 +16744,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -16748,7 +16767,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -16757,10 +16776,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -16780,7 +16799,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -16789,10 +16808,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -16812,7 +16831,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -16821,10 +16840,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -16844,7 +16863,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -16853,10 +16872,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -16876,7 +16895,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -16885,10 +16904,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -16908,7 +16927,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -16917,10 +16936,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -16940,7 +16959,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -16949,10 +16968,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -16972,7 +16991,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -16981,10 +17000,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -17004,7 +17023,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -17013,10 +17032,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -17036,7 +17055,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -17045,10 +17064,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -17068,7 +17087,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -17077,10 +17096,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -17100,7 +17119,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -17109,10 +17128,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -17132,7 +17151,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -17141,10 +17160,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -17164,7 +17183,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -17173,10 +17192,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -17196,7 +17215,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -17205,10 +17224,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -17228,7 +17247,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -17237,10 +17256,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -17260,7 +17279,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -17269,10 +17288,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17292,7 +17311,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17301,10 +17320,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17324,7 +17343,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17333,10 +17352,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -17356,7 +17375,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -17365,10 +17384,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -17388,7 +17407,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -17397,10 +17416,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -17420,7 +17439,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -17429,10 +17448,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -17452,7 +17471,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -17461,10 +17480,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17484,7 +17503,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17493,10 +17512,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17516,7 +17535,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17525,10 +17544,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17548,7 +17567,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17557,10 +17576,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -17580,7 +17599,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -17589,10 +17608,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -17612,7 +17631,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -17621,10 +17640,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -17644,7 +17663,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -17653,10 +17672,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -17676,7 +17695,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -17685,10 +17704,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -17708,7 +17727,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -17717,10 +17736,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -17740,7 +17759,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -17749,10 +17768,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -17772,7 +17791,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -17781,10 +17800,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -17804,7 +17823,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -17813,10 +17832,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -17836,7 +17855,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -17845,10 +17864,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -17868,7 +17887,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -17877,10 +17896,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -17900,7 +17919,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -17909,10 +17928,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -17932,7 +17951,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -17941,10 +17960,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -17964,7 +17983,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -17973,10 +17992,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -17996,7 +18015,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -18005,10 +18024,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -18028,7 +18047,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -18037,10 +18056,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -18060,7 +18079,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -18069,10 +18088,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -18092,7 +18111,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -18101,10 +18120,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -18124,7 +18143,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -18133,10 +18152,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -18156,7 +18175,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -18165,10 +18184,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -18188,7 +18207,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -18197,10 +18216,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -18220,7 +18239,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -18229,10 +18248,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -18252,7 +18271,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -18261,10 +18280,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18284,7 +18303,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18293,10 +18312,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18316,7 +18335,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18325,10 +18344,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18348,7 +18367,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -18357,10 +18376,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -18380,7 +18399,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -18389,10 +18408,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -18412,7 +18431,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -18421,10 +18440,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -18446,7 +18465,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -18455,10 +18474,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -18478,7 +18497,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18487,10 +18506,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18510,7 +18529,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18519,10 +18538,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18542,7 +18561,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18551,10 +18570,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -18574,7 +18593,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -18583,10 +18602,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -18606,7 +18625,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -18615,10 +18634,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -18638,7 +18657,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -18647,10 +18666,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -18670,7 +18689,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -18679,10 +18698,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -18702,7 +18721,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -18711,10 +18730,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -18734,7 +18753,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -18743,10 +18762,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -18768,7 +18787,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -18777,10 +18796,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -18802,7 +18821,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -18811,10 +18830,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -18836,7 +18855,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -18845,10 +18864,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -18868,7 +18887,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -18877,10 +18896,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -18900,7 +18919,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -18909,10 +18928,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -18932,7 +18951,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -18941,10 +18960,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -18966,7 +18985,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -18978,7 +18997,7 @@
         <v>329</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -19000,7 +19019,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -19009,10 +19028,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -19032,7 +19051,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -19041,10 +19060,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -19064,7 +19083,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -19073,10 +19092,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -19096,7 +19115,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -19105,10 +19124,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -19128,7 +19147,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -19137,10 +19156,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -19155,14 +19174,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -19171,10 +19190,10 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
@@ -19194,7 +19213,7 @@
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -19203,13 +19222,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -19218,25 +19237,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -19245,13 +19264,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -19260,25 +19279,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19287,13 +19306,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19302,25 +19321,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19329,13 +19348,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -19344,25 +19363,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -19371,10 +19390,10 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="F424" s="3"/>
       <c r="G424" s="3" t="s">
@@ -19394,7 +19413,7 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -19403,10 +19422,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -19426,7 +19445,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -19435,10 +19454,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -19458,7 +19477,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -19467,10 +19486,10 @@
         <v>10</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -19490,7 +19509,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19499,10 +19518,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19522,7 +19541,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -19531,10 +19550,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -19554,7 +19573,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -19563,10 +19582,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -19586,7 +19605,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -19595,10 +19614,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -19618,7 +19637,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -19627,10 +19646,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -19650,7 +19669,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -19659,10 +19678,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -19682,7 +19701,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -19691,10 +19710,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -19714,7 +19733,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -19723,10 +19742,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -19746,7 +19765,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -19755,10 +19774,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -19778,7 +19797,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -19787,10 +19806,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -19810,7 +19829,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -19819,10 +19838,10 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F438" s="3"/>
       <c r="G438" s="3" t="s">
@@ -19842,7 +19861,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -19851,13 +19870,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -19866,27 +19885,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -19895,13 +19914,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -19910,27 +19929,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -19939,13 +19958,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -19954,25 +19973,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -19981,13 +20000,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -19996,25 +20015,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>280</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -20023,10 +20042,10 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F443" s="3"/>
       <c r="G443" s="3" t="s">
@@ -20046,7 +20065,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -20055,10 +20074,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -20078,7 +20097,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -20087,10 +20106,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -20110,7 +20129,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -20119,10 +20138,10 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -20142,7 +20161,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -20151,10 +20170,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -20174,7 +20193,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -20183,10 +20202,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -20206,7 +20225,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -20215,10 +20234,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -20238,7 +20257,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -20247,10 +20266,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -20270,7 +20289,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -20279,10 +20298,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -20302,7 +20321,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -20311,10 +20330,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -20334,7 +20353,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -20343,10 +20362,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -20366,7 +20385,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -20375,10 +20394,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -20398,7 +20417,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -20407,10 +20426,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -20430,7 +20449,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -20439,10 +20458,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -20462,7 +20481,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -20471,10 +20490,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -20494,7 +20513,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -20503,10 +20522,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -20526,7 +20545,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -20535,10 +20554,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -20558,7 +20577,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -20567,10 +20586,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -20590,7 +20609,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -20599,10 +20618,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -20622,7 +20641,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -20631,10 +20650,10 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F462" s="3"/>
       <c r="G462" s="3" t="s">
@@ -20654,7 +20673,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -20663,10 +20682,10 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="3" t="s">
@@ -20686,7 +20705,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -20695,10 +20714,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -20718,7 +20737,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -20727,10 +20746,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -20745,7 +20764,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4168" uniqueCount="1453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="1494">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -1622,6 +1622,15 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Project Zero file table, set-up and run commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the seven-file table and the no-offline-fallback note</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC140</t>
   </si>
   <si>
@@ -1631,6 +1640,15 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_01_ai_model_vs_chatbot_vs_agent.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Model, chatbot and agent as plain Python classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3 › 3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code and explanation already in Python Ch 3 › 3.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC141</t>
   </si>
   <si>
@@ -1640,6 +1658,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_02_calling_the_ai_paid_and_free.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Four provider calls and the key picker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3 › 3.4; Pydantic › Ch 5 › 5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provider code and picker order already in the books</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run (needs keys). Model names may be out of date</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC142</t>
   </si>
   <si>
@@ -1670,6 +1700,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_04_giving_it_a_tool.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Manual tool call: extract a city, then call get_weather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3 › 3.6; LLM › Ch 2 › 2.3 (get_weather)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual pipeline in Python Ch 3 › 3.6; get_weather is shown in LLM Ch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run (needs keys)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC144</t>
   </si>
   <si>
@@ -1679,6 +1721,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_05_teaching_it_to_choose.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Tool schema and the model choosing a tool, with real transcripts in comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added full schema, real replies and the three-calls example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source quirks recorded: get_weather_schema mis-nested (parameters outside function); the three get_capital calls include two wrong arguments. Not run against a real model</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC145</t>
   </si>
   <si>
@@ -1688,6 +1742,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_06_project_zero_agent.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Assembled agent loop and terminal chat, one tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.4, 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the terminal chat and the memory list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run with a fake model: crashes with NameError on the first tool call (stray line with unquoted function); get_currency defined twice, second is pass and not in TOOL_SCHEMAS; scratch leftovers</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC146</t>
   </si>
   <si>
@@ -1697,6 +1763,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/_07_streamlit_app.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Agent loop behind a Streamlit chat with weather, calculator and live currency tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.4, 2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added three tools, calculator guard and session_state memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop and calculator run with a fake model; currency API and Streamlit page not run</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC147</t>
   </si>
   <si>
@@ -1706,6 +1784,18 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/Project 0/output</t>
   </si>
   <si>
+    <t xml:space="preserve">Saved sample of the agent's message list with a tool-call turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in the books before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSON sample data, 44 lines</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC148</t>
   </si>
   <si>
@@ -1718,6 +1808,15 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/04-05 - 5 Jul &amp; 11 Jul - Anatomy of an Agent &amp; The Agentic Loop/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 04-05 folder overview and file table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python › Ch 3; LLM › Ch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeats the class 04 and 05 summaries and the same file table</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC150</t>
   </si>
   <si>
@@ -3935,6 +4034,18 @@
     <t xml:space="preserve">classes_summary/05 - 11 Jul - The Agentic Loop.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Tool schema, assembled loop, terminal chat, Streamlit app, why the loop repeats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.3 to 2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM Ch 2 was empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code excerpts copied from the summary; loop behaviour checked with a fake model</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC424</t>
   </si>
   <si>
@@ -4164,6 +4275,18 @@
   </si>
   <si>
     <t xml:space="preserve">classes_transcription_summary/05 - 11 Jul - The Agentic Loop (Pure Python).md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Message roles, knowledge cutoff, real API demos, structured output, the agentic loop, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.1, 2.2, 2.4, 2.8; Ch 4 glossary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added roles, knowledge cutoff, response shape and usage, max_tokens, structured-output ways, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 02/03 'max_iterations' is called max_turns in the code files</t>
   </si>
   <si>
     <t xml:space="preserve">LC443</t>
@@ -4918,7 +5041,7 @@
       </c>
       <c r="B6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,B$3)</f>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,C$3)</f>
@@ -4926,7 +5049,7 @@
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,D$3)</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,E$3)</f>
@@ -5068,7 +5191,7 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
@@ -5076,7 +5199,7 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -5122,7 +5245,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -5137,7 +5260,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -5152,7 +5275,7 @@
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A16)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -5182,7 +5305,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5197,7 +5320,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5212,7 +5335,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -10188,27 +10311,33 @@
       <c r="E140" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="F140" s="3"/>
+      <c r="F140" s="3" t="s">
+        <v>532</v>
+      </c>
       <c r="G140" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I140" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>533</v>
+      </c>
       <c r="J140" s="3"/>
       <c r="K140" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L140" s="3"/>
-      <c r="M140" s="3"/>
-      <c r="N140" s="3" t="s">
-        <v>529</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N140" s="3"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -10217,32 +10346,38 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="F141" s="3"/>
+        <v>537</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>538</v>
+      </c>
       <c r="G141" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I141" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>539</v>
+      </c>
       <c r="J141" s="3"/>
       <c r="K141" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L141" s="3"/>
-      <c r="M141" s="3"/>
-      <c r="N141" s="3" t="s">
-        <v>529</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N141" s="3"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -10251,32 +10386,40 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="F142" s="3"/>
+        <v>543</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>544</v>
+      </c>
       <c r="G142" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I142" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>545</v>
+      </c>
       <c r="J142" s="3"/>
       <c r="K142" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L142" s="3"/>
-      <c r="M142" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="M142" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="N142" s="3" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -10285,13 +10428,13 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
@@ -10300,25 +10443,25 @@
         <v>2</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="M143" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -10327,32 +10470,40 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F144" s="3"/>
+        <v>557</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>558</v>
+      </c>
       <c r="G144" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I144" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>559</v>
+      </c>
       <c r="J144" s="3"/>
       <c r="K144" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L144" s="3"/>
-      <c r="M144" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="M144" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="N144" s="3" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -10361,32 +10512,40 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="F145" s="3"/>
+        <v>564</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>565</v>
+      </c>
       <c r="G145" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I145" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>566</v>
+      </c>
       <c r="J145" s="3"/>
       <c r="K145" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L145" s="3"/>
-      <c r="M145" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="M145" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="N145" s="3" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -10395,32 +10554,40 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="F146" s="3"/>
+        <v>571</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>572</v>
+      </c>
       <c r="G146" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I146" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>573</v>
+      </c>
       <c r="J146" s="3"/>
       <c r="K146" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L146" s="3"/>
-      <c r="M146" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="M146" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="N146" s="3" t="s">
-        <v>529</v>
+        <v>575</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -10429,32 +10596,40 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="F147" s="3"/>
+        <v>578</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>579</v>
+      </c>
       <c r="G147" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I147" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>580</v>
+      </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L147" s="3"/>
-      <c r="M147" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="M147" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="N147" s="3" t="s">
-        <v>529</v>
+        <v>582</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -10463,32 +10638,40 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="F148" s="3"/>
+        <v>585</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>586</v>
+      </c>
       <c r="G148" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I148" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>587</v>
+      </c>
       <c r="J148" s="3"/>
       <c r="K148" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L148" s="3"/>
-      <c r="M148" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="M148" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="N148" s="3" t="s">
-        <v>529</v>
+        <v>589</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -10500,7 +10683,7 @@
         <v>77</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -10524,7 +10707,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -10536,29 +10719,35 @@
         <v>58</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="F150" s="3"/>
+        <v>593</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>594</v>
+      </c>
       <c r="G150" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I150" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>595</v>
+      </c>
       <c r="J150" s="3"/>
       <c r="K150" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L150" s="3"/>
-      <c r="M150" s="3"/>
-      <c r="N150" s="3" t="s">
-        <v>529</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L150" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="M150" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N150" s="3"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -10570,7 +10759,7 @@
         <v>58</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>565</v>
+        <v>598</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="3" t="s">
@@ -10592,7 +10781,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -10604,7 +10793,7 @@
         <v>367</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>567</v>
+        <v>600</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -10624,7 +10813,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>568</v>
+        <v>601</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -10636,7 +10825,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -10658,7 +10847,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>570</v>
+        <v>603</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10670,7 +10859,7 @@
         <v>69</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>571</v>
+        <v>604</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10692,7 +10881,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>572</v>
+        <v>605</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -10701,10 +10890,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>573</v>
+        <v>606</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -10724,7 +10913,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>575</v>
+        <v>608</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10736,7 +10925,7 @@
         <v>58</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>576</v>
+        <v>609</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -10756,7 +10945,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -10765,10 +10954,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>578</v>
+        <v>611</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>579</v>
+        <v>612</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -10788,7 +10977,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -10797,10 +10986,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>581</v>
+        <v>614</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>582</v>
+        <v>615</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -10820,7 +11009,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -10829,10 +11018,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>584</v>
+        <v>617</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>585</v>
+        <v>618</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -10852,7 +11041,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>586</v>
+        <v>619</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -10864,7 +11053,7 @@
         <v>130</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>587</v>
+        <v>620</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -10884,7 +11073,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -10896,7 +11085,7 @@
         <v>77</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>589</v>
+        <v>622</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -10918,7 +11107,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>590</v>
+        <v>623</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -10930,7 +11119,7 @@
         <v>89</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>591</v>
+        <v>624</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -10952,7 +11141,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>592</v>
+        <v>625</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -10964,7 +11153,7 @@
         <v>58</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>593</v>
+        <v>626</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -10984,7 +11173,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -10996,7 +11185,7 @@
         <v>367</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -11013,12 +11202,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -11030,7 +11219,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -11049,12 +11238,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>599</v>
+        <v>632</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -11066,7 +11255,7 @@
         <v>69</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -11085,12 +11274,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>601</v>
+        <v>634</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -11099,10 +11288,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>603</v>
+        <v>636</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -11119,12 +11308,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>604</v>
+        <v>637</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -11133,10 +11322,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>606</v>
+        <v>639</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -11153,12 +11342,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -11167,10 +11356,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>608</v>
+        <v>641</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>609</v>
+        <v>642</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -11187,12 +11376,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>610</v>
+        <v>643</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -11201,10 +11390,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>611</v>
+        <v>644</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>612</v>
+        <v>645</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -11221,12 +11410,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>613</v>
+        <v>646</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -11235,10 +11424,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>614</v>
+        <v>647</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>615</v>
+        <v>648</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -11255,12 +11444,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>616</v>
+        <v>649</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -11269,10 +11458,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>617</v>
+        <v>650</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>618</v>
+        <v>651</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -11289,12 +11478,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>619</v>
+        <v>652</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -11306,7 +11495,7 @@
         <v>58</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>620</v>
+        <v>653</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -11323,12 +11512,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>621</v>
+        <v>654</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -11340,7 +11529,7 @@
         <v>130</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>622</v>
+        <v>655</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -11357,12 +11546,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>623</v>
+        <v>656</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -11374,7 +11563,7 @@
         <v>77</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>624</v>
+        <v>657</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -11393,12 +11582,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>625</v>
+        <v>658</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -11410,7 +11599,7 @@
         <v>349</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>626</v>
+        <v>659</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -11429,12 +11618,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>627</v>
+        <v>660</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -11446,7 +11635,7 @@
         <v>89</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>628</v>
+        <v>661</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -11465,12 +11654,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>629</v>
+        <v>662</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11479,10 +11668,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>630</v>
+        <v>663</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>631</v>
+        <v>664</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11499,12 +11688,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11513,10 +11702,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>633</v>
+        <v>666</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>634</v>
+        <v>667</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -11533,12 +11722,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>635</v>
+        <v>668</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -11547,10 +11736,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>636</v>
+        <v>669</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>637</v>
+        <v>670</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -11567,12 +11756,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>638</v>
+        <v>671</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -11581,10 +11770,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -11601,12 +11790,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>641</v>
+        <v>674</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -11615,10 +11804,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>642</v>
+        <v>675</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>643</v>
+        <v>676</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -11635,12 +11824,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>644</v>
+        <v>677</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -11649,10 +11838,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>645</v>
+        <v>678</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>646</v>
+        <v>679</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11669,12 +11858,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>647</v>
+        <v>680</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11686,7 +11875,7 @@
         <v>58</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>648</v>
+        <v>681</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11703,12 +11892,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>649</v>
+        <v>682</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11720,7 +11909,7 @@
         <v>58</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>650</v>
+        <v>683</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11737,12 +11926,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>651</v>
+        <v>684</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -11751,10 +11940,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>652</v>
+        <v>685</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>653</v>
+        <v>686</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -11771,12 +11960,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>655</v>
+        <v>688</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -11785,10 +11974,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>656</v>
+        <v>689</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>657</v>
+        <v>690</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -11805,12 +11994,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>658</v>
+        <v>691</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -11819,10 +12008,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>659</v>
+        <v>692</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>660</v>
+        <v>693</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -11839,12 +12028,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>661</v>
+        <v>694</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -11853,10 +12042,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>662</v>
+        <v>695</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>663</v>
+        <v>696</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -11873,12 +12062,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>664</v>
+        <v>697</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -11887,10 +12076,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>665</v>
+        <v>698</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>666</v>
+        <v>699</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -11907,12 +12096,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>667</v>
+        <v>700</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -11921,10 +12110,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>668</v>
+        <v>701</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>669</v>
+        <v>702</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -11941,12 +12130,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>670</v>
+        <v>703</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -11955,10 +12144,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>671</v>
+        <v>704</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>672</v>
+        <v>705</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -11975,12 +12164,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>673</v>
+        <v>706</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -11989,10 +12178,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>674</v>
+        <v>707</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>675</v>
+        <v>708</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -12009,12 +12198,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>676</v>
+        <v>709</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -12023,10 +12212,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>677</v>
+        <v>710</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>678</v>
+        <v>711</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -12043,12 +12232,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>679</v>
+        <v>712</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -12060,7 +12249,7 @@
         <v>58</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>680</v>
+        <v>713</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -12077,12 +12266,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>681</v>
+        <v>714</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -12094,7 +12283,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>682</v>
+        <v>715</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -12111,12 +12300,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>683</v>
+        <v>716</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -12125,10 +12314,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>684</v>
+        <v>717</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>685</v>
+        <v>718</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -12150,7 +12339,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>686</v>
+        <v>719</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -12159,10 +12348,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>687</v>
+        <v>720</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>688</v>
+        <v>721</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -12182,7 +12371,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>689</v>
+        <v>722</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -12191,10 +12380,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>690</v>
+        <v>723</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>691</v>
+        <v>724</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -12214,7 +12403,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>692</v>
+        <v>725</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -12223,10 +12412,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>693</v>
+        <v>726</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>694</v>
+        <v>727</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -12246,7 +12435,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>695</v>
+        <v>728</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -12255,10 +12444,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>696</v>
+        <v>729</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>697</v>
+        <v>730</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -12278,7 +12467,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>698</v>
+        <v>731</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -12287,10 +12476,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>699</v>
+        <v>732</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>700</v>
+        <v>733</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -12310,7 +12499,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>701</v>
+        <v>734</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -12322,7 +12511,7 @@
         <v>58</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>702</v>
+        <v>735</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -12342,7 +12531,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>703</v>
+        <v>736</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -12354,7 +12543,7 @@
         <v>58</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>704</v>
+        <v>737</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -12374,7 +12563,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>705</v>
+        <v>738</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -12383,10 +12572,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>684</v>
+        <v>717</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>706</v>
+        <v>739</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -12408,7 +12597,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>707</v>
+        <v>740</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -12417,10 +12606,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>687</v>
+        <v>720</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>708</v>
+        <v>741</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -12440,7 +12629,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>709</v>
+        <v>742</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -12449,10 +12638,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>710</v>
+        <v>743</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>711</v>
+        <v>744</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12474,7 +12663,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12483,10 +12672,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>696</v>
+        <v>729</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>713</v>
+        <v>746</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12506,7 +12695,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>714</v>
+        <v>747</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12518,7 +12707,7 @@
         <v>58</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>715</v>
+        <v>748</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -12538,7 +12727,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>716</v>
+        <v>749</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -12550,7 +12739,7 @@
         <v>58</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>717</v>
+        <v>750</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -12570,7 +12759,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>718</v>
+        <v>751</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -12582,7 +12771,7 @@
         <v>58</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>719</v>
+        <v>752</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -12602,7 +12791,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>720</v>
+        <v>753</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -12611,10 +12800,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>721</v>
+        <v>754</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>722</v>
+        <v>755</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -12636,7 +12825,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>723</v>
+        <v>756</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -12645,10 +12834,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>724</v>
+        <v>757</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>725</v>
+        <v>758</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12668,7 +12857,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>726</v>
+        <v>759</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12677,10 +12866,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>727</v>
+        <v>760</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>728</v>
+        <v>761</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12700,7 +12889,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>729</v>
+        <v>762</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12712,7 +12901,7 @@
         <v>55</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>730</v>
+        <v>763</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12732,7 +12921,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>731</v>
+        <v>764</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12741,10 +12930,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>732</v>
+        <v>765</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>733</v>
+        <v>766</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -12764,7 +12953,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>734</v>
+        <v>767</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -12776,7 +12965,7 @@
         <v>212</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>735</v>
+        <v>768</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -12796,7 +12985,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>736</v>
+        <v>769</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -12808,7 +12997,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>737</v>
+        <v>770</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -12830,7 +13019,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>738</v>
+        <v>771</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -12842,7 +13031,7 @@
         <v>69</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>739</v>
+        <v>772</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -12864,7 +13053,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>740</v>
+        <v>773</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -12876,7 +13065,7 @@
         <v>58</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>741</v>
+        <v>774</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -12896,7 +13085,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>742</v>
+        <v>775</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -12908,7 +13097,7 @@
         <v>77</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>743</v>
+        <v>776</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -12930,7 +13119,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>744</v>
+        <v>777</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -12942,7 +13131,7 @@
         <v>80</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>745</v>
+        <v>778</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -12962,7 +13151,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>746</v>
+        <v>779</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -12974,7 +13163,7 @@
         <v>86</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>747</v>
+        <v>780</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -12994,7 +13183,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>748</v>
+        <v>781</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -13006,7 +13195,7 @@
         <v>89</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>749</v>
+        <v>782</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -13028,7 +13217,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>750</v>
+        <v>783</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -13040,7 +13229,7 @@
         <v>265</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>751</v>
+        <v>784</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -13060,7 +13249,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>752</v>
+        <v>785</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -13072,7 +13261,7 @@
         <v>58</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>753</v>
+        <v>786</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -13092,7 +13281,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>754</v>
+        <v>787</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -13104,7 +13293,7 @@
         <v>58</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -13124,7 +13313,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>756</v>
+        <v>789</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -13133,10 +13322,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>757</v>
+        <v>790</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -13156,7 +13345,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>759</v>
+        <v>792</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -13165,10 +13354,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>760</v>
+        <v>793</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>761</v>
+        <v>794</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -13188,7 +13377,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>762</v>
+        <v>795</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -13197,10 +13386,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>764</v>
+        <v>797</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -13220,7 +13409,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>765</v>
+        <v>798</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -13229,10 +13418,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>766</v>
+        <v>799</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>767</v>
+        <v>800</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -13252,7 +13441,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>768</v>
+        <v>801</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -13264,7 +13453,7 @@
         <v>58</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -13284,7 +13473,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>770</v>
+        <v>803</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -13293,10 +13482,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>771</v>
+        <v>804</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>772</v>
+        <v>805</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -13318,7 +13507,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -13330,7 +13519,7 @@
         <v>259</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>774</v>
+        <v>807</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -13350,7 +13539,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>775</v>
+        <v>808</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -13362,7 +13551,7 @@
         <v>262</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>776</v>
+        <v>809</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -13382,7 +13571,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>777</v>
+        <v>810</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -13391,10 +13580,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>778</v>
+        <v>811</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>779</v>
+        <v>812</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -13414,7 +13603,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -13426,7 +13615,7 @@
         <v>58</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>781</v>
+        <v>814</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -13446,7 +13635,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>782</v>
+        <v>815</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -13458,7 +13647,7 @@
         <v>58</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>783</v>
+        <v>816</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13478,7 +13667,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>784</v>
+        <v>817</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13490,7 +13679,7 @@
         <v>61</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>785</v>
+        <v>818</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13510,7 +13699,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>786</v>
+        <v>819</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13522,7 +13711,7 @@
         <v>64</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -13542,7 +13731,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>788</v>
+        <v>821</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -13554,7 +13743,7 @@
         <v>58</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>789</v>
+        <v>822</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -13574,7 +13763,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>790</v>
+        <v>823</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -13586,7 +13775,7 @@
         <v>69</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>791</v>
+        <v>824</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -13608,7 +13797,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>792</v>
+        <v>825</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -13620,7 +13809,7 @@
         <v>58</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>793</v>
+        <v>826</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -13640,7 +13829,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>794</v>
+        <v>827</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -13652,7 +13841,7 @@
         <v>127</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>795</v>
+        <v>828</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13672,7 +13861,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>796</v>
+        <v>829</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13684,7 +13873,7 @@
         <v>130</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13704,7 +13893,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>798</v>
+        <v>831</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13716,7 +13905,7 @@
         <v>151</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>799</v>
+        <v>832</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13736,7 +13925,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>800</v>
+        <v>833</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -13748,7 +13937,7 @@
         <v>77</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>801</v>
+        <v>834</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -13770,7 +13959,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>802</v>
+        <v>835</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -13782,7 +13971,7 @@
         <v>193</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>803</v>
+        <v>836</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -13802,7 +13991,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>804</v>
+        <v>837</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -13814,7 +14003,7 @@
         <v>196</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>805</v>
+        <v>838</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -13836,7 +14025,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>806</v>
+        <v>839</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -13848,7 +14037,7 @@
         <v>199</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>807</v>
+        <v>840</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -13870,7 +14059,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>808</v>
+        <v>841</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -13882,7 +14071,7 @@
         <v>135</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>809</v>
+        <v>842</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -13904,7 +14093,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>810</v>
+        <v>843</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -13916,7 +14105,7 @@
         <v>89</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>811</v>
+        <v>844</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -13938,7 +14127,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>812</v>
+        <v>845</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -13950,7 +14139,7 @@
         <v>209</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>813</v>
+        <v>846</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -13970,7 +14159,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>814</v>
+        <v>847</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -13982,7 +14171,7 @@
         <v>69</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>815</v>
+        <v>848</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -14004,7 +14193,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>816</v>
+        <v>849</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -14016,7 +14205,7 @@
         <v>58</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>817</v>
+        <v>850</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -14036,7 +14225,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>818</v>
+        <v>851</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -14048,7 +14237,7 @@
         <v>222</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>819</v>
+        <v>852</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -14070,7 +14259,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>820</v>
+        <v>853</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -14082,7 +14271,7 @@
         <v>130</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>821</v>
+        <v>854</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -14102,7 +14291,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>822</v>
+        <v>855</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -14114,7 +14303,7 @@
         <v>77</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>823</v>
+        <v>856</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -14136,7 +14325,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>824</v>
+        <v>857</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -14148,7 +14337,7 @@
         <v>61</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>825</v>
+        <v>858</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -14168,7 +14357,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>826</v>
+        <v>859</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -14180,7 +14369,7 @@
         <v>64</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>827</v>
+        <v>860</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -14200,7 +14389,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>828</v>
+        <v>861</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -14212,7 +14401,7 @@
         <v>89</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>829</v>
+        <v>862</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -14234,7 +14423,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>830</v>
+        <v>863</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -14246,7 +14435,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>831</v>
+        <v>864</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -14268,7 +14457,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>832</v>
+        <v>865</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -14280,7 +14469,7 @@
         <v>69</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>833</v>
+        <v>866</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -14302,7 +14491,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>834</v>
+        <v>867</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -14314,7 +14503,7 @@
         <v>58</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>835</v>
+        <v>868</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -14334,7 +14523,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>836</v>
+        <v>869</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -14346,7 +14535,7 @@
         <v>74</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>837</v>
+        <v>870</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -14366,7 +14555,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>838</v>
+        <v>871</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -14378,7 +14567,7 @@
         <v>77</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>839</v>
+        <v>872</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -14400,7 +14589,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>840</v>
+        <v>873</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -14412,7 +14601,7 @@
         <v>80</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>841</v>
+        <v>874</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -14432,7 +14621,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>842</v>
+        <v>875</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -14444,7 +14633,7 @@
         <v>83</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>843</v>
+        <v>876</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -14464,7 +14653,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>844</v>
+        <v>877</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14476,7 +14665,7 @@
         <v>86</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>845</v>
+        <v>878</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14496,7 +14685,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>846</v>
+        <v>879</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14508,7 +14697,7 @@
         <v>89</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>847</v>
+        <v>880</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14530,7 +14719,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>848</v>
+        <v>881</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -14542,7 +14731,7 @@
         <v>58</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>849</v>
+        <v>882</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -14562,7 +14751,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -14574,7 +14763,7 @@
         <v>69</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>851</v>
+        <v>884</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -14596,7 +14785,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -14605,10 +14794,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>854</v>
+        <v>887</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -14628,7 +14817,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>855</v>
+        <v>888</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -14640,7 +14829,7 @@
         <v>58</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>856</v>
+        <v>889</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -14660,7 +14849,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>857</v>
+        <v>890</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14669,10 +14858,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>858</v>
+        <v>891</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>859</v>
+        <v>892</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14692,7 +14881,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>860</v>
+        <v>893</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14704,7 +14893,7 @@
         <v>130</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>861</v>
+        <v>894</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14724,7 +14913,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>862</v>
+        <v>895</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14736,7 +14925,7 @@
         <v>77</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>863</v>
+        <v>896</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -14758,7 +14947,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>864</v>
+        <v>897</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -14770,7 +14959,7 @@
         <v>89</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>865</v>
+        <v>898</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -14792,7 +14981,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>866</v>
+        <v>899</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -14804,7 +14993,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>867</v>
+        <v>900</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -14823,12 +15012,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>869</v>
+        <v>902</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -14837,10 +15026,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>870</v>
+        <v>903</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>871</v>
+        <v>904</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -14857,12 +15046,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>872</v>
+        <v>905</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -14871,10 +15060,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>873</v>
+        <v>906</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>874</v>
+        <v>907</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -14891,12 +15080,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>875</v>
+        <v>908</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -14905,10 +15094,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>876</v>
+        <v>909</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>877</v>
+        <v>910</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -14927,12 +15116,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>878</v>
+        <v>911</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -14941,10 +15130,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>879</v>
+        <v>912</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>880</v>
+        <v>913</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -14961,12 +15150,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>881</v>
+        <v>914</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -14975,10 +15164,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>882</v>
+        <v>915</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>883</v>
+        <v>916</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -14997,12 +15186,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>884</v>
+        <v>917</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -15011,10 +15200,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>885</v>
+        <v>918</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>886</v>
+        <v>919</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -15031,12 +15220,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>887</v>
+        <v>920</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -15045,10 +15234,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>888</v>
+        <v>921</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>889</v>
+        <v>922</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -15067,12 +15256,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>890</v>
+        <v>923</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -15081,10 +15270,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>891</v>
+        <v>924</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>892</v>
+        <v>925</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -15101,12 +15290,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>893</v>
+        <v>926</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -15118,7 +15307,7 @@
         <v>77</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>894</v>
+        <v>927</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -15137,12 +15326,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>895</v>
+        <v>928</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -15154,7 +15343,7 @@
         <v>89</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>896</v>
+        <v>929</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -15173,12 +15362,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>897</v>
+        <v>930</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -15190,7 +15379,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>898</v>
+        <v>931</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -15212,7 +15401,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>899</v>
+        <v>932</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -15221,10 +15410,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>900</v>
+        <v>933</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>901</v>
+        <v>934</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -15244,7 +15433,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>902</v>
+        <v>935</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -15253,10 +15442,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>903</v>
+        <v>936</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>904</v>
+        <v>937</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -15276,7 +15465,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>905</v>
+        <v>938</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -15285,10 +15474,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>906</v>
+        <v>939</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>907</v>
+        <v>940</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -15308,7 +15497,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>908</v>
+        <v>941</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -15317,10 +15506,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>909</v>
+        <v>942</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>910</v>
+        <v>943</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -15340,7 +15529,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>911</v>
+        <v>944</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -15349,10 +15538,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>912</v>
+        <v>945</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>913</v>
+        <v>946</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -15372,7 +15561,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>914</v>
+        <v>947</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -15381,10 +15570,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>915</v>
+        <v>948</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>916</v>
+        <v>949</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -15404,7 +15593,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>917</v>
+        <v>950</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -15416,7 +15605,7 @@
         <v>58</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>918</v>
+        <v>951</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -15436,7 +15625,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>919</v>
+        <v>952</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -15448,7 +15637,7 @@
         <v>77</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15470,7 +15659,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>921</v>
+        <v>954</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15479,10 +15668,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>922</v>
+        <v>955</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>923</v>
+        <v>956</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15502,7 +15691,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>924</v>
+        <v>957</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15514,7 +15703,7 @@
         <v>89</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>925</v>
+        <v>958</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -15536,7 +15725,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>926</v>
+        <v>959</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -15545,10 +15734,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>927</v>
+        <v>960</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>928</v>
+        <v>961</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -15570,7 +15759,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>929</v>
+        <v>962</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -15579,10 +15768,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>930</v>
+        <v>963</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>931</v>
+        <v>964</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -15604,7 +15793,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>932</v>
+        <v>965</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -15616,7 +15805,7 @@
         <v>367</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>933</v>
+        <v>966</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -15636,7 +15825,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>934</v>
+        <v>967</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -15645,10 +15834,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>935</v>
+        <v>968</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>936</v>
+        <v>969</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15670,7 +15859,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>937</v>
+        <v>970</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15682,7 +15871,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>938</v>
+        <v>971</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15704,7 +15893,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>939</v>
+        <v>972</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15713,10 +15902,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>940</v>
+        <v>973</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>941</v>
+        <v>974</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15736,7 +15925,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>942</v>
+        <v>975</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -15745,10 +15934,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>943</v>
+        <v>976</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>944</v>
+        <v>977</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -15770,7 +15959,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>945</v>
+        <v>978</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -15782,7 +15971,7 @@
         <v>58</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>946</v>
+        <v>979</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -15802,7 +15991,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>947</v>
+        <v>980</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -15814,7 +16003,7 @@
         <v>86</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>948</v>
+        <v>981</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -15834,7 +16023,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>949</v>
+        <v>982</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -15843,10 +16032,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>950</v>
+        <v>983</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>951</v>
+        <v>984</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -15866,7 +16055,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>952</v>
+        <v>985</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -15875,10 +16064,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>953</v>
+        <v>986</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>954</v>
+        <v>987</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -15898,7 +16087,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>955</v>
+        <v>988</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -15910,7 +16099,7 @@
         <v>361</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>956</v>
+        <v>989</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -15930,7 +16119,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>957</v>
+        <v>990</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -15942,7 +16131,7 @@
         <v>86</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>958</v>
+        <v>991</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -15962,7 +16151,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>959</v>
+        <v>992</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -15971,10 +16160,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>960</v>
+        <v>993</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>961</v>
+        <v>994</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -15994,7 +16183,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>962</v>
+        <v>995</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -16006,7 +16195,7 @@
         <v>130</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>963</v>
+        <v>996</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -16026,7 +16215,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -16035,10 +16224,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>965</v>
+        <v>998</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>966</v>
+        <v>999</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -16058,7 +16247,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>967</v>
+        <v>1000</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -16070,7 +16259,7 @@
         <v>86</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>968</v>
+        <v>1001</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -16090,7 +16279,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -16099,10 +16288,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>970</v>
+        <v>1003</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>971</v>
+        <v>1004</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -16122,7 +16311,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -16134,7 +16323,7 @@
         <v>86</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -16154,7 +16343,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -16163,10 +16352,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>975</v>
+        <v>1008</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>976</v>
+        <v>1009</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -16186,7 +16375,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>977</v>
+        <v>1010</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -16198,7 +16387,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>978</v>
+        <v>1011</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -16218,7 +16407,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>979</v>
+        <v>1012</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -16227,10 +16416,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>981</v>
+        <v>1014</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -16250,7 +16439,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>982</v>
+        <v>1015</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -16259,10 +16448,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>983</v>
+        <v>1016</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>984</v>
+        <v>1017</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -16282,7 +16471,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>985</v>
+        <v>1018</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -16291,10 +16480,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>986</v>
+        <v>1019</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>987</v>
+        <v>1020</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -16314,7 +16503,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>988</v>
+        <v>1021</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -16323,10 +16512,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>989</v>
+        <v>1022</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>990</v>
+        <v>1023</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -16346,7 +16535,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>991</v>
+        <v>1024</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -16355,10 +16544,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>992</v>
+        <v>1025</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>993</v>
+        <v>1026</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -16378,7 +16567,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>994</v>
+        <v>1027</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -16387,10 +16576,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>995</v>
+        <v>1028</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>996</v>
+        <v>1029</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -16410,7 +16599,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>997</v>
+        <v>1030</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -16419,10 +16608,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>998</v>
+        <v>1031</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>999</v>
+        <v>1032</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -16442,7 +16631,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>1000</v>
+        <v>1033</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -16451,10 +16640,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>1001</v>
+        <v>1034</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>1002</v>
+        <v>1035</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16476,7 +16665,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>1003</v>
+        <v>1036</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16485,10 +16674,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>1004</v>
+        <v>1037</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>1005</v>
+        <v>1038</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16510,7 +16699,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>1006</v>
+        <v>1039</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16519,10 +16708,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>1008</v>
+        <v>1041</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -16542,7 +16731,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>1009</v>
+        <v>1042</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -16554,7 +16743,7 @@
         <v>196</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>1010</v>
+        <v>1043</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -16576,7 +16765,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>1011</v>
+        <v>1044</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -16585,10 +16774,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1012</v>
+        <v>1045</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1013</v>
+        <v>1046</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -16610,7 +16799,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -16619,10 +16808,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1016</v>
+        <v>1049</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -16644,7 +16833,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -16653,10 +16842,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16676,7 +16865,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16685,10 +16874,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1021</v>
+        <v>1054</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1022</v>
+        <v>1055</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16708,7 +16897,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>1023</v>
+        <v>1056</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16717,10 +16906,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1024</v>
+        <v>1057</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1025</v>
+        <v>1058</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16740,7 +16929,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -16749,10 +16938,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1027</v>
+        <v>1060</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1028</v>
+        <v>1061</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -16774,7 +16963,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>1029</v>
+        <v>1062</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -16783,10 +16972,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1030</v>
+        <v>1063</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1031</v>
+        <v>1064</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -16806,7 +16995,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -16815,10 +17004,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1034</v>
+        <v>1067</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -16838,7 +17027,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>1035</v>
+        <v>1068</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -16847,10 +17036,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1036</v>
+        <v>1069</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1037</v>
+        <v>1070</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -16870,7 +17059,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>1038</v>
+        <v>1071</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -16879,10 +17068,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1039</v>
+        <v>1072</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1040</v>
+        <v>1073</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -16902,7 +17091,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>1041</v>
+        <v>1074</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -16911,10 +17100,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1042</v>
+        <v>1075</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1043</v>
+        <v>1076</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -16934,7 +17123,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>1044</v>
+        <v>1077</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -16943,10 +17132,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1045</v>
+        <v>1078</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1046</v>
+        <v>1079</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -16966,7 +17155,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>1047</v>
+        <v>1080</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -16975,10 +17164,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1048</v>
+        <v>1081</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1049</v>
+        <v>1082</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -16998,7 +17187,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>1050</v>
+        <v>1083</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -17007,10 +17196,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1051</v>
+        <v>1084</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1052</v>
+        <v>1085</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -17030,7 +17219,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>1053</v>
+        <v>1086</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -17039,10 +17228,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1054</v>
+        <v>1087</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1055</v>
+        <v>1088</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -17062,7 +17251,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>1056</v>
+        <v>1089</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -17071,10 +17260,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1057</v>
+        <v>1090</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1058</v>
+        <v>1091</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -17094,7 +17283,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>1059</v>
+        <v>1092</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -17103,10 +17292,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1060</v>
+        <v>1093</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1061</v>
+        <v>1094</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -17126,7 +17315,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>1062</v>
+        <v>1095</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -17135,10 +17324,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1063</v>
+        <v>1096</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1064</v>
+        <v>1097</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -17158,7 +17347,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>1065</v>
+        <v>1098</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -17167,10 +17356,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1066</v>
+        <v>1099</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1067</v>
+        <v>1100</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -17190,7 +17379,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>1068</v>
+        <v>1101</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -17199,10 +17388,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1069</v>
+        <v>1102</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1070</v>
+        <v>1103</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -17222,7 +17411,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1071</v>
+        <v>1104</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -17231,10 +17420,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1072</v>
+        <v>1105</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1073</v>
+        <v>1106</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -17254,7 +17443,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1074</v>
+        <v>1107</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -17263,10 +17452,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1075</v>
+        <v>1108</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -17286,7 +17475,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1077</v>
+        <v>1110</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -17295,10 +17484,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1078</v>
+        <v>1111</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1079</v>
+        <v>1112</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -17318,7 +17507,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1080</v>
+        <v>1113</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -17327,10 +17516,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1081</v>
+        <v>1114</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1082</v>
+        <v>1115</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -17350,7 +17539,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1083</v>
+        <v>1116</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -17359,10 +17548,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1085</v>
+        <v>1118</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -17382,7 +17571,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -17391,10 +17580,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1088</v>
+        <v>1121</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -17414,7 +17603,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -17423,10 +17612,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1090</v>
+        <v>1123</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1091</v>
+        <v>1124</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -17446,7 +17635,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1092</v>
+        <v>1125</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -17455,10 +17644,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1093</v>
+        <v>1126</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1094</v>
+        <v>1127</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17478,7 +17667,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1095</v>
+        <v>1128</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17487,10 +17676,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1096</v>
+        <v>1129</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1097</v>
+        <v>1130</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17510,7 +17699,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1098</v>
+        <v>1131</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17519,10 +17708,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1099</v>
+        <v>1132</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1100</v>
+        <v>1133</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -17542,7 +17731,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1101</v>
+        <v>1134</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -17551,10 +17740,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1102</v>
+        <v>1135</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1103</v>
+        <v>1136</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -17574,7 +17763,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1104</v>
+        <v>1137</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -17583,10 +17772,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1105</v>
+        <v>1138</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1106</v>
+        <v>1139</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -17606,7 +17795,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1107</v>
+        <v>1140</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -17615,10 +17804,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1108</v>
+        <v>1141</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1109</v>
+        <v>1142</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -17638,7 +17827,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1110</v>
+        <v>1143</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -17647,10 +17836,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1111</v>
+        <v>1144</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1112</v>
+        <v>1145</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17670,7 +17859,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1113</v>
+        <v>1146</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17679,10 +17868,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1114</v>
+        <v>1147</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1115</v>
+        <v>1148</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17702,7 +17891,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1116</v>
+        <v>1149</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17711,10 +17900,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1117</v>
+        <v>1150</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1118</v>
+        <v>1151</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17734,7 +17923,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1119</v>
+        <v>1152</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17743,10 +17932,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1120</v>
+        <v>1153</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1121</v>
+        <v>1154</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -17766,7 +17955,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1122</v>
+        <v>1155</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -17775,10 +17964,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1123</v>
+        <v>1156</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1124</v>
+        <v>1157</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -17798,7 +17987,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1125</v>
+        <v>1158</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -17807,10 +17996,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1126</v>
+        <v>1159</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1127</v>
+        <v>1160</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -17830,7 +18019,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1128</v>
+        <v>1161</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -17839,10 +18028,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1129</v>
+        <v>1162</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1130</v>
+        <v>1163</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -17862,7 +18051,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1131</v>
+        <v>1164</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -17871,10 +18060,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1132</v>
+        <v>1165</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1133</v>
+        <v>1166</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -17894,7 +18083,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1134</v>
+        <v>1167</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -17903,10 +18092,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1135</v>
+        <v>1168</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1136</v>
+        <v>1169</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -17926,7 +18115,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1137</v>
+        <v>1170</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -17935,10 +18124,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1138</v>
+        <v>1171</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1139</v>
+        <v>1172</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -17958,7 +18147,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1140</v>
+        <v>1173</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -17967,10 +18156,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1141</v>
+        <v>1174</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1142</v>
+        <v>1175</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -17990,7 +18179,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1143</v>
+        <v>1176</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -17999,10 +18188,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1144</v>
+        <v>1177</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1145</v>
+        <v>1178</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -18022,7 +18211,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1146</v>
+        <v>1179</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -18031,10 +18220,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1147</v>
+        <v>1180</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1148</v>
+        <v>1181</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -18054,7 +18243,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1149</v>
+        <v>1182</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -18063,10 +18252,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1150</v>
+        <v>1183</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1151</v>
+        <v>1184</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -18086,7 +18275,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1152</v>
+        <v>1185</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -18095,10 +18284,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1153</v>
+        <v>1186</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1154</v>
+        <v>1187</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -18118,7 +18307,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1155</v>
+        <v>1188</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -18127,10 +18316,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1156</v>
+        <v>1189</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1157</v>
+        <v>1190</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -18150,7 +18339,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1158</v>
+        <v>1191</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -18159,10 +18348,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1159</v>
+        <v>1192</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1160</v>
+        <v>1193</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -18182,7 +18371,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1161</v>
+        <v>1194</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -18191,10 +18380,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1162</v>
+        <v>1195</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1163</v>
+        <v>1196</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -18214,7 +18403,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1164</v>
+        <v>1197</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -18223,10 +18412,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1165</v>
+        <v>1198</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1166</v>
+        <v>1199</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -18246,7 +18435,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1167</v>
+        <v>1200</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -18255,10 +18444,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1168</v>
+        <v>1201</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1169</v>
+        <v>1202</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -18278,7 +18467,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1170</v>
+        <v>1203</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -18287,10 +18476,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1171</v>
+        <v>1204</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1172</v>
+        <v>1205</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -18310,7 +18499,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -18319,10 +18508,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1174</v>
+        <v>1207</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1175</v>
+        <v>1208</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -18342,7 +18531,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1176</v>
+        <v>1209</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -18351,10 +18540,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1177</v>
+        <v>1210</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1178</v>
+        <v>1211</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -18374,7 +18563,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1179</v>
+        <v>1212</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -18383,10 +18572,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1180</v>
+        <v>1213</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1181</v>
+        <v>1214</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -18406,7 +18595,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1182</v>
+        <v>1215</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -18415,10 +18604,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1183</v>
+        <v>1216</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1184</v>
+        <v>1217</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -18438,7 +18627,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1185</v>
+        <v>1218</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -18447,10 +18636,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1186</v>
+        <v>1219</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1187</v>
+        <v>1220</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18470,7 +18659,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1188</v>
+        <v>1221</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18479,10 +18668,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1189</v>
+        <v>1222</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1190</v>
+        <v>1223</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18502,7 +18691,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1191</v>
+        <v>1224</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18511,10 +18700,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1192</v>
+        <v>1225</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1193</v>
+        <v>1226</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18534,7 +18723,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1194</v>
+        <v>1227</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -18543,10 +18732,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1195</v>
+        <v>1228</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1196</v>
+        <v>1229</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -18566,7 +18755,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1197</v>
+        <v>1230</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -18575,10 +18764,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1192</v>
+        <v>1225</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1198</v>
+        <v>1231</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -18598,7 +18787,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1199</v>
+        <v>1232</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -18607,10 +18796,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1200</v>
+        <v>1233</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1201</v>
+        <v>1234</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -18632,7 +18821,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1202</v>
+        <v>1235</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -18641,10 +18830,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1203</v>
+        <v>1236</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1204</v>
+        <v>1237</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -18664,7 +18853,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1205</v>
+        <v>1238</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18673,10 +18862,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1206</v>
+        <v>1239</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1207</v>
+        <v>1240</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18696,7 +18885,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1208</v>
+        <v>1241</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18705,10 +18894,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1209</v>
+        <v>1242</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1210</v>
+        <v>1243</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18728,7 +18917,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1211</v>
+        <v>1244</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18737,10 +18926,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1212</v>
+        <v>1245</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1213</v>
+        <v>1246</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -18760,7 +18949,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1214</v>
+        <v>1247</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -18769,10 +18958,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1215</v>
+        <v>1248</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1216</v>
+        <v>1249</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -18792,7 +18981,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1217</v>
+        <v>1250</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -18801,10 +18990,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1218</v>
+        <v>1251</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1219</v>
+        <v>1252</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -18824,7 +19013,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1220</v>
+        <v>1253</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -18833,10 +19022,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1221</v>
+        <v>1254</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1222</v>
+        <v>1255</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -18856,7 +19045,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1223</v>
+        <v>1256</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -18865,10 +19054,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1224</v>
+        <v>1257</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1225</v>
+        <v>1258</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -18888,7 +19077,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1226</v>
+        <v>1259</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -18897,10 +19086,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1227</v>
+        <v>1260</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1228</v>
+        <v>1261</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -18920,7 +19109,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1229</v>
+        <v>1262</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -18929,10 +19118,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1230</v>
+        <v>1263</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1231</v>
+        <v>1264</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -18954,7 +19143,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1232</v>
+        <v>1265</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -18963,10 +19152,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1233</v>
+        <v>1266</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1234</v>
+        <v>1267</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -18988,7 +19177,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1235</v>
+        <v>1268</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -18997,10 +19186,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1236</v>
+        <v>1269</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1237</v>
+        <v>1270</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -19022,7 +19211,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1238</v>
+        <v>1271</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -19031,10 +19220,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1239</v>
+        <v>1272</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1240</v>
+        <v>1273</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -19054,7 +19243,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1241</v>
+        <v>1274</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -19063,10 +19252,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1242</v>
+        <v>1275</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1243</v>
+        <v>1276</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -19086,7 +19275,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1244</v>
+        <v>1277</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -19095,10 +19284,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1245</v>
+        <v>1278</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1246</v>
+        <v>1279</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -19118,7 +19307,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1247</v>
+        <v>1280</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -19127,10 +19316,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1248</v>
+        <v>1281</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1249</v>
+        <v>1282</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -19152,7 +19341,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1250</v>
+        <v>1283</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -19164,7 +19353,7 @@
         <v>349</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1251</v>
+        <v>1284</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -19186,7 +19375,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1252</v>
+        <v>1285</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -19195,10 +19384,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1253</v>
+        <v>1286</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1254</v>
+        <v>1287</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -19218,7 +19407,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1255</v>
+        <v>1288</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -19227,10 +19416,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1256</v>
+        <v>1289</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1257</v>
+        <v>1290</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -19250,7 +19439,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1258</v>
+        <v>1291</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -19259,10 +19448,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1259</v>
+        <v>1292</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1260</v>
+        <v>1293</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -19282,7 +19471,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1261</v>
+        <v>1294</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -19291,10 +19480,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1262</v>
+        <v>1295</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1263</v>
+        <v>1296</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -19314,7 +19503,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1264</v>
+        <v>1297</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -19323,10 +19512,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1265</v>
+        <v>1298</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1265</v>
+        <v>1298</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -19341,14 +19530,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1266</v>
+        <v>1299</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1267</v>
+        <v>1300</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -19357,13 +19546,13 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1268</v>
+        <v>1301</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1269</v>
+        <v>1302</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>1270</v>
+        <v>1303</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>22</v>
@@ -19372,27 +19561,27 @@
         <v>2</v>
       </c>
       <c r="I419" s="3" t="s">
-        <v>1271</v>
+        <v>1304</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1272</v>
+        <v>1305</v>
       </c>
       <c r="K419" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L419" s="3" t="s">
-        <v>1273</v>
+        <v>1306</v>
       </c>
       <c r="M419" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N419" s="3" t="s">
-        <v>1274</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1275</v>
+        <v>1308</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -19401,13 +19590,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1276</v>
+        <v>1309</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1277</v>
+        <v>1310</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1278</v>
+        <v>1311</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -19416,25 +19605,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1279</v>
+        <v>1312</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1280</v>
+        <v>1313</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1281</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1282</v>
+        <v>1315</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -19443,13 +19632,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1283</v>
+        <v>1316</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1284</v>
+        <v>1317</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1285</v>
+        <v>1318</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -19458,25 +19647,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1286</v>
+        <v>1319</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1280</v>
+        <v>1313</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1287</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1288</v>
+        <v>1321</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19485,13 +19674,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1289</v>
+        <v>1322</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1290</v>
+        <v>1323</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1291</v>
+        <v>1324</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19500,25 +19689,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1292</v>
+        <v>1325</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1280</v>
+        <v>1313</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1293</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1294</v>
+        <v>1327</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19527,13 +19716,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1295</v>
+        <v>1328</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1296</v>
+        <v>1329</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1297</v>
+        <v>1330</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -19542,25 +19731,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1298</v>
+        <v>1331</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1280</v>
+        <v>1313</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1299</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1300</v>
+        <v>1333</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -19569,30 +19758,40 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1301</v>
+        <v>1334</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1302</v>
-      </c>
-      <c r="F424" s="3"/>
+        <v>1335</v>
+      </c>
+      <c r="F424" s="3" t="s">
+        <v>1336</v>
+      </c>
       <c r="G424" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H424" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I424" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I424" s="3" t="s">
+        <v>1337</v>
+      </c>
       <c r="J424" s="3"/>
       <c r="K424" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L424" s="3"/>
-      <c r="M424" s="3"/>
-      <c r="N424" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L424" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="M424" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N424" s="3" t="s">
+        <v>1339</v>
+      </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1303</v>
+        <v>1340</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -19601,10 +19800,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1304</v>
+        <v>1341</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1305</v>
+        <v>1342</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -19624,7 +19823,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1306</v>
+        <v>1343</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -19633,10 +19832,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1307</v>
+        <v>1344</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1308</v>
+        <v>1345</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -19656,7 +19855,7 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1309</v>
+        <v>1346</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -19665,10 +19864,10 @@
         <v>10</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1310</v>
+        <v>1347</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1311</v>
+        <v>1348</v>
       </c>
       <c r="F427" s="3"/>
       <c r="G427" s="3" t="s">
@@ -19688,7 +19887,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1312</v>
+        <v>1349</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19697,10 +19896,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1313</v>
+        <v>1350</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1314</v>
+        <v>1351</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19720,7 +19919,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1315</v>
+        <v>1352</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -19729,10 +19928,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1316</v>
+        <v>1353</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1317</v>
+        <v>1354</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -19752,7 +19951,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1318</v>
+        <v>1355</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -19761,10 +19960,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1319</v>
+        <v>1356</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1320</v>
+        <v>1357</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -19784,7 +19983,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1321</v>
+        <v>1358</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -19793,10 +19992,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1322</v>
+        <v>1359</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1323</v>
+        <v>1360</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -19816,7 +20015,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1324</v>
+        <v>1361</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -19825,10 +20024,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1325</v>
+        <v>1362</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1326</v>
+        <v>1363</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -19848,7 +20047,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1327</v>
+        <v>1364</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -19857,10 +20056,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1328</v>
+        <v>1365</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1329</v>
+        <v>1366</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -19880,7 +20079,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1330</v>
+        <v>1367</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -19889,10 +20088,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1331</v>
+        <v>1368</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1332</v>
+        <v>1369</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -19912,7 +20111,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1333</v>
+        <v>1370</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -19921,10 +20120,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1334</v>
+        <v>1371</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1335</v>
+        <v>1372</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -19944,7 +20143,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1336</v>
+        <v>1373</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -19953,10 +20152,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1337</v>
+        <v>1374</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1338</v>
+        <v>1375</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -19976,7 +20175,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1339</v>
+        <v>1376</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -19985,10 +20184,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1340</v>
+        <v>1377</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1341</v>
+        <v>1378</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -20008,7 +20207,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1342</v>
+        <v>1379</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -20017,13 +20216,13 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1343</v>
+        <v>1380</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1344</v>
+        <v>1381</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>1345</v>
+        <v>1382</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>22</v>
@@ -20032,27 +20231,27 @@
         <v>3</v>
       </c>
       <c r="I438" s="3" t="s">
-        <v>1346</v>
+        <v>1383</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1347</v>
+        <v>1384</v>
       </c>
       <c r="K438" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L438" s="3" t="s">
-        <v>1348</v>
+        <v>1385</v>
       </c>
       <c r="M438" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N438" s="3" t="s">
-        <v>1349</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1350</v>
+        <v>1387</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -20061,13 +20260,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1351</v>
+        <v>1388</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1352</v>
+        <v>1389</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1353</v>
+        <v>1390</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -20076,27 +20275,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1354</v>
+        <v>1391</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1355</v>
+        <v>1392</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1356</v>
+        <v>1393</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1357</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1358</v>
+        <v>1395</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -20105,13 +20304,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1359</v>
+        <v>1396</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1360</v>
+        <v>1397</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1361</v>
+        <v>1398</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -20120,27 +20319,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1362</v>
+        <v>1399</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1363</v>
+        <v>1400</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1364</v>
+        <v>1401</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1365</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1366</v>
+        <v>1403</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -20149,13 +20348,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1289</v>
+        <v>1322</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1367</v>
+        <v>1404</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1368</v>
+        <v>1405</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -20164,25 +20363,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1292</v>
+        <v>1325</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1369</v>
+        <v>1406</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1370</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1371</v>
+        <v>1408</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -20191,13 +20390,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1295</v>
+        <v>1328</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1372</v>
+        <v>1409</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1373</v>
+        <v>1410</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -20206,25 +20405,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1374</v>
+        <v>1411</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1375</v>
+        <v>1412</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1376</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1377</v>
+        <v>1414</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -20233,30 +20432,40 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1378</v>
+        <v>1415</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="F443" s="3"/>
+        <v>1416</v>
+      </c>
+      <c r="F443" s="3" t="s">
+        <v>1417</v>
+      </c>
       <c r="G443" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H443" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I443" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I443" s="3" t="s">
+        <v>1418</v>
+      </c>
       <c r="J443" s="3"/>
       <c r="K443" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L443" s="3"/>
-      <c r="M443" s="3"/>
-      <c r="N443" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L443" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="M443" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N443" s="3" t="s">
+        <v>1420</v>
+      </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1380</v>
+        <v>1421</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -20265,10 +20474,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1304</v>
+        <v>1341</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1381</v>
+        <v>1422</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -20288,7 +20497,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1382</v>
+        <v>1423</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -20297,10 +20506,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1307</v>
+        <v>1344</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1383</v>
+        <v>1424</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -20320,7 +20529,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1384</v>
+        <v>1425</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -20329,10 +20538,10 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1385</v>
+        <v>1426</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1386</v>
+        <v>1427</v>
       </c>
       <c r="F446" s="3"/>
       <c r="G446" s="3" t="s">
@@ -20352,7 +20561,7 @@
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1387</v>
+        <v>1428</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -20361,10 +20570,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1388</v>
+        <v>1429</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1389</v>
+        <v>1430</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -20384,7 +20593,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1390</v>
+        <v>1431</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -20393,10 +20602,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1392</v>
+        <v>1433</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -20416,7 +20625,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1393</v>
+        <v>1434</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -20425,10 +20634,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1394</v>
+        <v>1435</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1395</v>
+        <v>1436</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -20448,7 +20657,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1396</v>
+        <v>1437</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -20457,10 +20666,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1397</v>
+        <v>1438</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1398</v>
+        <v>1439</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -20480,7 +20689,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1399</v>
+        <v>1440</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -20489,10 +20698,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1400</v>
+        <v>1441</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1401</v>
+        <v>1442</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -20512,7 +20721,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1402</v>
+        <v>1443</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -20521,10 +20730,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1403</v>
+        <v>1444</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1404</v>
+        <v>1445</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -20544,7 +20753,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1405</v>
+        <v>1446</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -20553,10 +20762,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1406</v>
+        <v>1447</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1407</v>
+        <v>1448</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -20576,7 +20785,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1408</v>
+        <v>1449</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -20585,10 +20794,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1334</v>
+        <v>1371</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1409</v>
+        <v>1450</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -20608,7 +20817,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1410</v>
+        <v>1451</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -20617,10 +20826,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1411</v>
+        <v>1452</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -20640,7 +20849,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1413</v>
+        <v>1454</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -20649,10 +20858,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1414</v>
+        <v>1455</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1415</v>
+        <v>1456</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -20672,7 +20881,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1416</v>
+        <v>1457</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -20681,10 +20890,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1417</v>
+        <v>1458</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1418</v>
+        <v>1459</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -20704,7 +20913,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1419</v>
+        <v>1460</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -20713,10 +20922,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1420</v>
+        <v>1461</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1421</v>
+        <v>1462</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -20736,7 +20945,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1422</v>
+        <v>1463</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -20745,10 +20954,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1423</v>
+        <v>1464</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1424</v>
+        <v>1465</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -20768,7 +20977,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1425</v>
+        <v>1466</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -20777,10 +20986,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1426</v>
+        <v>1467</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1427</v>
+        <v>1468</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -20800,7 +21009,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1428</v>
+        <v>1469</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -20809,10 +21018,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1429</v>
+        <v>1470</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1430</v>
+        <v>1471</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -20832,7 +21041,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1431</v>
+        <v>1472</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -20841,13 +21050,13 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1432</v>
+        <v>1473</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1433</v>
+        <v>1474</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>1434</v>
+        <v>1475</v>
       </c>
       <c r="G462" s="3" t="s">
         <v>22</v>
@@ -20856,25 +21065,25 @@
         <v>2</v>
       </c>
       <c r="I462" s="3" t="s">
-        <v>1435</v>
+        <v>1476</v>
       </c>
       <c r="J462" s="3"/>
       <c r="K462" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L462" s="3" t="s">
-        <v>1436</v>
+        <v>1477</v>
       </c>
       <c r="M462" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N462" s="3" t="s">
-        <v>1437</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1438</v>
+        <v>1479</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -20883,13 +21092,13 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1439</v>
+        <v>1480</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1440</v>
+        <v>1481</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>1441</v>
+        <v>1482</v>
       </c>
       <c r="G463" s="3" t="s">
         <v>22</v>
@@ -20898,27 +21107,27 @@
         <v>3</v>
       </c>
       <c r="I463" s="3" t="s">
-        <v>1442</v>
+        <v>1483</v>
       </c>
       <c r="J463" s="3" t="s">
-        <v>1443</v>
+        <v>1484</v>
       </c>
       <c r="K463" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L463" s="3" t="s">
-        <v>1444</v>
+        <v>1485</v>
       </c>
       <c r="M463" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N463" s="3" t="s">
-        <v>1445</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1446</v>
+        <v>1487</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -20927,10 +21136,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1447</v>
+        <v>1488</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1448</v>
+        <v>1489</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -20950,7 +21159,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1449</v>
+        <v>1490</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -20959,10 +21168,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1450</v>
+        <v>1491</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1451</v>
+        <v>1492</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -20977,7 +21186,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1452</v>
+        <v>1493</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="1494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1511">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -1589,6 +1589,24 @@
     <t xml:space="preserve">Weekend 01 - 27-28 Jun/AI_Industry_Handbook_2026.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">22-page business guide to AI in ten industries (ET Masterclass), marked Not for redistribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 1 › 1.8 (short description only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics, company profiles, role table, tool list and 30-day plan deliberately not copied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your choice: short original summary, no statistics or company claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marked 'Not for redistribution'; third-party marketing figures not verified</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC137</t>
   </si>
   <si>
@@ -1823,6 +1841,12 @@
     <t xml:space="preserve">Weekend 02 - 4-5 Jul/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Weekend 02 navigation page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation only; repeats the class 03 and 04 summaries</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC151</t>
   </si>
   <si>
@@ -4073,6 +4097,18 @@
     <t xml:space="preserve">classes_summary/08 - 19 Jul - Inside the Model.md</t>
   </si>
   <si>
+    <t xml:space="preserve">LangChain model layer: parameters, messages, AIMessage, streaming, batching, bind_tools, ToolMessage, structured output, prompt templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 3 (3.1 to 3.7), Ch 4 (4.1 to 4.4), Ch 5 (5.1, 5.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain chapters 3 to 5 were empty; moved here from the LLM book at your instruction ('Add in langchain')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run: LangChain not installed, calls need keys. Notebooks named in the summary were not opened. Class 07's first model calls will be added to Ch 3 later</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC427</t>
   </si>
   <si>
@@ -4308,6 +4344,21 @@
   </si>
   <si>
     <t xml:space="preserve">classes_transcription_summary/08 - 19 Jul - LangChain - Inside the Model.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 08 transcript: parameters, free vs paid limits, messages, few-shot story, streaming, batching, bind_tools, structured output, long Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 3 (3.2, 3.3, 3.5, 3.6, 3.8); Ch 4; Ch 5 › 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routing between specialised agents and the memory.md pattern are noted in Ch 3 but belong to the multi-agent and agents-and-memory chapters; freelancing Q&amp;A left out as off-topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the 2,000-word streaming demo, few-shot story, batching cost answer, Q&amp;A, ToolMessage walkthrough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-tier limits (20/min, 50/day) and the 50% batch price are the class's figures; check current ones</t>
   </si>
   <si>
     <t xml:space="preserve">LC446</t>
@@ -5045,11 +5096,11 @@
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,C$3)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,D$3)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,E$3)</f>
@@ -5057,11 +5108,11 @@
       </c>
       <c r="F6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,F$3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
         <f aca="false">SUM(B6:F6)</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3"/>
     </row>
@@ -5071,11 +5122,11 @@
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,B$3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,C$3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,D$3)</f>
@@ -5091,7 +5142,7 @@
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">SUM(B7:F7)</f>
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -5191,15 +5242,15 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -5207,7 +5258,7 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">SUM(G4:G10)</f>
@@ -5245,7 +5296,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -5260,7 +5311,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -5275,7 +5326,7 @@
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A16)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -5305,7 +5356,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5320,7 +5371,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5335,7 +5386,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -10201,25 +10252,37 @@
       <c r="E137" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="F137" s="3"/>
+      <c r="F137" s="3" t="s">
+        <v>521</v>
+      </c>
       <c r="G137" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I137" s="3"/>
-      <c r="J137" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>523</v>
+      </c>
       <c r="K137" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L137" s="3"/>
-      <c r="M137" s="3"/>
-      <c r="N137" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N137" s="3" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>38</v>
@@ -10231,10 +10294,10 @@
         <v>58</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>22</v>
@@ -10244,24 +10307,24 @@
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="K138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="M138" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>38</v>
@@ -10273,7 +10336,7 @@
         <v>45</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
@@ -10292,12 +10355,12 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>38</v>
@@ -10309,10 +10372,10 @@
         <v>58</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>22</v>
@@ -10321,14 +10384,14 @@
         <v>2</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="J140" s="3"/>
       <c r="K140" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="M140" s="3" t="s">
         <v>52</v>
@@ -10337,7 +10400,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>38</v>
@@ -10346,13 +10409,13 @@
         <v>10</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>22</v>
@@ -10361,14 +10424,14 @@
         <v>2</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J141" s="3"/>
       <c r="K141" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M141" s="3" t="s">
         <v>52</v>
@@ -10377,7 +10440,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>38</v>
@@ -10386,13 +10449,13 @@
         <v>10</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>22</v>
@@ -10401,25 +10464,25 @@
         <v>2</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="J142" s="3"/>
       <c r="K142" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="M142" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N142" s="3" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>38</v>
@@ -10428,13 +10491,13 @@
         <v>9</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
@@ -10443,25 +10506,25 @@
         <v>2</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="M143" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>38</v>
@@ -10470,13 +10533,13 @@
         <v>10</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>22</v>
@@ -10485,25 +10548,25 @@
         <v>2</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="J144" s="3"/>
       <c r="K144" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="M144" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N144" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>38</v>
@@ -10512,13 +10575,13 @@
         <v>10</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>22</v>
@@ -10527,25 +10590,25 @@
         <v>2</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="J145" s="3"/>
       <c r="K145" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="M145" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N145" s="3" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>38</v>
@@ -10554,13 +10617,13 @@
         <v>10</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>22</v>
@@ -10569,25 +10632,25 @@
         <v>2</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="J146" s="3"/>
       <c r="K146" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="M146" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N146" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>38</v>
@@ -10596,13 +10659,13 @@
         <v>10</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>22</v>
@@ -10611,25 +10674,25 @@
         <v>2</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="M147" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N147" s="3" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>38</v>
@@ -10638,13 +10701,13 @@
         <v>10</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>22</v>
@@ -10653,25 +10716,25 @@
         <v>2</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="J148" s="3"/>
       <c r="K148" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M148" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N148" s="3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>38</v>
@@ -10683,7 +10746,7 @@
         <v>77</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
@@ -10702,12 +10765,12 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>38</v>
@@ -10719,10 +10782,10 @@
         <v>58</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>22</v>
@@ -10731,14 +10794,14 @@
         <v>2</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J150" s="3"/>
       <c r="K150" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="M150" s="3" t="s">
         <v>52</v>
@@ -10747,7 +10810,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>38</v>
@@ -10759,29 +10822,33 @@
         <v>58</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="F151" s="3"/>
+        <v>604</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>605</v>
+      </c>
       <c r="G151" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3" t="s">
-        <v>529</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L151" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="M151" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N151" s="3"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>38</v>
@@ -10793,7 +10860,7 @@
         <v>367</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="3" t="s">
@@ -10813,7 +10880,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -10825,7 +10892,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -10847,7 +10914,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10859,7 +10926,7 @@
         <v>69</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10881,7 +10948,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
@@ -10890,10 +10957,10 @@
         <v>11</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
@@ -10913,7 +10980,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10925,7 +10992,7 @@
         <v>58</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="3" t="s">
@@ -10945,7 +11012,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -10954,10 +11021,10 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
@@ -10977,7 +11044,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -10986,10 +11053,10 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -11009,7 +11076,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -11018,10 +11085,10 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
@@ -11041,7 +11108,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -11053,7 +11120,7 @@
         <v>130</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
@@ -11073,7 +11140,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -11085,7 +11152,7 @@
         <v>77</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -11107,7 +11174,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -11119,7 +11186,7 @@
         <v>89</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -11141,7 +11208,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -11153,7 +11220,7 @@
         <v>58</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
@@ -11173,7 +11240,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -11185,7 +11252,7 @@
         <v>367</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -11202,12 +11269,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -11219,7 +11286,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -11238,12 +11305,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -11255,7 +11322,7 @@
         <v>69</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -11274,12 +11341,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -11288,10 +11355,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -11308,12 +11375,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -11322,10 +11389,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -11342,12 +11409,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -11356,10 +11423,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -11376,12 +11443,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -11390,10 +11457,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -11410,12 +11477,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -11424,10 +11491,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -11444,12 +11511,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -11458,10 +11525,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -11478,12 +11545,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -11495,7 +11562,7 @@
         <v>58</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -11512,12 +11579,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -11529,7 +11596,7 @@
         <v>130</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -11546,12 +11613,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -11563,7 +11630,7 @@
         <v>77</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -11582,12 +11649,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -11599,7 +11666,7 @@
         <v>349</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -11618,12 +11685,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -11635,7 +11702,7 @@
         <v>89</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -11654,12 +11721,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11668,10 +11735,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11688,12 +11755,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11702,10 +11769,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -11722,12 +11789,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -11736,10 +11803,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -11756,12 +11823,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -11770,10 +11837,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -11790,12 +11857,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -11804,10 +11871,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -11824,12 +11891,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -11838,10 +11905,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11858,12 +11925,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11875,7 +11942,7 @@
         <v>58</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11892,12 +11959,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11909,7 +11976,7 @@
         <v>58</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11926,12 +11993,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -11940,10 +12007,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -11960,12 +12027,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -11974,10 +12041,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -11994,12 +12061,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -12008,10 +12075,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -12028,12 +12095,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -12042,10 +12109,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -12062,12 +12129,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -12076,10 +12143,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -12096,12 +12163,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -12110,10 +12177,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -12130,12 +12197,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -12144,10 +12211,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -12164,12 +12231,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -12178,10 +12245,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -12198,12 +12265,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -12212,10 +12279,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -12232,12 +12299,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -12249,7 +12316,7 @@
         <v>58</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -12266,12 +12333,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -12283,7 +12350,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -12300,12 +12367,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -12314,10 +12381,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -12339,7 +12406,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -12348,10 +12415,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -12371,7 +12438,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -12380,10 +12447,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -12403,7 +12470,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -12412,10 +12479,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -12435,7 +12502,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -12444,10 +12511,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -12467,7 +12534,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -12476,10 +12543,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -12499,7 +12566,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -12511,7 +12578,7 @@
         <v>58</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -12531,7 +12598,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -12543,7 +12610,7 @@
         <v>58</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -12563,7 +12630,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -12572,10 +12639,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -12597,7 +12664,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -12606,10 +12673,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -12629,7 +12696,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -12638,10 +12705,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12663,7 +12730,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12672,10 +12739,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12695,7 +12762,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12707,7 +12774,7 @@
         <v>58</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -12727,7 +12794,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -12739,7 +12806,7 @@
         <v>58</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -12759,7 +12826,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -12771,7 +12838,7 @@
         <v>58</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -12791,7 +12858,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -12800,10 +12867,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -12825,7 +12892,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -12834,10 +12901,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12857,7 +12924,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12866,10 +12933,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12889,7 +12956,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12901,7 +12968,7 @@
         <v>55</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12921,7 +12988,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12930,10 +12997,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -12953,7 +13020,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -12965,7 +13032,7 @@
         <v>212</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -12985,7 +13052,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -12997,7 +13064,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -13019,7 +13086,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -13031,7 +13098,7 @@
         <v>69</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -13053,7 +13120,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -13065,7 +13132,7 @@
         <v>58</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -13085,7 +13152,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -13097,7 +13164,7 @@
         <v>77</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -13119,7 +13186,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -13131,7 +13198,7 @@
         <v>80</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -13151,7 +13218,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -13163,7 +13230,7 @@
         <v>86</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -13183,7 +13250,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -13195,7 +13262,7 @@
         <v>89</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -13217,7 +13284,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -13229,7 +13296,7 @@
         <v>265</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -13249,7 +13316,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -13261,7 +13328,7 @@
         <v>58</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -13281,7 +13348,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -13293,7 +13360,7 @@
         <v>58</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -13313,7 +13380,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -13322,10 +13389,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -13345,7 +13412,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -13354,10 +13421,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -13377,7 +13444,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -13386,10 +13453,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -13409,7 +13476,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -13418,10 +13485,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -13441,7 +13508,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -13453,7 +13520,7 @@
         <v>58</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -13473,7 +13540,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -13482,10 +13549,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -13507,7 +13574,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -13519,7 +13586,7 @@
         <v>259</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -13539,7 +13606,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -13551,7 +13618,7 @@
         <v>262</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -13571,7 +13638,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -13580,10 +13647,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -13603,7 +13670,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -13615,7 +13682,7 @@
         <v>58</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -13635,7 +13702,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -13647,7 +13714,7 @@
         <v>58</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13667,7 +13734,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13679,7 +13746,7 @@
         <v>61</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13699,7 +13766,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13711,7 +13778,7 @@
         <v>64</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -13731,7 +13798,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -13743,7 +13810,7 @@
         <v>58</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -13763,7 +13830,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -13775,7 +13842,7 @@
         <v>69</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -13797,7 +13864,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -13809,7 +13876,7 @@
         <v>58</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -13829,7 +13896,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -13841,7 +13908,7 @@
         <v>127</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13861,7 +13928,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13873,7 +13940,7 @@
         <v>130</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13893,7 +13960,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13905,7 +13972,7 @@
         <v>151</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13925,7 +13992,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -13937,7 +14004,7 @@
         <v>77</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -13959,7 +14026,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -13971,7 +14038,7 @@
         <v>193</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -13991,7 +14058,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -14003,7 +14070,7 @@
         <v>196</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -14025,7 +14092,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -14037,7 +14104,7 @@
         <v>199</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -14059,7 +14126,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -14071,7 +14138,7 @@
         <v>135</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -14093,7 +14160,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -14105,7 +14172,7 @@
         <v>89</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -14127,7 +14194,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -14139,7 +14206,7 @@
         <v>209</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -14159,7 +14226,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -14171,7 +14238,7 @@
         <v>69</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -14193,7 +14260,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -14205,7 +14272,7 @@
         <v>58</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -14225,7 +14292,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -14237,7 +14304,7 @@
         <v>222</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -14259,7 +14326,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -14271,7 +14338,7 @@
         <v>130</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -14291,7 +14358,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -14303,7 +14370,7 @@
         <v>77</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -14325,7 +14392,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -14337,7 +14404,7 @@
         <v>61</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -14357,7 +14424,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -14369,7 +14436,7 @@
         <v>64</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -14389,7 +14456,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -14401,7 +14468,7 @@
         <v>89</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -14423,7 +14490,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -14435,7 +14502,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -14457,7 +14524,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -14469,7 +14536,7 @@
         <v>69</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -14491,7 +14558,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -14503,7 +14570,7 @@
         <v>58</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -14523,7 +14590,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -14535,7 +14602,7 @@
         <v>74</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -14555,7 +14622,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -14567,7 +14634,7 @@
         <v>77</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -14589,7 +14656,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -14601,7 +14668,7 @@
         <v>80</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -14621,7 +14688,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -14633,7 +14700,7 @@
         <v>83</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -14653,7 +14720,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14665,7 +14732,7 @@
         <v>86</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14685,7 +14752,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14697,7 +14764,7 @@
         <v>89</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14719,7 +14786,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -14731,7 +14798,7 @@
         <v>58</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -14751,7 +14818,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -14763,7 +14830,7 @@
         <v>69</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -14785,7 +14852,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -14794,10 +14861,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -14817,7 +14884,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -14829,7 +14896,7 @@
         <v>58</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -14849,7 +14916,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14858,10 +14925,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14881,7 +14948,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14893,7 +14960,7 @@
         <v>130</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14913,7 +14980,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14925,7 +14992,7 @@
         <v>77</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -14947,7 +15014,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -14959,7 +15026,7 @@
         <v>89</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -14981,7 +15048,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -14993,7 +15060,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -15012,12 +15079,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -15026,10 +15093,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -15046,12 +15113,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -15060,10 +15127,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -15080,12 +15147,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -15094,10 +15161,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -15116,12 +15183,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -15130,10 +15197,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -15150,12 +15217,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -15164,10 +15231,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -15186,12 +15253,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -15200,10 +15267,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -15220,12 +15287,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -15234,10 +15301,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -15256,12 +15323,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -15270,10 +15337,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -15290,12 +15357,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -15307,7 +15374,7 @@
         <v>77</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -15326,12 +15393,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -15343,7 +15410,7 @@
         <v>89</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -15362,12 +15429,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -15379,7 +15446,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -15401,7 +15468,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -15410,10 +15477,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -15433,7 +15500,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -15442,10 +15509,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -15465,7 +15532,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -15474,10 +15541,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -15497,7 +15564,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -15506,10 +15573,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -15529,7 +15596,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -15538,10 +15605,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -15561,7 +15628,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -15570,10 +15637,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -15593,7 +15660,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -15605,7 +15672,7 @@
         <v>58</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -15625,7 +15692,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -15637,7 +15704,7 @@
         <v>77</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15659,7 +15726,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15668,10 +15735,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15691,7 +15758,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15703,7 +15770,7 @@
         <v>89</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -15725,7 +15792,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -15734,10 +15801,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -15759,7 +15826,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -15768,10 +15835,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -15793,7 +15860,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -15805,7 +15872,7 @@
         <v>367</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -15825,7 +15892,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -15834,10 +15901,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15859,7 +15926,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15871,7 +15938,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15893,7 +15960,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15902,10 +15969,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15925,7 +15992,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -15934,10 +16001,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -15959,7 +16026,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -15971,7 +16038,7 @@
         <v>58</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -15991,7 +16058,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -16003,7 +16070,7 @@
         <v>86</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -16023,7 +16090,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -16032,10 +16099,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -16055,7 +16122,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -16064,10 +16131,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -16087,7 +16154,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -16099,7 +16166,7 @@
         <v>361</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -16119,7 +16186,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -16131,7 +16198,7 @@
         <v>86</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -16151,7 +16218,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -16160,10 +16227,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -16183,7 +16250,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -16195,7 +16262,7 @@
         <v>130</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -16215,7 +16282,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -16224,10 +16291,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -16247,7 +16314,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -16259,7 +16326,7 @@
         <v>86</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -16279,7 +16346,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -16288,10 +16355,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -16311,7 +16378,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -16323,7 +16390,7 @@
         <v>86</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -16343,7 +16410,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -16352,10 +16419,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -16375,7 +16442,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -16387,7 +16454,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -16407,7 +16474,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -16416,10 +16483,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -16439,7 +16506,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -16448,10 +16515,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -16471,7 +16538,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -16480,10 +16547,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -16503,7 +16570,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -16512,10 +16579,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -16535,7 +16602,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -16544,10 +16611,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -16567,7 +16634,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -16576,10 +16643,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -16599,7 +16666,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -16608,10 +16675,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -16631,7 +16698,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -16640,10 +16707,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16665,7 +16732,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16674,10 +16741,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16699,7 +16766,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16708,10 +16775,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -16731,7 +16798,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -16743,7 +16810,7 @@
         <v>196</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -16765,7 +16832,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -16774,10 +16841,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -16799,7 +16866,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -16808,10 +16875,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -16833,7 +16900,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -16842,10 +16909,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16865,7 +16932,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16874,10 +16941,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16897,7 +16964,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16906,10 +16973,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16929,7 +16996,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -16938,10 +17005,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -16963,7 +17030,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -16972,10 +17039,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -16995,7 +17062,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -17004,10 +17071,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -17027,7 +17094,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -17036,10 +17103,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -17059,7 +17126,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -17068,10 +17135,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -17091,7 +17158,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -17100,10 +17167,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -17123,7 +17190,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -17132,10 +17199,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -17155,7 +17222,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -17164,10 +17231,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -17187,7 +17254,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -17196,10 +17263,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -17219,7 +17286,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -17228,10 +17295,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -17251,7 +17318,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -17260,10 +17327,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -17283,7 +17350,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -17292,10 +17359,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -17315,7 +17382,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -17324,10 +17391,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -17347,7 +17414,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -17356,10 +17423,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -17379,7 +17446,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -17388,10 +17455,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -17411,7 +17478,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -17420,10 +17487,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -17443,7 +17510,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -17452,10 +17519,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -17475,7 +17542,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -17484,10 +17551,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -17507,7 +17574,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -17516,10 +17583,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -17539,7 +17606,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -17548,10 +17615,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -17571,7 +17638,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -17580,10 +17647,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -17603,7 +17670,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -17612,10 +17679,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -17635,7 +17702,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -17644,10 +17711,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17667,7 +17734,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17676,10 +17743,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17699,7 +17766,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17708,10 +17775,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -17731,7 +17798,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -17740,10 +17807,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -17763,7 +17830,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -17772,10 +17839,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -17795,7 +17862,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -17804,10 +17871,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -17827,7 +17894,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -17836,10 +17903,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17859,7 +17926,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17868,10 +17935,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17891,7 +17958,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17900,10 +17967,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17923,7 +17990,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17932,10 +17999,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -17955,7 +18022,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -17964,10 +18031,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -17987,7 +18054,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -17996,10 +18063,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -18019,7 +18086,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -18028,10 +18095,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -18051,7 +18118,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -18060,10 +18127,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -18083,7 +18150,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -18092,10 +18159,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -18115,7 +18182,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -18124,10 +18191,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -18147,7 +18214,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -18156,10 +18223,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -18179,7 +18246,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -18188,10 +18255,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -18211,7 +18278,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -18220,10 +18287,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -18243,7 +18310,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -18252,10 +18319,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -18275,7 +18342,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -18284,10 +18351,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -18307,7 +18374,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -18316,10 +18383,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -18339,7 +18406,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -18348,10 +18415,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -18371,7 +18438,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -18380,10 +18447,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -18403,7 +18470,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -18412,10 +18479,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -18435,7 +18502,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -18444,10 +18511,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -18467,7 +18534,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -18476,10 +18543,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -18499,7 +18566,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -18508,10 +18575,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -18531,7 +18598,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -18540,10 +18607,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -18563,7 +18630,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -18572,10 +18639,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -18595,7 +18662,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -18604,10 +18671,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -18627,7 +18694,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -18636,10 +18703,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18659,7 +18726,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18668,10 +18735,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18691,7 +18758,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18700,10 +18767,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18723,7 +18790,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -18732,10 +18799,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -18755,7 +18822,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -18764,10 +18831,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -18787,7 +18854,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -18796,10 +18863,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -18821,7 +18888,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -18830,10 +18897,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -18853,7 +18920,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18862,10 +18929,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18885,7 +18952,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18894,10 +18961,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18917,7 +18984,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18926,10 +18993,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -18949,7 +19016,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -18958,10 +19025,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -18981,7 +19048,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -18990,10 +19057,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -19013,7 +19080,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -19022,10 +19089,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -19045,7 +19112,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -19054,10 +19121,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -19077,7 +19144,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -19086,10 +19153,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -19109,7 +19176,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -19118,10 +19185,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -19143,7 +19210,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -19152,10 +19219,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -19177,7 +19244,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -19186,10 +19253,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -19211,7 +19278,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -19220,10 +19287,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -19243,7 +19310,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -19252,10 +19319,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -19275,7 +19342,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -19284,10 +19351,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -19307,7 +19374,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -19316,10 +19383,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -19341,7 +19408,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -19353,7 +19420,7 @@
         <v>349</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -19375,7 +19442,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -19384,10 +19451,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -19407,7 +19474,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -19416,10 +19483,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -19439,7 +19506,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -19448,10 +19515,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -19471,7 +19538,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -19480,10 +19547,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -19503,7 +19570,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -19512,10 +19579,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -19530,14 +19597,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -19546,13 +19613,13 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>22</v>
@@ -19561,27 +19628,27 @@
         <v>2</v>
       </c>
       <c r="I419" s="3" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="K419" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L419" s="3" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="M419" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N419" s="3" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -19590,13 +19657,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -19605,25 +19672,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -19632,13 +19699,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -19647,25 +19714,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19674,13 +19741,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19689,25 +19756,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19716,13 +19783,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -19731,25 +19798,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -19758,13 +19825,13 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="G424" s="3" t="s">
         <v>22</v>
@@ -19773,25 +19840,25 @@
         <v>2</v>
       </c>
       <c r="I424" s="3" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="J424" s="3"/>
       <c r="K424" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L424" s="3" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="M424" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N424" s="3" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -19800,10 +19867,10 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="F425" s="3"/>
       <c r="G425" s="3" t="s">
@@ -19823,7 +19890,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -19832,10 +19899,10 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="F426" s="3"/>
       <c r="G426" s="3" t="s">
@@ -19855,39 +19922,49 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="F427" s="3"/>
+        <v>1356</v>
+      </c>
+      <c r="F427" s="3" t="s">
+        <v>1357</v>
+      </c>
       <c r="G427" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H427" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I427" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I427" s="3" t="s">
+        <v>1358</v>
+      </c>
       <c r="J427" s="3"/>
       <c r="K427" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L427" s="3"/>
-      <c r="M427" s="3"/>
-      <c r="N427" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L427" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M427" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N427" s="3" t="s">
+        <v>1360</v>
+      </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1349</v>
+        <v>1361</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19896,10 +19973,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1350</v>
+        <v>1362</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1351</v>
+        <v>1363</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19919,7 +19996,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1352</v>
+        <v>1364</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -19928,10 +20005,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1353</v>
+        <v>1365</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1354</v>
+        <v>1366</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -19951,7 +20028,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1355</v>
+        <v>1367</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -19960,10 +20037,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1356</v>
+        <v>1368</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1357</v>
+        <v>1369</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -19983,7 +20060,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1358</v>
+        <v>1370</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -19992,10 +20069,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1359</v>
+        <v>1371</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1360</v>
+        <v>1372</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -20015,7 +20092,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -20024,10 +20101,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1362</v>
+        <v>1374</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1363</v>
+        <v>1375</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -20047,7 +20124,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1364</v>
+        <v>1376</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -20056,10 +20133,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1366</v>
+        <v>1378</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -20079,7 +20156,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -20088,10 +20165,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1368</v>
+        <v>1380</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -20111,7 +20188,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1370</v>
+        <v>1382</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -20120,10 +20197,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1371</v>
+        <v>1383</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1372</v>
+        <v>1384</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -20143,7 +20220,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1373</v>
+        <v>1385</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -20152,10 +20229,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1374</v>
+        <v>1386</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1375</v>
+        <v>1387</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -20175,7 +20252,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -20184,10 +20261,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1377</v>
+        <v>1389</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -20207,7 +20284,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1379</v>
+        <v>1391</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -20216,13 +20293,13 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1381</v>
+        <v>1393</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>1382</v>
+        <v>1394</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>22</v>
@@ -20231,27 +20308,27 @@
         <v>3</v>
       </c>
       <c r="I438" s="3" t="s">
-        <v>1383</v>
+        <v>1395</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1384</v>
+        <v>1396</v>
       </c>
       <c r="K438" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L438" s="3" t="s">
-        <v>1385</v>
+        <v>1397</v>
       </c>
       <c r="M438" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N438" s="3" t="s">
-        <v>1386</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -20260,13 +20337,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1388</v>
+        <v>1400</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1389</v>
+        <v>1401</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1390</v>
+        <v>1402</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -20275,27 +20352,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1392</v>
+        <v>1404</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1393</v>
+        <v>1405</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1394</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -20304,13 +20381,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1396</v>
+        <v>1408</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1397</v>
+        <v>1409</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -20319,27 +20396,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1401</v>
+        <v>1413</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1402</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1403</v>
+        <v>1415</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -20348,13 +20425,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1404</v>
+        <v>1416</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1405</v>
+        <v>1417</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -20363,25 +20440,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1406</v>
+        <v>1418</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1407</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1408</v>
+        <v>1420</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -20390,13 +20467,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1409</v>
+        <v>1421</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1410</v>
+        <v>1422</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -20405,25 +20482,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1411</v>
+        <v>1423</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1412</v>
+        <v>1424</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1413</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1414</v>
+        <v>1426</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -20432,13 +20509,13 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1415</v>
+        <v>1427</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1416</v>
+        <v>1428</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>1417</v>
+        <v>1429</v>
       </c>
       <c r="G443" s="3" t="s">
         <v>22</v>
@@ -20447,25 +20524,25 @@
         <v>2</v>
       </c>
       <c r="I443" s="3" t="s">
-        <v>1418</v>
+        <v>1430</v>
       </c>
       <c r="J443" s="3"/>
       <c r="K443" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L443" s="3" t="s">
-        <v>1419</v>
+        <v>1431</v>
       </c>
       <c r="M443" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N443" s="3" t="s">
-        <v>1420</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1421</v>
+        <v>1433</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -20474,10 +20551,10 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1422</v>
+        <v>1434</v>
       </c>
       <c r="F444" s="3"/>
       <c r="G444" s="3" t="s">
@@ -20497,7 +20574,7 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1423</v>
+        <v>1435</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -20506,10 +20583,10 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1424</v>
+        <v>1436</v>
       </c>
       <c r="F445" s="3"/>
       <c r="G445" s="3" t="s">
@@ -20529,39 +20606,51 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1425</v>
+        <v>1437</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1426</v>
+        <v>1438</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F446" s="3"/>
+        <v>1439</v>
+      </c>
+      <c r="F446" s="3" t="s">
+        <v>1440</v>
+      </c>
       <c r="G446" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H446" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I446" s="3"/>
-      <c r="J446" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I446" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J446" s="3" t="s">
+        <v>1442</v>
+      </c>
       <c r="K446" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L446" s="3"/>
-      <c r="M446" s="3"/>
-      <c r="N446" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L446" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="M446" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N446" s="3" t="s">
+        <v>1444</v>
+      </c>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1428</v>
+        <v>1445</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -20570,10 +20659,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1429</v>
+        <v>1446</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1430</v>
+        <v>1447</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -20593,7 +20682,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1431</v>
+        <v>1448</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -20602,10 +20691,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1432</v>
+        <v>1449</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -20625,7 +20714,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1434</v>
+        <v>1451</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -20634,10 +20723,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1435</v>
+        <v>1452</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1436</v>
+        <v>1453</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -20657,7 +20746,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1437</v>
+        <v>1454</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -20666,10 +20755,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1438</v>
+        <v>1455</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1439</v>
+        <v>1456</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -20689,7 +20778,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1440</v>
+        <v>1457</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -20698,10 +20787,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1441</v>
+        <v>1458</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1442</v>
+        <v>1459</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -20721,7 +20810,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1443</v>
+        <v>1460</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -20730,10 +20819,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1444</v>
+        <v>1461</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1445</v>
+        <v>1462</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -20753,7 +20842,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1446</v>
+        <v>1463</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -20762,10 +20851,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1447</v>
+        <v>1464</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1448</v>
+        <v>1465</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -20785,7 +20874,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1449</v>
+        <v>1466</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -20794,10 +20883,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1371</v>
+        <v>1383</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1450</v>
+        <v>1467</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -20817,7 +20906,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1451</v>
+        <v>1468</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -20826,10 +20915,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1452</v>
+        <v>1469</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1453</v>
+        <v>1470</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -20849,7 +20938,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1454</v>
+        <v>1471</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -20858,10 +20947,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1455</v>
+        <v>1472</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1456</v>
+        <v>1473</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -20881,7 +20970,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1457</v>
+        <v>1474</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -20890,10 +20979,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1458</v>
+        <v>1475</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1459</v>
+        <v>1476</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -20913,7 +21002,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1460</v>
+        <v>1477</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -20922,10 +21011,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1461</v>
+        <v>1478</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1462</v>
+        <v>1479</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -20945,7 +21034,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1463</v>
+        <v>1480</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -20954,10 +21043,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1464</v>
+        <v>1481</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1465</v>
+        <v>1482</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -20977,7 +21066,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1466</v>
+        <v>1483</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -20986,10 +21075,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1467</v>
+        <v>1484</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1468</v>
+        <v>1485</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -21009,7 +21098,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1469</v>
+        <v>1486</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -21018,10 +21107,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1470</v>
+        <v>1487</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1471</v>
+        <v>1488</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -21041,7 +21130,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1472</v>
+        <v>1489</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -21050,13 +21139,13 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1473</v>
+        <v>1490</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1474</v>
+        <v>1491</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>1475</v>
+        <v>1492</v>
       </c>
       <c r="G462" s="3" t="s">
         <v>22</v>
@@ -21065,25 +21154,25 @@
         <v>2</v>
       </c>
       <c r="I462" s="3" t="s">
-        <v>1476</v>
+        <v>1493</v>
       </c>
       <c r="J462" s="3"/>
       <c r="K462" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L462" s="3" t="s">
-        <v>1477</v>
+        <v>1494</v>
       </c>
       <c r="M462" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N462" s="3" t="s">
-        <v>1478</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1479</v>
+        <v>1496</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -21092,13 +21181,13 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1480</v>
+        <v>1497</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1481</v>
+        <v>1498</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>1482</v>
+        <v>1499</v>
       </c>
       <c r="G463" s="3" t="s">
         <v>22</v>
@@ -21107,27 +21196,27 @@
         <v>3</v>
       </c>
       <c r="I463" s="3" t="s">
-        <v>1483</v>
+        <v>1500</v>
       </c>
       <c r="J463" s="3" t="s">
-        <v>1484</v>
+        <v>1501</v>
       </c>
       <c r="K463" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L463" s="3" t="s">
-        <v>1485</v>
+        <v>1502</v>
       </c>
       <c r="M463" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N463" s="3" t="s">
-        <v>1486</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1487</v>
+        <v>1504</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -21136,10 +21225,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1488</v>
+        <v>1505</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1489</v>
+        <v>1506</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -21159,7 +21248,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1490</v>
+        <v>1507</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -21168,10 +21257,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1491</v>
+        <v>1508</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1492</v>
+        <v>1509</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -21186,7 +21275,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1493</v>
+        <v>1510</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4230" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4289" uniqueCount="1556">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -1853,6 +1853,18 @@
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/.env.example</t>
   </si>
   <si>
+    <t xml:space="preserve">Five empty key lines: OpenAI, Groq, Anthropic, Gemini, OpenRouter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 1 › 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set-up note in Ch 1 lists the five keys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked for secrets: values are empty</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC152</t>
   </si>
   <si>
@@ -1874,12 +1886,36 @@
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/Agentic-Python.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 05 whiteboard: question, chatbot, agent, paid vs free providers, tool schema, drop_user joke, GitHub push-blocked screenshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM › Ch 2 › 2.1, 2.3; Langchain › Ch 1 › 1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The meaning of the drop_user joke is not written on the slide (my reading is marked in the chapter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added provider credits, tool-name clarity, decision fork, push-blocked note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiteboard PDF: read text and viewed the page. Placed the GitHub screenshot in Langchain Ch 1, not LLM Ch 2 as planned, because it concerns keys</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC155</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 06 folder overview and file table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeats the class 06 summary and the same file table</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC156</t>
   </si>
   <si>
@@ -1889,6 +1925,18 @@
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/Untitled-scene.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">One-slide intro: many agents, many frameworks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 1 › 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the one-sentence framing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whiteboard PDF: viewed the page</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC157</t>
   </si>
   <si>
@@ -1898,6 +1946,18 @@
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/langchain_agents.py</t>
   </si>
   <si>
+    <t xml:space="preserve">First working create_agent with a plain tool and a decorated URL fetcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 1 › 1.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the file and what it shows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC158</t>
   </si>
   <si>
@@ -1907,12 +1967,30 @@
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/langchain_basics.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Great Gatsby research agent with a grounding prompt and checkpointer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the agent, its prompt and the quirks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source quirks: checkpointer used but never defined (NameError); prompt mentions how_you_computed_counts with no schema; create_agent imported three times; deepagents imported and unused. Not run</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC159</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/06 - 12 Jul - Introduction to LangChain/main.py</t>
   </si>
   <si>
+    <t xml:space="preserve">Hello scaffold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only prints 'Hello from class-6-langchain-starts!'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed in the Ch 1 file table</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC160</t>
   </si>
   <si>
@@ -1931,6 +2009,12 @@
     <t xml:space="preserve">Weekend 03 - 11-12 Jul/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Weekend 03 overview and navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation only; repeats class 05 and 06 summaries</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC163</t>
   </si>
   <si>
@@ -4079,6 +4163,18 @@
     <t xml:space="preserve">classes_summary/06 - 12 Jul - Introduction to LangChain.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Why LangChain, create_agent, Gatsby research agent, 5-step quickstart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 1 › 1.1 to 1.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain Ch 1 was empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code from the summary and files; not run (LangChain not installed, keys needed)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC425</t>
   </si>
   <si>
@@ -4088,6 +4184,18 @@
     <t xml:space="preserve">classes_summary/07 - 18 Jul - LangChain Family &amp; Harness Engineering.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Four products, LangSmith, agent and harness sentence, timeline, outdated-tutorial signal, FAQs, self-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2 › 2.1 to 2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain Ch 2 was empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notebook 01_landscape_student_notes.ipynb named but not opened. Summary dates first agents Dec 2022; transcript says late 2022 or 2023</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC426</t>
   </si>
   <si>
@@ -4331,10 +4439,37 @@
     <t xml:space="preserve">classes_transcription_summary/06 - 12 Jul - Introduction to LangChain.md</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 06 transcript: recap, Swiggy analogy, career detour, project set-up, create_agent, messages, trade-offs, memory, caching, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 1 › 1.1 to 1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The mentor's credentials in the career-advice detour (left out)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added project set-up, message anatomy, trade-offs, memory demo, caching, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model names (gpt-5.5, gpt-4o-mini) may be out of date</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC444</t>
   </si>
   <si>
     <t xml:space="preserve">classes_transcription_summary/07 - 18 Jul - LangChain Family &amp; Harness Engineering.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 07 transcript: goal, analogies, family, timeline, Colab vs VS Code, set-up, init_chat_model, messages, open vs closed, Q&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2; Ch 3 › 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pomodoro study-format note (logistics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added analogies, LangFuse, set-up, key names, init_chat_model and pirate demo, open vs closed, Q&amp;A</t>
   </si>
   <si>
     <t xml:space="preserve">LC445</t>
@@ -5092,7 +5227,7 @@
       </c>
       <c r="B6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,B$3)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A6,Master!$H$2:$H$465,C$3)</f>
@@ -5112,7 +5247,7 @@
       </c>
       <c r="G6" s="3" t="n">
         <f aca="false">SUM(B6:F6)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3"/>
     </row>
@@ -5122,15 +5257,15 @@
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,B$3)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,C$3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,D$3)</f>
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,E$3)</f>
@@ -5138,11 +5273,11 @@
       </c>
       <c r="F7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,F$3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">SUM(B7:F7)</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -5242,15 +5377,15 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -5258,7 +5393,7 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">SUM(G4:G10)</f>
@@ -5296,7 +5431,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -5311,7 +5446,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -5326,7 +5461,7 @@
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A16)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -5356,7 +5491,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5371,7 +5506,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5386,7 +5521,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -10862,25 +10997,35 @@
       <c r="E152" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="F152" s="3"/>
+      <c r="F152" s="3" t="s">
+        <v>609</v>
+      </c>
       <c r="G152" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I152" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>610</v>
+      </c>
       <c r="J152" s="3"/>
       <c r="K152" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L152" s="3"/>
-      <c r="M152" s="3"/>
-      <c r="N152" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="M152" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N152" s="3" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>38</v>
@@ -10892,7 +11037,7 @@
         <v>45</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
@@ -10914,7 +11059,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>38</v>
@@ -10926,7 +11071,7 @@
         <v>69</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
@@ -10948,39 +11093,51 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="F155" s="3"/>
+        <v>619</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>620</v>
+      </c>
       <c r="G155" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I155" s="3"/>
-      <c r="J155" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>622</v>
+      </c>
       <c r="K155" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L155" s="3"/>
-      <c r="M155" s="3"/>
-      <c r="N155" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L155" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="M155" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N155" s="3" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>38</v>
@@ -10992,27 +11149,35 @@
         <v>58</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="F156" s="3"/>
+        <v>626</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>627</v>
+      </c>
       <c r="G156" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I156" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>628</v>
+      </c>
       <c r="J156" s="3"/>
       <c r="K156" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L156" s="3"/>
-      <c r="M156" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L156" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="M156" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N156" s="3"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>38</v>
@@ -11021,30 +11186,40 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="F157" s="3"/>
+        <v>632</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>633</v>
+      </c>
       <c r="G157" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I157" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>634</v>
+      </c>
       <c r="J157" s="3"/>
       <c r="K157" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L157" s="3"/>
-      <c r="M157" s="3"/>
-      <c r="N157" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="M157" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N157" s="3" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>38</v>
@@ -11053,30 +11228,40 @@
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="F158" s="3"/>
+        <v>639</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>640</v>
+      </c>
       <c r="G158" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I158" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>641</v>
+      </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L158" s="3"/>
-      <c r="M158" s="3"/>
-      <c r="N158" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="M158" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N158" s="3" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>38</v>
@@ -11085,30 +11270,40 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="F159" s="3"/>
+        <v>646</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>647</v>
+      </c>
       <c r="G159" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I159" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>641</v>
+      </c>
       <c r="J159" s="3"/>
       <c r="K159" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L159" s="3"/>
-      <c r="M159" s="3"/>
-      <c r="N159" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L159" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="M159" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N159" s="3" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>38</v>
@@ -11120,27 +11315,35 @@
         <v>130</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="F160" s="3"/>
+        <v>651</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>652</v>
+      </c>
       <c r="G160" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L160" s="3"/>
-      <c r="M160" s="3"/>
-      <c r="N160" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L160" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="M160" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N160" s="3" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>38</v>
@@ -11152,7 +11355,7 @@
         <v>77</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
@@ -11174,7 +11377,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>38</v>
@@ -11186,7 +11389,7 @@
         <v>89</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
@@ -11208,7 +11411,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>38</v>
@@ -11220,27 +11423,33 @@
         <v>58</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="F163" s="3"/>
+        <v>660</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>661</v>
+      </c>
       <c r="G163" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L163" s="3"/>
-      <c r="M163" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L163" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="M163" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N163" s="3"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>38</v>
@@ -11252,7 +11461,7 @@
         <v>367</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
@@ -11269,12 +11478,12 @@
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -11286,7 +11495,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -11305,12 +11514,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -11322,7 +11531,7 @@
         <v>69</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -11341,12 +11550,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -11355,10 +11564,10 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>643</v>
+        <v>671</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
@@ -11375,12 +11584,12 @@
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -11389,10 +11598,10 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
@@ -11409,12 +11618,12 @@
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -11423,10 +11632,10 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
@@ -11443,12 +11652,12 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -11457,10 +11666,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -11477,12 +11686,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -11491,10 +11700,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>656</v>
+        <v>684</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -11511,12 +11720,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -11525,10 +11734,10 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>658</v>
+        <v>686</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
@@ -11545,12 +11754,12 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -11562,7 +11771,7 @@
         <v>58</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
@@ -11579,12 +11788,12 @@
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
       <c r="N173" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>662</v>
+        <v>690</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -11596,7 +11805,7 @@
         <v>130</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -11613,12 +11822,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -11630,7 +11839,7 @@
         <v>77</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -11649,12 +11858,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -11666,7 +11875,7 @@
         <v>349</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>667</v>
+        <v>695</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -11685,12 +11894,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -11702,7 +11911,7 @@
         <v>89</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -11721,12 +11930,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>670</v>
+        <v>698</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11735,10 +11944,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11755,12 +11964,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11769,10 +11978,10 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
@@ -11789,12 +11998,12 @@
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
       <c r="N179" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -11803,10 +12012,10 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
@@ -11823,12 +12032,12 @@
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
       <c r="N180" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -11837,10 +12046,10 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>680</v>
+        <v>708</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
@@ -11857,12 +12066,12 @@
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -11871,10 +12080,10 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
@@ -11891,12 +12100,12 @@
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
       <c r="N182" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>685</v>
+        <v>713</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -11905,10 +12114,10 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>686</v>
+        <v>714</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>687</v>
+        <v>715</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
@@ -11925,12 +12134,12 @@
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
       <c r="N183" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>688</v>
+        <v>716</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -11942,7 +12151,7 @@
         <v>58</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
@@ -11959,12 +12168,12 @@
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
       <c r="N184" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>690</v>
+        <v>718</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -11976,7 +12185,7 @@
         <v>58</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -11993,12 +12202,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>692</v>
+        <v>720</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -12007,10 +12216,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>693</v>
+        <v>721</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>694</v>
+        <v>722</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -12027,12 +12236,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -12041,10 +12250,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -12061,12 +12270,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -12075,10 +12284,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>700</v>
+        <v>728</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>701</v>
+        <v>729</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -12095,12 +12304,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -12109,10 +12318,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>703</v>
+        <v>731</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -12129,12 +12338,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>705</v>
+        <v>733</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -12143,10 +12352,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>706</v>
+        <v>734</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>707</v>
+        <v>735</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -12163,12 +12372,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>708</v>
+        <v>736</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -12177,10 +12386,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>709</v>
+        <v>737</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>710</v>
+        <v>738</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -12197,12 +12406,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>711</v>
+        <v>739</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -12211,10 +12420,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>713</v>
+        <v>741</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -12231,12 +12440,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>714</v>
+        <v>742</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -12245,10 +12454,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>715</v>
+        <v>743</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>716</v>
+        <v>744</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -12265,12 +12474,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>717</v>
+        <v>745</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -12279,10 +12488,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>718</v>
+        <v>746</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>719</v>
+        <v>747</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -12299,12 +12508,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -12316,7 +12525,7 @@
         <v>58</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>721</v>
+        <v>749</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -12333,12 +12542,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>722</v>
+        <v>750</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -12350,7 +12559,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -12367,12 +12576,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>724</v>
+        <v>752</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -12381,10 +12590,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>725</v>
+        <v>753</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>726</v>
+        <v>754</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -12406,7 +12615,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>727</v>
+        <v>755</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -12415,10 +12624,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>728</v>
+        <v>756</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>729</v>
+        <v>757</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -12438,7 +12647,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>730</v>
+        <v>758</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -12447,10 +12656,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>731</v>
+        <v>759</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>732</v>
+        <v>760</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -12470,7 +12679,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>733</v>
+        <v>761</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -12479,10 +12688,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>734</v>
+        <v>762</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>735</v>
+        <v>763</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -12502,7 +12711,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>736</v>
+        <v>764</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -12511,10 +12720,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>737</v>
+        <v>765</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>738</v>
+        <v>766</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -12534,7 +12743,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>739</v>
+        <v>767</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -12543,10 +12752,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>740</v>
+        <v>768</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>741</v>
+        <v>769</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -12566,7 +12775,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>742</v>
+        <v>770</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -12578,7 +12787,7 @@
         <v>58</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -12598,7 +12807,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -12610,7 +12819,7 @@
         <v>58</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>745</v>
+        <v>773</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -12630,7 +12839,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>746</v>
+        <v>774</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -12639,10 +12848,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>725</v>
+        <v>753</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>747</v>
+        <v>775</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -12664,7 +12873,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>748</v>
+        <v>776</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -12673,10 +12882,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>728</v>
+        <v>756</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>749</v>
+        <v>777</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -12696,7 +12905,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>750</v>
+        <v>778</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -12705,10 +12914,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>751</v>
+        <v>779</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>752</v>
+        <v>780</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12730,7 +12939,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>753</v>
+        <v>781</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12739,10 +12948,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>737</v>
+        <v>765</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>754</v>
+        <v>782</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12762,7 +12971,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>755</v>
+        <v>783</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12774,7 +12983,7 @@
         <v>58</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -12794,7 +13003,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>757</v>
+        <v>785</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -12806,7 +13015,7 @@
         <v>58</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>758</v>
+        <v>786</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -12826,7 +13035,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>759</v>
+        <v>787</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -12838,7 +13047,7 @@
         <v>58</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -12858,7 +13067,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>761</v>
+        <v>789</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -12867,10 +13076,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>762</v>
+        <v>790</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -12892,7 +13101,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>764</v>
+        <v>792</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -12901,10 +13110,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>765</v>
+        <v>793</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>766</v>
+        <v>794</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -12924,7 +13133,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>767</v>
+        <v>795</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -12933,10 +13142,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>768</v>
+        <v>796</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -12956,7 +13165,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>770</v>
+        <v>798</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -12968,7 +13177,7 @@
         <v>55</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>771</v>
+        <v>799</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -12988,7 +13197,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>772</v>
+        <v>800</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -12997,10 +13206,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>773</v>
+        <v>801</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>774</v>
+        <v>802</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -13020,7 +13229,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>775</v>
+        <v>803</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -13032,7 +13241,7 @@
         <v>212</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>776</v>
+        <v>804</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -13052,7 +13261,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>777</v>
+        <v>805</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -13064,7 +13273,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>778</v>
+        <v>806</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -13086,7 +13295,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>779</v>
+        <v>807</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -13098,7 +13307,7 @@
         <v>69</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>780</v>
+        <v>808</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -13120,7 +13329,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>781</v>
+        <v>809</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -13132,7 +13341,7 @@
         <v>58</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>782</v>
+        <v>810</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -13152,7 +13361,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>783</v>
+        <v>811</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -13164,7 +13373,7 @@
         <v>77</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>784</v>
+        <v>812</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -13186,7 +13395,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>785</v>
+        <v>813</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -13198,7 +13407,7 @@
         <v>80</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>786</v>
+        <v>814</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -13218,7 +13427,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -13230,7 +13439,7 @@
         <v>86</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -13250,7 +13459,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -13262,7 +13471,7 @@
         <v>89</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>790</v>
+        <v>818</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -13284,7 +13493,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -13296,7 +13505,7 @@
         <v>265</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -13316,7 +13525,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -13328,7 +13537,7 @@
         <v>58</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>794</v>
+        <v>822</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -13348,7 +13557,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>795</v>
+        <v>823</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -13360,7 +13569,7 @@
         <v>58</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>796</v>
+        <v>824</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -13380,7 +13589,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -13389,10 +13598,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>798</v>
+        <v>826</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -13412,7 +13621,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>800</v>
+        <v>828</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -13421,10 +13630,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>801</v>
+        <v>829</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>802</v>
+        <v>830</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -13444,7 +13653,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>803</v>
+        <v>831</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -13453,10 +13662,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>805</v>
+        <v>833</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -13476,7 +13685,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>806</v>
+        <v>834</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -13485,10 +13694,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>807</v>
+        <v>835</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>808</v>
+        <v>836</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -13508,7 +13717,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>809</v>
+        <v>837</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -13520,7 +13729,7 @@
         <v>58</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>810</v>
+        <v>838</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -13540,7 +13749,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>811</v>
+        <v>839</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -13549,10 +13758,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>812</v>
+        <v>840</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>813</v>
+        <v>841</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -13574,7 +13783,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>814</v>
+        <v>842</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -13586,7 +13795,7 @@
         <v>259</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>815</v>
+        <v>843</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -13606,7 +13815,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>816</v>
+        <v>844</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -13618,7 +13827,7 @@
         <v>262</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>817</v>
+        <v>845</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -13638,7 +13847,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>818</v>
+        <v>846</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -13647,10 +13856,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>819</v>
+        <v>847</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>820</v>
+        <v>848</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -13670,7 +13879,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>821</v>
+        <v>849</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -13682,7 +13891,7 @@
         <v>58</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>822</v>
+        <v>850</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -13702,7 +13911,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>823</v>
+        <v>851</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -13714,7 +13923,7 @@
         <v>58</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>824</v>
+        <v>852</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13734,7 +13943,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>825</v>
+        <v>853</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13746,7 +13955,7 @@
         <v>61</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>826</v>
+        <v>854</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13766,7 +13975,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>827</v>
+        <v>855</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13778,7 +13987,7 @@
         <v>64</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>828</v>
+        <v>856</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -13798,7 +14007,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>829</v>
+        <v>857</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -13810,7 +14019,7 @@
         <v>58</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>830</v>
+        <v>858</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -13830,7 +14039,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>831</v>
+        <v>859</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -13842,7 +14051,7 @@
         <v>69</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>832</v>
+        <v>860</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -13864,7 +14073,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>833</v>
+        <v>861</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -13876,7 +14085,7 @@
         <v>58</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>834</v>
+        <v>862</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -13896,7 +14105,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>835</v>
+        <v>863</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -13908,7 +14117,7 @@
         <v>127</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>836</v>
+        <v>864</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -13928,7 +14137,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>837</v>
+        <v>865</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -13940,7 +14149,7 @@
         <v>130</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>838</v>
+        <v>866</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -13960,7 +14169,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>839</v>
+        <v>867</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -13972,7 +14181,7 @@
         <v>151</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>840</v>
+        <v>868</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -13992,7 +14201,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>841</v>
+        <v>869</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -14004,7 +14213,7 @@
         <v>77</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>842</v>
+        <v>870</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -14026,7 +14235,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>843</v>
+        <v>871</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -14038,7 +14247,7 @@
         <v>193</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>844</v>
+        <v>872</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -14058,7 +14267,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>845</v>
+        <v>873</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -14070,7 +14279,7 @@
         <v>196</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -14092,7 +14301,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>847</v>
+        <v>875</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -14104,7 +14313,7 @@
         <v>199</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -14126,7 +14335,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>849</v>
+        <v>877</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -14138,7 +14347,7 @@
         <v>135</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>850</v>
+        <v>878</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -14160,7 +14369,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>851</v>
+        <v>879</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -14172,7 +14381,7 @@
         <v>89</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -14194,7 +14403,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>853</v>
+        <v>881</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -14206,7 +14415,7 @@
         <v>209</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>854</v>
+        <v>882</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -14226,7 +14435,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>855</v>
+        <v>883</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -14238,7 +14447,7 @@
         <v>69</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>856</v>
+        <v>884</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -14260,7 +14469,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>857</v>
+        <v>885</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -14272,7 +14481,7 @@
         <v>58</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -14292,7 +14501,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>859</v>
+        <v>887</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -14304,7 +14513,7 @@
         <v>222</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>860</v>
+        <v>888</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -14326,7 +14535,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>861</v>
+        <v>889</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -14338,7 +14547,7 @@
         <v>130</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>862</v>
+        <v>890</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -14358,7 +14567,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>863</v>
+        <v>891</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -14370,7 +14579,7 @@
         <v>77</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>864</v>
+        <v>892</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -14392,7 +14601,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>865</v>
+        <v>893</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -14404,7 +14613,7 @@
         <v>61</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>866</v>
+        <v>894</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -14424,7 +14633,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>867</v>
+        <v>895</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -14436,7 +14645,7 @@
         <v>64</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>868</v>
+        <v>896</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -14456,7 +14665,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>869</v>
+        <v>897</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -14468,7 +14677,7 @@
         <v>89</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>870</v>
+        <v>898</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -14490,7 +14699,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>871</v>
+        <v>899</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -14502,7 +14711,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>872</v>
+        <v>900</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -14524,7 +14733,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>873</v>
+        <v>901</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -14536,7 +14745,7 @@
         <v>69</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>874</v>
+        <v>902</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -14558,7 +14767,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>875</v>
+        <v>903</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -14570,7 +14779,7 @@
         <v>58</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>876</v>
+        <v>904</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -14590,7 +14799,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>877</v>
+        <v>905</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -14602,7 +14811,7 @@
         <v>74</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>878</v>
+        <v>906</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -14622,7 +14831,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>879</v>
+        <v>907</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -14634,7 +14843,7 @@
         <v>77</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>880</v>
+        <v>908</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -14656,7 +14865,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>881</v>
+        <v>909</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -14668,7 +14877,7 @@
         <v>80</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>882</v>
+        <v>910</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -14688,7 +14897,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>883</v>
+        <v>911</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -14700,7 +14909,7 @@
         <v>83</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>884</v>
+        <v>912</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -14720,7 +14929,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>885</v>
+        <v>913</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14732,7 +14941,7 @@
         <v>86</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>886</v>
+        <v>914</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14752,7 +14961,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>887</v>
+        <v>915</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14764,7 +14973,7 @@
         <v>89</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>888</v>
+        <v>916</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14786,7 +14995,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>889</v>
+        <v>917</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -14798,7 +15007,7 @@
         <v>58</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>890</v>
+        <v>918</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -14818,7 +15027,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>891</v>
+        <v>919</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -14830,7 +15039,7 @@
         <v>69</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>892</v>
+        <v>920</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -14852,7 +15061,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>893</v>
+        <v>921</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -14861,10 +15070,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>894</v>
+        <v>922</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>895</v>
+        <v>923</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -14884,7 +15093,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>896</v>
+        <v>924</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -14896,7 +15105,7 @@
         <v>58</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>897</v>
+        <v>925</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -14916,7 +15125,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>898</v>
+        <v>926</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -14925,10 +15134,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>899</v>
+        <v>927</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>900</v>
+        <v>928</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -14948,7 +15157,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>901</v>
+        <v>929</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -14960,7 +15169,7 @@
         <v>130</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>902</v>
+        <v>930</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -14980,7 +15189,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>903</v>
+        <v>931</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -14992,7 +15201,7 @@
         <v>77</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>904</v>
+        <v>932</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -15014,7 +15223,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>905</v>
+        <v>933</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -15026,7 +15235,7 @@
         <v>89</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>906</v>
+        <v>934</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -15048,7 +15257,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>907</v>
+        <v>935</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -15060,7 +15269,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>908</v>
+        <v>936</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -15079,12 +15288,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>910</v>
+        <v>938</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -15093,10 +15302,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>911</v>
+        <v>939</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>912</v>
+        <v>940</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -15113,12 +15322,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>913</v>
+        <v>941</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -15127,10 +15336,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>914</v>
+        <v>942</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>915</v>
+        <v>943</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -15147,12 +15356,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>916</v>
+        <v>944</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -15161,10 +15370,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>917</v>
+        <v>945</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>918</v>
+        <v>946</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -15183,12 +15392,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>919</v>
+        <v>947</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -15197,10 +15406,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>920</v>
+        <v>948</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>921</v>
+        <v>949</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -15217,12 +15426,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>922</v>
+        <v>950</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -15231,10 +15440,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>923</v>
+        <v>951</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -15253,12 +15462,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>925</v>
+        <v>953</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -15267,10 +15476,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>926</v>
+        <v>954</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>927</v>
+        <v>955</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -15287,12 +15496,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>928</v>
+        <v>956</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -15301,10 +15510,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>929</v>
+        <v>957</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>930</v>
+        <v>958</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -15323,12 +15532,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>931</v>
+        <v>959</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -15337,10 +15546,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>932</v>
+        <v>960</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>933</v>
+        <v>961</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -15357,12 +15566,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>934</v>
+        <v>962</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -15374,7 +15583,7 @@
         <v>77</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>935</v>
+        <v>963</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -15393,12 +15602,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>936</v>
+        <v>964</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -15410,7 +15619,7 @@
         <v>89</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>937</v>
+        <v>965</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -15429,12 +15638,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>909</v>
+        <v>937</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>938</v>
+        <v>966</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -15446,7 +15655,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>939</v>
+        <v>967</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -15468,7 +15677,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>940</v>
+        <v>968</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -15477,10 +15686,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>941</v>
+        <v>969</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>942</v>
+        <v>970</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -15500,7 +15709,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -15509,10 +15718,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>944</v>
+        <v>972</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>945</v>
+        <v>973</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -15532,7 +15741,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>946</v>
+        <v>974</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -15541,10 +15750,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>947</v>
+        <v>975</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>948</v>
+        <v>976</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -15564,7 +15773,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>949</v>
+        <v>977</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -15573,10 +15782,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>950</v>
+        <v>978</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>951</v>
+        <v>979</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -15596,7 +15805,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>952</v>
+        <v>980</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -15605,10 +15814,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>953</v>
+        <v>981</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>954</v>
+        <v>982</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -15628,7 +15837,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>955</v>
+        <v>983</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -15637,10 +15846,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>956</v>
+        <v>984</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>957</v>
+        <v>985</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -15660,7 +15869,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>958</v>
+        <v>986</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -15672,7 +15881,7 @@
         <v>58</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>959</v>
+        <v>987</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -15692,7 +15901,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>960</v>
+        <v>988</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -15704,7 +15913,7 @@
         <v>77</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>961</v>
+        <v>989</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15726,7 +15935,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>962</v>
+        <v>990</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15735,10 +15944,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>963</v>
+        <v>991</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15758,7 +15967,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>965</v>
+        <v>993</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15770,7 +15979,7 @@
         <v>89</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>966</v>
+        <v>994</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -15792,7 +16001,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>967</v>
+        <v>995</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -15801,10 +16010,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>968</v>
+        <v>996</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -15826,7 +16035,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>970</v>
+        <v>998</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -15835,10 +16044,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>971</v>
+        <v>999</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>972</v>
+        <v>1000</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -15860,7 +16069,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -15872,7 +16081,7 @@
         <v>367</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>974</v>
+        <v>1002</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -15892,7 +16101,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>975</v>
+        <v>1003</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -15901,10 +16110,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>976</v>
+        <v>1004</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>977</v>
+        <v>1005</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -15926,7 +16135,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>978</v>
+        <v>1006</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -15938,7 +16147,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>979</v>
+        <v>1007</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -15960,7 +16169,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -15969,10 +16178,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>981</v>
+        <v>1009</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>982</v>
+        <v>1010</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -15992,7 +16201,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>983</v>
+        <v>1011</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -16001,10 +16210,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>984</v>
+        <v>1012</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>985</v>
+        <v>1013</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -16026,7 +16235,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>986</v>
+        <v>1014</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -16038,7 +16247,7 @@
         <v>58</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>987</v>
+        <v>1015</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -16058,7 +16267,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>988</v>
+        <v>1016</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -16070,7 +16279,7 @@
         <v>86</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>989</v>
+        <v>1017</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -16090,7 +16299,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>990</v>
+        <v>1018</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -16099,10 +16308,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>991</v>
+        <v>1019</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>992</v>
+        <v>1020</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -16122,7 +16331,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>993</v>
+        <v>1021</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -16131,10 +16340,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>994</v>
+        <v>1022</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>995</v>
+        <v>1023</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -16154,7 +16363,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>996</v>
+        <v>1024</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -16166,7 +16375,7 @@
         <v>361</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>997</v>
+        <v>1025</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -16186,7 +16395,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>998</v>
+        <v>1026</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -16198,7 +16407,7 @@
         <v>86</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>999</v>
+        <v>1027</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -16218,7 +16427,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>1000</v>
+        <v>1028</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -16227,10 +16436,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>1001</v>
+        <v>1029</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>1002</v>
+        <v>1030</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -16250,7 +16459,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>1003</v>
+        <v>1031</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -16262,7 +16471,7 @@
         <v>130</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>1004</v>
+        <v>1032</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -16282,7 +16491,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -16291,10 +16500,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>1006</v>
+        <v>1034</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>1007</v>
+        <v>1035</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -16314,7 +16523,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>1008</v>
+        <v>1036</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -16326,7 +16535,7 @@
         <v>86</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>1009</v>
+        <v>1037</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -16346,7 +16555,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>1010</v>
+        <v>1038</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -16355,10 +16564,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>1011</v>
+        <v>1039</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>1012</v>
+        <v>1040</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -16378,7 +16587,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>1013</v>
+        <v>1041</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -16390,7 +16599,7 @@
         <v>86</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>1014</v>
+        <v>1042</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -16410,7 +16619,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>1015</v>
+        <v>1043</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -16419,10 +16628,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>1016</v>
+        <v>1044</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>1017</v>
+        <v>1045</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -16442,7 +16651,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>1018</v>
+        <v>1046</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -16454,7 +16663,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>1019</v>
+        <v>1047</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -16474,7 +16683,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>1020</v>
+        <v>1048</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -16483,10 +16692,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>1021</v>
+        <v>1049</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>1022</v>
+        <v>1050</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -16506,7 +16715,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>1023</v>
+        <v>1051</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -16515,10 +16724,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>1024</v>
+        <v>1052</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>1025</v>
+        <v>1053</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -16538,7 +16747,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>1026</v>
+        <v>1054</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -16547,10 +16756,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>1027</v>
+        <v>1055</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -16570,7 +16779,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>1029</v>
+        <v>1057</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -16579,10 +16788,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>1030</v>
+        <v>1058</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -16602,7 +16811,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>1032</v>
+        <v>1060</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -16611,10 +16820,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>1033</v>
+        <v>1061</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>1034</v>
+        <v>1062</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -16634,7 +16843,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>1035</v>
+        <v>1063</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -16643,10 +16852,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>1036</v>
+        <v>1064</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>1037</v>
+        <v>1065</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -16666,7 +16875,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>1038</v>
+        <v>1066</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -16675,10 +16884,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>1039</v>
+        <v>1067</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -16698,7 +16907,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>1041</v>
+        <v>1069</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -16707,10 +16916,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>1042</v>
+        <v>1070</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>1043</v>
+        <v>1071</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16732,7 +16941,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>1044</v>
+        <v>1072</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16741,10 +16950,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>1046</v>
+        <v>1074</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16766,7 +16975,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>1047</v>
+        <v>1075</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16775,10 +16984,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>1048</v>
+        <v>1076</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>1049</v>
+        <v>1077</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -16798,7 +17007,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -16810,7 +17019,7 @@
         <v>196</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -16832,7 +17041,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>1052</v>
+        <v>1080</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -16841,10 +17050,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1053</v>
+        <v>1081</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1054</v>
+        <v>1082</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -16866,7 +17075,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>1055</v>
+        <v>1083</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -16875,10 +17084,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1056</v>
+        <v>1084</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1057</v>
+        <v>1085</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -16900,7 +17109,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>1058</v>
+        <v>1086</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -16909,10 +17118,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1059</v>
+        <v>1087</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -16932,7 +17141,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>1061</v>
+        <v>1089</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -16941,10 +17150,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1062</v>
+        <v>1090</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -16964,7 +17173,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>1064</v>
+        <v>1092</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -16973,10 +17182,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1066</v>
+        <v>1094</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -16996,7 +17205,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>1067</v>
+        <v>1095</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -17005,10 +17214,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1068</v>
+        <v>1096</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1069</v>
+        <v>1097</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -17030,7 +17239,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>1070</v>
+        <v>1098</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -17039,10 +17248,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1071</v>
+        <v>1099</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1072</v>
+        <v>1100</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -17062,7 +17271,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>1073</v>
+        <v>1101</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -17071,10 +17280,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1074</v>
+        <v>1102</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1075</v>
+        <v>1103</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -17094,7 +17303,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>1076</v>
+        <v>1104</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -17103,10 +17312,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1077</v>
+        <v>1105</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1078</v>
+        <v>1106</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -17126,7 +17335,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>1079</v>
+        <v>1107</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -17135,10 +17344,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1080</v>
+        <v>1108</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1081</v>
+        <v>1109</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -17158,7 +17367,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>1082</v>
+        <v>1110</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -17167,10 +17376,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1083</v>
+        <v>1111</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1084</v>
+        <v>1112</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -17190,7 +17399,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>1085</v>
+        <v>1113</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -17199,10 +17408,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1086</v>
+        <v>1114</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1087</v>
+        <v>1115</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -17222,7 +17431,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>1088</v>
+        <v>1116</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -17231,10 +17440,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1089</v>
+        <v>1117</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1090</v>
+        <v>1118</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -17254,7 +17463,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>1091</v>
+        <v>1119</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -17263,10 +17472,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1092</v>
+        <v>1120</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1093</v>
+        <v>1121</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -17286,7 +17495,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>1094</v>
+        <v>1122</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -17295,10 +17504,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1095</v>
+        <v>1123</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1096</v>
+        <v>1124</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -17318,7 +17527,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>1097</v>
+        <v>1125</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -17327,10 +17536,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1098</v>
+        <v>1126</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -17350,7 +17559,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>1100</v>
+        <v>1128</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -17359,10 +17568,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1101</v>
+        <v>1129</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1102</v>
+        <v>1130</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -17382,7 +17591,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>1103</v>
+        <v>1131</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -17391,10 +17600,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1104</v>
+        <v>1132</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1105</v>
+        <v>1133</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -17414,7 +17623,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>1106</v>
+        <v>1134</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -17423,10 +17632,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1107</v>
+        <v>1135</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -17446,7 +17655,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>1109</v>
+        <v>1137</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -17455,10 +17664,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1110</v>
+        <v>1138</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1111</v>
+        <v>1139</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -17478,7 +17687,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -17487,10 +17696,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1113</v>
+        <v>1141</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1114</v>
+        <v>1142</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -17510,7 +17719,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -17519,10 +17728,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1117</v>
+        <v>1145</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -17542,7 +17751,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1118</v>
+        <v>1146</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -17551,10 +17760,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1119</v>
+        <v>1147</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1120</v>
+        <v>1148</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -17574,7 +17783,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1121</v>
+        <v>1149</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -17583,10 +17792,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1122</v>
+        <v>1150</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1123</v>
+        <v>1151</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -17606,7 +17815,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1124</v>
+        <v>1152</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -17615,10 +17824,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1125</v>
+        <v>1153</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1126</v>
+        <v>1154</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -17638,7 +17847,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1127</v>
+        <v>1155</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -17647,10 +17856,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1128</v>
+        <v>1156</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1129</v>
+        <v>1157</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -17670,7 +17879,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1130</v>
+        <v>1158</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -17679,10 +17888,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1131</v>
+        <v>1159</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1132</v>
+        <v>1160</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -17702,7 +17911,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -17711,10 +17920,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17734,7 +17943,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1136</v>
+        <v>1164</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17743,10 +17952,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17766,7 +17975,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17775,10 +17984,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -17798,7 +18007,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -17807,10 +18016,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1144</v>
+        <v>1172</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -17830,7 +18039,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1145</v>
+        <v>1173</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -17839,10 +18048,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1146</v>
+        <v>1174</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1147</v>
+        <v>1175</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -17862,7 +18071,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1148</v>
+        <v>1176</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -17871,10 +18080,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1149</v>
+        <v>1177</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1150</v>
+        <v>1178</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -17894,7 +18103,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1151</v>
+        <v>1179</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -17903,10 +18112,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1152</v>
+        <v>1180</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1153</v>
+        <v>1181</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -17926,7 +18135,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -17935,10 +18144,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1155</v>
+        <v>1183</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1156</v>
+        <v>1184</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -17958,7 +18167,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1157</v>
+        <v>1185</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -17967,10 +18176,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1158</v>
+        <v>1186</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1159</v>
+        <v>1187</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -17990,7 +18199,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -17999,10 +18208,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1161</v>
+        <v>1189</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1162</v>
+        <v>1190</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -18022,7 +18231,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1163</v>
+        <v>1191</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -18031,10 +18240,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1164</v>
+        <v>1192</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1165</v>
+        <v>1193</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -18054,7 +18263,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1166</v>
+        <v>1194</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -18063,10 +18272,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1167</v>
+        <v>1195</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1168</v>
+        <v>1196</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -18086,7 +18295,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1169</v>
+        <v>1197</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -18095,10 +18304,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1170</v>
+        <v>1198</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1171</v>
+        <v>1199</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -18118,7 +18327,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1172</v>
+        <v>1200</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -18127,10 +18336,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1173</v>
+        <v>1201</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1174</v>
+        <v>1202</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -18150,7 +18359,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1175</v>
+        <v>1203</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -18159,10 +18368,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1177</v>
+        <v>1205</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -18182,7 +18391,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1178</v>
+        <v>1206</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -18191,10 +18400,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1179</v>
+        <v>1207</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1180</v>
+        <v>1208</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -18214,7 +18423,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1181</v>
+        <v>1209</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -18223,10 +18432,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1182</v>
+        <v>1210</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1183</v>
+        <v>1211</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -18246,7 +18455,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1184</v>
+        <v>1212</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -18255,10 +18464,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1185</v>
+        <v>1213</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1186</v>
+        <v>1214</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -18278,7 +18487,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1187</v>
+        <v>1215</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -18287,10 +18496,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1188</v>
+        <v>1216</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1189</v>
+        <v>1217</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -18310,7 +18519,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1190</v>
+        <v>1218</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -18319,10 +18528,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1191</v>
+        <v>1219</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1192</v>
+        <v>1220</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -18342,7 +18551,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1193</v>
+        <v>1221</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -18351,10 +18560,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1194</v>
+        <v>1222</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1195</v>
+        <v>1223</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -18374,7 +18583,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1196</v>
+        <v>1224</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -18383,10 +18592,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1197</v>
+        <v>1225</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1198</v>
+        <v>1226</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -18406,7 +18615,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1199</v>
+        <v>1227</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -18415,10 +18624,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1200</v>
+        <v>1228</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1201</v>
+        <v>1229</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -18438,7 +18647,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1202</v>
+        <v>1230</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -18447,10 +18656,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1203</v>
+        <v>1231</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1204</v>
+        <v>1232</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -18470,7 +18679,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1205</v>
+        <v>1233</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -18479,10 +18688,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1206</v>
+        <v>1234</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1207</v>
+        <v>1235</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -18502,7 +18711,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1208</v>
+        <v>1236</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -18511,10 +18720,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1209</v>
+        <v>1237</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1210</v>
+        <v>1238</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -18534,7 +18743,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1211</v>
+        <v>1239</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -18543,10 +18752,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1212</v>
+        <v>1240</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1213</v>
+        <v>1241</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -18566,7 +18775,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1214</v>
+        <v>1242</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -18575,10 +18784,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1215</v>
+        <v>1243</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1216</v>
+        <v>1244</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -18598,7 +18807,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1217</v>
+        <v>1245</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -18607,10 +18816,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1218</v>
+        <v>1246</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1219</v>
+        <v>1247</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -18630,7 +18839,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1220</v>
+        <v>1248</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -18639,10 +18848,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1221</v>
+        <v>1249</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1222</v>
+        <v>1250</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -18662,7 +18871,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1223</v>
+        <v>1251</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -18671,10 +18880,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1224</v>
+        <v>1252</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1225</v>
+        <v>1253</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -18694,7 +18903,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1226</v>
+        <v>1254</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -18703,10 +18912,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1227</v>
+        <v>1255</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1228</v>
+        <v>1256</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18726,7 +18935,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1229</v>
+        <v>1257</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18735,10 +18944,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1230</v>
+        <v>1258</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1231</v>
+        <v>1259</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18758,7 +18967,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1232</v>
+        <v>1260</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18767,10 +18976,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1233</v>
+        <v>1261</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1234</v>
+        <v>1262</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18790,7 +18999,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1235</v>
+        <v>1263</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -18799,10 +19008,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1236</v>
+        <v>1264</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1237</v>
+        <v>1265</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -18822,7 +19031,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1238</v>
+        <v>1266</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -18831,10 +19040,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1233</v>
+        <v>1261</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1239</v>
+        <v>1267</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -18854,7 +19063,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1240</v>
+        <v>1268</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -18863,10 +19072,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1241</v>
+        <v>1269</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1242</v>
+        <v>1270</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -18888,7 +19097,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1243</v>
+        <v>1271</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -18897,10 +19106,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1244</v>
+        <v>1272</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1245</v>
+        <v>1273</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -18920,7 +19129,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1246</v>
+        <v>1274</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -18929,10 +19138,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1247</v>
+        <v>1275</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1248</v>
+        <v>1276</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -18952,7 +19161,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1249</v>
+        <v>1277</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -18961,10 +19170,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1250</v>
+        <v>1278</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1251</v>
+        <v>1279</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -18984,7 +19193,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1252</v>
+        <v>1280</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -18993,10 +19202,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1253</v>
+        <v>1281</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1254</v>
+        <v>1282</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -19016,7 +19225,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1255</v>
+        <v>1283</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -19025,10 +19234,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1256</v>
+        <v>1284</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1257</v>
+        <v>1285</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -19048,7 +19257,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1258</v>
+        <v>1286</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -19057,10 +19266,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1259</v>
+        <v>1287</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1260</v>
+        <v>1288</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -19080,7 +19289,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1261</v>
+        <v>1289</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -19089,10 +19298,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1262</v>
+        <v>1290</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1263</v>
+        <v>1291</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -19112,7 +19321,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1264</v>
+        <v>1292</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -19121,10 +19330,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1265</v>
+        <v>1293</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1266</v>
+        <v>1294</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -19144,7 +19353,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1267</v>
+        <v>1295</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -19153,10 +19362,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1268</v>
+        <v>1296</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1269</v>
+        <v>1297</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -19176,7 +19385,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1270</v>
+        <v>1298</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -19185,10 +19394,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1271</v>
+        <v>1299</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1272</v>
+        <v>1300</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -19210,7 +19419,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1273</v>
+        <v>1301</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -19219,10 +19428,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1274</v>
+        <v>1302</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1275</v>
+        <v>1303</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -19244,7 +19453,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1276</v>
+        <v>1304</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -19253,10 +19462,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1277</v>
+        <v>1305</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1278</v>
+        <v>1306</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -19278,7 +19487,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1279</v>
+        <v>1307</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -19287,10 +19496,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1280</v>
+        <v>1308</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1281</v>
+        <v>1309</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -19310,7 +19519,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1282</v>
+        <v>1310</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -19319,10 +19528,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1283</v>
+        <v>1311</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1284</v>
+        <v>1312</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -19342,7 +19551,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1285</v>
+        <v>1313</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -19351,10 +19560,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1286</v>
+        <v>1314</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1287</v>
+        <v>1315</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -19374,7 +19583,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1288</v>
+        <v>1316</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -19383,10 +19592,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1289</v>
+        <v>1317</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1290</v>
+        <v>1318</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -19408,7 +19617,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1291</v>
+        <v>1319</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -19420,7 +19629,7 @@
         <v>349</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1292</v>
+        <v>1320</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -19442,7 +19651,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1293</v>
+        <v>1321</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -19451,10 +19660,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1294</v>
+        <v>1322</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1295</v>
+        <v>1323</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -19474,7 +19683,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1296</v>
+        <v>1324</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -19483,10 +19692,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1297</v>
+        <v>1325</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1298</v>
+        <v>1326</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -19506,7 +19715,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1299</v>
+        <v>1327</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -19515,10 +19724,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1300</v>
+        <v>1328</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1301</v>
+        <v>1329</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -19538,7 +19747,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1302</v>
+        <v>1330</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -19547,10 +19756,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1303</v>
+        <v>1331</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1304</v>
+        <v>1332</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -19570,7 +19779,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1305</v>
+        <v>1333</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -19579,10 +19788,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1306</v>
+        <v>1334</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1306</v>
+        <v>1334</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -19597,14 +19806,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1307</v>
+        <v>1335</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1308</v>
+        <v>1336</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -19613,13 +19822,13 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1309</v>
+        <v>1337</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1310</v>
+        <v>1338</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>1311</v>
+        <v>1339</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>22</v>
@@ -19628,27 +19837,27 @@
         <v>2</v>
       </c>
       <c r="I419" s="3" t="s">
-        <v>1312</v>
+        <v>1340</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1313</v>
+        <v>1341</v>
       </c>
       <c r="K419" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L419" s="3" t="s">
-        <v>1314</v>
+        <v>1342</v>
       </c>
       <c r="M419" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N419" s="3" t="s">
-        <v>1315</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1316</v>
+        <v>1344</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -19657,13 +19866,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1317</v>
+        <v>1345</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1318</v>
+        <v>1346</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1319</v>
+        <v>1347</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -19672,25 +19881,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1320</v>
+        <v>1348</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1322</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1323</v>
+        <v>1351</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -19699,13 +19908,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1324</v>
+        <v>1352</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1325</v>
+        <v>1353</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1326</v>
+        <v>1354</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -19714,25 +19923,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1327</v>
+        <v>1355</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1328</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1329</v>
+        <v>1357</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19741,13 +19950,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1330</v>
+        <v>1358</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1331</v>
+        <v>1359</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1332</v>
+        <v>1360</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19756,25 +19965,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1333</v>
+        <v>1361</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1334</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1335</v>
+        <v>1363</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19783,13 +19992,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1336</v>
+        <v>1364</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1337</v>
+        <v>1365</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -19798,25 +20007,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1339</v>
+        <v>1367</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1321</v>
+        <v>1349</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1340</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1341</v>
+        <v>1369</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -19825,13 +20034,13 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1342</v>
+        <v>1370</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1343</v>
+        <v>1371</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>1344</v>
+        <v>1372</v>
       </c>
       <c r="G424" s="3" t="s">
         <v>22</v>
@@ -19840,25 +20049,25 @@
         <v>2</v>
       </c>
       <c r="I424" s="3" t="s">
-        <v>1345</v>
+        <v>1373</v>
       </c>
       <c r="J424" s="3"/>
       <c r="K424" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L424" s="3" t="s">
-        <v>1346</v>
+        <v>1374</v>
       </c>
       <c r="M424" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N424" s="3" t="s">
-        <v>1347</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1348</v>
+        <v>1376</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -19867,30 +20076,40 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1350</v>
-      </c>
-      <c r="F425" s="3"/>
+        <v>1378</v>
+      </c>
+      <c r="F425" s="3" t="s">
+        <v>1379</v>
+      </c>
       <c r="G425" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H425" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I425" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I425" s="3" t="s">
+        <v>1380</v>
+      </c>
       <c r="J425" s="3"/>
       <c r="K425" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L425" s="3"/>
-      <c r="M425" s="3"/>
-      <c r="N425" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L425" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="M425" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N425" s="3" t="s">
+        <v>1382</v>
+      </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1351</v>
+        <v>1383</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -19899,30 +20118,40 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1352</v>
+        <v>1384</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1353</v>
-      </c>
-      <c r="F426" s="3"/>
+        <v>1385</v>
+      </c>
+      <c r="F426" s="3" t="s">
+        <v>1386</v>
+      </c>
       <c r="G426" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H426" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I426" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I426" s="3" t="s">
+        <v>1387</v>
+      </c>
       <c r="J426" s="3"/>
       <c r="K426" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L426" s="3"/>
-      <c r="M426" s="3"/>
-      <c r="N426" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L426" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="M426" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N426" s="3" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1354</v>
+        <v>1390</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -19931,13 +20160,13 @@
         <v>11</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1355</v>
+        <v>1391</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1356</v>
+        <v>1392</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>1357</v>
+        <v>1393</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>22</v>
@@ -19946,25 +20175,25 @@
         <v>2</v>
       </c>
       <c r="I427" s="3" t="s">
-        <v>1358</v>
+        <v>1394</v>
       </c>
       <c r="J427" s="3"/>
       <c r="K427" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L427" s="3" t="s">
-        <v>1359</v>
+        <v>1395</v>
       </c>
       <c r="M427" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N427" s="3" t="s">
-        <v>1360</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1361</v>
+        <v>1397</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -19973,10 +20202,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1362</v>
+        <v>1398</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1363</v>
+        <v>1399</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -19996,7 +20225,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1364</v>
+        <v>1400</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -20005,10 +20234,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1365</v>
+        <v>1401</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1366</v>
+        <v>1402</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -20028,7 +20257,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -20037,10 +20266,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1368</v>
+        <v>1404</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1369</v>
+        <v>1405</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -20060,7 +20289,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1370</v>
+        <v>1406</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -20069,10 +20298,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1371</v>
+        <v>1407</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1372</v>
+        <v>1408</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -20092,7 +20321,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1373</v>
+        <v>1409</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -20101,10 +20330,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1374</v>
+        <v>1410</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1375</v>
+        <v>1411</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -20124,7 +20353,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1376</v>
+        <v>1412</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -20133,10 +20362,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1377</v>
+        <v>1413</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1378</v>
+        <v>1414</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -20156,7 +20385,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1379</v>
+        <v>1415</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -20165,10 +20394,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1380</v>
+        <v>1416</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1381</v>
+        <v>1417</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -20188,7 +20417,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1382</v>
+        <v>1418</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -20197,10 +20426,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1383</v>
+        <v>1419</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1384</v>
+        <v>1420</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -20220,7 +20449,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1385</v>
+        <v>1421</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -20229,10 +20458,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1386</v>
+        <v>1422</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1387</v>
+        <v>1423</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -20252,7 +20481,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1388</v>
+        <v>1424</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -20261,10 +20490,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1389</v>
+        <v>1425</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1390</v>
+        <v>1426</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -20284,7 +20513,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1391</v>
+        <v>1427</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -20293,13 +20522,13 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1392</v>
+        <v>1428</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1393</v>
+        <v>1429</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>1394</v>
+        <v>1430</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>22</v>
@@ -20308,27 +20537,27 @@
         <v>3</v>
       </c>
       <c r="I438" s="3" t="s">
-        <v>1395</v>
+        <v>1431</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1396</v>
+        <v>1432</v>
       </c>
       <c r="K438" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L438" s="3" t="s">
-        <v>1397</v>
+        <v>1433</v>
       </c>
       <c r="M438" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N438" s="3" t="s">
-        <v>1398</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1399</v>
+        <v>1435</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -20337,13 +20566,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1400</v>
+        <v>1436</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1401</v>
+        <v>1437</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1402</v>
+        <v>1438</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -20352,27 +20581,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1403</v>
+        <v>1439</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1404</v>
+        <v>1440</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1405</v>
+        <v>1441</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1406</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1407</v>
+        <v>1443</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -20381,13 +20610,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1409</v>
+        <v>1445</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1410</v>
+        <v>1446</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -20396,27 +20625,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1411</v>
+        <v>1447</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1412</v>
+        <v>1448</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1413</v>
+        <v>1449</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1414</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1415</v>
+        <v>1451</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -20425,13 +20654,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1330</v>
+        <v>1358</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1416</v>
+        <v>1452</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1417</v>
+        <v>1453</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -20440,25 +20669,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1333</v>
+        <v>1361</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1418</v>
+        <v>1454</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1419</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1420</v>
+        <v>1456</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -20467,13 +20696,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1336</v>
+        <v>1364</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1421</v>
+        <v>1457</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1422</v>
+        <v>1458</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -20482,25 +20711,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1423</v>
+        <v>1459</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1424</v>
+        <v>1460</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1425</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1426</v>
+        <v>1462</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -20509,13 +20738,13 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1427</v>
+        <v>1463</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1428</v>
+        <v>1464</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>1429</v>
+        <v>1465</v>
       </c>
       <c r="G443" s="3" t="s">
         <v>22</v>
@@ -20524,25 +20753,25 @@
         <v>2</v>
       </c>
       <c r="I443" s="3" t="s">
-        <v>1430</v>
+        <v>1466</v>
       </c>
       <c r="J443" s="3"/>
       <c r="K443" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L443" s="3" t="s">
-        <v>1431</v>
+        <v>1467</v>
       </c>
       <c r="M443" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N443" s="3" t="s">
-        <v>1432</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1433</v>
+        <v>1469</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -20551,30 +20780,42 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F444" s="3"/>
+        <v>1470</v>
+      </c>
+      <c r="F444" s="3" t="s">
+        <v>1471</v>
+      </c>
       <c r="G444" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H444" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I444" s="3"/>
-      <c r="J444" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="I444" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="J444" s="3" t="s">
+        <v>1473</v>
+      </c>
       <c r="K444" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L444" s="3"/>
-      <c r="M444" s="3"/>
-      <c r="N444" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L444" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M444" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N444" s="3" t="s">
+        <v>1475</v>
+      </c>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1435</v>
+        <v>1476</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -20583,30 +20824,42 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1352</v>
+        <v>1384</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F445" s="3"/>
+        <v>1477</v>
+      </c>
+      <c r="F445" s="3" t="s">
+        <v>1478</v>
+      </c>
       <c r="G445" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H445" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I445" s="3"/>
-      <c r="J445" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I445" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J445" s="3" t="s">
+        <v>1480</v>
+      </c>
       <c r="K445" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L445" s="3"/>
-      <c r="M445" s="3"/>
-      <c r="N445" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L445" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="M445" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N445" s="3" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1437</v>
+        <v>1482</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -20615,13 +20868,13 @@
         <v>11</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1438</v>
+        <v>1483</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1439</v>
+        <v>1484</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>1440</v>
+        <v>1485</v>
       </c>
       <c r="G446" s="3" t="s">
         <v>22</v>
@@ -20630,27 +20883,27 @@
         <v>3</v>
       </c>
       <c r="I446" s="3" t="s">
-        <v>1441</v>
+        <v>1486</v>
       </c>
       <c r="J446" s="3" t="s">
-        <v>1442</v>
+        <v>1487</v>
       </c>
       <c r="K446" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L446" s="3" t="s">
-        <v>1443</v>
+        <v>1488</v>
       </c>
       <c r="M446" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N446" s="3" t="s">
-        <v>1444</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -20659,10 +20912,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1446</v>
+        <v>1491</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1447</v>
+        <v>1492</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -20682,7 +20935,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1448</v>
+        <v>1493</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -20691,10 +20944,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1449</v>
+        <v>1494</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1450</v>
+        <v>1495</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -20714,7 +20967,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1451</v>
+        <v>1496</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -20723,10 +20976,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1452</v>
+        <v>1497</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1453</v>
+        <v>1498</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -20746,7 +20999,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1454</v>
+        <v>1499</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -20755,10 +21008,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1455</v>
+        <v>1500</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1456</v>
+        <v>1501</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -20778,7 +21031,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1457</v>
+        <v>1502</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -20787,10 +21040,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1458</v>
+        <v>1503</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1459</v>
+        <v>1504</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -20810,7 +21063,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1460</v>
+        <v>1505</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -20819,10 +21072,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1461</v>
+        <v>1506</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1462</v>
+        <v>1507</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -20842,7 +21095,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1463</v>
+        <v>1508</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -20851,10 +21104,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1464</v>
+        <v>1509</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1465</v>
+        <v>1510</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -20874,7 +21127,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1466</v>
+        <v>1511</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -20883,10 +21136,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1383</v>
+        <v>1419</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1467</v>
+        <v>1512</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -20906,7 +21159,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1468</v>
+        <v>1513</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -20915,10 +21168,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1469</v>
+        <v>1514</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1470</v>
+        <v>1515</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -20938,7 +21191,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1471</v>
+        <v>1516</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -20947,10 +21200,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1472</v>
+        <v>1517</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1473</v>
+        <v>1518</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -20970,7 +21223,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1474</v>
+        <v>1519</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -20979,10 +21232,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1475</v>
+        <v>1520</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1476</v>
+        <v>1521</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -21002,7 +21255,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1477</v>
+        <v>1522</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -21011,10 +21264,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1478</v>
+        <v>1523</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1479</v>
+        <v>1524</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -21034,7 +21287,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1480</v>
+        <v>1525</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -21043,10 +21296,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1481</v>
+        <v>1526</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1482</v>
+        <v>1527</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -21066,7 +21319,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1483</v>
+        <v>1528</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -21075,10 +21328,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1484</v>
+        <v>1529</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1485</v>
+        <v>1530</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -21098,7 +21351,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1486</v>
+        <v>1531</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -21107,10 +21360,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1487</v>
+        <v>1532</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1488</v>
+        <v>1533</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -21130,7 +21383,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1489</v>
+        <v>1534</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -21139,13 +21392,13 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1490</v>
+        <v>1535</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1491</v>
+        <v>1536</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>1492</v>
+        <v>1537</v>
       </c>
       <c r="G462" s="3" t="s">
         <v>22</v>
@@ -21154,25 +21407,25 @@
         <v>2</v>
       </c>
       <c r="I462" s="3" t="s">
-        <v>1493</v>
+        <v>1538</v>
       </c>
       <c r="J462" s="3"/>
       <c r="K462" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L462" s="3" t="s">
-        <v>1494</v>
+        <v>1539</v>
       </c>
       <c r="M462" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N462" s="3" t="s">
-        <v>1495</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
-        <v>1496</v>
+        <v>1541</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>38</v>
@@ -21181,13 +21434,13 @@
         <v>10</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>1497</v>
+        <v>1542</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1498</v>
+        <v>1543</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>1499</v>
+        <v>1544</v>
       </c>
       <c r="G463" s="3" t="s">
         <v>22</v>
@@ -21196,27 +21449,27 @@
         <v>3</v>
       </c>
       <c r="I463" s="3" t="s">
-        <v>1500</v>
+        <v>1545</v>
       </c>
       <c r="J463" s="3" t="s">
-        <v>1501</v>
+        <v>1546</v>
       </c>
       <c r="K463" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L463" s="3" t="s">
-        <v>1502</v>
+        <v>1547</v>
       </c>
       <c r="M463" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N463" s="3" t="s">
-        <v>1503</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
-        <v>1504</v>
+        <v>1549</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>38</v>
@@ -21225,10 +21478,10 @@
         <v>12</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>1505</v>
+        <v>1550</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>1506</v>
+        <v>1551</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="3" t="s">
@@ -21248,7 +21501,7 @@
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
-        <v>1507</v>
+        <v>1552</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>38</v>
@@ -21257,10 +21510,10 @@
         <v>14</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>1508</v>
+        <v>1553</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1509</v>
+        <v>1554</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="3" t="s">
@@ -21275,7 +21528,7 @@
         <v>21</v>
       </c>
       <c r="L465" s="3" t="s">
-        <v>1510</v>
+        <v>1555</v>
       </c>
       <c r="M465" s="3"/>
       <c r="N465" s="3"/>

--- a/master/master.xlsx
+++ b/master/master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4289" uniqueCount="1556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4334" uniqueCount="1596">
   <si>
     <t xml:space="preserve">Master summary (live formulas)</t>
   </si>
@@ -2021,15 +2021,21 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/.env.example</t>
   </si>
   <si>
+    <t xml:space="preserve">Four empty key lines: OpenAI, Groq, OpenRouter, Anthropic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same pattern as the Weekend 03 template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LC164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/.gitignore</t>
+  </si>
+  <si>
     <t xml:space="preserve">Folder mixes class 07 and class 08 (Inside the Model, LLM per your mapping); placed in Langchain</t>
   </si>
   <si>
-    <t xml:space="preserve">LC164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/.gitignore</t>
-  </si>
-  <si>
     <t xml:space="preserve">LC165</t>
   </si>
   <si>
@@ -2045,6 +2051,15 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/Learning/Part - 0 Overview/Common FAQs</t>
   </si>
   <si>
+    <t xml:space="preserve">Six FAQs on LangSmith cost, LangGraph, print vs trace, upgrading, Deep Agents, overkill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2 › 2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added free tier, upgrade ImportError, Deep Agents built on create_agent</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC167</t>
   </si>
   <si>
@@ -2054,6 +2069,15 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/Learning/Part 1  - Environment Setup/commands.txt</t>
   </si>
   <si>
+    <t xml:space="preserve">Four uv commands for the course project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2 › 2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The uv add lines are now in Ch 2 › 2.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC168</t>
   </si>
   <si>
@@ -2063,6 +2087,15 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/Learning/Part 1  - Environment Setup/setup_check.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Recorded set-up check with a create_agent quickstart run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the recorded content_blocks output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The recorded run printed the first five characters of a key; not copied</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC169</t>
   </si>
   <si>
@@ -2090,12 +2123,27 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/Learning/Part 3  - Messages/messages.py</t>
   </si>
   <si>
+    <t xml:space="preserve">One unfinished line: from langchain.messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A single incomplete import line (a SyntaxError); nothing to teach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested: SyntaxError</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC172</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Langchain Practical/langchain-course/README.md</t>
   </si>
   <si>
+    <t xml:space="preserve">langchain-course folder structure and set-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeats the folder structure and set-up steps</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC173</t>
   </si>
   <si>
@@ -2138,6 +2186,18 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Notebook For Reference/01_landscape_student_notes.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Class 07 landscape notebook: four products, LangSmith, key sentence, timeline, self-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2 › 2.1 to 2.5, 2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added official-docs line on LangGraph, OpenTelemetry, the hand-parsed JSON era, RAG chain example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source of the class 07 summary; most of it was already in Ch 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC179</t>
   </si>
   <si>
@@ -2147,6 +2207,18 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Notebook For Reference/02_03_environment_models_messages_student_notes.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Environment set-up, init_chat_model, message types, AIMessage anatomy, streaming, bind_tools, ToolMessage, free vs local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2 › 2.6; Ch 3 › 3.1 to 3.6; Ch 5 › 5.1, 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added extra uv add packages, message-list rationale, ToolMessage as fourth type, .text vs .content, usage_metadata detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not run (LangChain not installed, keys needed)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC180</t>
   </si>
   <si>
@@ -2156,6 +2228,15 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Notebook For Reference/04_05_prompt_templates_structured_output_student_notes.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Prompt templates, structured output problem, with_structured_output, TypedDict, strategies, template-to-structured pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 3 › 3.8; Ch 4 › 4.1 to 4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added third template example, strategy code and auto-selection, TypedDict guidance, full pipeline</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC181</t>
   </si>
   <si>
@@ -2165,6 +2246,18 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Notebook For Reference/Langchain_structured_output_tools_agents.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Two diagrams: CineBot arc over Parts 5 to 7, and the provider-native-feature decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 4 (intro and 4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added the decision and the CineBot running-example plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two cells only</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC182</t>
   </si>
   <si>
@@ -2174,10 +2267,37 @@
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/Notebook For Reference/Revision_Parts_1-4.ipynb</t>
   </si>
   <si>
+    <t xml:space="preserve">Revision notebook: landscape, set-up, models and messages, batching, tool loop by hand, prompt templates, braces bug, MessagesPlaceholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2 › 2.3, 2.6; Ch 3 › 3.3, 3.4, 3.7, 3.8; Ch 5 › 5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-check questions on runtime.state vs runtime.context and INVALID_PROMPT_INPUT: the notebook does not teach them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added temperature demo, HumanMessage name and id, message shapes, batch order, curly-braces bug, MessagesPlaceholder, tool loop by hand, analogies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source quirk: step 2 of the by-hand loop runs get_weather for a set_password request (TypeError, tested); corrected version in Ch 5. Not run against a model</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC183</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend 04 - 18-19 Jul/07-08 - 18-19 Jul - LangChain Family &amp; the Model Layer/README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 07-08 folder overview and notebook table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain › Ch 2, Ch 3, Ch 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeats the class 07 and 08 summaries and a notebook table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colab links held with COLAB_NOTEBOOKS.md for the Langchain book</t>
   </si>
   <si>
     <t xml:space="preserve">LC184</t>
@@ -5257,7 +5377,7 @@
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,B$3)</f>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,C$3)</f>
@@ -5265,7 +5385,7 @@
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,D$3)</f>
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,E$3)</f>
@@ -5273,7 +5393,7 @@
       </c>
       <c r="F7" s="3" t="n">
         <f aca="false">COUNTIFS(Master!$C$2:$C$465,$A7,Master!$H$2:$H$465,F$3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">SUM(B7:F7)</f>
@@ -5377,7 +5497,7 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">SUM(B4:B10)</f>
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(C4:C10)</f>
@@ -5385,7 +5505,7 @@
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">SUM(D4:D10)</f>
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">SUM(E4:E10)</f>
@@ -5393,7 +5513,7 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">SUM(F4:F10)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">SUM(G4:G10)</f>
@@ -5431,7 +5551,7 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A14)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -5446,7 +5566,7 @@
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A15)</f>
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -5491,7 +5611,7 @@
       </c>
       <c r="B18" s="3" t="n">
         <f aca="false">COUNTIF(Master!$K$2:$K$465,A18)</f>
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5506,7 +5626,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Read fully")</f>
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5521,7 +5641,7 @@
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(Master!$G$2:$G$465,"Not read")</f>
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -11463,27 +11583,35 @@
       <c r="E164" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="F164" s="3"/>
+      <c r="F164" s="3" t="s">
+        <v>665</v>
+      </c>
       <c r="G164" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I164" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>610</v>
+      </c>
       <c r="J164" s="3"/>
       <c r="K164" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L164" s="3"/>
-      <c r="M164" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L164" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="M164" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N164" s="3" t="s">
-        <v>665</v>
+        <v>612</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>38</v>
@@ -11495,7 +11623,7 @@
         <v>45</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
@@ -11514,12 +11642,12 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>38</v>
@@ -11531,7 +11659,7 @@
         <v>69</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
@@ -11550,12 +11678,12 @@
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>38</v>
@@ -11564,32 +11692,38 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="F167" s="3"/>
+        <v>674</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>675</v>
+      </c>
       <c r="G167" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I167" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>676</v>
+      </c>
       <c r="J167" s="3"/>
       <c r="K167" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L167" s="3"/>
-      <c r="M167" s="3"/>
-      <c r="N167" s="3" t="s">
-        <v>665</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L167" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="M167" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N167" s="3"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>38</v>
@@ -11598,32 +11732,38 @@
         <v>11</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="F168" s="3"/>
+        <v>680</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>681</v>
+      </c>
       <c r="G168" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I168" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>682</v>
+      </c>
       <c r="J168" s="3"/>
       <c r="K168" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L168" s="3"/>
-      <c r="M168" s="3"/>
-      <c r="N168" s="3" t="s">
-        <v>665</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L168" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="M168" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N168" s="3"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>38</v>
@@ -11632,32 +11772,40 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="F169" s="3"/>
+        <v>686</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>687</v>
+      </c>
       <c r="G169" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I169" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>682</v>
+      </c>
       <c r="J169" s="3"/>
       <c r="K169" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L169" s="3"/>
-      <c r="M169" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L169" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="M169" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N169" s="3" t="s">
-        <v>665</v>
+        <v>689</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>38</v>
@@ -11666,10 +11814,10 @@
         <v>11</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
@@ -11686,12 +11834,12 @@
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>38</v>
@@ -11700,10 +11848,10 @@
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
@@ -11720,12 +11868,12 @@
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>38</v>
@@ -11734,32 +11882,38 @@
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="F172" s="3"/>
+        <v>698</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>699</v>
+      </c>
       <c r="G172" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L172" s="3"/>
-      <c r="M172" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L172" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="M172" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N172" s="3" t="s">
-        <v>665</v>
+        <v>701</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>38</v>
@@ -11771,29 +11925,35 @@
         <v>58</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="F173" s="3"/>
+        <v>703</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>704</v>
+      </c>
       <c r="G173" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I173" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>682</v>
+      </c>
       <c r="J173" s="3"/>
       <c r="K173" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L173" s="3"/>
-      <c r="M173" s="3"/>
-      <c r="N173" s="3" t="s">
-        <v>665</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L173" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="M173" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="N173" s="3"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>38</v>
@@ -11805,7 +11965,7 @@
         <v>130</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -11822,12 +11982,12 @@
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
       <c r="N174" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>38</v>
@@ -11839,7 +11999,7 @@
         <v>77</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
@@ -11858,12 +12018,12 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>38</v>
@@ -11875,7 +12035,7 @@
         <v>349</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
@@ -11894,12 +12054,12 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>38</v>
@@ -11911,7 +12071,7 @@
         <v>89</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
@@ -11930,12 +12090,12 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>38</v>
@@ -11944,10 +12104,10 @@
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
@@ -11964,12 +12124,12 @@
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
       <c r="N178" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>38</v>
@@ -11978,32 +12138,40 @@
         <v>11</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="F179" s="3"/>
+        <v>719</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>720</v>
+      </c>
       <c r="G179" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I179" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>721</v>
+      </c>
       <c r="J179" s="3"/>
       <c r="K179" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L179" s="3"/>
-      <c r="M179" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L179" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="M179" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N179" s="3" t="s">
-        <v>665</v>
+        <v>723</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>38</v>
@@ -12012,32 +12180,40 @@
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="F180" s="3"/>
+        <v>726</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>727</v>
+      </c>
       <c r="G180" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I180" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>728</v>
+      </c>
       <c r="J180" s="3"/>
       <c r="K180" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L180" s="3"/>
-      <c r="M180" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L180" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="M180" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N180" s="3" t="s">
-        <v>665</v>
+        <v>730</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>38</v>
@@ -12046,32 +12222,40 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="F181" s="3"/>
+        <v>733</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>734</v>
+      </c>
       <c r="G181" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I181" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>735</v>
+      </c>
       <c r="J181" s="3"/>
       <c r="K181" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L181" s="3"/>
-      <c r="M181" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L181" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="M181" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N181" s="3" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>38</v>
@@ -12080,32 +12264,40 @@
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="F182" s="3"/>
+        <v>739</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>740</v>
+      </c>
       <c r="G182" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I182" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>741</v>
+      </c>
       <c r="J182" s="3"/>
       <c r="K182" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L182" s="3"/>
-      <c r="M182" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L182" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="M182" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N182" s="3" t="s">
-        <v>665</v>
+        <v>743</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>713</v>
+        <v>744</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>38</v>
@@ -12114,32 +12306,42 @@
         <v>11</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="F183" s="3"/>
+        <v>746</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>747</v>
+      </c>
       <c r="G183" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I183" s="3"/>
-      <c r="J183" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>749</v>
+      </c>
       <c r="K183" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L183" s="3"/>
-      <c r="M183" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="L183" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="M183" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N183" s="3" t="s">
-        <v>665</v>
+        <v>751</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>716</v>
+        <v>752</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>38</v>
@@ -12151,29 +12353,37 @@
         <v>58</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="F184" s="3"/>
+        <v>753</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>754</v>
+      </c>
       <c r="G184" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I184" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>755</v>
+      </c>
       <c r="J184" s="3"/>
       <c r="K184" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L184" s="3"/>
-      <c r="M184" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="L184" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="M184" s="3" t="s">
+        <v>525</v>
+      </c>
       <c r="N184" s="3" t="s">
-        <v>665</v>
+        <v>757</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>718</v>
+        <v>758</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>38</v>
@@ -12185,7 +12395,7 @@
         <v>58</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>719</v>
+        <v>759</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="3" t="s">
@@ -12202,12 +12412,12 @@
       <c r="L185" s="3"/>
       <c r="M185" s="3"/>
       <c r="N185" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>720</v>
+        <v>760</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>38</v>
@@ -12216,10 +12426,10 @@
         <v>11</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>721</v>
+        <v>761</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="3" t="s">
@@ -12236,12 +12446,12 @@
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
       <c r="N186" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>724</v>
+        <v>764</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>38</v>
@@ -12250,10 +12460,10 @@
         <v>11</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>725</v>
+        <v>765</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>726</v>
+        <v>766</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
@@ -12270,12 +12480,12 @@
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
       <c r="N187" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>727</v>
+        <v>767</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>38</v>
@@ -12284,10 +12494,10 @@
         <v>11</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>728</v>
+        <v>768</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>729</v>
+        <v>769</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="3" t="s">
@@ -12304,12 +12514,12 @@
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
       <c r="N188" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>38</v>
@@ -12318,10 +12528,10 @@
         <v>11</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>731</v>
+        <v>771</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="3" t="s">
@@ -12338,12 +12548,12 @@
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>733</v>
+        <v>773</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>38</v>
@@ -12352,10 +12562,10 @@
         <v>11</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>734</v>
+        <v>774</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>735</v>
+        <v>775</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
@@ -12372,12 +12582,12 @@
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>736</v>
+        <v>776</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>38</v>
@@ -12386,10 +12596,10 @@
         <v>11</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>737</v>
+        <v>777</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>738</v>
+        <v>778</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
@@ -12406,12 +12616,12 @@
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
       <c r="N191" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>739</v>
+        <v>779</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>38</v>
@@ -12420,10 +12630,10 @@
         <v>11</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>741</v>
+        <v>781</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
@@ -12440,12 +12650,12 @@
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
       <c r="N192" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>38</v>
@@ -12454,10 +12664,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>743</v>
+        <v>783</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>744</v>
+        <v>784</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
@@ -12474,12 +12684,12 @@
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
       <c r="N193" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>745</v>
+        <v>785</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>38</v>
@@ -12488,10 +12698,10 @@
         <v>11</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>746</v>
+        <v>786</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>747</v>
+        <v>787</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
@@ -12508,12 +12718,12 @@
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
       <c r="N194" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>748</v>
+        <v>788</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>38</v>
@@ -12525,7 +12735,7 @@
         <v>58</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>749</v>
+        <v>789</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
@@ -12542,12 +12752,12 @@
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
       <c r="N195" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>750</v>
+        <v>790</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>38</v>
@@ -12559,7 +12769,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>751</v>
+        <v>791</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
@@ -12576,12 +12786,12 @@
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
       <c r="N196" s="3" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>38</v>
@@ -12590,10 +12800,10 @@
         <v>11</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>753</v>
+        <v>793</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>754</v>
+        <v>794</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
@@ -12615,7 +12825,7 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>755</v>
+        <v>795</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -12624,10 +12834,10 @@
         <v>11</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>756</v>
+        <v>796</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>757</v>
+        <v>797</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
@@ -12647,7 +12857,7 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>758</v>
+        <v>798</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>38</v>
@@ -12656,10 +12866,10 @@
         <v>11</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>759</v>
+        <v>799</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
@@ -12679,7 +12889,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>761</v>
+        <v>801</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>38</v>
@@ -12688,10 +12898,10 @@
         <v>11</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>762</v>
+        <v>802</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>763</v>
+        <v>803</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
@@ -12711,7 +12921,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>764</v>
+        <v>804</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>38</v>
@@ -12720,10 +12930,10 @@
         <v>11</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>765</v>
+        <v>805</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
@@ -12743,7 +12953,7 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>767</v>
+        <v>807</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>38</v>
@@ -12752,10 +12962,10 @@
         <v>11</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>768</v>
+        <v>808</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
@@ -12775,7 +12985,7 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>38</v>
@@ -12787,7 +12997,7 @@
         <v>58</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>771</v>
+        <v>811</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
@@ -12807,7 +13017,7 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>772</v>
+        <v>812</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>38</v>
@@ -12819,7 +13029,7 @@
         <v>58</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>773</v>
+        <v>813</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
@@ -12839,7 +13049,7 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>774</v>
+        <v>814</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>38</v>
@@ -12848,10 +13058,10 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>753</v>
+        <v>793</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
@@ -12873,7 +13083,7 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>776</v>
+        <v>816</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>38</v>
@@ -12882,10 +13092,10 @@
         <v>11</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>756</v>
+        <v>796</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>777</v>
+        <v>817</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
@@ -12905,7 +13115,7 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>778</v>
+        <v>818</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>38</v>
@@ -12914,10 +13124,10 @@
         <v>11</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>779</v>
+        <v>819</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
@@ -12939,7 +13149,7 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>781</v>
+        <v>821</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>38</v>
@@ -12948,10 +13158,10 @@
         <v>11</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>765</v>
+        <v>805</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>782</v>
+        <v>822</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
@@ -12971,7 +13181,7 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>783</v>
+        <v>823</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>38</v>
@@ -12983,7 +13193,7 @@
         <v>58</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>784</v>
+        <v>824</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
@@ -13003,7 +13213,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>785</v>
+        <v>825</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>38</v>
@@ -13015,7 +13225,7 @@
         <v>58</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
@@ -13035,7 +13245,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>38</v>
@@ -13047,7 +13257,7 @@
         <v>58</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
@@ -13067,7 +13277,7 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>789</v>
+        <v>829</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>38</v>
@@ -13076,10 +13286,10 @@
         <v>11</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>790</v>
+        <v>830</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>791</v>
+        <v>831</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
@@ -13101,7 +13311,7 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>38</v>
@@ -13110,10 +13320,10 @@
         <v>11</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3" t="s">
@@ -13133,7 +13343,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>795</v>
+        <v>835</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>38</v>
@@ -13142,10 +13352,10 @@
         <v>11</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>796</v>
+        <v>836</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>797</v>
+        <v>837</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="3" t="s">
@@ -13165,7 +13375,7 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>798</v>
+        <v>838</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>38</v>
@@ -13177,7 +13387,7 @@
         <v>55</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>799</v>
+        <v>839</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="3" t="s">
@@ -13197,7 +13407,7 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>38</v>
@@ -13206,10 +13416,10 @@
         <v>12</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>801</v>
+        <v>841</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>802</v>
+        <v>842</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
@@ -13229,7 +13439,7 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="s">
-        <v>803</v>
+        <v>843</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>38</v>
@@ -13241,7 +13451,7 @@
         <v>212</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>804</v>
+        <v>844</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="3" t="s">
@@ -13261,7 +13471,7 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="s">
-        <v>805</v>
+        <v>845</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>38</v>
@@ -13273,7 +13483,7 @@
         <v>45</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>806</v>
+        <v>846</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3" t="s">
@@ -13295,7 +13505,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="s">
-        <v>807</v>
+        <v>847</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>38</v>
@@ -13307,7 +13517,7 @@
         <v>69</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>808</v>
+        <v>848</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3" t="s">
@@ -13329,7 +13539,7 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="s">
-        <v>809</v>
+        <v>849</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>38</v>
@@ -13341,7 +13551,7 @@
         <v>58</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3" t="s">
@@ -13361,7 +13571,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="s">
-        <v>811</v>
+        <v>851</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>38</v>
@@ -13373,7 +13583,7 @@
         <v>77</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>812</v>
+        <v>852</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3" t="s">
@@ -13395,7 +13605,7 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="s">
-        <v>813</v>
+        <v>853</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>38</v>
@@ -13407,7 +13617,7 @@
         <v>80</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>814</v>
+        <v>854</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="3" t="s">
@@ -13427,7 +13637,7 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="s">
-        <v>815</v>
+        <v>855</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>38</v>
@@ -13439,7 +13649,7 @@
         <v>86</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>816</v>
+        <v>856</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="3" t="s">
@@ -13459,7 +13669,7 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="s">
-        <v>817</v>
+        <v>857</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>38</v>
@@ -13471,7 +13681,7 @@
         <v>89</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>818</v>
+        <v>858</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="3" t="s">
@@ -13493,7 +13703,7 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="s">
-        <v>819</v>
+        <v>859</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>38</v>
@@ -13505,7 +13715,7 @@
         <v>265</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="3" t="s">
@@ -13525,7 +13735,7 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>821</v>
+        <v>861</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>38</v>
@@ -13537,7 +13747,7 @@
         <v>58</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>822</v>
+        <v>862</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3" t="s">
@@ -13557,7 +13767,7 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>823</v>
+        <v>863</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>38</v>
@@ -13569,7 +13779,7 @@
         <v>58</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>824</v>
+        <v>864</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3" t="s">
@@ -13589,7 +13799,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>825</v>
+        <v>865</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>38</v>
@@ -13598,10 +13808,10 @@
         <v>13</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>826</v>
+        <v>866</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>827</v>
+        <v>867</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3" t="s">
@@ -13621,7 +13831,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>828</v>
+        <v>868</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>38</v>
@@ -13630,10 +13840,10 @@
         <v>12</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>829</v>
+        <v>869</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>830</v>
+        <v>870</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3" t="s">
@@ -13653,7 +13863,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="s">
-        <v>831</v>
+        <v>871</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>38</v>
@@ -13662,10 +13872,10 @@
         <v>12</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>832</v>
+        <v>872</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>833</v>
+        <v>873</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="3" t="s">
@@ -13685,7 +13895,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>834</v>
+        <v>874</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>38</v>
@@ -13694,10 +13904,10 @@
         <v>12</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>835</v>
+        <v>875</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>836</v>
+        <v>876</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="3" t="s">
@@ -13717,7 +13927,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>837</v>
+        <v>877</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>38</v>
@@ -13729,7 +13939,7 @@
         <v>58</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>838</v>
+        <v>878</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3" t="s">
@@ -13749,7 +13959,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>839</v>
+        <v>879</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>38</v>
@@ -13758,10 +13968,10 @@
         <v>12</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>841</v>
+        <v>881</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3" t="s">
@@ -13783,7 +13993,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="s">
-        <v>842</v>
+        <v>882</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>38</v>
@@ -13795,7 +14005,7 @@
         <v>259</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>843</v>
+        <v>883</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3" t="s">
@@ -13815,7 +14025,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="s">
-        <v>844</v>
+        <v>884</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>38</v>
@@ -13827,7 +14037,7 @@
         <v>262</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>845</v>
+        <v>885</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3" t="s">
@@ -13847,7 +14057,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="s">
-        <v>846</v>
+        <v>886</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>38</v>
@@ -13856,10 +14066,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>847</v>
+        <v>887</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>848</v>
+        <v>888</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="3" t="s">
@@ -13879,7 +14089,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="s">
-        <v>849</v>
+        <v>889</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>38</v>
@@ -13891,7 +14101,7 @@
         <v>58</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>850</v>
+        <v>890</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="3" t="s">
@@ -13911,7 +14121,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>851</v>
+        <v>891</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>38</v>
@@ -13923,7 +14133,7 @@
         <v>58</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>852</v>
+        <v>892</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="3" t="s">
@@ -13943,7 +14153,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>853</v>
+        <v>893</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>38</v>
@@ -13955,7 +14165,7 @@
         <v>61</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>854</v>
+        <v>894</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="3" t="s">
@@ -13975,7 +14185,7 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>855</v>
+        <v>895</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>38</v>
@@ -13987,7 +14197,7 @@
         <v>64</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>856</v>
+        <v>896</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3" t="s">
@@ -14007,7 +14217,7 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>857</v>
+        <v>897</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>38</v>
@@ -14019,7 +14229,7 @@
         <v>58</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>858</v>
+        <v>898</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3" t="s">
@@ -14039,7 +14249,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="s">
-        <v>859</v>
+        <v>899</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>38</v>
@@ -14051,7 +14261,7 @@
         <v>69</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3" t="s">
@@ -14073,7 +14283,7 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="s">
-        <v>861</v>
+        <v>901</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>38</v>
@@ -14085,7 +14295,7 @@
         <v>58</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>862</v>
+        <v>902</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="3" t="s">
@@ -14105,7 +14315,7 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="s">
-        <v>863</v>
+        <v>903</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>38</v>
@@ -14117,7 +14327,7 @@
         <v>127</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>864</v>
+        <v>904</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="3" t="s">
@@ -14137,7 +14347,7 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="s">
-        <v>865</v>
+        <v>905</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>38</v>
@@ -14149,7 +14359,7 @@
         <v>130</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>866</v>
+        <v>906</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
@@ -14169,7 +14379,7 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>867</v>
+        <v>907</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>38</v>
@@ -14181,7 +14391,7 @@
         <v>151</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>868</v>
+        <v>908</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="3" t="s">
@@ -14201,7 +14411,7 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>869</v>
+        <v>909</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>38</v>
@@ -14213,7 +14423,7 @@
         <v>77</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>870</v>
+        <v>910</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="3" t="s">
@@ -14235,7 +14445,7 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="s">
-        <v>871</v>
+        <v>911</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>38</v>
@@ -14247,7 +14457,7 @@
         <v>193</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>872</v>
+        <v>912</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="3" t="s">
@@ -14267,7 +14477,7 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="s">
-        <v>873</v>
+        <v>913</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>38</v>
@@ -14279,7 +14489,7 @@
         <v>196</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>874</v>
+        <v>914</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="3" t="s">
@@ -14301,7 +14511,7 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>875</v>
+        <v>915</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>38</v>
@@ -14313,7 +14523,7 @@
         <v>199</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>876</v>
+        <v>916</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="3" t="s">
@@ -14335,7 +14545,7 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="s">
-        <v>877</v>
+        <v>917</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>38</v>
@@ -14347,7 +14557,7 @@
         <v>135</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>878</v>
+        <v>918</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="3" t="s">
@@ -14369,7 +14579,7 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="s">
-        <v>879</v>
+        <v>919</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>38</v>
@@ -14381,7 +14591,7 @@
         <v>89</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>880</v>
+        <v>920</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="3" t="s">
@@ -14403,7 +14613,7 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="s">
-        <v>881</v>
+        <v>921</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>38</v>
@@ -14415,7 +14625,7 @@
         <v>209</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>882</v>
+        <v>922</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="3" t="s">
@@ -14435,7 +14645,7 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="s">
-        <v>883</v>
+        <v>923</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>38</v>
@@ -14447,7 +14657,7 @@
         <v>69</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>884</v>
+        <v>924</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="3" t="s">
@@ -14469,7 +14679,7 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>885</v>
+        <v>925</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>38</v>
@@ -14481,7 +14691,7 @@
         <v>58</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>886</v>
+        <v>926</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="3" t="s">
@@ -14501,7 +14711,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>887</v>
+        <v>927</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>38</v>
@@ -14513,7 +14723,7 @@
         <v>222</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>888</v>
+        <v>928</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="3" t="s">
@@ -14535,7 +14745,7 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>889</v>
+        <v>929</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>38</v>
@@ -14547,7 +14757,7 @@
         <v>130</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>890</v>
+        <v>930</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="3" t="s">
@@ -14567,7 +14777,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>891</v>
+        <v>931</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>38</v>
@@ -14579,7 +14789,7 @@
         <v>77</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>892</v>
+        <v>932</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="3" t="s">
@@ -14601,7 +14811,7 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>893</v>
+        <v>933</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>38</v>
@@ -14613,7 +14823,7 @@
         <v>61</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>894</v>
+        <v>934</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3" t="s">
@@ -14633,7 +14843,7 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>895</v>
+        <v>935</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>38</v>
@@ -14645,7 +14855,7 @@
         <v>64</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>896</v>
+        <v>936</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="3" t="s">
@@ -14665,7 +14875,7 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>38</v>
@@ -14677,7 +14887,7 @@
         <v>89</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>898</v>
+        <v>938</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="3" t="s">
@@ -14699,7 +14909,7 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="s">
-        <v>899</v>
+        <v>939</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>38</v>
@@ -14711,7 +14921,7 @@
         <v>45</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>900</v>
+        <v>940</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="3" t="s">
@@ -14733,7 +14943,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="s">
-        <v>901</v>
+        <v>941</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>38</v>
@@ -14745,7 +14955,7 @@
         <v>69</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>902</v>
+        <v>942</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="3" t="s">
@@ -14767,7 +14977,7 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="s">
-        <v>903</v>
+        <v>943</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>38</v>
@@ -14779,7 +14989,7 @@
         <v>58</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>904</v>
+        <v>944</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="3" t="s">
@@ -14799,7 +15009,7 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="s">
-        <v>905</v>
+        <v>945</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>38</v>
@@ -14811,7 +15021,7 @@
         <v>74</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>906</v>
+        <v>946</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="3" t="s">
@@ -14831,7 +15041,7 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="s">
-        <v>907</v>
+        <v>947</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>38</v>
@@ -14843,7 +15053,7 @@
         <v>77</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>908</v>
+        <v>948</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="3" t="s">
@@ -14865,7 +15075,7 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="s">
-        <v>909</v>
+        <v>949</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>38</v>
@@ -14877,7 +15087,7 @@
         <v>80</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>910</v>
+        <v>950</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="3" t="s">
@@ -14897,7 +15107,7 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="s">
-        <v>911</v>
+        <v>951</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>38</v>
@@ -14909,7 +15119,7 @@
         <v>83</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>912</v>
+        <v>952</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="3" t="s">
@@ -14929,7 +15139,7 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>913</v>
+        <v>953</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>38</v>
@@ -14941,7 +15151,7 @@
         <v>86</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>914</v>
+        <v>954</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="3" t="s">
@@ -14961,7 +15171,7 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>915</v>
+        <v>955</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>38</v>
@@ -14973,7 +15183,7 @@
         <v>89</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>916</v>
+        <v>956</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="3" t="s">
@@ -14995,7 +15205,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="s">
-        <v>917</v>
+        <v>957</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>38</v>
@@ -15007,7 +15217,7 @@
         <v>58</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="3" t="s">
@@ -15027,7 +15237,7 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="s">
-        <v>919</v>
+        <v>959</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>38</v>
@@ -15039,7 +15249,7 @@
         <v>69</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="3" t="s">
@@ -15061,7 +15271,7 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="s">
-        <v>921</v>
+        <v>961</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>38</v>
@@ -15070,10 +15280,10 @@
         <v>11</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>922</v>
+        <v>962</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>923</v>
+        <v>963</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="3" t="s">
@@ -15093,7 +15303,7 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="s">
-        <v>924</v>
+        <v>964</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>38</v>
@@ -15105,7 +15315,7 @@
         <v>58</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>925</v>
+        <v>965</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
@@ -15125,7 +15335,7 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>926</v>
+        <v>966</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>38</v>
@@ -15134,10 +15344,10 @@
         <v>11</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>927</v>
+        <v>967</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>928</v>
+        <v>968</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="3" t="s">
@@ -15157,7 +15367,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>929</v>
+        <v>969</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>38</v>
@@ -15169,7 +15379,7 @@
         <v>130</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="3" t="s">
@@ -15189,7 +15399,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="s">
-        <v>931</v>
+        <v>971</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>38</v>
@@ -15201,7 +15411,7 @@
         <v>77</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>932</v>
+        <v>972</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="3" t="s">
@@ -15223,7 +15433,7 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="s">
-        <v>933</v>
+        <v>973</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>38</v>
@@ -15235,7 +15445,7 @@
         <v>89</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>934</v>
+        <v>974</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3" t="s">
@@ -15257,7 +15467,7 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="s">
-        <v>935</v>
+        <v>975</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>38</v>
@@ -15269,7 +15479,7 @@
         <v>45</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>936</v>
+        <v>976</v>
       </c>
       <c r="F279" s="3"/>
       <c r="G279" s="3" t="s">
@@ -15288,12 +15498,12 @@
       </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="s">
-        <v>938</v>
+        <v>978</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>38</v>
@@ -15302,10 +15512,10 @@
         <v>11</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>939</v>
+        <v>979</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>940</v>
+        <v>980</v>
       </c>
       <c r="F280" s="3"/>
       <c r="G280" s="3" t="s">
@@ -15322,12 +15532,12 @@
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
       <c r="N280" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>941</v>
+        <v>981</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>38</v>
@@ -15336,10 +15546,10 @@
         <v>11</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>942</v>
+        <v>982</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>943</v>
+        <v>983</v>
       </c>
       <c r="F281" s="3"/>
       <c r="G281" s="3" t="s">
@@ -15356,12 +15566,12 @@
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
       <c r="N281" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>944</v>
+        <v>984</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>38</v>
@@ -15370,10 +15580,10 @@
         <v>11</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>945</v>
+        <v>985</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>946</v>
+        <v>986</v>
       </c>
       <c r="F282" s="3"/>
       <c r="G282" s="3" t="s">
@@ -15392,12 +15602,12 @@
       </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="s">
-        <v>947</v>
+        <v>987</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>38</v>
@@ -15406,10 +15616,10 @@
         <v>11</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>948</v>
+        <v>988</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>949</v>
+        <v>989</v>
       </c>
       <c r="F283" s="3"/>
       <c r="G283" s="3" t="s">
@@ -15426,12 +15636,12 @@
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
       <c r="N283" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="s">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>38</v>
@@ -15440,10 +15650,10 @@
         <v>11</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>951</v>
+        <v>991</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>952</v>
+        <v>992</v>
       </c>
       <c r="F284" s="3"/>
       <c r="G284" s="3" t="s">
@@ -15462,12 +15672,12 @@
       </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>953</v>
+        <v>993</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>38</v>
@@ -15476,10 +15686,10 @@
         <v>11</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>954</v>
+        <v>994</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>955</v>
+        <v>995</v>
       </c>
       <c r="F285" s="3"/>
       <c r="G285" s="3" t="s">
@@ -15496,12 +15706,12 @@
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
       <c r="N285" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>956</v>
+        <v>996</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>38</v>
@@ -15510,10 +15720,10 @@
         <v>11</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>957</v>
+        <v>997</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>958</v>
+        <v>998</v>
       </c>
       <c r="F286" s="3"/>
       <c r="G286" s="3" t="s">
@@ -15532,12 +15742,12 @@
       </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>959</v>
+        <v>999</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>38</v>
@@ -15546,10 +15756,10 @@
         <v>11</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>961</v>
+        <v>1001</v>
       </c>
       <c r="F287" s="3"/>
       <c r="G287" s="3" t="s">
@@ -15566,12 +15776,12 @@
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
       <c r="N287" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>962</v>
+        <v>1002</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>38</v>
@@ -15583,7 +15793,7 @@
         <v>77</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>963</v>
+        <v>1003</v>
       </c>
       <c r="F288" s="3"/>
       <c r="G288" s="3" t="s">
@@ -15602,12 +15812,12 @@
       </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>964</v>
+        <v>1004</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>38</v>
@@ -15619,7 +15829,7 @@
         <v>89</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>965</v>
+        <v>1005</v>
       </c>
       <c r="F289" s="3"/>
       <c r="G289" s="3" t="s">
@@ -15638,12 +15848,12 @@
       </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>966</v>
+        <v>1006</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>38</v>
@@ -15655,7 +15865,7 @@
         <v>45</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>967</v>
+        <v>1007</v>
       </c>
       <c r="F290" s="3"/>
       <c r="G290" s="3" t="s">
@@ -15677,7 +15887,7 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="s">
-        <v>968</v>
+        <v>1008</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>38</v>
@@ -15686,10 +15896,10 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>969</v>
+        <v>1009</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>970</v>
+        <v>1010</v>
       </c>
       <c r="F291" s="3"/>
       <c r="G291" s="3" t="s">
@@ -15709,7 +15919,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="s">
-        <v>971</v>
+        <v>1011</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>38</v>
@@ -15718,10 +15928,10 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>972</v>
+        <v>1012</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>973</v>
+        <v>1013</v>
       </c>
       <c r="F292" s="3"/>
       <c r="G292" s="3" t="s">
@@ -15741,7 +15951,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="s">
-        <v>974</v>
+        <v>1014</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>38</v>
@@ -15750,10 +15960,10 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>975</v>
+        <v>1015</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>976</v>
+        <v>1016</v>
       </c>
       <c r="F293" s="3"/>
       <c r="G293" s="3" t="s">
@@ -15773,7 +15983,7 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="s">
-        <v>977</v>
+        <v>1017</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>38</v>
@@ -15782,10 +15992,10 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>978</v>
+        <v>1018</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>979</v>
+        <v>1019</v>
       </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3" t="s">
@@ -15805,7 +16015,7 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="s">
-        <v>980</v>
+        <v>1020</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>38</v>
@@ -15814,10 +16024,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>981</v>
+        <v>1021</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>982</v>
+        <v>1022</v>
       </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3" t="s">
@@ -15837,7 +16047,7 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="s">
-        <v>983</v>
+        <v>1023</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>38</v>
@@ -15846,10 +16056,10 @@
         <v>11</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>984</v>
+        <v>1024</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3" t="s">
@@ -15869,7 +16079,7 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="s">
-        <v>986</v>
+        <v>1026</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>38</v>
@@ -15881,7 +16091,7 @@
         <v>58</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>987</v>
+        <v>1027</v>
       </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3" t="s">
@@ -15901,7 +16111,7 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="s">
-        <v>988</v>
+        <v>1028</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>38</v>
@@ -15913,7 +16123,7 @@
         <v>77</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>989</v>
+        <v>1029</v>
       </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3" t="s">
@@ -15935,7 +16145,7 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="s">
-        <v>990</v>
+        <v>1030</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>38</v>
@@ -15944,10 +16154,10 @@
         <v>11</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>991</v>
+        <v>1031</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3" t="s">
@@ -15967,7 +16177,7 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>38</v>
@@ -15979,7 +16189,7 @@
         <v>89</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="F300" s="3"/>
       <c r="G300" s="3" t="s">
@@ -16001,7 +16211,7 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>995</v>
+        <v>1035</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>38</v>
@@ -16010,10 +16220,10 @@
         <v>13</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>996</v>
+        <v>1036</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="F301" s="3"/>
       <c r="G301" s="3" t="s">
@@ -16035,7 +16245,7 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>998</v>
+        <v>1038</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>38</v>
@@ -16044,10 +16254,10 @@
         <v>13</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>999</v>
+        <v>1039</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="F302" s="3"/>
       <c r="G302" s="3" t="s">
@@ -16069,7 +16279,7 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="s">
-        <v>1001</v>
+        <v>1041</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>38</v>
@@ -16081,7 +16291,7 @@
         <v>367</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
@@ -16101,7 +16311,7 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="s">
-        <v>1003</v>
+        <v>1043</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>38</v>
@@ -16110,10 +16320,10 @@
         <v>13</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>1004</v>
+        <v>1044</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>1005</v>
+        <v>1045</v>
       </c>
       <c r="F304" s="3"/>
       <c r="G304" s="3" t="s">
@@ -16135,7 +16345,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>1006</v>
+        <v>1046</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>38</v>
@@ -16147,7 +16357,7 @@
         <v>45</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>1007</v>
+        <v>1047</v>
       </c>
       <c r="F305" s="3"/>
       <c r="G305" s="3" t="s">
@@ -16169,7 +16379,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>1008</v>
+        <v>1048</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>38</v>
@@ -16178,10 +16388,10 @@
         <v>13</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>1009</v>
+        <v>1049</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>1010</v>
+        <v>1050</v>
       </c>
       <c r="F306" s="3"/>
       <c r="G306" s="3" t="s">
@@ -16201,7 +16411,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="s">
-        <v>1011</v>
+        <v>1051</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>38</v>
@@ -16210,10 +16420,10 @@
         <v>13</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>1012</v>
+        <v>1052</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>1013</v>
+        <v>1053</v>
       </c>
       <c r="F307" s="3"/>
       <c r="G307" s="3" t="s">
@@ -16235,7 +16445,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="s">
-        <v>1014</v>
+        <v>1054</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>38</v>
@@ -16247,7 +16457,7 @@
         <v>58</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>1015</v>
+        <v>1055</v>
       </c>
       <c r="F308" s="3"/>
       <c r="G308" s="3" t="s">
@@ -16267,7 +16477,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="s">
-        <v>1016</v>
+        <v>1056</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>38</v>
@@ -16279,7 +16489,7 @@
         <v>86</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>1017</v>
+        <v>1057</v>
       </c>
       <c r="F309" s="3"/>
       <c r="G309" s="3" t="s">
@@ -16299,7 +16509,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="s">
-        <v>1018</v>
+        <v>1058</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>38</v>
@@ -16308,10 +16518,10 @@
         <v>13</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>1019</v>
+        <v>1059</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>1020</v>
+        <v>1060</v>
       </c>
       <c r="F310" s="3"/>
       <c r="G310" s="3" t="s">
@@ -16331,7 +16541,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>1021</v>
+        <v>1061</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>38</v>
@@ -16340,10 +16550,10 @@
         <v>13</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>1022</v>
+        <v>1062</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>1023</v>
+        <v>1063</v>
       </c>
       <c r="F311" s="3"/>
       <c r="G311" s="3" t="s">
@@ -16363,7 +16573,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>1024</v>
+        <v>1064</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>38</v>
@@ -16375,7 +16585,7 @@
         <v>361</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>1025</v>
+        <v>1065</v>
       </c>
       <c r="F312" s="3"/>
       <c r="G312" s="3" t="s">
@@ -16395,7 +16605,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="s">
-        <v>1026</v>
+        <v>1066</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>38</v>
@@ -16407,7 +16617,7 @@
         <v>86</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>1027</v>
+        <v>1067</v>
       </c>
       <c r="F313" s="3"/>
       <c r="G313" s="3" t="s">
@@ -16427,7 +16637,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="s">
-        <v>1028</v>
+        <v>1068</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>38</v>
@@ -16436,10 +16646,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>1029</v>
+        <v>1069</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>1030</v>
+        <v>1070</v>
       </c>
       <c r="F314" s="3"/>
       <c r="G314" s="3" t="s">
@@ -16459,7 +16669,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>1031</v>
+        <v>1071</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>38</v>
@@ -16471,7 +16681,7 @@
         <v>130</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>1032</v>
+        <v>1072</v>
       </c>
       <c r="F315" s="3"/>
       <c r="G315" s="3" t="s">
@@ -16491,7 +16701,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>1033</v>
+        <v>1073</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>38</v>
@@ -16500,10 +16710,10 @@
         <v>13</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>1034</v>
+        <v>1074</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>1035</v>
+        <v>1075</v>
       </c>
       <c r="F316" s="3"/>
       <c r="G316" s="3" t="s">
@@ -16523,7 +16733,7 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="s">
-        <v>1036</v>
+        <v>1076</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>38</v>
@@ -16535,7 +16745,7 @@
         <v>86</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>1037</v>
+        <v>1077</v>
       </c>
       <c r="F317" s="3"/>
       <c r="G317" s="3" t="s">
@@ -16555,7 +16765,7 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="s">
-        <v>1038</v>
+        <v>1078</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>38</v>
@@ -16564,10 +16774,10 @@
         <v>13</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>1039</v>
+        <v>1079</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>1040</v>
+        <v>1080</v>
       </c>
       <c r="F318" s="3"/>
       <c r="G318" s="3" t="s">
@@ -16587,7 +16797,7 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>1041</v>
+        <v>1081</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>38</v>
@@ -16599,7 +16809,7 @@
         <v>86</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>1042</v>
+        <v>1082</v>
       </c>
       <c r="F319" s="3"/>
       <c r="G319" s="3" t="s">
@@ -16619,7 +16829,7 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>1043</v>
+        <v>1083</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>38</v>
@@ -16628,10 +16838,10 @@
         <v>13</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>1044</v>
+        <v>1084</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>1045</v>
+        <v>1085</v>
       </c>
       <c r="F320" s="3"/>
       <c r="G320" s="3" t="s">
@@ -16651,7 +16861,7 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="s">
-        <v>1046</v>
+        <v>1086</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>38</v>
@@ -16663,7 +16873,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>1047</v>
+        <v>1087</v>
       </c>
       <c r="F321" s="3"/>
       <c r="G321" s="3" t="s">
@@ -16683,7 +16893,7 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="s">
-        <v>1048</v>
+        <v>1088</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>38</v>
@@ -16692,10 +16902,10 @@
         <v>13</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>1049</v>
+        <v>1089</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>1050</v>
+        <v>1090</v>
       </c>
       <c r="F322" s="3"/>
       <c r="G322" s="3" t="s">
@@ -16715,7 +16925,7 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="s">
-        <v>1051</v>
+        <v>1091</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>38</v>
@@ -16724,10 +16934,10 @@
         <v>13</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>1052</v>
+        <v>1092</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>1053</v>
+        <v>1093</v>
       </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3" t="s">
@@ -16747,7 +16957,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>1054</v>
+        <v>1094</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>38</v>
@@ -16756,10 +16966,10 @@
         <v>13</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>1055</v>
+        <v>1095</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>1056</v>
+        <v>1096</v>
       </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3" t="s">
@@ -16779,7 +16989,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>1057</v>
+        <v>1097</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>38</v>
@@ -16788,10 +16998,10 @@
         <v>13</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>1058</v>
+        <v>1098</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>1059</v>
+        <v>1099</v>
       </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3" t="s">
@@ -16811,7 +17021,7 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="s">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>38</v>
@@ -16820,10 +17030,10 @@
         <v>13</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>1061</v>
+        <v>1101</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>1062</v>
+        <v>1102</v>
       </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3" t="s">
@@ -16843,7 +17053,7 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="s">
-        <v>1063</v>
+        <v>1103</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>38</v>
@@ -16852,10 +17062,10 @@
         <v>13</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>1065</v>
+        <v>1105</v>
       </c>
       <c r="F327" s="3"/>
       <c r="G327" s="3" t="s">
@@ -16875,7 +17085,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>1066</v>
+        <v>1106</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>38</v>
@@ -16884,10 +17094,10 @@
         <v>13</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>1067</v>
+        <v>1107</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>1068</v>
+        <v>1108</v>
       </c>
       <c r="F328" s="3"/>
       <c r="G328" s="3" t="s">
@@ -16907,7 +17117,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>1069</v>
+        <v>1109</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>38</v>
@@ -16916,10 +17126,10 @@
         <v>13</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>1070</v>
+        <v>1110</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>1071</v>
+        <v>1111</v>
       </c>
       <c r="F329" s="3"/>
       <c r="G329" s="3" t="s">
@@ -16941,7 +17151,7 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="s">
-        <v>1072</v>
+        <v>1112</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>38</v>
@@ -16950,10 +17160,10 @@
         <v>13</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>1073</v>
+        <v>1113</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>1074</v>
+        <v>1114</v>
       </c>
       <c r="F330" s="3"/>
       <c r="G330" s="3" t="s">
@@ -16975,7 +17185,7 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>1075</v>
+        <v>1115</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>38</v>
@@ -16984,10 +17194,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>1076</v>
+        <v>1116</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>1077</v>
+        <v>1117</v>
       </c>
       <c r="F331" s="3"/>
       <c r="G331" s="3" t="s">
@@ -17007,7 +17217,7 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>1078</v>
+        <v>1118</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>38</v>
@@ -17019,7 +17229,7 @@
         <v>196</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>1079</v>
+        <v>1119</v>
       </c>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
@@ -17041,7 +17251,7 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="s">
-        <v>1080</v>
+        <v>1120</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>38</v>
@@ -17050,10 +17260,10 @@
         <v>13</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1081</v>
+        <v>1121</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1082</v>
+        <v>1122</v>
       </c>
       <c r="F333" s="3"/>
       <c r="G333" s="3" t="s">
@@ -17075,7 +17285,7 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>1083</v>
+        <v>1123</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>38</v>
@@ -17084,10 +17294,10 @@
         <v>13</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1084</v>
+        <v>1124</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1085</v>
+        <v>1125</v>
       </c>
       <c r="F334" s="3"/>
       <c r="G334" s="3" t="s">
@@ -17109,7 +17319,7 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="s">
-        <v>1086</v>
+        <v>1126</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>38</v>
@@ -17118,10 +17328,10 @@
         <v>13</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1087</v>
+        <v>1127</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1088</v>
+        <v>1128</v>
       </c>
       <c r="F335" s="3"/>
       <c r="G335" s="3" t="s">
@@ -17141,7 +17351,7 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="s">
-        <v>1089</v>
+        <v>1129</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>38</v>
@@ -17150,10 +17360,10 @@
         <v>13</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1090</v>
+        <v>1130</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1091</v>
+        <v>1131</v>
       </c>
       <c r="F336" s="3"/>
       <c r="G336" s="3" t="s">
@@ -17173,7 +17383,7 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="s">
-        <v>1092</v>
+        <v>1132</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>38</v>
@@ -17182,10 +17392,10 @@
         <v>13</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1093</v>
+        <v>1133</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1094</v>
+        <v>1134</v>
       </c>
       <c r="F337" s="3"/>
       <c r="G337" s="3" t="s">
@@ -17205,7 +17415,7 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="s">
-        <v>1095</v>
+        <v>1135</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>38</v>
@@ -17214,10 +17424,10 @@
         <v>13</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1096</v>
+        <v>1136</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1097</v>
+        <v>1137</v>
       </c>
       <c r="F338" s="3"/>
       <c r="G338" s="3" t="s">
@@ -17239,7 +17449,7 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>1098</v>
+        <v>1138</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>38</v>
@@ -17248,10 +17458,10 @@
         <v>13</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1099</v>
+        <v>1139</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1100</v>
+        <v>1140</v>
       </c>
       <c r="F339" s="3"/>
       <c r="G339" s="3" t="s">
@@ -17271,7 +17481,7 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>1101</v>
+        <v>1141</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>38</v>
@@ -17280,10 +17490,10 @@
         <v>13</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1102</v>
+        <v>1142</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1103</v>
+        <v>1143</v>
       </c>
       <c r="F340" s="3"/>
       <c r="G340" s="3" t="s">
@@ -17303,7 +17513,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>1104</v>
+        <v>1144</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>38</v>
@@ -17312,10 +17522,10 @@
         <v>13</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1105</v>
+        <v>1145</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1106</v>
+        <v>1146</v>
       </c>
       <c r="F341" s="3"/>
       <c r="G341" s="3" t="s">
@@ -17335,7 +17545,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>1107</v>
+        <v>1147</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>38</v>
@@ -17344,10 +17554,10 @@
         <v>13</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1108</v>
+        <v>1148</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>1109</v>
+        <v>1149</v>
       </c>
       <c r="F342" s="3"/>
       <c r="G342" s="3" t="s">
@@ -17367,7 +17577,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>1110</v>
+        <v>1150</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>38</v>
@@ -17376,10 +17586,10 @@
         <v>13</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1111</v>
+        <v>1151</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>1112</v>
+        <v>1152</v>
       </c>
       <c r="F343" s="3"/>
       <c r="G343" s="3" t="s">
@@ -17399,7 +17609,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>1113</v>
+        <v>1153</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>38</v>
@@ -17408,10 +17618,10 @@
         <v>13</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1114</v>
+        <v>1154</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1115</v>
+        <v>1155</v>
       </c>
       <c r="F344" s="3"/>
       <c r="G344" s="3" t="s">
@@ -17431,7 +17641,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>1116</v>
+        <v>1156</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>38</v>
@@ -17440,10 +17650,10 @@
         <v>13</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1117</v>
+        <v>1157</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1118</v>
+        <v>1158</v>
       </c>
       <c r="F345" s="3"/>
       <c r="G345" s="3" t="s">
@@ -17463,7 +17673,7 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>1119</v>
+        <v>1159</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>38</v>
@@ -17472,10 +17682,10 @@
         <v>13</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1121</v>
+        <v>1161</v>
       </c>
       <c r="F346" s="3"/>
       <c r="G346" s="3" t="s">
@@ -17495,7 +17705,7 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>1122</v>
+        <v>1162</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>38</v>
@@ -17504,10 +17714,10 @@
         <v>13</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1123</v>
+        <v>1163</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1124</v>
+        <v>1164</v>
       </c>
       <c r="F347" s="3"/>
       <c r="G347" s="3" t="s">
@@ -17527,7 +17737,7 @@
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>1125</v>
+        <v>1165</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>38</v>
@@ -17536,10 +17746,10 @@
         <v>13</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1126</v>
+        <v>1166</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1127</v>
+        <v>1167</v>
       </c>
       <c r="F348" s="3"/>
       <c r="G348" s="3" t="s">
@@ -17559,7 +17769,7 @@
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>1128</v>
+        <v>1168</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>38</v>
@@ -17568,10 +17778,10 @@
         <v>13</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1129</v>
+        <v>1169</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1130</v>
+        <v>1170</v>
       </c>
       <c r="F349" s="3"/>
       <c r="G349" s="3" t="s">
@@ -17591,7 +17801,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
-        <v>1131</v>
+        <v>1171</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>38</v>
@@ -17600,10 +17810,10 @@
         <v>13</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1132</v>
+        <v>1172</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1133</v>
+        <v>1173</v>
       </c>
       <c r="F350" s="3"/>
       <c r="G350" s="3" t="s">
@@ -17623,7 +17833,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
-        <v>1134</v>
+        <v>1174</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>38</v>
@@ -17632,10 +17842,10 @@
         <v>13</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1135</v>
+        <v>1175</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1136</v>
+        <v>1176</v>
       </c>
       <c r="F351" s="3"/>
       <c r="G351" s="3" t="s">
@@ -17655,7 +17865,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
-        <v>1137</v>
+        <v>1177</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>38</v>
@@ -17664,10 +17874,10 @@
         <v>13</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1138</v>
+        <v>1178</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1139</v>
+        <v>1179</v>
       </c>
       <c r="F352" s="3"/>
       <c r="G352" s="3" t="s">
@@ -17687,7 +17897,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
-        <v>1140</v>
+        <v>1180</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>38</v>
@@ -17696,10 +17906,10 @@
         <v>13</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1141</v>
+        <v>1181</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1142</v>
+        <v>1182</v>
       </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3" t="s">
@@ -17719,7 +17929,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
-        <v>1143</v>
+        <v>1183</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>38</v>
@@ -17728,10 +17938,10 @@
         <v>13</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1144</v>
+        <v>1184</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1145</v>
+        <v>1185</v>
       </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3" t="s">
@@ -17751,7 +17961,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>1146</v>
+        <v>1186</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>38</v>
@@ -17760,10 +17970,10 @@
         <v>13</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1147</v>
+        <v>1187</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1148</v>
+        <v>1188</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3" t="s">
@@ -17783,7 +17993,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
-        <v>1149</v>
+        <v>1189</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>38</v>
@@ -17792,10 +18002,10 @@
         <v>13</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1150</v>
+        <v>1190</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1151</v>
+        <v>1191</v>
       </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3" t="s">
@@ -17815,7 +18025,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
-        <v>1152</v>
+        <v>1192</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>38</v>
@@ -17824,10 +18034,10 @@
         <v>13</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1153</v>
+        <v>1193</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1154</v>
+        <v>1194</v>
       </c>
       <c r="F357" s="3"/>
       <c r="G357" s="3" t="s">
@@ -17847,7 +18057,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>1155</v>
+        <v>1195</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>38</v>
@@ -17856,10 +18066,10 @@
         <v>13</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1156</v>
+        <v>1196</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1157</v>
+        <v>1197</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="3" t="s">
@@ -17879,7 +18089,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>1158</v>
+        <v>1198</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>38</v>
@@ -17888,10 +18098,10 @@
         <v>13</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1159</v>
+        <v>1199</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="F359" s="3"/>
       <c r="G359" s="3" t="s">
@@ -17911,7 +18121,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
-        <v>1161</v>
+        <v>1201</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>38</v>
@@ -17920,10 +18130,10 @@
         <v>13</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1162</v>
+        <v>1202</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1163</v>
+        <v>1203</v>
       </c>
       <c r="F360" s="3"/>
       <c r="G360" s="3" t="s">
@@ -17943,7 +18153,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>1164</v>
+        <v>1204</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>38</v>
@@ -17952,10 +18162,10 @@
         <v>13</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1165</v>
+        <v>1205</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1166</v>
+        <v>1206</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
@@ -17975,7 +18185,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
-        <v>1167</v>
+        <v>1207</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>38</v>
@@ -17984,10 +18194,10 @@
         <v>13</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1168</v>
+        <v>1208</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1169</v>
+        <v>1209</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="3" t="s">
@@ -18007,7 +18217,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
-        <v>1170</v>
+        <v>1210</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>38</v>
@@ -18016,10 +18226,10 @@
         <v>13</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1171</v>
+        <v>1211</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1172</v>
+        <v>1212</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="3" t="s">
@@ -18039,7 +18249,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
-        <v>1173</v>
+        <v>1213</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>38</v>
@@ -18048,10 +18258,10 @@
         <v>13</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1174</v>
+        <v>1214</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1175</v>
+        <v>1215</v>
       </c>
       <c r="F364" s="3"/>
       <c r="G364" s="3" t="s">
@@ -18071,7 +18281,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
-        <v>1176</v>
+        <v>1216</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>38</v>
@@ -18080,10 +18290,10 @@
         <v>13</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1177</v>
+        <v>1217</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1178</v>
+        <v>1218</v>
       </c>
       <c r="F365" s="3"/>
       <c r="G365" s="3" t="s">
@@ -18103,7 +18313,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
-        <v>1179</v>
+        <v>1219</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>38</v>
@@ -18112,10 +18322,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1180</v>
+        <v>1220</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1181</v>
+        <v>1221</v>
       </c>
       <c r="F366" s="3"/>
       <c r="G366" s="3" t="s">
@@ -18135,7 +18345,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>1182</v>
+        <v>1222</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>38</v>
@@ -18144,10 +18354,10 @@
         <v>13</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1183</v>
+        <v>1223</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1184</v>
+        <v>1224</v>
       </c>
       <c r="F367" s="3"/>
       <c r="G367" s="3" t="s">
@@ -18167,7 +18377,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="s">
-        <v>1185</v>
+        <v>1225</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>38</v>
@@ -18176,10 +18386,10 @@
         <v>13</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1186</v>
+        <v>1226</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1187</v>
+        <v>1227</v>
       </c>
       <c r="F368" s="3"/>
       <c r="G368" s="3" t="s">
@@ -18199,7 +18409,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="s">
-        <v>1188</v>
+        <v>1228</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>38</v>
@@ -18208,10 +18418,10 @@
         <v>13</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1189</v>
+        <v>1229</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1190</v>
+        <v>1230</v>
       </c>
       <c r="F369" s="3"/>
       <c r="G369" s="3" t="s">
@@ -18231,7 +18441,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
-        <v>1191</v>
+        <v>1231</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>38</v>
@@ -18240,10 +18450,10 @@
         <v>13</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1192</v>
+        <v>1232</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1193</v>
+        <v>1233</v>
       </c>
       <c r="F370" s="3"/>
       <c r="G370" s="3" t="s">
@@ -18263,7 +18473,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
-        <v>1194</v>
+        <v>1234</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>38</v>
@@ -18272,10 +18482,10 @@
         <v>13</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1195</v>
+        <v>1235</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1196</v>
+        <v>1236</v>
       </c>
       <c r="F371" s="3"/>
       <c r="G371" s="3" t="s">
@@ -18295,7 +18505,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
-        <v>1197</v>
+        <v>1237</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>38</v>
@@ -18304,10 +18514,10 @@
         <v>13</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1198</v>
+        <v>1238</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1199</v>
+        <v>1239</v>
       </c>
       <c r="F372" s="3"/>
       <c r="G372" s="3" t="s">
@@ -18327,7 +18537,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>38</v>
@@ -18336,10 +18546,10 @@
         <v>13</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1201</v>
+        <v>1241</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1202</v>
+        <v>1242</v>
       </c>
       <c r="F373" s="3"/>
       <c r="G373" s="3" t="s">
@@ -18359,7 +18569,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
-        <v>1203</v>
+        <v>1243</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>38</v>
@@ -18368,10 +18578,10 @@
         <v>13</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1204</v>
+        <v>1244</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1205</v>
+        <v>1245</v>
       </c>
       <c r="F374" s="3"/>
       <c r="G374" s="3" t="s">
@@ -18391,7 +18601,7 @@
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
-        <v>1206</v>
+        <v>1246</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>38</v>
@@ -18400,10 +18610,10 @@
         <v>13</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1207</v>
+        <v>1247</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1208</v>
+        <v>1248</v>
       </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3" t="s">
@@ -18423,7 +18633,7 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
-        <v>1209</v>
+        <v>1249</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>38</v>
@@ -18432,10 +18642,10 @@
         <v>13</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1210</v>
+        <v>1250</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1211</v>
+        <v>1251</v>
       </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3" t="s">
@@ -18455,7 +18665,7 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
-        <v>1212</v>
+        <v>1252</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>38</v>
@@ -18464,10 +18674,10 @@
         <v>13</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1213</v>
+        <v>1253</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1214</v>
+        <v>1254</v>
       </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3" t="s">
@@ -18487,7 +18697,7 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
-        <v>1215</v>
+        <v>1255</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>38</v>
@@ -18496,10 +18706,10 @@
         <v>13</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1216</v>
+        <v>1256</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1217</v>
+        <v>1257</v>
       </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3" t="s">
@@ -18519,7 +18729,7 @@
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
-        <v>1218</v>
+        <v>1258</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>38</v>
@@ -18528,10 +18738,10 @@
         <v>13</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1219</v>
+        <v>1259</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1220</v>
+        <v>1260</v>
       </c>
       <c r="F379" s="3"/>
       <c r="G379" s="3" t="s">
@@ -18551,7 +18761,7 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>1221</v>
+        <v>1261</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>38</v>
@@ -18560,10 +18770,10 @@
         <v>13</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1222</v>
+        <v>1262</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1223</v>
+        <v>1263</v>
       </c>
       <c r="F380" s="3"/>
       <c r="G380" s="3" t="s">
@@ -18583,7 +18793,7 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>1224</v>
+        <v>1264</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>38</v>
@@ -18592,10 +18802,10 @@
         <v>13</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1225</v>
+        <v>1265</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1226</v>
+        <v>1266</v>
       </c>
       <c r="F381" s="3"/>
       <c r="G381" s="3" t="s">
@@ -18615,7 +18825,7 @@
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
-        <v>1227</v>
+        <v>1267</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>38</v>
@@ -18624,10 +18834,10 @@
         <v>13</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1228</v>
+        <v>1268</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1229</v>
+        <v>1269</v>
       </c>
       <c r="F382" s="3"/>
       <c r="G382" s="3" t="s">
@@ -18647,7 +18857,7 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>1230</v>
+        <v>1270</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>38</v>
@@ -18656,10 +18866,10 @@
         <v>13</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1231</v>
+        <v>1271</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1232</v>
+        <v>1272</v>
       </c>
       <c r="F383" s="3"/>
       <c r="G383" s="3" t="s">
@@ -18679,7 +18889,7 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
-        <v>1233</v>
+        <v>1273</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>38</v>
@@ -18688,10 +18898,10 @@
         <v>13</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1234</v>
+        <v>1274</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1235</v>
+        <v>1275</v>
       </c>
       <c r="F384" s="3"/>
       <c r="G384" s="3" t="s">
@@ -18711,7 +18921,7 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
-        <v>1236</v>
+        <v>1276</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>38</v>
@@ -18720,10 +18930,10 @@
         <v>13</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1237</v>
+        <v>1277</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1238</v>
+        <v>1278</v>
       </c>
       <c r="F385" s="3"/>
       <c r="G385" s="3" t="s">
@@ -18743,7 +18953,7 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
-        <v>1239</v>
+        <v>1279</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>38</v>
@@ -18752,10 +18962,10 @@
         <v>13</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1240</v>
+        <v>1280</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1241</v>
+        <v>1281</v>
       </c>
       <c r="F386" s="3"/>
       <c r="G386" s="3" t="s">
@@ -18775,7 +18985,7 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
-        <v>1242</v>
+        <v>1282</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>38</v>
@@ -18784,10 +18994,10 @@
         <v>13</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1243</v>
+        <v>1283</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1244</v>
+        <v>1284</v>
       </c>
       <c r="F387" s="3"/>
       <c r="G387" s="3" t="s">
@@ -18807,7 +19017,7 @@
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
-        <v>1245</v>
+        <v>1285</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>38</v>
@@ -18816,10 +19026,10 @@
         <v>13</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1246</v>
+        <v>1286</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>1247</v>
+        <v>1287</v>
       </c>
       <c r="F388" s="3"/>
       <c r="G388" s="3" t="s">
@@ -18839,7 +19049,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>1248</v>
+        <v>1288</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>38</v>
@@ -18848,10 +19058,10 @@
         <v>13</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1249</v>
+        <v>1289</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>1250</v>
+        <v>1290</v>
       </c>
       <c r="F389" s="3"/>
       <c r="G389" s="3" t="s">
@@ -18871,7 +19081,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>1251</v>
+        <v>1291</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>38</v>
@@ -18880,10 +19090,10 @@
         <v>13</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1252</v>
+        <v>1292</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1253</v>
+        <v>1293</v>
       </c>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
@@ -18903,7 +19113,7 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>1254</v>
+        <v>1294</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>38</v>
@@ -18912,10 +19122,10 @@
         <v>13</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1255</v>
+        <v>1295</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1256</v>
+        <v>1296</v>
       </c>
       <c r="F391" s="3"/>
       <c r="G391" s="3" t="s">
@@ -18935,7 +19145,7 @@
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
-        <v>1257</v>
+        <v>1297</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>38</v>
@@ -18944,10 +19154,10 @@
         <v>13</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1258</v>
+        <v>1298</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>1259</v>
+        <v>1299</v>
       </c>
       <c r="F392" s="3"/>
       <c r="G392" s="3" t="s">
@@ -18967,7 +19177,7 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
-        <v>1260</v>
+        <v>1300</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>38</v>
@@ -18976,10 +19186,10 @@
         <v>13</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1261</v>
+        <v>1301</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>1262</v>
+        <v>1302</v>
       </c>
       <c r="F393" s="3"/>
       <c r="G393" s="3" t="s">
@@ -18999,7 +19209,7 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
-        <v>1263</v>
+        <v>1303</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>38</v>
@@ -19008,10 +19218,10 @@
         <v>13</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1264</v>
+        <v>1304</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1265</v>
+        <v>1305</v>
       </c>
       <c r="F394" s="3"/>
       <c r="G394" s="3" t="s">
@@ -19031,7 +19241,7 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
-        <v>1266</v>
+        <v>1306</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>38</v>
@@ -19040,10 +19250,10 @@
         <v>13</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1261</v>
+        <v>1301</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1267</v>
+        <v>1307</v>
       </c>
       <c r="F395" s="3"/>
       <c r="G395" s="3" t="s">
@@ -19063,7 +19273,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
-        <v>1268</v>
+        <v>1308</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>38</v>
@@ -19072,10 +19282,10 @@
         <v>13</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1269</v>
+        <v>1309</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>1270</v>
+        <v>1310</v>
       </c>
       <c r="F396" s="3"/>
       <c r="G396" s="3" t="s">
@@ -19097,7 +19307,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
-        <v>1271</v>
+        <v>1311</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>38</v>
@@ -19106,10 +19316,10 @@
         <v>13</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1272</v>
+        <v>1312</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1273</v>
+        <v>1313</v>
       </c>
       <c r="F397" s="3"/>
       <c r="G397" s="3" t="s">
@@ -19129,7 +19339,7 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
-        <v>1274</v>
+        <v>1314</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>38</v>
@@ -19138,10 +19348,10 @@
         <v>13</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1275</v>
+        <v>1315</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1276</v>
+        <v>1316</v>
       </c>
       <c r="F398" s="3"/>
       <c r="G398" s="3" t="s">
@@ -19161,7 +19371,7 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
-        <v>1277</v>
+        <v>1317</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>38</v>
@@ -19170,10 +19380,10 @@
         <v>13</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1278</v>
+        <v>1318</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1279</v>
+        <v>1319</v>
       </c>
       <c r="F399" s="3"/>
       <c r="G399" s="3" t="s">
@@ -19193,7 +19403,7 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
-        <v>1280</v>
+        <v>1320</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>38</v>
@@ -19202,10 +19412,10 @@
         <v>13</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1281</v>
+        <v>1321</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1282</v>
+        <v>1322</v>
       </c>
       <c r="F400" s="3"/>
       <c r="G400" s="3" t="s">
@@ -19225,7 +19435,7 @@
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
-        <v>1283</v>
+        <v>1323</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>38</v>
@@ -19234,10 +19444,10 @@
         <v>13</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1284</v>
+        <v>1324</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1285</v>
+        <v>1325</v>
       </c>
       <c r="F401" s="3"/>
       <c r="G401" s="3" t="s">
@@ -19257,7 +19467,7 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
-        <v>1286</v>
+        <v>1326</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>38</v>
@@ -19266,10 +19476,10 @@
         <v>13</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1287</v>
+        <v>1327</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>1288</v>
+        <v>1328</v>
       </c>
       <c r="F402" s="3"/>
       <c r="G402" s="3" t="s">
@@ -19289,7 +19499,7 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
-        <v>1289</v>
+        <v>1329</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>38</v>
@@ -19298,10 +19508,10 @@
         <v>13</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1290</v>
+        <v>1330</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1291</v>
+        <v>1331</v>
       </c>
       <c r="F403" s="3"/>
       <c r="G403" s="3" t="s">
@@ -19321,7 +19531,7 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
-        <v>1292</v>
+        <v>1332</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>38</v>
@@ -19330,10 +19540,10 @@
         <v>13</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1293</v>
+        <v>1333</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>1294</v>
+        <v>1334</v>
       </c>
       <c r="F404" s="3"/>
       <c r="G404" s="3" t="s">
@@ -19353,7 +19563,7 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
-        <v>1295</v>
+        <v>1335</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>38</v>
@@ -19362,10 +19572,10 @@
         <v>13</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1296</v>
+        <v>1336</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1297</v>
+        <v>1337</v>
       </c>
       <c r="F405" s="3"/>
       <c r="G405" s="3" t="s">
@@ -19385,7 +19595,7 @@
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
-        <v>1298</v>
+        <v>1338</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>38</v>
@@ -19394,10 +19604,10 @@
         <v>13</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1299</v>
+        <v>1339</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>1300</v>
+        <v>1340</v>
       </c>
       <c r="F406" s="3"/>
       <c r="G406" s="3" t="s">
@@ -19419,7 +19629,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
-        <v>1301</v>
+        <v>1341</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>38</v>
@@ -19428,10 +19638,10 @@
         <v>13</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1302</v>
+        <v>1342</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>1303</v>
+        <v>1343</v>
       </c>
       <c r="F407" s="3"/>
       <c r="G407" s="3" t="s">
@@ -19453,7 +19663,7 @@
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
-        <v>1304</v>
+        <v>1344</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>38</v>
@@ -19462,10 +19672,10 @@
         <v>13</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1305</v>
+        <v>1345</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>1306</v>
+        <v>1346</v>
       </c>
       <c r="F408" s="3"/>
       <c r="G408" s="3" t="s">
@@ -19487,7 +19697,7 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
-        <v>1307</v>
+        <v>1347</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>38</v>
@@ -19496,10 +19706,10 @@
         <v>13</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1308</v>
+        <v>1348</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1309</v>
+        <v>1349</v>
       </c>
       <c r="F409" s="3"/>
       <c r="G409" s="3" t="s">
@@ -19519,7 +19729,7 @@
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
-        <v>1310</v>
+        <v>1350</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>38</v>
@@ -19528,10 +19738,10 @@
         <v>13</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1311</v>
+        <v>1351</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1312</v>
+        <v>1352</v>
       </c>
       <c r="F410" s="3"/>
       <c r="G410" s="3" t="s">
@@ -19551,7 +19761,7 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
-        <v>1313</v>
+        <v>1353</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>38</v>
@@ -19560,10 +19770,10 @@
         <v>13</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1314</v>
+        <v>1354</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1315</v>
+        <v>1355</v>
       </c>
       <c r="F411" s="3"/>
       <c r="G411" s="3" t="s">
@@ -19583,7 +19793,7 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
-        <v>1316</v>
+        <v>1356</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>38</v>
@@ -19592,10 +19802,10 @@
         <v>13</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1317</v>
+        <v>1357</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1318</v>
+        <v>1358</v>
       </c>
       <c r="F412" s="3"/>
       <c r="G412" s="3" t="s">
@@ -19617,7 +19827,7 @@
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
-        <v>1319</v>
+        <v>1359</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>38</v>
@@ -19629,7 +19839,7 @@
         <v>349</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>1320</v>
+        <v>1360</v>
       </c>
       <c r="F413" s="3"/>
       <c r="G413" s="3" t="s">
@@ -19651,7 +19861,7 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
-        <v>1321</v>
+        <v>1361</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>38</v>
@@ -19660,10 +19870,10 @@
         <v>13</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1322</v>
+        <v>1362</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1323</v>
+        <v>1363</v>
       </c>
       <c r="F414" s="3"/>
       <c r="G414" s="3" t="s">
@@ -19683,7 +19893,7 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
-        <v>1324</v>
+        <v>1364</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>38</v>
@@ -19692,10 +19902,10 @@
         <v>13</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1325</v>
+        <v>1365</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1326</v>
+        <v>1366</v>
       </c>
       <c r="F415" s="3"/>
       <c r="G415" s="3" t="s">
@@ -19715,7 +19925,7 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>1327</v>
+        <v>1367</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>38</v>
@@ -19724,10 +19934,10 @@
         <v>13</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1328</v>
+        <v>1368</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>1329</v>
+        <v>1369</v>
       </c>
       <c r="F416" s="3"/>
       <c r="G416" s="3" t="s">
@@ -19747,7 +19957,7 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="s">
-        <v>1330</v>
+        <v>1370</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>38</v>
@@ -19756,10 +19966,10 @@
         <v>13</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1331</v>
+        <v>1371</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1332</v>
+        <v>1372</v>
       </c>
       <c r="F417" s="3"/>
       <c r="G417" s="3" t="s">
@@ -19779,7 +19989,7 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>1333</v>
+        <v>1373</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>38</v>
@@ -19788,10 +19998,10 @@
         <v>14</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1334</v>
+        <v>1374</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1334</v>
+        <v>1374</v>
       </c>
       <c r="F418" s="3"/>
       <c r="G418" s="3" t="s">
@@ -19806,14 +20016,14 @@
         <v>21</v>
       </c>
       <c r="L418" s="3" t="s">
-        <v>1335</v>
+        <v>1375</v>
       </c>
       <c r="M418" s="3"/>
       <c r="N418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="s">
-        <v>1336</v>
+        <v>1376</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>38</v>
@@ -19822,13 +20032,13 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1337</v>
+        <v>1377</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1338</v>
+        <v>1378</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>1339</v>
+        <v>1379</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>22</v>
@@ -19837,27 +20047,27 @@
         <v>2</v>
       </c>
       <c r="I419" s="3" t="s">
-        <v>1340</v>
+        <v>1380</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1341</v>
+        <v>1381</v>
       </c>
       <c r="K419" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L419" s="3" t="s">
-        <v>1342</v>
+        <v>1382</v>
       </c>
       <c r="M419" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N419" s="3" t="s">
-        <v>1343</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="s">
-        <v>1344</v>
+        <v>1384</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>38</v>
@@ -19866,13 +20076,13 @@
         <v>8</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1345</v>
+        <v>1385</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1346</v>
+        <v>1386</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1347</v>
+        <v>1387</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>22</v>
@@ -19881,25 +20091,25 @@
         <v>2</v>
       </c>
       <c r="I420" s="3" t="s">
-        <v>1348</v>
+        <v>1388</v>
       </c>
       <c r="J420" s="3"/>
       <c r="K420" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L420" s="3" t="s">
-        <v>1349</v>
+        <v>1389</v>
       </c>
       <c r="M420" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N420" s="3" t="s">
-        <v>1350</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
-        <v>1351</v>
+        <v>1391</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>38</v>
@@ -19908,13 +20118,13 @@
         <v>8</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1352</v>
+        <v>1392</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1353</v>
+        <v>1393</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1354</v>
+        <v>1394</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>22</v>
@@ -19923,25 +20133,25 @@
         <v>2</v>
       </c>
       <c r="I421" s="3" t="s">
-        <v>1355</v>
+        <v>1395</v>
       </c>
       <c r="J421" s="3"/>
       <c r="K421" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L421" s="3" t="s">
-        <v>1349</v>
+        <v>1389</v>
       </c>
       <c r="M421" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1356</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
-        <v>1357</v>
+        <v>1397</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>38</v>
@@ -19950,13 +20160,13 @@
         <v>9</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>1358</v>
+        <v>1398</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>1359</v>
+        <v>1399</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>1360</v>
+        <v>1400</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>22</v>
@@ -19965,25 +20175,25 @@
         <v>2</v>
       </c>
       <c r="I422" s="3" t="s">
-        <v>1361</v>
+        <v>1401</v>
       </c>
       <c r="J422" s="3"/>
       <c r="K422" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L422" s="3" t="s">
-        <v>1349</v>
+        <v>1389</v>
       </c>
       <c r="M422" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1362</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>1363</v>
+        <v>1403</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>38</v>
@@ -19992,13 +20202,13 @@
         <v>8</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1364</v>
+        <v>1404</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>1365</v>
+        <v>1405</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>1366</v>
+        <v>1406</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>22</v>
@@ -20007,25 +20217,25 @@
         <v>2</v>
       </c>
       <c r="I423" s="3" t="s">
-        <v>1367</v>
+        <v>1407</v>
       </c>
       <c r="J423" s="3"/>
       <c r="K423" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L423" s="3" t="s">
-        <v>1349</v>
+        <v>1389</v>
       </c>
       <c r="M423" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1368</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="s">
-        <v>1369</v>
+        <v>1409</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>38</v>
@@ -20034,13 +20244,13 @@
         <v>10</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>1370</v>
+        <v>1410</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>1371</v>
+        <v>1411</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>1372</v>
+        <v>1412</v>
       </c>
       <c r="G424" s="3" t="s">
         <v>22</v>
@@ -20049,25 +20259,25 @@
         <v>2</v>
       </c>
       <c r="I424" s="3" t="s">
-        <v>1373</v>
+        <v>1413</v>
       </c>
       <c r="J424" s="3"/>
       <c r="K424" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L424" s="3" t="s">
-        <v>1374</v>
+        <v>1414</v>
       </c>
       <c r="M424" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N424" s="3" t="s">
-        <v>1375</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>1376</v>
+        <v>1416</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>38</v>
@@ -20076,13 +20286,13 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1377</v>
+        <v>1417</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1378</v>
+        <v>1418</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>1379</v>
+        <v>1419</v>
       </c>
       <c r="G425" s="3" t="s">
         <v>22</v>
@@ -20091,25 +20301,25 @@
         <v>2</v>
       </c>
       <c r="I425" s="3" t="s">
-        <v>1380</v>
+        <v>1420</v>
       </c>
       <c r="J425" s="3"/>
       <c r="K425" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L425" s="3" t="s">
-        <v>1381</v>
+        <v>1421</v>
       </c>
       <c r="M425" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N425" s="3" t="s">
-        <v>1382</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
-        <v>1383</v>
+        <v>1423</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>38</v>
@@ -20118,13 +20328,13 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1384</v>
+        <v>1424</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1385</v>
+        <v>1425</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>1386</v>
+        <v>1426</v>
       </c>
       <c r="G426" s="3" t="s">
         <v>22</v>
@@ -20133,25 +20343,25 @@
         <v>2</v>
       </c>
       <c r="I426" s="3" t="s">
-        <v>1387</v>
+        <v>1427</v>
       </c>
       <c r="J426" s="3"/>
       <c r="K426" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L426" s="3" t="s">
-        <v>1388</v>
+        <v>1428</v>
       </c>
       <c r="M426" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N426" s="3" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>38</v>
@@ -20160,13 +20370,13 @@
         <v>11</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1391</v>
+        <v>1431</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1392</v>
+        <v>1432</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>1393</v>
+        <v>1433</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>22</v>
@@ -20175,25 +20385,25 @@
         <v>2</v>
       </c>
       <c r="I427" s="3" t="s">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="J427" s="3"/>
       <c r="K427" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L427" s="3" t="s">
-        <v>1395</v>
+        <v>1435</v>
       </c>
       <c r="M427" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N427" s="3" t="s">
-        <v>1396</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
-        <v>1397</v>
+        <v>1437</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>38</v>
@@ -20202,10 +20412,10 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1398</v>
+        <v>1438</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>1399</v>
+        <v>1439</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="3" t="s">
@@ -20225,7 +20435,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
-        <v>1400</v>
+        <v>1440</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>38</v>
@@ -20234,10 +20444,10 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1401</v>
+        <v>1441</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>1402</v>
+        <v>1442</v>
       </c>
       <c r="F429" s="3"/>
       <c r="G429" s="3" t="s">
@@ -20257,7 +20467,7 @@
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
-        <v>1403</v>
+        <v>1443</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>38</v>
@@ -20266,10 +20476,10 @@
         <v>11</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1404</v>
+        <v>1444</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>1405</v>
+        <v>1445</v>
       </c>
       <c r="F430" s="3"/>
       <c r="G430" s="3" t="s">
@@ -20289,7 +20499,7 @@
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
-        <v>1406</v>
+        <v>1446</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>38</v>
@@ -20298,10 +20508,10 @@
         <v>11</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1407</v>
+        <v>1447</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>1408</v>
+        <v>1448</v>
       </c>
       <c r="F431" s="3"/>
       <c r="G431" s="3" t="s">
@@ -20321,7 +20531,7 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
-        <v>1409</v>
+        <v>1449</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>38</v>
@@ -20330,10 +20540,10 @@
         <v>11</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>1410</v>
+        <v>1450</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>1411</v>
+        <v>1451</v>
       </c>
       <c r="F432" s="3"/>
       <c r="G432" s="3" t="s">
@@ -20353,7 +20563,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>38</v>
@@ -20362,10 +20572,10 @@
         <v>11</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1413</v>
+        <v>1453</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1414</v>
+        <v>1454</v>
       </c>
       <c r="F433" s="3"/>
       <c r="G433" s="3" t="s">
@@ -20385,7 +20595,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
-        <v>1415</v>
+        <v>1455</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>38</v>
@@ -20394,10 +20604,10 @@
         <v>11</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>1416</v>
+        <v>1456</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>1417</v>
+        <v>1457</v>
       </c>
       <c r="F434" s="3"/>
       <c r="G434" s="3" t="s">
@@ -20417,7 +20627,7 @@
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
-        <v>1418</v>
+        <v>1458</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>38</v>
@@ -20426,10 +20636,10 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>1419</v>
+        <v>1459</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="F435" s="3"/>
       <c r="G435" s="3" t="s">
@@ -20449,7 +20659,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
-        <v>1421</v>
+        <v>1461</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>38</v>
@@ -20458,10 +20668,10 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>1422</v>
+        <v>1462</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>1423</v>
+        <v>1463</v>
       </c>
       <c r="F436" s="3"/>
       <c r="G436" s="3" t="s">
@@ -20481,7 +20691,7 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
-        <v>1424</v>
+        <v>1464</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>38</v>
@@ -20490,10 +20700,10 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>1425</v>
+        <v>1465</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>1426</v>
+        <v>1466</v>
       </c>
       <c r="F437" s="3"/>
       <c r="G437" s="3" t="s">
@@ -20513,7 +20723,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
-        <v>1427</v>
+        <v>1467</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>38</v>
@@ -20522,13 +20732,13 @@
         <v>10</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>1428</v>
+        <v>1468</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1429</v>
+        <v>1469</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>1430</v>
+        <v>1470</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>22</v>
@@ -20537,27 +20747,27 @@
         <v>3</v>
       </c>
       <c r="I438" s="3" t="s">
-        <v>1431</v>
+        <v>1471</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1432</v>
+        <v>1472</v>
       </c>
       <c r="K438" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L438" s="3" t="s">
-        <v>1433</v>
+        <v>1473</v>
       </c>
       <c r="M438" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N438" s="3" t="s">
-        <v>1434</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
-        <v>1435</v>
+        <v>1475</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>38</v>
@@ -20566,13 +20776,13 @@
         <v>8</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>1436</v>
+        <v>1476</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1437</v>
+        <v>1477</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>1438</v>
+        <v>1478</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>22</v>
@@ -20581,27 +20791,27 @@
         <v>3</v>
       </c>
       <c r="I439" s="3" t="s">
-        <v>1439</v>
+        <v>1479</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1440</v>
+        <v>1480</v>
       </c>
       <c r="K439" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L439" s="3" t="s">
-        <v>1441</v>
+        <v>1481</v>
       </c>
       <c r="M439" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N439" s="3" t="s">
-        <v>1442</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
-        <v>1443</v>
+        <v>1483</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>38</v>
@@ -20610,13 +20820,13 @@
         <v>8</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>1444</v>
+        <v>1484</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1445</v>
+        <v>1485</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>1446</v>
+        <v>1486</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>22</v>
@@ -20625,27 +20835,27 @@
         <v>3</v>
       </c>
       <c r="I440" s="3" t="s">
-        <v>1447</v>
+        <v>1487</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1448</v>
+        <v>1488</v>
       </c>
       <c r="K440" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L440" s="3" t="s">
-        <v>1449</v>
+        <v>1489</v>
       </c>
       <c r="M440" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>1450</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>38</v>
@@ -20654,13 +20864,13 @@
         <v>9</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>1358</v>
+        <v>1398</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>1453</v>
+        <v>1493</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>22</v>
@@ -20669,25 +20879,25 @@
         <v>2</v>
       </c>
       <c r="I441" s="3" t="s">
-        <v>1361</v>
+        <v>1401</v>
       </c>
       <c r="J441" s="3"/>
       <c r="K441" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L441" s="3" t="s">
-        <v>1454</v>
+        <v>1494</v>
       </c>
       <c r="M441" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>1455</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
-        <v>1456</v>
+        <v>1496</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>38</v>
@@ -20696,13 +20906,13 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>1364</v>
+        <v>1404</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1457</v>
+        <v>1497</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>1458</v>
+        <v>1498</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>22</v>
@@ -20711,25 +20921,25 @@
         <v>2</v>
       </c>
       <c r="I442" s="3" t="s">
-        <v>1459</v>
+        <v>1499</v>
       </c>
       <c r="J442" s="3"/>
       <c r="K442" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L442" s="3" t="s">
-        <v>1460</v>
+        <v>1500</v>
       </c>
       <c r="M442" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1461</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>1462</v>
+        <v>1502</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>38</v>
@@ -20738,13 +20948,13 @@
         <v>10</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>1463</v>
+        <v>1503</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>1464</v>
+        <v>1504</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>1465</v>
+        <v>1505</v>
       </c>
       <c r="G443" s="3" t="s">
         <v>22</v>
@@ -20753,25 +20963,25 @@
         <v>2</v>
       </c>
       <c r="I443" s="3" t="s">
-        <v>1466</v>
+        <v>1506</v>
       </c>
       <c r="J443" s="3"/>
       <c r="K443" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L443" s="3" t="s">
-        <v>1467</v>
+        <v>1507</v>
       </c>
       <c r="M443" s="3" t="s">
         <v>52</v>
       </c>
       <c r="N443" s="3" t="s">
-        <v>1468</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="s">
-        <v>1469</v>
+        <v>1509</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>38</v>
@@ -20780,13 +20990,13 @@
         <v>11</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>1377</v>
+        <v>1417</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>1470</v>
+        <v>1510</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>1471</v>
+        <v>1511</v>
       </c>
       <c r="G444" s="3" t="s">
         <v>22</v>
@@ -20795,27 +21005,27 @@
         <v>3</v>
       </c>
       <c r="I444" s="3" t="s">
-        <v>1472</v>
+        <v>1512</v>
       </c>
       <c r="J444" s="3" t="s">
-        <v>1473</v>
+        <v>1513</v>
       </c>
       <c r="K444" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L444" s="3" t="s">
-        <v>1474</v>
+        <v>1514</v>
       </c>
       <c r="M444" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N444" s="3" t="s">
-        <v>1475</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>1476</v>
+        <v>1516</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>38</v>
@@ -20824,13 +21034,13 @@
         <v>11</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>1384</v>
+        <v>1424</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>1477</v>
+        <v>1517</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>1478</v>
+        <v>1518</v>
       </c>
       <c r="G445" s="3" t="s">
         <v>22</v>
@@ -20839,16 +21049,16 @@
         <v>2</v>
       </c>
       <c r="I445" s="3" t="s">
-        <v>1479</v>
+        <v>1519</v>
       </c>
       <c r="J445" s="3" t="s">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="K445" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L445" s="3" t="s">
-        <v>1481</v>
+        <v>1521</v>
       </c>
       <c r="M445" s="3" t="s">
         <v>525</v>
@@ -20859,7 +21069,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="s">
-        <v>1482</v>
+        <v>1522</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>38</v>
@@ -20868,13 +21078,13 @@
         <v>11</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>1483</v>
+        <v>1523</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>1484</v>
+        <v>1524</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>1485</v>
+        <v>1525</v>
       </c>
       <c r="G446" s="3" t="s">
         <v>22</v>
@@ -20883,27 +21093,27 @@
         <v>3</v>
       </c>
       <c r="I446" s="3" t="s">
-        <v>1486</v>
+        <v>1526</v>
       </c>
       <c r="J446" s="3" t="s">
-        <v>1487</v>
+        <v>1527</v>
       </c>
       <c r="K446" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L446" s="3" t="s">
-        <v>1488</v>
+        <v>1528</v>
       </c>
       <c r="M446" s="3" t="s">
         <v>525</v>
       </c>
       <c r="N446" s="3" t="s">
-        <v>1489</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="s">
-        <v>1490</v>
+        <v>1530</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>38</v>
@@ -20912,10 +21122,10 @@
         <v>11</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>1491</v>
+        <v>1531</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1492</v>
+        <v>1532</v>
       </c>
       <c r="F447" s="3"/>
       <c r="G447" s="3" t="s">
@@ -20935,7 +21145,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
-        <v>1493</v>
+        <v>1533</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>38</v>
@@ -20944,10 +21154,10 @@
         <v>11</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>1494</v>
+        <v>1534</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>1495</v>
+        <v>1535</v>
       </c>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
@@ -20967,7 +21177,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
-        <v>1496</v>
+        <v>1536</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>38</v>
@@ -20976,10 +21186,10 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>1497</v>
+        <v>1537</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1498</v>
+        <v>1538</v>
       </c>
       <c r="F449" s="3"/>
       <c r="G449" s="3" t="s">
@@ -20999,7 +21209,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
-        <v>1499</v>
+        <v>1539</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>38</v>
@@ -21008,10 +21218,10 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1500</v>
+        <v>1540</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>1501</v>
+        <v>1541</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="3" t="s">
@@ -21031,7 +21241,7 @@
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
-        <v>1502</v>
+        <v>1542</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>38</v>
@@ -21040,10 +21250,10 @@
         <v>11</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>1503</v>
+        <v>1543</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>1504</v>
+        <v>1544</v>
       </c>
       <c r="F451" s="3"/>
       <c r="G451" s="3" t="s">
@@ -21063,7 +21273,7 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
-        <v>1505</v>
+        <v>1545</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>38</v>
@@ -21072,10 +21282,10 @@
         <v>11</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>1506</v>
+        <v>1546</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>1507</v>
+        <v>1547</v>
       </c>
       <c r="F452" s="3"/>
       <c r="G452" s="3" t="s">
@@ -21095,7 +21305,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
-        <v>1508</v>
+        <v>1548</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>38</v>
@@ -21104,10 +21314,10 @@
         <v>11</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>1509</v>
+        <v>1549</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>1510</v>
+        <v>1550</v>
       </c>
       <c r="F453" s="3"/>
       <c r="G453" s="3" t="s">
@@ -21127,7 +21337,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
-        <v>1511</v>
+        <v>1551</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>38</v>
@@ -21136,10 +21346,10 @@
         <v>12</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>1419</v>
+        <v>1459</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>1512</v>
+        <v>1552</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="3" t="s">
@@ -21159,7 +21369,7 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
-        <v>1513</v>
+        <v>1553</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>38</v>
@@ -21168,10 +21378,10 @@
         <v>12</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>1514</v>
+        <v>1554</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1515</v>
+        <v>1555</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="3" t="s">
@@ -21191,7 +21401,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
-        <v>1516</v>
+        <v>1556</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>38</v>
@@ -21200,10 +21410,10 @@
         <v>12</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>1517</v>
+        <v>1557</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>1518</v>
+        <v>1558</v>
       </c>
       <c r="F456" s="3"/>
       <c r="G456" s="3" t="s">
@@ -21223,7 +21433,7 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
-        <v>1519</v>
+        <v>1559</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>38</v>
@@ -21232,10 +21442,10 @@
         <v>12</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>1520</v>
+        <v>1560</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1521</v>
+        <v>1561</v>
       </c>
       <c r="F457" s="3"/>
       <c r="G457" s="3" t="s">
@@ -21255,7 +21465,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
-        <v>1522</v>
+        <v>1562</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>38</v>
@@ -21264,10 +21474,10 @@
         <v>12</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>1523</v>
+        <v>1563</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>1524</v>
+        <v>1564</v>
       </c>
       <c r="F458" s="3"/>
       <c r="G458" s="3" t="s">
@@ -21287,7 +21497,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
-        <v>1525</v>
+        <v>1565</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>38</v>
@@ -21296,10 +21506,10 @@
         <v>12</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>1526</v>
+        <v>1566</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>1527</v>
+        <v>1567</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="3" t="s">
@@ -21319,7 +21529,7 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
-        <v>1528</v>
+        <v>1568</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>38</v>
@@ -21328,10 +21538,10 @@
         <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>1529</v>
+        <v>1569</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>1530</v>
+        <v>1570</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="3" t="s">
@@ -21351,7 +21561,7 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
-        <v>1531</v>
+        <v>1571</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>38</v>
@@ -21360,10 +21570,10 @@
         <v>11</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>1532</v>
+        <v>1572</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>1533</v>
+        <v>1573</v>
       </c>
       <c r="F461" s="3"/>
       <c r="G461" s="3" t="s">
@@ -21383,7 +21593,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
-        <v>1534</v>
+        <v>1574</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>38</v>
@@ -21392,13 +21602,13 @@
         <v>10</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>1535</v>
+        <v>1575</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>1536</v>
+        <v>1576</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>1537</v>
+        <v>1577</v>
       </c>
       <c r="G462" s="3" t="s">
         <v>22</v>
@@ -21407,25 +21617,25 @@
         <v>2</v>
       </c>
   